--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_genero.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_genero.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="datos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metadatos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="datos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="metadatos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -54,6 +54,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -346,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q331"/>
+  <dimension ref="A1:Q332"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,7 +575,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -582,7 +650,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -657,7 +725,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -732,7 +800,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -807,7 +875,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -882,7 +950,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -957,7 +1025,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -1032,7 +1100,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1175,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -1182,7 +1250,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -1257,7 +1325,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1403,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -1413,7 +1481,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -1491,7 +1559,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1637,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -1647,7 +1715,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -1725,7 +1793,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1871,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -1881,7 +1949,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -1959,7 +2027,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2105,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2112,7 +2180,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2187,7 +2255,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2265,7 +2333,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2411,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2421,7 +2489,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2499,7 +2567,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2577,7 +2645,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2655,7 +2723,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2733,7 +2801,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2808,7 +2876,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2886,7 +2954,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2964,7 +3032,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -3042,7 +3110,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -3117,7 +3185,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -3192,7 +3260,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -3270,7 +3338,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3416,7 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -3423,7 +3491,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -3501,7 +3569,7 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3647,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -3657,7 +3725,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3803,7 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -3813,7 +3881,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -3891,7 +3959,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -3969,7 +4037,7 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -4047,7 +4115,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4193,7 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -4203,7 +4271,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -4281,7 +4349,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -4359,7 +4427,7 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -4437,7 +4505,7 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -4515,7 +4583,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -4593,7 +4661,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -4671,7 +4739,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4817,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -4827,7 +4895,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -4905,7 +4973,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -4980,7 +5048,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -5055,7 +5123,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -5130,7 +5198,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -5205,7 +5273,7 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5348,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -5355,7 +5423,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -5430,7 +5498,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -5505,7 +5573,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -5580,7 +5648,12 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -5655,7 +5728,12 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -5730,7 +5808,12 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -5805,7 +5888,12 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5968,12 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -5955,7 +6048,12 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -6030,7 +6128,12 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -6105,7 +6208,12 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -6180,7 +6288,12 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -6255,7 +6368,12 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -6330,7 +6448,12 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -6398,9 +6521,6 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N79" t="n">
-        <v>1.06591999530792</v>
-      </c>
       <c r="O79" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -6408,7 +6528,12 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -6476,9 +6601,6 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N80" t="n">
-        <v>1.07165002822876</v>
-      </c>
       <c r="O80" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -6486,7 +6608,12 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -6554,9 +6681,6 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N81" t="n">
-        <v>1.09589004516602</v>
-      </c>
       <c r="O81" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -6564,7 +6688,12 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -6632,9 +6761,6 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N82" t="n">
-        <v>1.13256001472473</v>
-      </c>
       <c r="O82" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -6642,7 +6768,12 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -6710,9 +6841,6 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N83" t="n">
-        <v>1.13680994510651</v>
-      </c>
       <c r="O83" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -6720,7 +6848,12 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -6795,7 +6928,12 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -6870,7 +7008,12 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -6945,7 +7088,12 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7168,12 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -7095,7 +7248,12 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -7170,7 +7328,12 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -7245,7 +7408,12 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -7320,7 +7488,12 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -7388,9 +7561,6 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N92" t="n">
-        <v>1.24408996105194</v>
-      </c>
       <c r="O92" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -7398,7 +7568,12 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -7466,9 +7641,6 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N93" t="n">
-        <v>1.25617003440857</v>
-      </c>
       <c r="O93" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -7476,7 +7648,12 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -7544,9 +7721,6 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N94" t="n">
-        <v>1.23227000236511</v>
-      </c>
       <c r="O94" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -7554,7 +7728,12 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -7622,9 +7801,6 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N95" t="n">
-        <v>1.23520004749298</v>
-      </c>
       <c r="O95" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -7632,7 +7808,12 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -7700,9 +7881,6 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N96" t="n">
-        <v>1.23055994510651</v>
-      </c>
       <c r="O96" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -7710,7 +7888,12 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -7778,9 +7961,6 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N97" t="n">
-        <v>1.23713004589081</v>
-      </c>
       <c r="O97" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -7788,7 +7968,12 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -7863,7 +8048,12 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -7931,9 +8121,6 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N99" t="n">
-        <v>1.24015998840332</v>
-      </c>
       <c r="O99" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -7941,7 +8128,12 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -8009,9 +8201,6 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N100" t="n">
-        <v>1.2406200170517</v>
-      </c>
       <c r="O100" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8019,7 +8208,12 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -8087,9 +8281,6 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N101" t="n">
-        <v>1.24875998497009</v>
-      </c>
       <c r="O101" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8097,7 +8288,12 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -8172,7 +8368,12 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -8247,7 +8448,12 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8528,12 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -8397,7 +8608,12 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -8472,7 +8688,12 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -8540,9 +8761,6 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N107" t="n">
-        <v>1.22622001171112</v>
-      </c>
       <c r="O107" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8550,7 +8768,12 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -8618,9 +8841,6 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N108" t="n">
-        <v>1.19964003562927</v>
-      </c>
       <c r="O108" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8628,7 +8848,12 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -8696,9 +8921,6 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N109" t="n">
-        <v>1.17510998249054</v>
-      </c>
       <c r="O109" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8706,7 +8928,12 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -8774,9 +9001,6 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N110" t="n">
-        <v>1.16194999217987</v>
-      </c>
       <c r="O110" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8784,7 +9008,12 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -8852,9 +9081,6 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N111" t="n">
-        <v>1.15086996555328</v>
-      </c>
       <c r="O111" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8862,7 +9088,12 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -8930,9 +9161,6 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N112" t="n">
-        <v>1.13995003700256</v>
-      </c>
       <c r="O112" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8940,7 +9168,12 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -9008,9 +9241,6 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N113" t="n">
-        <v>1.13028001785278</v>
-      </c>
       <c r="O113" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9018,7 +9248,12 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -9086,9 +9321,6 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N114" t="n">
-        <v>1.12556004524231</v>
-      </c>
       <c r="O114" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9096,7 +9328,12 @@
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -9164,9 +9401,6 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N115" t="n">
-        <v>1.11647999286652</v>
-      </c>
       <c r="O115" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9174,7 +9408,12 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -9242,9 +9481,6 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N116" t="n">
-        <v>1.10140001773834</v>
-      </c>
       <c r="O116" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9252,7 +9488,12 @@
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -9320,9 +9561,6 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N117" t="n">
-        <v>1.09311997890472</v>
-      </c>
       <c r="O117" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9330,7 +9568,12 @@
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -9398,9 +9641,6 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N118" t="n">
-        <v>1.09621000289917</v>
-      </c>
       <c r="O118" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9408,7 +9648,12 @@
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -9476,9 +9721,6 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N119" t="n">
-        <v>1.09371995925903</v>
-      </c>
       <c r="O119" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9486,7 +9728,12 @@
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -9554,9 +9801,6 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N120" t="n">
-        <v>1.09325003623962</v>
-      </c>
       <c r="O120" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9564,7 +9808,12 @@
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -9632,9 +9881,6 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N121" t="n">
-        <v>1.09049999713898</v>
-      </c>
       <c r="O121" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9642,7 +9888,12 @@
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -9710,9 +9961,6 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N122" t="n">
-        <v>1.07729995250702</v>
-      </c>
       <c r="O122" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9720,7 +9968,12 @@
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -9788,9 +10041,6 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N123" t="n">
-        <v>1.07729005813599</v>
-      </c>
       <c r="O123" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9798,7 +10048,12 @@
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -9866,9 +10121,6 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N124" t="n">
-        <v>1.07924997806549</v>
-      </c>
       <c r="O124" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9876,7 +10128,12 @@
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -9944,9 +10201,6 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N125" t="n">
-        <v>1.0806200504303</v>
-      </c>
       <c r="O125" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9954,7 +10208,12 @@
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -10029,7 +10288,12 @@
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -10104,7 +10368,12 @@
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -10179,7 +10448,12 @@
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10528,12 @@
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -10329,7 +10608,12 @@
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -10404,7 +10688,12 @@
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -10479,7 +10768,12 @@
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -10554,7 +10848,12 @@
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -10590,7 +10889,7 @@
         </is>
       </c>
       <c r="G134" t="n">
-        <v>1960</v>
+        <v>2026</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
@@ -10604,22 +10903,22 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Participación política</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>participacion_politica</t>
+          <t>educacion</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>SG.GEN.PARL.ZS</t>
+          <t>SE.ENR.SECO.FM.ZS</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Mujeres en parlamentos nacionales</t>
+          <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
       <c r="O134" t="inlineStr">
@@ -10629,7 +10928,12 @@
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -10665,7 +10969,7 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -10704,7 +11008,7 @@
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -10740,7 +11044,7 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -10779,7 +11083,7 @@
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -10815,7 +11119,7 @@
         </is>
       </c>
       <c r="G137" t="n">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
@@ -10854,7 +11158,7 @@
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -10890,7 +11194,7 @@
         </is>
       </c>
       <c r="G138" t="n">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
@@ -10929,7 +11233,7 @@
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -10965,7 +11269,7 @@
         </is>
       </c>
       <c r="G139" t="n">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
@@ -11004,7 +11308,7 @@
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -11040,7 +11344,7 @@
         </is>
       </c>
       <c r="G140" t="n">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
@@ -11079,7 +11383,7 @@
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -11115,7 +11419,7 @@
         </is>
       </c>
       <c r="G141" t="n">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -11154,7 +11458,7 @@
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -11190,7 +11494,7 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
@@ -11229,7 +11533,7 @@
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -11265,7 +11569,7 @@
         </is>
       </c>
       <c r="G143" t="n">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
@@ -11304,7 +11608,7 @@
       </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -11340,7 +11644,7 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
@@ -11379,7 +11683,7 @@
       </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -11415,7 +11719,7 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
@@ -11454,7 +11758,7 @@
       </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -11490,7 +11794,7 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
@@ -11529,7 +11833,7 @@
       </c>
       <c r="P146" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -11565,7 +11869,7 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
@@ -11604,7 +11908,7 @@
       </c>
       <c r="P147" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -11640,7 +11944,7 @@
         </is>
       </c>
       <c r="G148" t="n">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
@@ -11679,7 +11983,7 @@
       </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -11715,7 +12019,7 @@
         </is>
       </c>
       <c r="G149" t="n">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
@@ -11754,7 +12058,7 @@
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -11790,7 +12094,7 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
@@ -11829,7 +12133,7 @@
       </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -11865,7 +12169,7 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
@@ -11904,7 +12208,7 @@
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -11940,7 +12244,7 @@
         </is>
       </c>
       <c r="G152" t="n">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
@@ -11979,7 +12283,7 @@
       </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -12015,7 +12319,7 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
@@ -12054,7 +12358,7 @@
       </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -12090,7 +12394,7 @@
         </is>
       </c>
       <c r="G154" t="n">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
@@ -12129,7 +12433,7 @@
       </c>
       <c r="P154" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -12165,7 +12469,7 @@
         </is>
       </c>
       <c r="G155" t="n">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
@@ -12204,7 +12508,7 @@
       </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -12240,7 +12544,7 @@
         </is>
       </c>
       <c r="G156" t="n">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
@@ -12279,7 +12583,7 @@
       </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -12315,7 +12619,7 @@
         </is>
       </c>
       <c r="G157" t="n">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
@@ -12354,7 +12658,7 @@
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -12390,7 +12694,7 @@
         </is>
       </c>
       <c r="G158" t="n">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
@@ -12429,7 +12733,7 @@
       </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -12465,7 +12769,7 @@
         </is>
       </c>
       <c r="G159" t="n">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
@@ -12504,7 +12808,7 @@
       </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -12540,7 +12844,7 @@
         </is>
       </c>
       <c r="G160" t="n">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="H160" t="inlineStr">
         <is>
@@ -12579,7 +12883,7 @@
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -12615,7 +12919,7 @@
         </is>
       </c>
       <c r="G161" t="n">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="H161" t="inlineStr">
         <is>
@@ -12654,7 +12958,7 @@
       </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -12690,7 +12994,7 @@
         </is>
       </c>
       <c r="G162" t="n">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
@@ -12729,7 +13033,7 @@
       </c>
       <c r="P162" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -12765,7 +13069,7 @@
         </is>
       </c>
       <c r="G163" t="n">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="H163" t="inlineStr">
         <is>
@@ -12804,7 +13108,7 @@
       </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -12840,7 +13144,7 @@
         </is>
       </c>
       <c r="G164" t="n">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
@@ -12879,7 +13183,7 @@
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -12915,7 +13219,7 @@
         </is>
       </c>
       <c r="G165" t="n">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
@@ -12954,7 +13258,7 @@
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -12990,7 +13294,7 @@
         </is>
       </c>
       <c r="G166" t="n">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
@@ -13029,7 +13333,7 @@
       </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -13065,7 +13369,7 @@
         </is>
       </c>
       <c r="G167" t="n">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
@@ -13104,7 +13408,7 @@
       </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -13140,7 +13444,7 @@
         </is>
       </c>
       <c r="G168" t="n">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
@@ -13179,7 +13483,7 @@
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -13215,7 +13519,7 @@
         </is>
       </c>
       <c r="G169" t="n">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="H169" t="inlineStr">
         <is>
@@ -13254,7 +13558,7 @@
       </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -13290,7 +13594,7 @@
         </is>
       </c>
       <c r="G170" t="n">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="H170" t="inlineStr">
         <is>
@@ -13329,7 +13633,7 @@
       </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -13365,7 +13669,7 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
@@ -13397,9 +13701,6 @@
           <t>Mujeres en parlamentos nacionales</t>
         </is>
       </c>
-      <c r="N171" t="n">
-        <v>5.91133004926108</v>
-      </c>
       <c r="O171" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -13407,7 +13708,7 @@
       </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -13443,7 +13744,7 @@
         </is>
       </c>
       <c r="G172" t="n">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="H172" t="inlineStr">
         <is>
@@ -13485,7 +13786,7 @@
       </c>
       <c r="P172" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -13521,7 +13822,7 @@
         </is>
       </c>
       <c r="G173" t="n">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
@@ -13554,7 +13855,7 @@
         </is>
       </c>
       <c r="N173" t="n">
-        <v>12.1359223300971</v>
+        <v>5.91133004926108</v>
       </c>
       <c r="O173" t="inlineStr">
         <is>
@@ -13563,7 +13864,7 @@
       </c>
       <c r="P173" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -13599,7 +13900,7 @@
         </is>
       </c>
       <c r="G174" t="n">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
@@ -13631,6 +13932,9 @@
           <t>Mujeres en parlamentos nacionales</t>
         </is>
       </c>
+      <c r="N174" t="n">
+        <v>12.1359223300971</v>
+      </c>
       <c r="O174" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -13638,7 +13942,7 @@
       </c>
       <c r="P174" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -13674,7 +13978,7 @@
         </is>
       </c>
       <c r="G175" t="n">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="H175" t="inlineStr">
         <is>
@@ -13706,9 +14010,6 @@
           <t>Mujeres en parlamentos nacionales</t>
         </is>
       </c>
-      <c r="N175" t="n">
-        <v>9.696969696969701</v>
-      </c>
       <c r="O175" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -13716,7 +14017,7 @@
       </c>
       <c r="P175" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -13752,7 +14053,7 @@
         </is>
       </c>
       <c r="G176" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
@@ -13794,7 +14095,7 @@
       </c>
       <c r="P176" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -13830,7 +14131,7 @@
         </is>
       </c>
       <c r="G177" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>
@@ -13872,7 +14173,7 @@
       </c>
       <c r="P177" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -13908,7 +14209,7 @@
         </is>
       </c>
       <c r="G178" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="H178" t="inlineStr">
         <is>
@@ -13950,7 +14251,7 @@
       </c>
       <c r="P178" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -13986,7 +14287,7 @@
         </is>
       </c>
       <c r="G179" t="n">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
@@ -14019,7 +14320,7 @@
         </is>
       </c>
       <c r="N179" t="n">
-        <v>17.3652694610778</v>
+        <v>9.696969696969701</v>
       </c>
       <c r="O179" t="inlineStr">
         <is>
@@ -14028,7 +14329,7 @@
       </c>
       <c r="P179" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -14064,7 +14365,7 @@
         </is>
       </c>
       <c r="G180" t="n">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
@@ -14097,7 +14398,7 @@
         </is>
       </c>
       <c r="N180" t="n">
-        <v>17.9640718562874</v>
+        <v>17.3652694610778</v>
       </c>
       <c r="O180" t="inlineStr">
         <is>
@@ -14106,7 +14407,7 @@
       </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -14142,7 +14443,7 @@
         </is>
       </c>
       <c r="G181" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="H181" t="inlineStr">
         <is>
@@ -14175,7 +14476,7 @@
         </is>
       </c>
       <c r="N181" t="n">
-        <v>18.562874251497</v>
+        <v>17.9640718562874</v>
       </c>
       <c r="O181" t="inlineStr">
         <is>
@@ -14184,7 +14485,7 @@
       </c>
       <c r="P181" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -14220,7 +14521,7 @@
         </is>
       </c>
       <c r="G182" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="H182" t="inlineStr">
         <is>
@@ -14262,7 +14563,7 @@
       </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -14298,7 +14599,7 @@
         </is>
       </c>
       <c r="G183" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="H183" t="inlineStr">
         <is>
@@ -14331,7 +14632,7 @@
         </is>
       </c>
       <c r="N183" t="n">
-        <v>17.4698795180723</v>
+        <v>18.562874251497</v>
       </c>
       <c r="O183" t="inlineStr">
         <is>
@@ -14340,7 +14641,7 @@
       </c>
       <c r="P183" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -14376,7 +14677,7 @@
         </is>
       </c>
       <c r="G184" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="H184" t="inlineStr">
         <is>
@@ -14409,7 +14710,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>16.969696969697</v>
+        <v>17.4698795180723</v>
       </c>
       <c r="O184" t="inlineStr">
         <is>
@@ -14418,7 +14719,7 @@
       </c>
       <c r="P184" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14755,7 @@
         </is>
       </c>
       <c r="G185" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="H185" t="inlineStr">
         <is>
@@ -14496,7 +14797,7 @@
       </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -14532,7 +14833,7 @@
         </is>
       </c>
       <c r="G186" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
@@ -14574,7 +14875,7 @@
       </c>
       <c r="P186" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -14610,7 +14911,7 @@
         </is>
       </c>
       <c r="G187" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
@@ -14652,7 +14953,7 @@
       </c>
       <c r="P187" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -14688,7 +14989,7 @@
         </is>
       </c>
       <c r="G188" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="H188" t="inlineStr">
         <is>
@@ -14730,7 +15031,7 @@
       </c>
       <c r="P188" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -14766,7 +15067,7 @@
         </is>
       </c>
       <c r="G189" t="n">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
@@ -14808,7 +15109,7 @@
       </c>
       <c r="P189" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -14844,7 +15145,7 @@
         </is>
       </c>
       <c r="G190" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="H190" t="inlineStr">
         <is>
@@ -14877,7 +15178,7 @@
         </is>
       </c>
       <c r="N190" t="n">
-        <v>14.3712574850299</v>
+        <v>16.969696969697</v>
       </c>
       <c r="O190" t="inlineStr">
         <is>
@@ -14886,7 +15187,7 @@
       </c>
       <c r="P190" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -14922,7 +15223,7 @@
         </is>
       </c>
       <c r="G191" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="H191" t="inlineStr">
         <is>
@@ -14955,7 +15256,7 @@
         </is>
       </c>
       <c r="N191" t="n">
-        <v>22.1556886227545</v>
+        <v>14.3712574850299</v>
       </c>
       <c r="O191" t="inlineStr">
         <is>
@@ -14964,7 +15265,7 @@
       </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -15000,7 +15301,7 @@
         </is>
       </c>
       <c r="G192" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="H192" t="inlineStr">
         <is>
@@ -15042,7 +15343,7 @@
       </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -15078,7 +15379,7 @@
         </is>
       </c>
       <c r="G193" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="H193" t="inlineStr">
         <is>
@@ -15120,7 +15421,7 @@
       </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -15156,7 +15457,7 @@
         </is>
       </c>
       <c r="G194" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="H194" t="inlineStr">
         <is>
@@ -15198,7 +15499,7 @@
       </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -15234,7 +15535,7 @@
         </is>
       </c>
       <c r="G195" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="H195" t="inlineStr">
         <is>
@@ -15276,7 +15577,7 @@
       </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -15312,7 +15613,7 @@
         </is>
       </c>
       <c r="G196" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H196" t="inlineStr">
         <is>
@@ -15344,6 +15645,9 @@
           <t>Mujeres en parlamentos nacionales</t>
         </is>
       </c>
+      <c r="N196" t="n">
+        <v>22.1556886227545</v>
+      </c>
       <c r="O196" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -15351,7 +15655,7 @@
       </c>
       <c r="P196" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -15387,7 +15691,7 @@
         </is>
       </c>
       <c r="G197" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="H197" t="inlineStr">
         <is>
@@ -15426,7 +15730,7 @@
       </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -15462,7 +15766,7 @@
         </is>
       </c>
       <c r="G198" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
@@ -15501,7 +15805,7 @@
       </c>
       <c r="P198" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -15537,7 +15841,7 @@
         </is>
       </c>
       <c r="G199" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="H199" t="inlineStr">
         <is>
@@ -15569,9 +15873,6 @@
           <t>Mujeres en parlamentos nacionales</t>
         </is>
       </c>
-      <c r="N199" t="n">
-        <v>32.129963898917</v>
-      </c>
       <c r="O199" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -15579,7 +15880,7 @@
       </c>
       <c r="P199" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -15615,7 +15916,7 @@
         </is>
       </c>
       <c r="G200" t="n">
-        <v>1960</v>
+        <v>2025</v>
       </c>
       <c r="H200" t="inlineStr">
         <is>
@@ -15629,23 +15930,26 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>Mercado laboral</t>
+          <t>Participación política</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>mercado_laboral</t>
+          <t>participacion_politica</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>SL.TLF.CACT.FE.ZS</t>
+          <t>SG.GEN.PARL.ZS</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Participación laboral femenina</t>
-        </is>
+          <t>Mujeres en parlamentos nacionales</t>
+        </is>
+      </c>
+      <c r="N200" t="n">
+        <v>32.129963898917</v>
       </c>
       <c r="O200" t="inlineStr">
         <is>
@@ -15654,7 +15958,7 @@
       </c>
       <c r="P200" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -15690,7 +15994,7 @@
         </is>
       </c>
       <c r="G201" t="n">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="H201" t="inlineStr">
         <is>
@@ -15729,7 +16033,7 @@
       </c>
       <c r="P201" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -15765,7 +16069,7 @@
         </is>
       </c>
       <c r="G202" t="n">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="H202" t="inlineStr">
         <is>
@@ -15804,7 +16108,7 @@
       </c>
       <c r="P202" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -15840,7 +16144,7 @@
         </is>
       </c>
       <c r="G203" t="n">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="H203" t="inlineStr">
         <is>
@@ -15879,7 +16183,7 @@
       </c>
       <c r="P203" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -15915,7 +16219,7 @@
         </is>
       </c>
       <c r="G204" t="n">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="H204" t="inlineStr">
         <is>
@@ -15954,7 +16258,7 @@
       </c>
       <c r="P204" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -15990,7 +16294,7 @@
         </is>
       </c>
       <c r="G205" t="n">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="H205" t="inlineStr">
         <is>
@@ -16029,7 +16333,7 @@
       </c>
       <c r="P205" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -16065,7 +16369,7 @@
         </is>
       </c>
       <c r="G206" t="n">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="H206" t="inlineStr">
         <is>
@@ -16104,7 +16408,7 @@
       </c>
       <c r="P206" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -16140,7 +16444,7 @@
         </is>
       </c>
       <c r="G207" t="n">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
@@ -16179,7 +16483,7 @@
       </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -16215,7 +16519,7 @@
         </is>
       </c>
       <c r="G208" t="n">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="H208" t="inlineStr">
         <is>
@@ -16254,7 +16558,7 @@
       </c>
       <c r="P208" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -16290,7 +16594,7 @@
         </is>
       </c>
       <c r="G209" t="n">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="H209" t="inlineStr">
         <is>
@@ -16329,7 +16633,7 @@
       </c>
       <c r="P209" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -16365,7 +16669,7 @@
         </is>
       </c>
       <c r="G210" t="n">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="H210" t="inlineStr">
         <is>
@@ -16404,7 +16708,7 @@
       </c>
       <c r="P210" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -16440,7 +16744,7 @@
         </is>
       </c>
       <c r="G211" t="n">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="H211" t="inlineStr">
         <is>
@@ -16479,7 +16783,7 @@
       </c>
       <c r="P211" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -16515,7 +16819,7 @@
         </is>
       </c>
       <c r="G212" t="n">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="H212" t="inlineStr">
         <is>
@@ -16554,7 +16858,7 @@
       </c>
       <c r="P212" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -16590,7 +16894,7 @@
         </is>
       </c>
       <c r="G213" t="n">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="H213" t="inlineStr">
         <is>
@@ -16629,7 +16933,7 @@
       </c>
       <c r="P213" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -16665,7 +16969,7 @@
         </is>
       </c>
       <c r="G214" t="n">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="H214" t="inlineStr">
         <is>
@@ -16704,7 +17008,7 @@
       </c>
       <c r="P214" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -16740,7 +17044,7 @@
         </is>
       </c>
       <c r="G215" t="n">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="H215" t="inlineStr">
         <is>
@@ -16779,7 +17083,7 @@
       </c>
       <c r="P215" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -16815,7 +17119,7 @@
         </is>
       </c>
       <c r="G216" t="n">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
@@ -16854,7 +17158,7 @@
       </c>
       <c r="P216" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -16890,7 +17194,7 @@
         </is>
       </c>
       <c r="G217" t="n">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="H217" t="inlineStr">
         <is>
@@ -16929,7 +17233,7 @@
       </c>
       <c r="P217" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -16965,7 +17269,7 @@
         </is>
       </c>
       <c r="G218" t="n">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="H218" t="inlineStr">
         <is>
@@ -17004,7 +17308,7 @@
       </c>
       <c r="P218" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -17040,7 +17344,7 @@
         </is>
       </c>
       <c r="G219" t="n">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="H219" t="inlineStr">
         <is>
@@ -17079,7 +17383,7 @@
       </c>
       <c r="P219" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -17115,7 +17419,7 @@
         </is>
       </c>
       <c r="G220" t="n">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="H220" t="inlineStr">
         <is>
@@ -17154,7 +17458,7 @@
       </c>
       <c r="P220" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -17190,7 +17494,7 @@
         </is>
       </c>
       <c r="G221" t="n">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="H221" t="inlineStr">
         <is>
@@ -17229,7 +17533,7 @@
       </c>
       <c r="P221" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -17265,7 +17569,7 @@
         </is>
       </c>
       <c r="G222" t="n">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="H222" t="inlineStr">
         <is>
@@ -17304,7 +17608,7 @@
       </c>
       <c r="P222" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -17340,7 +17644,7 @@
         </is>
       </c>
       <c r="G223" t="n">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="H223" t="inlineStr">
         <is>
@@ -17379,7 +17683,7 @@
       </c>
       <c r="P223" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -17415,7 +17719,7 @@
         </is>
       </c>
       <c r="G224" t="n">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="H224" t="inlineStr">
         <is>
@@ -17454,7 +17758,7 @@
       </c>
       <c r="P224" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -17490,7 +17794,7 @@
         </is>
       </c>
       <c r="G225" t="n">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
@@ -17529,7 +17833,7 @@
       </c>
       <c r="P225" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -17565,7 +17869,7 @@
         </is>
       </c>
       <c r="G226" t="n">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="H226" t="inlineStr">
         <is>
@@ -17604,7 +17908,7 @@
       </c>
       <c r="P226" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -17640,7 +17944,7 @@
         </is>
       </c>
       <c r="G227" t="n">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="H227" t="inlineStr">
         <is>
@@ -17679,7 +17983,7 @@
       </c>
       <c r="P227" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -17715,7 +18019,7 @@
         </is>
       </c>
       <c r="G228" t="n">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="H228" t="inlineStr">
         <is>
@@ -17754,7 +18058,7 @@
       </c>
       <c r="P228" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -17790,7 +18094,7 @@
         </is>
       </c>
       <c r="G229" t="n">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="H229" t="inlineStr">
         <is>
@@ -17829,7 +18133,7 @@
       </c>
       <c r="P229" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -17865,7 +18169,7 @@
         </is>
       </c>
       <c r="G230" t="n">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="H230" t="inlineStr">
         <is>
@@ -17897,9 +18201,6 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N230" t="n">
-        <v>48.56</v>
-      </c>
       <c r="O230" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -17907,7 +18208,7 @@
       </c>
       <c r="P230" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -17943,7 +18244,7 @@
         </is>
       </c>
       <c r="G231" t="n">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="H231" t="inlineStr">
         <is>
@@ -17976,7 +18277,7 @@
         </is>
       </c>
       <c r="N231" t="n">
-        <v>49.027</v>
+        <v>48.56</v>
       </c>
       <c r="O231" t="inlineStr">
         <is>
@@ -17985,7 +18286,7 @@
       </c>
       <c r="P231" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -18021,7 +18322,7 @@
         </is>
       </c>
       <c r="G232" t="n">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="H232" t="inlineStr">
         <is>
@@ -18054,7 +18355,7 @@
         </is>
       </c>
       <c r="N232" t="n">
-        <v>49.439</v>
+        <v>49.027</v>
       </c>
       <c r="O232" t="inlineStr">
         <is>
@@ -18063,7 +18364,7 @@
       </c>
       <c r="P232" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -18099,7 +18400,7 @@
         </is>
       </c>
       <c r="G233" t="n">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="H233" t="inlineStr">
         <is>
@@ -18132,7 +18433,7 @@
         </is>
       </c>
       <c r="N233" t="n">
-        <v>49.121</v>
+        <v>49.439</v>
       </c>
       <c r="O233" t="inlineStr">
         <is>
@@ -18141,7 +18442,7 @@
       </c>
       <c r="P233" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -18177,7 +18478,7 @@
         </is>
       </c>
       <c r="G234" t="n">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="H234" t="inlineStr">
         <is>
@@ -18210,7 +18511,7 @@
         </is>
       </c>
       <c r="N234" t="n">
-        <v>48.519</v>
+        <v>49.121</v>
       </c>
       <c r="O234" t="inlineStr">
         <is>
@@ -18219,7 +18520,7 @@
       </c>
       <c r="P234" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -18255,7 +18556,7 @@
         </is>
       </c>
       <c r="G235" t="n">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="H235" t="inlineStr">
         <is>
@@ -18288,7 +18589,7 @@
         </is>
       </c>
       <c r="N235" t="n">
-        <v>48.502</v>
+        <v>48.519</v>
       </c>
       <c r="O235" t="inlineStr">
         <is>
@@ -18297,7 +18598,7 @@
       </c>
       <c r="P235" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -18333,7 +18634,7 @@
         </is>
       </c>
       <c r="G236" t="n">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="H236" t="inlineStr">
         <is>
@@ -18366,7 +18667,7 @@
         </is>
       </c>
       <c r="N236" t="n">
-        <v>48.683</v>
+        <v>48.502</v>
       </c>
       <c r="O236" t="inlineStr">
         <is>
@@ -18375,7 +18676,7 @@
       </c>
       <c r="P236" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -18411,7 +18712,7 @@
         </is>
       </c>
       <c r="G237" t="n">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="H237" t="inlineStr">
         <is>
@@ -18444,7 +18745,7 @@
         </is>
       </c>
       <c r="N237" t="n">
-        <v>48.743</v>
+        <v>48.683</v>
       </c>
       <c r="O237" t="inlineStr">
         <is>
@@ -18453,7 +18754,7 @@
       </c>
       <c r="P237" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -18489,7 +18790,7 @@
         </is>
       </c>
       <c r="G238" t="n">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="H238" t="inlineStr">
         <is>
@@ -18522,7 +18823,7 @@
         </is>
       </c>
       <c r="N238" t="n">
-        <v>48.976</v>
+        <v>48.743</v>
       </c>
       <c r="O238" t="inlineStr">
         <is>
@@ -18531,7 +18832,7 @@
       </c>
       <c r="P238" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -18567,7 +18868,7 @@
         </is>
       </c>
       <c r="G239" t="n">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="H239" t="inlineStr">
         <is>
@@ -18600,7 +18901,7 @@
         </is>
       </c>
       <c r="N239" t="n">
-        <v>48.119</v>
+        <v>48.976</v>
       </c>
       <c r="O239" t="inlineStr">
         <is>
@@ -18609,7 +18910,7 @@
       </c>
       <c r="P239" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -18645,7 +18946,7 @@
         </is>
       </c>
       <c r="G240" t="n">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="H240" t="inlineStr">
         <is>
@@ -18678,7 +18979,7 @@
         </is>
       </c>
       <c r="N240" t="n">
-        <v>47.914</v>
+        <v>48.119</v>
       </c>
       <c r="O240" t="inlineStr">
         <is>
@@ -18687,7 +18988,7 @@
       </c>
       <c r="P240" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -18723,7 +19024,7 @@
         </is>
       </c>
       <c r="G241" t="n">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="H241" t="inlineStr">
         <is>
@@ -18756,7 +19057,7 @@
         </is>
       </c>
       <c r="N241" t="n">
-        <v>48.527</v>
+        <v>47.914</v>
       </c>
       <c r="O241" t="inlineStr">
         <is>
@@ -18765,7 +19066,7 @@
       </c>
       <c r="P241" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -18801,7 +19102,7 @@
         </is>
       </c>
       <c r="G242" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="H242" t="inlineStr">
         <is>
@@ -18834,7 +19135,7 @@
         </is>
       </c>
       <c r="N242" t="n">
-        <v>47.765</v>
+        <v>48.527</v>
       </c>
       <c r="O242" t="inlineStr">
         <is>
@@ -18843,7 +19144,7 @@
       </c>
       <c r="P242" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -18879,7 +19180,7 @@
         </is>
       </c>
       <c r="G243" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="H243" t="inlineStr">
         <is>
@@ -18912,7 +19213,7 @@
         </is>
       </c>
       <c r="N243" t="n">
-        <v>46.462</v>
+        <v>47.765</v>
       </c>
       <c r="O243" t="inlineStr">
         <is>
@@ -18921,7 +19222,7 @@
       </c>
       <c r="P243" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -18957,7 +19258,7 @@
         </is>
       </c>
       <c r="G244" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="H244" t="inlineStr">
         <is>
@@ -18990,7 +19291,7 @@
         </is>
       </c>
       <c r="N244" t="n">
-        <v>47.558</v>
+        <v>46.462</v>
       </c>
       <c r="O244" t="inlineStr">
         <is>
@@ -18999,7 +19300,7 @@
       </c>
       <c r="P244" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -19035,7 +19336,7 @@
         </is>
       </c>
       <c r="G245" t="n">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="H245" t="inlineStr">
         <is>
@@ -19068,7 +19369,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>49.457</v>
+        <v>47.558</v>
       </c>
       <c r="O245" t="inlineStr">
         <is>
@@ -19077,7 +19378,7 @@
       </c>
       <c r="P245" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -19113,7 +19414,7 @@
         </is>
       </c>
       <c r="G246" t="n">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="H246" t="inlineStr">
         <is>
@@ -19146,7 +19447,7 @@
         </is>
       </c>
       <c r="N246" t="n">
-        <v>50.019</v>
+        <v>49.457</v>
       </c>
       <c r="O246" t="inlineStr">
         <is>
@@ -19155,7 +19456,7 @@
       </c>
       <c r="P246" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -19191,7 +19492,7 @@
         </is>
       </c>
       <c r="G247" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="H247" t="inlineStr">
         <is>
@@ -19224,7 +19525,7 @@
         </is>
       </c>
       <c r="N247" t="n">
-        <v>49.726</v>
+        <v>50.019</v>
       </c>
       <c r="O247" t="inlineStr">
         <is>
@@ -19233,7 +19534,7 @@
       </c>
       <c r="P247" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -19269,7 +19570,7 @@
         </is>
       </c>
       <c r="G248" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="H248" t="inlineStr">
         <is>
@@ -19302,7 +19603,7 @@
         </is>
       </c>
       <c r="N248" t="n">
-        <v>49.734</v>
+        <v>49.726</v>
       </c>
       <c r="O248" t="inlineStr">
         <is>
@@ -19311,7 +19612,7 @@
       </c>
       <c r="P248" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -19347,7 +19648,7 @@
         </is>
       </c>
       <c r="G249" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="H249" t="inlineStr">
         <is>
@@ -19380,7 +19681,7 @@
         </is>
       </c>
       <c r="N249" t="n">
-        <v>50.004</v>
+        <v>49.734</v>
       </c>
       <c r="O249" t="inlineStr">
         <is>
@@ -19389,7 +19690,7 @@
       </c>
       <c r="P249" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -19425,7 +19726,7 @@
         </is>
       </c>
       <c r="G250" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="H250" t="inlineStr">
         <is>
@@ -19458,7 +19759,7 @@
         </is>
       </c>
       <c r="N250" t="n">
-        <v>49.601</v>
+        <v>50.004</v>
       </c>
       <c r="O250" t="inlineStr">
         <is>
@@ -19467,7 +19768,7 @@
       </c>
       <c r="P250" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -19503,7 +19804,7 @@
         </is>
       </c>
       <c r="G251" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="H251" t="inlineStr">
         <is>
@@ -19536,7 +19837,7 @@
         </is>
       </c>
       <c r="N251" t="n">
-        <v>49.643</v>
+        <v>49.601</v>
       </c>
       <c r="O251" t="inlineStr">
         <is>
@@ -19545,7 +19846,7 @@
       </c>
       <c r="P251" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -19581,7 +19882,7 @@
         </is>
       </c>
       <c r="G252" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="H252" t="inlineStr">
         <is>
@@ -19614,7 +19915,7 @@
         </is>
       </c>
       <c r="N252" t="n">
-        <v>49.493</v>
+        <v>49.643</v>
       </c>
       <c r="O252" t="inlineStr">
         <is>
@@ -19623,7 +19924,7 @@
       </c>
       <c r="P252" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -19659,7 +19960,7 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="H253" t="inlineStr">
         <is>
@@ -19692,7 +19993,7 @@
         </is>
       </c>
       <c r="N253" t="n">
-        <v>49.084</v>
+        <v>49.493</v>
       </c>
       <c r="O253" t="inlineStr">
         <is>
@@ -19701,7 +20002,7 @@
       </c>
       <c r="P253" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -19737,7 +20038,7 @@
         </is>
       </c>
       <c r="G254" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="H254" t="inlineStr">
         <is>
@@ -19770,7 +20071,7 @@
         </is>
       </c>
       <c r="N254" t="n">
-        <v>48.676</v>
+        <v>49.084</v>
       </c>
       <c r="O254" t="inlineStr">
         <is>
@@ -19779,7 +20080,7 @@
       </c>
       <c r="P254" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -19815,7 +20116,7 @@
         </is>
       </c>
       <c r="G255" t="n">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="H255" t="inlineStr">
         <is>
@@ -19848,7 +20149,7 @@
         </is>
       </c>
       <c r="N255" t="n">
-        <v>48.27</v>
+        <v>48.676</v>
       </c>
       <c r="O255" t="inlineStr">
         <is>
@@ -19857,7 +20158,7 @@
       </c>
       <c r="P255" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -19893,7 +20194,7 @@
         </is>
       </c>
       <c r="G256" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="H256" t="inlineStr">
         <is>
@@ -19926,7 +20227,7 @@
         </is>
       </c>
       <c r="N256" t="n">
-        <v>47.867</v>
+        <v>48.27</v>
       </c>
       <c r="O256" t="inlineStr">
         <is>
@@ -19935,7 +20236,7 @@
       </c>
       <c r="P256" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -19971,7 +20272,7 @@
         </is>
       </c>
       <c r="G257" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="H257" t="inlineStr">
         <is>
@@ -20004,7 +20305,7 @@
         </is>
       </c>
       <c r="N257" t="n">
-        <v>46.185</v>
+        <v>47.867</v>
       </c>
       <c r="O257" t="inlineStr">
         <is>
@@ -20013,7 +20314,7 @@
       </c>
       <c r="P257" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -20049,7 +20350,7 @@
         </is>
       </c>
       <c r="G258" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="H258" t="inlineStr">
         <is>
@@ -20082,7 +20383,7 @@
         </is>
       </c>
       <c r="N258" t="n">
-        <v>44.85</v>
+        <v>46.185</v>
       </c>
       <c r="O258" t="inlineStr">
         <is>
@@ -20091,7 +20392,7 @@
       </c>
       <c r="P258" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -20127,7 +20428,7 @@
         </is>
       </c>
       <c r="G259" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="H259" t="inlineStr">
         <is>
@@ -20160,7 +20461,7 @@
         </is>
       </c>
       <c r="N259" t="n">
-        <v>42.344</v>
+        <v>44.85</v>
       </c>
       <c r="O259" t="inlineStr">
         <is>
@@ -20169,7 +20470,7 @@
       </c>
       <c r="P259" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -20205,7 +20506,7 @@
         </is>
       </c>
       <c r="G260" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="H260" t="inlineStr">
         <is>
@@ -20238,7 +20539,7 @@
         </is>
       </c>
       <c r="N260" t="n">
-        <v>36.887</v>
+        <v>42.344</v>
       </c>
       <c r="O260" t="inlineStr">
         <is>
@@ -20247,7 +20548,7 @@
       </c>
       <c r="P260" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -20283,7 +20584,7 @@
         </is>
       </c>
       <c r="G261" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
@@ -20316,7 +20617,7 @@
         </is>
       </c>
       <c r="N261" t="n">
-        <v>37.368</v>
+        <v>36.887</v>
       </c>
       <c r="O261" t="inlineStr">
         <is>
@@ -20325,7 +20626,7 @@
       </c>
       <c r="P261" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -20361,7 +20662,7 @@
         </is>
       </c>
       <c r="G262" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H262" t="inlineStr">
         <is>
@@ -20394,7 +20695,7 @@
         </is>
       </c>
       <c r="N262" t="n">
-        <v>35.32</v>
+        <v>37.368</v>
       </c>
       <c r="O262" t="inlineStr">
         <is>
@@ -20403,7 +20704,7 @@
       </c>
       <c r="P262" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -20439,7 +20740,7 @@
         </is>
       </c>
       <c r="G263" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="H263" t="inlineStr">
         <is>
@@ -20472,7 +20773,7 @@
         </is>
       </c>
       <c r="N263" t="n">
-        <v>36.158</v>
+        <v>35.32</v>
       </c>
       <c r="O263" t="inlineStr">
         <is>
@@ -20481,7 +20782,7 @@
       </c>
       <c r="P263" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -20517,7 +20818,7 @@
         </is>
       </c>
       <c r="G264" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="H264" t="inlineStr">
         <is>
@@ -20550,7 +20851,7 @@
         </is>
       </c>
       <c r="N264" t="n">
-        <v>37.332</v>
+        <v>36.158</v>
       </c>
       <c r="O264" t="inlineStr">
         <is>
@@ -20559,7 +20860,7 @@
       </c>
       <c r="P264" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -20595,7 +20896,7 @@
         </is>
       </c>
       <c r="G265" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="H265" t="inlineStr">
         <is>
@@ -20628,7 +20929,7 @@
         </is>
       </c>
       <c r="N265" t="n">
-        <v>37.098</v>
+        <v>37.332</v>
       </c>
       <c r="O265" t="inlineStr">
         <is>
@@ -20637,7 +20938,7 @@
       </c>
       <c r="P265" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -20673,7 +20974,7 @@
         </is>
       </c>
       <c r="G266" t="n">
-        <v>1960</v>
+        <v>2025</v>
       </c>
       <c r="H266" t="inlineStr">
         <is>
@@ -20697,13 +20998,16 @@
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t>SL.UEM.TOTL.FE.ZS</t>
+          <t>SL.TLF.CACT.FE.ZS</t>
         </is>
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Desempleo femenino</t>
-        </is>
+          <t>Participación laboral femenina</t>
+        </is>
+      </c>
+      <c r="N266" t="n">
+        <v>37.098</v>
       </c>
       <c r="O266" t="inlineStr">
         <is>
@@ -20712,7 +21016,7 @@
       </c>
       <c r="P266" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -20748,7 +21052,7 @@
         </is>
       </c>
       <c r="G267" t="n">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="H267" t="inlineStr">
         <is>
@@ -20787,7 +21091,7 @@
       </c>
       <c r="P267" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -20823,7 +21127,7 @@
         </is>
       </c>
       <c r="G268" t="n">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="H268" t="inlineStr">
         <is>
@@ -20862,7 +21166,7 @@
       </c>
       <c r="P268" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -20898,7 +21202,7 @@
         </is>
       </c>
       <c r="G269" t="n">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="H269" t="inlineStr">
         <is>
@@ -20937,7 +21241,7 @@
       </c>
       <c r="P269" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -20973,7 +21277,7 @@
         </is>
       </c>
       <c r="G270" t="n">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="H270" t="inlineStr">
         <is>
@@ -21012,7 +21316,7 @@
       </c>
       <c r="P270" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -21048,7 +21352,7 @@
         </is>
       </c>
       <c r="G271" t="n">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="H271" t="inlineStr">
         <is>
@@ -21087,7 +21391,7 @@
       </c>
       <c r="P271" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -21123,7 +21427,7 @@
         </is>
       </c>
       <c r="G272" t="n">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="H272" t="inlineStr">
         <is>
@@ -21162,7 +21466,7 @@
       </c>
       <c r="P272" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -21198,7 +21502,7 @@
         </is>
       </c>
       <c r="G273" t="n">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="H273" t="inlineStr">
         <is>
@@ -21237,7 +21541,7 @@
       </c>
       <c r="P273" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -21273,7 +21577,7 @@
         </is>
       </c>
       <c r="G274" t="n">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="H274" t="inlineStr">
         <is>
@@ -21312,7 +21616,7 @@
       </c>
       <c r="P274" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -21348,7 +21652,7 @@
         </is>
       </c>
       <c r="G275" t="n">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="H275" t="inlineStr">
         <is>
@@ -21387,7 +21691,7 @@
       </c>
       <c r="P275" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -21423,7 +21727,7 @@
         </is>
       </c>
       <c r="G276" t="n">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="H276" t="inlineStr">
         <is>
@@ -21462,7 +21766,7 @@
       </c>
       <c r="P276" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -21498,7 +21802,7 @@
         </is>
       </c>
       <c r="G277" t="n">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="H277" t="inlineStr">
         <is>
@@ -21537,7 +21841,7 @@
       </c>
       <c r="P277" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -21573,7 +21877,7 @@
         </is>
       </c>
       <c r="G278" t="n">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="H278" t="inlineStr">
         <is>
@@ -21612,7 +21916,7 @@
       </c>
       <c r="P278" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -21648,7 +21952,7 @@
         </is>
       </c>
       <c r="G279" t="n">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="H279" t="inlineStr">
         <is>
@@ -21687,7 +21991,7 @@
       </c>
       <c r="P279" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -21723,7 +22027,7 @@
         </is>
       </c>
       <c r="G280" t="n">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="H280" t="inlineStr">
         <is>
@@ -21762,7 +22066,7 @@
       </c>
       <c r="P280" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -21798,7 +22102,7 @@
         </is>
       </c>
       <c r="G281" t="n">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="H281" t="inlineStr">
         <is>
@@ -21837,7 +22141,7 @@
       </c>
       <c r="P281" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -21873,7 +22177,7 @@
         </is>
       </c>
       <c r="G282" t="n">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="H282" t="inlineStr">
         <is>
@@ -21912,7 +22216,7 @@
       </c>
       <c r="P282" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -21948,7 +22252,7 @@
         </is>
       </c>
       <c r="G283" t="n">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="H283" t="inlineStr">
         <is>
@@ -21987,7 +22291,7 @@
       </c>
       <c r="P283" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -22023,7 +22327,7 @@
         </is>
       </c>
       <c r="G284" t="n">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="H284" t="inlineStr">
         <is>
@@ -22062,7 +22366,7 @@
       </c>
       <c r="P284" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -22098,7 +22402,7 @@
         </is>
       </c>
       <c r="G285" t="n">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="H285" t="inlineStr">
         <is>
@@ -22137,7 +22441,7 @@
       </c>
       <c r="P285" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -22173,7 +22477,7 @@
         </is>
       </c>
       <c r="G286" t="n">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="H286" t="inlineStr">
         <is>
@@ -22212,7 +22516,7 @@
       </c>
       <c r="P286" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -22248,7 +22552,7 @@
         </is>
       </c>
       <c r="G287" t="n">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="H287" t="inlineStr">
         <is>
@@ -22287,7 +22591,7 @@
       </c>
       <c r="P287" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -22323,7 +22627,7 @@
         </is>
       </c>
       <c r="G288" t="n">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="H288" t="inlineStr">
         <is>
@@ -22362,7 +22666,7 @@
       </c>
       <c r="P288" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -22398,7 +22702,7 @@
         </is>
       </c>
       <c r="G289" t="n">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="H289" t="inlineStr">
         <is>
@@ -22437,7 +22741,7 @@
       </c>
       <c r="P289" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -22473,7 +22777,7 @@
         </is>
       </c>
       <c r="G290" t="n">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="H290" t="inlineStr">
         <is>
@@ -22512,7 +22816,7 @@
       </c>
       <c r="P290" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -22548,7 +22852,7 @@
         </is>
       </c>
       <c r="G291" t="n">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="H291" t="inlineStr">
         <is>
@@ -22587,7 +22891,7 @@
       </c>
       <c r="P291" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -22623,7 +22927,7 @@
         </is>
       </c>
       <c r="G292" t="n">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="H292" t="inlineStr">
         <is>
@@ -22662,7 +22966,7 @@
       </c>
       <c r="P292" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -22698,7 +23002,7 @@
         </is>
       </c>
       <c r="G293" t="n">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="H293" t="inlineStr">
         <is>
@@ -22737,7 +23041,7 @@
       </c>
       <c r="P293" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -22773,7 +23077,7 @@
         </is>
       </c>
       <c r="G294" t="n">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="H294" t="inlineStr">
         <is>
@@ -22812,7 +23116,7 @@
       </c>
       <c r="P294" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -22848,7 +23152,7 @@
         </is>
       </c>
       <c r="G295" t="n">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="H295" t="inlineStr">
         <is>
@@ -22887,7 +23191,7 @@
       </c>
       <c r="P295" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -22923,7 +23227,7 @@
         </is>
       </c>
       <c r="G296" t="n">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="H296" t="inlineStr">
         <is>
@@ -22962,7 +23266,7 @@
       </c>
       <c r="P296" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -22998,7 +23302,7 @@
         </is>
       </c>
       <c r="G297" t="n">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="H297" t="inlineStr">
         <is>
@@ -23030,9 +23334,6 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N297" t="n">
-        <v>9.32</v>
-      </c>
       <c r="O297" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -23040,7 +23341,7 @@
       </c>
       <c r="P297" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -23076,7 +23377,7 @@
         </is>
       </c>
       <c r="G298" t="n">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="H298" t="inlineStr">
         <is>
@@ -23109,7 +23410,7 @@
         </is>
       </c>
       <c r="N298" t="n">
-        <v>6.925</v>
+        <v>9.32</v>
       </c>
       <c r="O298" t="inlineStr">
         <is>
@@ -23118,7 +23419,7 @@
       </c>
       <c r="P298" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -23154,7 +23455,7 @@
         </is>
       </c>
       <c r="G299" t="n">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="H299" t="inlineStr">
         <is>
@@ -23187,7 +23488,7 @@
         </is>
       </c>
       <c r="N299" t="n">
-        <v>5.679</v>
+        <v>6.925</v>
       </c>
       <c r="O299" t="inlineStr">
         <is>
@@ -23196,7 +23497,7 @@
       </c>
       <c r="P299" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -23232,7 +23533,7 @@
         </is>
       </c>
       <c r="G300" t="n">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="H300" t="inlineStr">
         <is>
@@ -23265,7 +23566,7 @@
         </is>
       </c>
       <c r="N300" t="n">
-        <v>9.557</v>
+        <v>5.679</v>
       </c>
       <c r="O300" t="inlineStr">
         <is>
@@ -23274,7 +23575,7 @@
       </c>
       <c r="P300" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -23310,7 +23611,7 @@
         </is>
       </c>
       <c r="G301" t="n">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="H301" t="inlineStr">
         <is>
@@ -23343,7 +23644,7 @@
         </is>
       </c>
       <c r="N301" t="n">
-        <v>12.604</v>
+        <v>9.557</v>
       </c>
       <c r="O301" t="inlineStr">
         <is>
@@ -23352,7 +23653,7 @@
       </c>
       <c r="P301" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -23388,7 +23689,7 @@
         </is>
       </c>
       <c r="G302" t="n">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="H302" t="inlineStr">
         <is>
@@ -23421,7 +23722,7 @@
         </is>
       </c>
       <c r="N302" t="n">
-        <v>14.345</v>
+        <v>12.604</v>
       </c>
       <c r="O302" t="inlineStr">
         <is>
@@ -23430,7 +23731,7 @@
       </c>
       <c r="P302" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -23466,7 +23767,7 @@
         </is>
       </c>
       <c r="G303" t="n">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="H303" t="inlineStr">
         <is>
@@ -23499,7 +23800,7 @@
         </is>
       </c>
       <c r="N303" t="n">
-        <v>13.627</v>
+        <v>14.345</v>
       </c>
       <c r="O303" t="inlineStr">
         <is>
@@ -23508,7 +23809,7 @@
       </c>
       <c r="P303" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -23544,7 +23845,7 @@
         </is>
       </c>
       <c r="G304" t="n">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="H304" t="inlineStr">
         <is>
@@ -23577,7 +23878,7 @@
         </is>
       </c>
       <c r="N304" t="n">
-        <v>13.306</v>
+        <v>13.627</v>
       </c>
       <c r="O304" t="inlineStr">
         <is>
@@ -23586,7 +23887,7 @@
       </c>
       <c r="P304" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -23622,7 +23923,7 @@
         </is>
       </c>
       <c r="G305" t="n">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="H305" t="inlineStr">
         <is>
@@ -23655,7 +23956,7 @@
         </is>
       </c>
       <c r="N305" t="n">
-        <v>16.482</v>
+        <v>13.306</v>
       </c>
       <c r="O305" t="inlineStr">
         <is>
@@ -23664,7 +23965,7 @@
       </c>
       <c r="P305" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -23700,7 +24001,7 @@
         </is>
       </c>
       <c r="G306" t="n">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="H306" t="inlineStr">
         <is>
@@ -23733,7 +24034,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>14.605</v>
+        <v>16.482</v>
       </c>
       <c r="O306" t="inlineStr">
         <is>
@@ -23742,7 +24043,7 @@
       </c>
       <c r="P306" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -23778,7 +24079,7 @@
         </is>
       </c>
       <c r="G307" t="n">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="H307" t="inlineStr">
         <is>
@@ -23811,7 +24112,7 @@
         </is>
       </c>
       <c r="N307" t="n">
-        <v>14.109</v>
+        <v>14.605</v>
       </c>
       <c r="O307" t="inlineStr">
         <is>
@@ -23820,7 +24121,7 @@
       </c>
       <c r="P307" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -23856,7 +24157,7 @@
         </is>
       </c>
       <c r="G308" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="H308" t="inlineStr">
         <is>
@@ -23889,7 +24190,7 @@
         </is>
       </c>
       <c r="N308" t="n">
-        <v>18.895</v>
+        <v>14.109</v>
       </c>
       <c r="O308" t="inlineStr">
         <is>
@@ -23898,7 +24199,7 @@
       </c>
       <c r="P308" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -23934,7 +24235,7 @@
         </is>
       </c>
       <c r="G309" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="H309" t="inlineStr">
         <is>
@@ -23967,7 +24268,7 @@
         </is>
       </c>
       <c r="N309" t="n">
-        <v>20.483</v>
+        <v>18.895</v>
       </c>
       <c r="O309" t="inlineStr">
         <is>
@@ -23976,7 +24277,7 @@
       </c>
       <c r="P309" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -24012,7 +24313,7 @@
         </is>
       </c>
       <c r="G310" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="H310" t="inlineStr">
         <is>
@@ -24045,7 +24346,7 @@
         </is>
       </c>
       <c r="N310" t="n">
-        <v>17.974</v>
+        <v>20.483</v>
       </c>
       <c r="O310" t="inlineStr">
         <is>
@@ -24054,7 +24355,7 @@
       </c>
       <c r="P310" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -24090,7 +24391,7 @@
         </is>
       </c>
       <c r="G311" t="n">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="H311" t="inlineStr">
         <is>
@@ -24123,7 +24424,7 @@
         </is>
       </c>
       <c r="N311" t="n">
-        <v>11.64</v>
+        <v>17.974</v>
       </c>
       <c r="O311" t="inlineStr">
         <is>
@@ -24132,7 +24433,7 @@
       </c>
       <c r="P311" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -24168,7 +24469,7 @@
         </is>
       </c>
       <c r="G312" t="n">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="H312" t="inlineStr">
         <is>
@@ -24201,7 +24502,7 @@
         </is>
       </c>
       <c r="N312" t="n">
-        <v>9.380000000000001</v>
+        <v>11.64</v>
       </c>
       <c r="O312" t="inlineStr">
         <is>
@@ -24210,7 +24511,7 @@
       </c>
       <c r="P312" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -24246,7 +24547,7 @@
         </is>
       </c>
       <c r="G313" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="H313" t="inlineStr">
         <is>
@@ -24279,7 +24580,7 @@
         </is>
       </c>
       <c r="N313" t="n">
-        <v>7.643</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="O313" t="inlineStr">
         <is>
@@ -24288,7 +24589,7 @@
       </c>
       <c r="P313" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -24324,7 +24625,7 @@
         </is>
       </c>
       <c r="G314" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="H314" t="inlineStr">
         <is>
@@ -24357,7 +24658,7 @@
         </is>
       </c>
       <c r="N314" t="n">
-        <v>6.218</v>
+        <v>7.643</v>
       </c>
       <c r="O314" t="inlineStr">
         <is>
@@ -24366,7 +24667,7 @@
       </c>
       <c r="P314" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -24402,7 +24703,7 @@
         </is>
       </c>
       <c r="G315" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="H315" t="inlineStr">
         <is>
@@ -24435,7 +24736,7 @@
         </is>
       </c>
       <c r="N315" t="n">
-        <v>5.965</v>
+        <v>6.218</v>
       </c>
       <c r="O315" t="inlineStr">
         <is>
@@ -24444,7 +24745,7 @@
       </c>
       <c r="P315" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -24480,7 +24781,7 @@
         </is>
       </c>
       <c r="G316" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="H316" t="inlineStr">
         <is>
@@ -24513,7 +24814,7 @@
         </is>
       </c>
       <c r="N316" t="n">
-        <v>6.952</v>
+        <v>5.965</v>
       </c>
       <c r="O316" t="inlineStr">
         <is>
@@ -24522,7 +24823,7 @@
       </c>
       <c r="P316" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -24558,7 +24859,7 @@
         </is>
       </c>
       <c r="G317" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="H317" t="inlineStr">
         <is>
@@ -24591,7 +24892,7 @@
         </is>
       </c>
       <c r="N317" t="n">
-        <v>7.206</v>
+        <v>6.952</v>
       </c>
       <c r="O317" t="inlineStr">
         <is>
@@ -24600,7 +24901,7 @@
       </c>
       <c r="P317" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -24636,7 +24937,7 @@
         </is>
       </c>
       <c r="G318" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="H318" t="inlineStr">
         <is>
@@ -24669,7 +24970,7 @@
         </is>
       </c>
       <c r="N318" t="n">
-        <v>7.109</v>
+        <v>7.206</v>
       </c>
       <c r="O318" t="inlineStr">
         <is>
@@ -24678,7 +24979,7 @@
       </c>
       <c r="P318" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -24714,7 +25015,7 @@
         </is>
       </c>
       <c r="G319" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="H319" t="inlineStr">
         <is>
@@ -24747,7 +25048,7 @@
         </is>
       </c>
       <c r="N319" t="n">
-        <v>8.605</v>
+        <v>7.109</v>
       </c>
       <c r="O319" t="inlineStr">
         <is>
@@ -24756,7 +25057,7 @@
       </c>
       <c r="P319" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -24792,7 +25093,7 @@
         </is>
       </c>
       <c r="G320" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="H320" t="inlineStr">
         <is>
@@ -24825,7 +25126,7 @@
         </is>
       </c>
       <c r="N320" t="n">
-        <v>7.578</v>
+        <v>8.605</v>
       </c>
       <c r="O320" t="inlineStr">
         <is>
@@ -24834,7 +25135,7 @@
       </c>
       <c r="P320" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -24870,7 +25171,7 @@
         </is>
       </c>
       <c r="G321" t="n">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="H321" t="inlineStr">
         <is>
@@ -24903,7 +25204,7 @@
         </is>
       </c>
       <c r="N321" t="n">
-        <v>6.572</v>
+        <v>7.578</v>
       </c>
       <c r="O321" t="inlineStr">
         <is>
@@ -24912,7 +25213,7 @@
       </c>
       <c r="P321" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -24948,7 +25249,7 @@
         </is>
       </c>
       <c r="G322" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="H322" t="inlineStr">
         <is>
@@ -24981,7 +25282,7 @@
         </is>
       </c>
       <c r="N322" t="n">
-        <v>5.413</v>
+        <v>6.572</v>
       </c>
       <c r="O322" t="inlineStr">
         <is>
@@ -24990,7 +25291,7 @@
       </c>
       <c r="P322" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -25026,7 +25327,7 @@
         </is>
       </c>
       <c r="G323" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="H323" t="inlineStr">
         <is>
@@ -25059,7 +25360,7 @@
         </is>
       </c>
       <c r="N323" t="n">
-        <v>5.858</v>
+        <v>5.413</v>
       </c>
       <c r="O323" t="inlineStr">
         <is>
@@ -25068,7 +25369,7 @@
       </c>
       <c r="P323" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -25104,7 +25405,7 @@
         </is>
       </c>
       <c r="G324" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="H324" t="inlineStr">
         <is>
@@ -25137,7 +25438,7 @@
         </is>
       </c>
       <c r="N324" t="n">
-        <v>6.178</v>
+        <v>5.858</v>
       </c>
       <c r="O324" t="inlineStr">
         <is>
@@ -25146,7 +25447,7 @@
       </c>
       <c r="P324" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -25182,7 +25483,7 @@
         </is>
       </c>
       <c r="G325" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="H325" t="inlineStr">
         <is>
@@ -25215,7 +25516,7 @@
         </is>
       </c>
       <c r="N325" t="n">
-        <v>6.497</v>
+        <v>6.178</v>
       </c>
       <c r="O325" t="inlineStr">
         <is>
@@ -25224,7 +25525,7 @@
       </c>
       <c r="P325" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -25260,7 +25561,7 @@
         </is>
       </c>
       <c r="G326" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="H326" t="inlineStr">
         <is>
@@ -25293,7 +25594,7 @@
         </is>
       </c>
       <c r="N326" t="n">
-        <v>7.907</v>
+        <v>6.497</v>
       </c>
       <c r="O326" t="inlineStr">
         <is>
@@ -25302,7 +25603,7 @@
       </c>
       <c r="P326" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -25338,7 +25639,7 @@
         </is>
       </c>
       <c r="G327" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="H327" t="inlineStr">
         <is>
@@ -25371,7 +25672,7 @@
         </is>
       </c>
       <c r="N327" t="n">
-        <v>7.541</v>
+        <v>7.907</v>
       </c>
       <c r="O327" t="inlineStr">
         <is>
@@ -25380,7 +25681,7 @@
       </c>
       <c r="P327" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -25416,7 +25717,7 @@
         </is>
       </c>
       <c r="G328" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H328" t="inlineStr">
         <is>
@@ -25449,7 +25750,7 @@
         </is>
       </c>
       <c r="N328" t="n">
-        <v>6.179</v>
+        <v>7.541</v>
       </c>
       <c r="O328" t="inlineStr">
         <is>
@@ -25458,7 +25759,7 @@
       </c>
       <c r="P328" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -25494,7 +25795,7 @@
         </is>
       </c>
       <c r="G329" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="H329" t="inlineStr">
         <is>
@@ -25527,7 +25828,7 @@
         </is>
       </c>
       <c r="N329" t="n">
-        <v>5.937</v>
+        <v>6.179</v>
       </c>
       <c r="O329" t="inlineStr">
         <is>
@@ -25536,7 +25837,7 @@
       </c>
       <c r="P329" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -25572,7 +25873,7 @@
         </is>
       </c>
       <c r="G330" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="H330" t="inlineStr">
         <is>
@@ -25605,7 +25906,7 @@
         </is>
       </c>
       <c r="N330" t="n">
-        <v>5.845</v>
+        <v>5.937</v>
       </c>
       <c r="O330" t="inlineStr">
         <is>
@@ -25614,7 +25915,7 @@
       </c>
       <c r="P330" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -25650,49 +25951,127 @@
         </is>
       </c>
       <c r="G331" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>Género</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>genero</t>
+        </is>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>Mercado laboral</t>
+        </is>
+      </c>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>mercado_laboral</t>
+        </is>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>SL.UEM.TOTL.FE.ZS</t>
+        </is>
+      </c>
+      <c r="M331" t="inlineStr">
+        <is>
+          <t>Desempleo femenino</t>
+        </is>
+      </c>
+      <c r="N331" t="n">
+        <v>5.845</v>
+      </c>
+      <c r="O331" t="inlineStr">
+        <is>
+          <t>Banco Mundial - World Development Indicators</t>
+        </is>
+      </c>
+      <c r="P331" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Venezuela, RB</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>Not classified</t>
+        </is>
+      </c>
+      <c r="G332" t="n">
         <v>2025</v>
       </c>
-      <c r="H331" t="inlineStr">
-        <is>
-          <t>Género</t>
-        </is>
-      </c>
-      <c r="I331" t="inlineStr">
-        <is>
-          <t>genero</t>
-        </is>
-      </c>
-      <c r="J331" t="inlineStr">
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>Género</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>genero</t>
+        </is>
+      </c>
+      <c r="J332" t="inlineStr">
         <is>
           <t>Mercado laboral</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr">
+      <c r="K332" t="inlineStr">
         <is>
           <t>mercado_laboral</t>
         </is>
       </c>
-      <c r="L331" t="inlineStr">
+      <c r="L332" t="inlineStr">
         <is>
           <t>SL.UEM.TOTL.FE.ZS</t>
         </is>
       </c>
-      <c r="M331" t="inlineStr">
+      <c r="M332" t="inlineStr">
         <is>
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N331" t="n">
+      <c r="N332" t="n">
         <v>5.835</v>
       </c>
-      <c r="O331" t="inlineStr">
-        <is>
-          <t>Banco Mundial - World Development Indicators</t>
-        </is>
-      </c>
-      <c r="P331" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
+      <c r="O332" t="inlineStr">
+        <is>
+          <t>Banco Mundial - World Development Indicators</t>
+        </is>
+      </c>
+      <c r="P332" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -25742,7 +26121,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -25763,7 +26142,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
   </sheetData>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_genero.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_genero.xlsx
@@ -17,7 +17,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="[$-es-ES]#,##0"/>
+    <numFmt numFmtId="165" formatCode="[$-es-ES]#,##0.00"/>
+  </numFmts>
   <fonts count="5">
     <font>
       <name val="Calibri"/>
@@ -69,7 +72,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -83,6 +86,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -114,6 +123,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -144,6 +156,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -597,7 +612,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="G7" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -674,7 +689,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="G8" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -751,7 +766,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="G9" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -828,7 +843,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="G10" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -905,7 +920,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="G11" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -982,7 +997,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="G12" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -1059,7 +1074,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="G13" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1136,7 +1151,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="G14" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -1213,7 +1228,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="G15" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H15" s="4" t="inlineStr">
@@ -1290,7 +1305,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="G16" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -1367,7 +1382,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="G17" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H17" s="4" t="inlineStr">
@@ -1444,7 +1459,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G18" s="4" t="n">
+      <c r="G18" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H18" s="4" t="inlineStr">
@@ -1477,7 +1492,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N18" s="4" t="n">
+      <c r="N18" s="8" t="n">
         <v>1.02354001998901</v>
       </c>
       <c r="O18" s="4" t="inlineStr">
@@ -1523,7 +1538,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="G19" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -1556,7 +1571,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N19" s="4" t="n">
+      <c r="N19" s="8" t="n">
         <v>1.02113997936249</v>
       </c>
       <c r="O19" s="4" t="inlineStr">
@@ -1602,7 +1617,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G20" s="4" t="n">
+      <c r="G20" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H20" s="4" t="inlineStr">
@@ -1635,7 +1650,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N20" s="4" t="n">
+      <c r="N20" s="8" t="n">
         <v>1.01996004581451</v>
       </c>
       <c r="O20" s="4" t="inlineStr">
@@ -1681,7 +1696,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G21" s="4" t="n">
+      <c r="G21" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H21" s="4" t="inlineStr">
@@ -1714,7 +1729,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N21" s="4" t="n">
+      <c r="N21" s="8" t="n">
         <v>1.01884996891022</v>
       </c>
       <c r="O21" s="4" t="inlineStr">
@@ -1760,7 +1775,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G22" s="4" t="n">
+      <c r="G22" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -1793,7 +1808,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N22" s="4" t="n">
+      <c r="N22" s="8" t="n">
         <v>1.01637005805969</v>
       </c>
       <c r="O22" s="4" t="inlineStr">
@@ -1839,7 +1854,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G23" s="4" t="n">
+      <c r="G23" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -1872,7 +1887,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N23" s="4" t="n">
+      <c r="N23" s="8" t="n">
         <v>1.01276004314423</v>
       </c>
       <c r="O23" s="4" t="inlineStr">
@@ -1918,7 +1933,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G24" s="4" t="n">
+      <c r="G24" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -1951,7 +1966,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N24" s="4" t="n">
+      <c r="N24" s="8" t="n">
         <v>1.00941002368927</v>
       </c>
       <c r="O24" s="4" t="inlineStr">
@@ -1997,7 +2012,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G25" s="4" t="n">
+      <c r="G25" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H25" s="4" t="inlineStr">
@@ -2030,7 +2045,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N25" s="4" t="n">
+      <c r="N25" s="8" t="n">
         <v>1.01135003566742</v>
       </c>
       <c r="O25" s="4" t="inlineStr">
@@ -2076,7 +2091,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G26" s="4" t="n">
+      <c r="G26" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -2109,7 +2124,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N26" s="4" t="n">
+      <c r="N26" s="8" t="n">
         <v>1.01270997524261</v>
       </c>
       <c r="O26" s="4" t="inlineStr">
@@ -2155,7 +2170,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G27" s="4" t="n">
+      <c r="G27" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -2188,7 +2203,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N27" s="4" t="n">
+      <c r="N27" s="8" t="n">
         <v>1.0116800069809</v>
       </c>
       <c r="O27" s="4" t="inlineStr">
@@ -2234,7 +2249,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G28" s="4" t="n">
+      <c r="G28" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H28" s="4" t="inlineStr">
@@ -2311,7 +2326,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G29" s="4" t="n">
+      <c r="G29" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H29" s="4" t="inlineStr">
@@ -2388,7 +2403,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G30" s="4" t="n">
+      <c r="G30" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H30" s="4" t="inlineStr">
@@ -2421,7 +2436,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N30" s="4" t="n">
+      <c r="N30" s="8" t="n">
         <v>1.0331699848175</v>
       </c>
       <c r="O30" s="4" t="inlineStr">
@@ -2467,7 +2482,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G31" s="4" t="n">
+      <c r="G31" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H31" s="4" t="inlineStr">
@@ -2500,7 +2515,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N31" s="4" t="n">
+      <c r="N31" s="8" t="n">
         <v>0.99974000453949</v>
       </c>
       <c r="O31" s="4" t="inlineStr">
@@ -2546,7 +2561,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G32" s="4" t="n">
+      <c r="G32" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -2579,7 +2594,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N32" s="4" t="n">
+      <c r="N32" s="8" t="n">
         <v>0.9933900237083439</v>
       </c>
       <c r="O32" s="4" t="inlineStr">
@@ -2625,7 +2640,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G33" s="4" t="n">
+      <c r="G33" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H33" s="4" t="inlineStr">
@@ -2658,7 +2673,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N33" s="4" t="n">
+      <c r="N33" s="8" t="n">
         <v>0.9947800040245059</v>
       </c>
       <c r="O33" s="4" t="inlineStr">
@@ -2704,7 +2719,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G34" s="4" t="n">
+      <c r="G34" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H34" s="4" t="inlineStr">
@@ -2737,7 +2752,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N34" s="4" t="n">
+      <c r="N34" s="8" t="n">
         <v>0.995450019836426</v>
       </c>
       <c r="O34" s="4" t="inlineStr">
@@ -2783,7 +2798,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G35" s="4" t="n">
+      <c r="G35" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H35" s="4" t="inlineStr">
@@ -2816,7 +2831,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N35" s="4" t="n">
+      <c r="N35" s="8" t="n">
         <v>0.997699975967407</v>
       </c>
       <c r="O35" s="4" t="inlineStr">
@@ -2862,7 +2877,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G36" s="4" t="n">
+      <c r="G36" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H36" s="4" t="inlineStr">
@@ -2895,7 +2910,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N36" s="4" t="n">
+      <c r="N36" s="8" t="n">
         <v>1.00051999092102</v>
       </c>
       <c r="O36" s="4" t="inlineStr">
@@ -2941,7 +2956,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G37" s="4" t="n">
+      <c r="G37" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H37" s="4" t="inlineStr">
@@ -3018,7 +3033,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G38" s="4" t="n">
+      <c r="G38" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H38" s="4" t="inlineStr">
@@ -3051,7 +3066,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N38" s="4" t="n">
+      <c r="N38" s="8" t="n">
         <v>0.989409983158112</v>
       </c>
       <c r="O38" s="4" t="inlineStr">
@@ -3097,7 +3112,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G39" s="4" t="n">
+      <c r="G39" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H39" s="4" t="inlineStr">
@@ -3130,7 +3145,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N39" s="4" t="n">
+      <c r="N39" s="8" t="n">
         <v>0.98183000087738</v>
       </c>
       <c r="O39" s="4" t="inlineStr">
@@ -3176,7 +3191,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G40" s="4" t="n">
+      <c r="G40" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H40" s="4" t="inlineStr">
@@ -3209,7 +3224,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N40" s="4" t="n">
+      <c r="N40" s="8" t="n">
         <v>0.978500008583069</v>
       </c>
       <c r="O40" s="4" t="inlineStr">
@@ -3255,7 +3270,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G41" s="4" t="n">
+      <c r="G41" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H41" s="4" t="inlineStr">
@@ -3332,7 +3347,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G42" s="4" t="n">
+      <c r="G42" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H42" s="4" t="inlineStr">
@@ -3409,7 +3424,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G43" s="4" t="n">
+      <c r="G43" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H43" s="4" t="inlineStr">
@@ -3442,7 +3457,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N43" s="4" t="n">
+      <c r="N43" s="8" t="n">
         <v>0.986720025539398</v>
       </c>
       <c r="O43" s="4" t="inlineStr">
@@ -3488,7 +3503,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G44" s="4" t="n">
+      <c r="G44" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H44" s="4" t="inlineStr">
@@ -3521,7 +3536,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N44" s="4" t="n">
+      <c r="N44" s="8" t="n">
         <v>0.97969001531601</v>
       </c>
       <c r="O44" s="4" t="inlineStr">
@@ -3567,7 +3582,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G45" s="4" t="n">
+      <c r="G45" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H45" s="4" t="inlineStr">
@@ -3644,7 +3659,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G46" s="4" t="n">
+      <c r="G46" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H46" s="4" t="inlineStr">
@@ -3677,7 +3692,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N46" s="4" t="n">
+      <c r="N46" s="8" t="n">
         <v>0.983089983463287</v>
       </c>
       <c r="O46" s="4" t="inlineStr">
@@ -3723,7 +3738,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G47" s="4" t="n">
+      <c r="G47" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H47" s="4" t="inlineStr">
@@ -3756,7 +3771,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N47" s="4" t="n">
+      <c r="N47" s="8" t="n">
         <v>0.983439981937408</v>
       </c>
       <c r="O47" s="4" t="inlineStr">
@@ -3802,7 +3817,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G48" s="4" t="n">
+      <c r="G48" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H48" s="4" t="inlineStr">
@@ -3835,7 +3850,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N48" s="4" t="n">
+      <c r="N48" s="8" t="n">
         <v>0.982729971408844</v>
       </c>
       <c r="O48" s="4" t="inlineStr">
@@ -3881,7 +3896,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G49" s="4" t="n">
+      <c r="G49" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H49" s="4" t="inlineStr">
@@ -3914,7 +3929,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N49" s="4" t="n">
+      <c r="N49" s="8" t="n">
         <v>0.98131000995636</v>
       </c>
       <c r="O49" s="4" t="inlineStr">
@@ -3960,7 +3975,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G50" s="4" t="n">
+      <c r="G50" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H50" s="4" t="inlineStr">
@@ -3993,7 +4008,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N50" s="4" t="n">
+      <c r="N50" s="8" t="n">
         <v>0.980359971523285</v>
       </c>
       <c r="O50" s="4" t="inlineStr">
@@ -4039,7 +4054,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G51" s="4" t="n">
+      <c r="G51" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H51" s="4" t="inlineStr">
@@ -4072,7 +4087,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N51" s="4" t="n">
+      <c r="N51" s="8" t="n">
         <v>0.979730010032654</v>
       </c>
       <c r="O51" s="4" t="inlineStr">
@@ -4118,7 +4133,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G52" s="4" t="n">
+      <c r="G52" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H52" s="4" t="inlineStr">
@@ -4151,7 +4166,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N52" s="4" t="n">
+      <c r="N52" s="8" t="n">
         <v>0.981199979782104</v>
       </c>
       <c r="O52" s="4" t="inlineStr">
@@ -4197,7 +4212,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G53" s="4" t="n">
+      <c r="G53" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H53" s="4" t="inlineStr">
@@ -4230,7 +4245,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N53" s="4" t="n">
+      <c r="N53" s="8" t="n">
         <v>0.977609992027283</v>
       </c>
       <c r="O53" s="4" t="inlineStr">
@@ -4276,7 +4291,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G54" s="4" t="n">
+      <c r="G54" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H54" s="4" t="inlineStr">
@@ -4309,7 +4324,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N54" s="4" t="n">
+      <c r="N54" s="8" t="n">
         <v>0.974629998207092</v>
       </c>
       <c r="O54" s="4" t="inlineStr">
@@ -4355,7 +4370,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G55" s="4" t="n">
+      <c r="G55" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H55" s="4" t="inlineStr">
@@ -4388,7 +4403,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N55" s="4" t="n">
+      <c r="N55" s="8" t="n">
         <v>0.974510014057159</v>
       </c>
       <c r="O55" s="4" t="inlineStr">
@@ -4434,7 +4449,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G56" s="4" t="n">
+      <c r="G56" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H56" s="4" t="inlineStr">
@@ -4467,7 +4482,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N56" s="4" t="n">
+      <c r="N56" s="8" t="n">
         <v>0.974039971828461</v>
       </c>
       <c r="O56" s="4" t="inlineStr">
@@ -4513,7 +4528,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G57" s="4" t="n">
+      <c r="G57" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H57" s="4" t="inlineStr">
@@ -4546,7 +4561,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N57" s="4" t="n">
+      <c r="N57" s="8" t="n">
         <v>0.972440004348755</v>
       </c>
       <c r="O57" s="4" t="inlineStr">
@@ -4592,7 +4607,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G58" s="4" t="n">
+      <c r="G58" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H58" s="4" t="inlineStr">
@@ -4625,7 +4640,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N58" s="4" t="n">
+      <c r="N58" s="8" t="n">
         <v>0.975350022315979</v>
       </c>
       <c r="O58" s="4" t="inlineStr">
@@ -4671,7 +4686,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G59" s="4" t="n">
+      <c r="G59" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H59" s="4" t="inlineStr">
@@ -4704,7 +4719,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N59" s="4" t="n">
+      <c r="N59" s="8" t="n">
         <v>0.98063999414444</v>
       </c>
       <c r="O59" s="4" t="inlineStr">
@@ -4750,7 +4765,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G60" s="4" t="n">
+      <c r="G60" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H60" s="4" t="inlineStr">
@@ -4783,7 +4798,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N60" s="4" t="n">
+      <c r="N60" s="8" t="n">
         <v>0.9868900179862981</v>
       </c>
       <c r="O60" s="4" t="inlineStr">
@@ -4829,7 +4844,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G61" s="4" t="n">
+      <c r="G61" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H61" s="4" t="inlineStr">
@@ -4862,7 +4877,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N61" s="4" t="n">
+      <c r="N61" s="8" t="n">
         <v>0.9825199842453</v>
       </c>
       <c r="O61" s="4" t="inlineStr">
@@ -4908,7 +4923,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G62" s="4" t="n">
+      <c r="G62" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H62" s="4" t="inlineStr">
@@ -4941,7 +4956,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N62" s="4" t="n">
+      <c r="N62" s="8" t="n">
         <v>0.977729976177216</v>
       </c>
       <c r="O62" s="4" t="inlineStr">
@@ -4987,7 +5002,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G63" s="4" t="n">
+      <c r="G63" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H63" s="4" t="inlineStr">
@@ -5020,7 +5035,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N63" s="4" t="n">
+      <c r="N63" s="8" t="n">
         <v>0.976989984512329</v>
       </c>
       <c r="O63" s="4" t="inlineStr">
@@ -5066,7 +5081,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G64" s="4" t="n">
+      <c r="G64" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H64" s="4" t="inlineStr">
@@ -5099,7 +5114,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N64" s="4" t="n">
+      <c r="N64" s="8" t="n">
         <v>0.9770799875259401</v>
       </c>
       <c r="O64" s="4" t="inlineStr">
@@ -5145,7 +5160,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G65" s="4" t="n">
+      <c r="G65" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H65" s="4" t="inlineStr">
@@ -5222,7 +5237,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G66" s="4" t="n">
+      <c r="G66" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H66" s="4" t="inlineStr">
@@ -5299,7 +5314,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G67" s="4" t="n">
+      <c r="G67" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H67" s="4" t="inlineStr">
@@ -5376,7 +5391,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G68" s="4" t="n">
+      <c r="G68" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H68" s="4" t="inlineStr">
@@ -5453,7 +5468,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G69" s="4" t="n">
+      <c r="G69" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H69" s="4" t="inlineStr">
@@ -5530,7 +5545,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G70" s="4" t="n">
+      <c r="G70" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H70" s="4" t="inlineStr">
@@ -5607,7 +5622,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G71" s="4" t="n">
+      <c r="G71" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H71" s="4" t="inlineStr">
@@ -5684,7 +5699,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G72" s="4" t="n">
+      <c r="G72" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H72" s="4" t="inlineStr">
@@ -5761,7 +5776,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G73" s="4" t="n">
+      <c r="G73" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H73" s="4" t="inlineStr">
@@ -5842,7 +5857,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G74" s="4" t="n">
+      <c r="G74" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H74" s="4" t="inlineStr">
@@ -5923,7 +5938,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G75" s="4" t="n">
+      <c r="G75" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H75" s="4" t="inlineStr">
@@ -6004,7 +6019,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G76" s="4" t="n">
+      <c r="G76" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H76" s="4" t="inlineStr">
@@ -6085,7 +6100,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G77" s="4" t="n">
+      <c r="G77" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H77" s="4" t="inlineStr">
@@ -6166,7 +6181,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G78" s="4" t="n">
+      <c r="G78" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H78" s="4" t="inlineStr">
@@ -6247,7 +6262,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G79" s="4" t="n">
+      <c r="G79" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H79" s="4" t="inlineStr">
@@ -6328,7 +6343,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G80" s="4" t="n">
+      <c r="G80" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H80" s="4" t="inlineStr">
@@ -6409,7 +6424,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G81" s="4" t="n">
+      <c r="G81" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H81" s="4" t="inlineStr">
@@ -6490,7 +6505,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G82" s="4" t="n">
+      <c r="G82" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H82" s="4" t="inlineStr">
@@ -6571,7 +6586,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G83" s="4" t="n">
+      <c r="G83" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H83" s="4" t="inlineStr">
@@ -6652,7 +6667,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G84" s="4" t="n">
+      <c r="G84" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H84" s="4" t="inlineStr">
@@ -6733,7 +6748,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G85" s="4" t="n">
+      <c r="G85" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H85" s="4" t="inlineStr">
@@ -6814,7 +6829,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G86" s="4" t="n">
+      <c r="G86" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H86" s="4" t="inlineStr">
@@ -6895,7 +6910,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G87" s="4" t="n">
+      <c r="G87" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H87" s="4" t="inlineStr">
@@ -6976,7 +6991,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G88" s="4" t="n">
+      <c r="G88" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H88" s="4" t="inlineStr">
@@ -7057,7 +7072,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G89" s="4" t="n">
+      <c r="G89" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H89" s="4" t="inlineStr">
@@ -7138,7 +7153,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G90" s="4" t="n">
+      <c r="G90" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H90" s="4" t="inlineStr">
@@ -7219,7 +7234,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G91" s="4" t="n">
+      <c r="G91" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H91" s="4" t="inlineStr">
@@ -7300,7 +7315,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G92" s="4" t="n">
+      <c r="G92" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H92" s="4" t="inlineStr">
@@ -7381,7 +7396,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G93" s="4" t="n">
+      <c r="G93" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H93" s="4" t="inlineStr">
@@ -7462,7 +7477,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G94" s="4" t="n">
+      <c r="G94" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H94" s="4" t="inlineStr">
@@ -7543,7 +7558,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G95" s="4" t="n">
+      <c r="G95" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H95" s="4" t="inlineStr">
@@ -7624,7 +7639,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G96" s="4" t="n">
+      <c r="G96" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H96" s="4" t="inlineStr">
@@ -7705,7 +7720,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G97" s="4" t="n">
+      <c r="G97" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H97" s="4" t="inlineStr">
@@ -7786,7 +7801,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G98" s="4" t="n">
+      <c r="G98" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H98" s="4" t="inlineStr">
@@ -7867,7 +7882,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G99" s="4" t="n">
+      <c r="G99" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H99" s="4" t="inlineStr">
@@ -7948,7 +7963,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G100" s="4" t="n">
+      <c r="G100" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H100" s="4" t="inlineStr">
@@ -8029,7 +8044,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G101" s="4" t="n">
+      <c r="G101" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H101" s="4" t="inlineStr">
@@ -8110,7 +8125,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G102" s="4" t="n">
+      <c r="G102" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H102" s="4" t="inlineStr">
@@ -8191,7 +8206,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G103" s="4" t="n">
+      <c r="G103" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H103" s="4" t="inlineStr">
@@ -8272,7 +8287,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G104" s="4" t="n">
+      <c r="G104" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H104" s="4" t="inlineStr">
@@ -8353,7 +8368,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G105" s="4" t="n">
+      <c r="G105" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H105" s="4" t="inlineStr">
@@ -8434,7 +8449,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G106" s="4" t="n">
+      <c r="G106" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H106" s="4" t="inlineStr">
@@ -8515,7 +8530,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G107" s="4" t="n">
+      <c r="G107" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H107" s="4" t="inlineStr">
@@ -8596,7 +8611,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G108" s="4" t="n">
+      <c r="G108" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H108" s="4" t="inlineStr">
@@ -8677,7 +8692,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G109" s="4" t="n">
+      <c r="G109" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H109" s="4" t="inlineStr">
@@ -8758,7 +8773,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G110" s="4" t="n">
+      <c r="G110" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H110" s="4" t="inlineStr">
@@ -8839,7 +8854,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G111" s="4" t="n">
+      <c r="G111" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H111" s="4" t="inlineStr">
@@ -8920,7 +8935,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G112" s="4" t="n">
+      <c r="G112" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H112" s="4" t="inlineStr">
@@ -9001,7 +9016,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G113" s="4" t="n">
+      <c r="G113" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H113" s="4" t="inlineStr">
@@ -9082,7 +9097,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G114" s="4" t="n">
+      <c r="G114" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H114" s="4" t="inlineStr">
@@ -9163,7 +9178,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G115" s="4" t="n">
+      <c r="G115" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H115" s="4" t="inlineStr">
@@ -9244,7 +9259,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G116" s="4" t="n">
+      <c r="G116" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H116" s="4" t="inlineStr">
@@ -9325,7 +9340,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G117" s="4" t="n">
+      <c r="G117" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H117" s="4" t="inlineStr">
@@ -9406,7 +9421,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G118" s="4" t="n">
+      <c r="G118" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H118" s="4" t="inlineStr">
@@ -9487,7 +9502,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G119" s="4" t="n">
+      <c r="G119" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H119" s="4" t="inlineStr">
@@ -9568,7 +9583,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G120" s="4" t="n">
+      <c r="G120" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H120" s="4" t="inlineStr">
@@ -9649,7 +9664,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G121" s="4" t="n">
+      <c r="G121" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H121" s="4" t="inlineStr">
@@ -9730,7 +9745,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G122" s="4" t="n">
+      <c r="G122" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H122" s="4" t="inlineStr">
@@ -9811,7 +9826,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G123" s="4" t="n">
+      <c r="G123" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H123" s="4" t="inlineStr">
@@ -9892,7 +9907,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G124" s="4" t="n">
+      <c r="G124" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H124" s="4" t="inlineStr">
@@ -9973,7 +9988,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G125" s="4" t="n">
+      <c r="G125" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H125" s="4" t="inlineStr">
@@ -10054,7 +10069,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G126" s="4" t="n">
+      <c r="G126" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H126" s="4" t="inlineStr">
@@ -10135,7 +10150,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G127" s="4" t="n">
+      <c r="G127" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H127" s="4" t="inlineStr">
@@ -10216,7 +10231,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G128" s="4" t="n">
+      <c r="G128" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H128" s="4" t="inlineStr">
@@ -10297,7 +10312,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G129" s="4" t="n">
+      <c r="G129" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H129" s="4" t="inlineStr">
@@ -10378,7 +10393,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G130" s="4" t="n">
+      <c r="G130" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H130" s="4" t="inlineStr">
@@ -10459,7 +10474,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G131" s="4" t="n">
+      <c r="G131" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H131" s="4" t="inlineStr">
@@ -10540,7 +10555,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G132" s="4" t="n">
+      <c r="G132" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H132" s="4" t="inlineStr">
@@ -10621,7 +10636,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G133" s="4" t="n">
+      <c r="G133" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H133" s="4" t="inlineStr">
@@ -10702,7 +10717,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G134" s="4" t="n">
+      <c r="G134" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H134" s="4" t="inlineStr">
@@ -10783,7 +10798,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G135" s="4" t="n">
+      <c r="G135" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H135" s="4" t="inlineStr">
@@ -10864,7 +10879,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G136" s="4" t="n">
+      <c r="G136" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H136" s="4" t="inlineStr">
@@ -10945,7 +10960,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G137" s="4" t="n">
+      <c r="G137" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H137" s="4" t="inlineStr">
@@ -11026,7 +11041,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G138" s="4" t="n">
+      <c r="G138" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H138" s="4" t="inlineStr">
@@ -11107,7 +11122,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G139" s="4" t="n">
+      <c r="G139" s="7" t="n">
         <v>2026</v>
       </c>
       <c r="H139" s="4" t="inlineStr">
@@ -11188,7 +11203,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G140" s="4" t="n">
+      <c r="G140" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H140" s="4" t="inlineStr">
@@ -11265,7 +11280,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G141" s="4" t="n">
+      <c r="G141" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H141" s="4" t="inlineStr">
@@ -11342,7 +11357,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G142" s="4" t="n">
+      <c r="G142" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H142" s="4" t="inlineStr">
@@ -11419,7 +11434,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G143" s="4" t="n">
+      <c r="G143" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H143" s="4" t="inlineStr">
@@ -11496,7 +11511,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G144" s="4" t="n">
+      <c r="G144" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H144" s="4" t="inlineStr">
@@ -11573,7 +11588,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G145" s="4" t="n">
+      <c r="G145" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H145" s="4" t="inlineStr">
@@ -11650,7 +11665,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G146" s="4" t="n">
+      <c r="G146" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H146" s="4" t="inlineStr">
@@ -11727,7 +11742,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G147" s="4" t="n">
+      <c r="G147" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H147" s="4" t="inlineStr">
@@ -11804,7 +11819,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G148" s="4" t="n">
+      <c r="G148" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H148" s="4" t="inlineStr">
@@ -11881,7 +11896,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G149" s="4" t="n">
+      <c r="G149" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H149" s="4" t="inlineStr">
@@ -11958,7 +11973,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G150" s="4" t="n">
+      <c r="G150" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H150" s="4" t="inlineStr">
@@ -12035,7 +12050,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G151" s="4" t="n">
+      <c r="G151" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H151" s="4" t="inlineStr">
@@ -12112,7 +12127,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G152" s="4" t="n">
+      <c r="G152" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H152" s="4" t="inlineStr">
@@ -12189,7 +12204,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G153" s="4" t="n">
+      <c r="G153" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H153" s="4" t="inlineStr">
@@ -12266,7 +12281,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G154" s="4" t="n">
+      <c r="G154" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H154" s="4" t="inlineStr">
@@ -12343,7 +12358,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G155" s="4" t="n">
+      <c r="G155" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H155" s="4" t="inlineStr">
@@ -12420,7 +12435,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G156" s="4" t="n">
+      <c r="G156" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H156" s="4" t="inlineStr">
@@ -12497,7 +12512,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G157" s="4" t="n">
+      <c r="G157" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H157" s="4" t="inlineStr">
@@ -12574,7 +12589,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G158" s="4" t="n">
+      <c r="G158" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H158" s="4" t="inlineStr">
@@ -12651,7 +12666,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G159" s="4" t="n">
+      <c r="G159" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H159" s="4" t="inlineStr">
@@ -12728,7 +12743,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G160" s="4" t="n">
+      <c r="G160" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H160" s="4" t="inlineStr">
@@ -12805,7 +12820,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G161" s="4" t="n">
+      <c r="G161" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H161" s="4" t="inlineStr">
@@ -12882,7 +12897,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G162" s="4" t="n">
+      <c r="G162" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H162" s="4" t="inlineStr">
@@ -12959,7 +12974,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G163" s="4" t="n">
+      <c r="G163" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H163" s="4" t="inlineStr">
@@ -13036,7 +13051,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G164" s="4" t="n">
+      <c r="G164" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H164" s="4" t="inlineStr">
@@ -13113,7 +13128,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G165" s="4" t="n">
+      <c r="G165" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H165" s="4" t="inlineStr">
@@ -13190,7 +13205,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G166" s="4" t="n">
+      <c r="G166" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H166" s="4" t="inlineStr">
@@ -13267,7 +13282,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G167" s="4" t="n">
+      <c r="G167" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H167" s="4" t="inlineStr">
@@ -13344,7 +13359,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G168" s="4" t="n">
+      <c r="G168" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H168" s="4" t="inlineStr">
@@ -13421,7 +13436,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G169" s="4" t="n">
+      <c r="G169" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H169" s="4" t="inlineStr">
@@ -13498,7 +13513,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G170" s="4" t="n">
+      <c r="G170" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H170" s="4" t="inlineStr">
@@ -13575,7 +13590,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G171" s="4" t="n">
+      <c r="G171" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H171" s="4" t="inlineStr">
@@ -13652,7 +13667,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G172" s="4" t="n">
+      <c r="G172" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H172" s="4" t="inlineStr">
@@ -13729,7 +13744,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G173" s="4" t="n">
+      <c r="G173" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H173" s="4" t="inlineStr">
@@ -13806,7 +13821,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G174" s="4" t="n">
+      <c r="G174" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H174" s="4" t="inlineStr">
@@ -13883,7 +13898,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G175" s="4" t="n">
+      <c r="G175" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H175" s="4" t="inlineStr">
@@ -13960,7 +13975,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G176" s="4" t="n">
+      <c r="G176" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H176" s="4" t="inlineStr">
@@ -14037,7 +14052,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G177" s="4" t="n">
+      <c r="G177" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H177" s="4" t="inlineStr">
@@ -14070,7 +14085,7 @@
           <t>Mujeres en parlamentos nacionales</t>
         </is>
       </c>
-      <c r="N177" s="4" t="n">
+      <c r="N177" s="8" t="n">
         <v>5.91133004926108</v>
       </c>
       <c r="O177" s="4" t="inlineStr">
@@ -14116,7 +14131,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G178" s="4" t="n">
+      <c r="G178" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H178" s="4" t="inlineStr">
@@ -14149,7 +14164,7 @@
           <t>Mujeres en parlamentos nacionales</t>
         </is>
       </c>
-      <c r="N178" s="4" t="n">
+      <c r="N178" s="8" t="n">
         <v>5.91133004926108</v>
       </c>
       <c r="O178" s="4" t="inlineStr">
@@ -14195,7 +14210,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G179" s="4" t="n">
+      <c r="G179" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H179" s="4" t="inlineStr">
@@ -14228,7 +14243,7 @@
           <t>Mujeres en parlamentos nacionales</t>
         </is>
       </c>
-      <c r="N179" s="4" t="n">
+      <c r="N179" s="8" t="n">
         <v>12.1359223300971</v>
       </c>
       <c r="O179" s="4" t="inlineStr">
@@ -14274,7 +14289,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G180" s="4" t="n">
+      <c r="G180" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H180" s="4" t="inlineStr">
@@ -14351,7 +14366,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G181" s="4" t="n">
+      <c r="G181" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H181" s="4" t="inlineStr">
@@ -14384,7 +14399,7 @@
           <t>Mujeres en parlamentos nacionales</t>
         </is>
       </c>
-      <c r="N181" s="4" t="n">
+      <c r="N181" s="8" t="n">
         <v>9.696969696969701</v>
       </c>
       <c r="O181" s="4" t="inlineStr">
@@ -14430,7 +14445,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G182" s="4" t="n">
+      <c r="G182" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H182" s="4" t="inlineStr">
@@ -14463,7 +14478,7 @@
           <t>Mujeres en parlamentos nacionales</t>
         </is>
       </c>
-      <c r="N182" s="4" t="n">
+      <c r="N182" s="8" t="n">
         <v>9.696969696969701</v>
       </c>
       <c r="O182" s="4" t="inlineStr">
@@ -14509,7 +14524,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G183" s="4" t="n">
+      <c r="G183" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H183" s="4" t="inlineStr">
@@ -14542,7 +14557,7 @@
           <t>Mujeres en parlamentos nacionales</t>
         </is>
       </c>
-      <c r="N183" s="4" t="n">
+      <c r="N183" s="8" t="n">
         <v>9.696969696969701</v>
       </c>
       <c r="O183" s="4" t="inlineStr">
@@ -14588,7 +14603,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G184" s="4" t="n">
+      <c r="G184" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H184" s="4" t="inlineStr">
@@ -14621,7 +14636,7 @@
           <t>Mujeres en parlamentos nacionales</t>
         </is>
       </c>
-      <c r="N184" s="4" t="n">
+      <c r="N184" s="8" t="n">
         <v>9.696969696969701</v>
       </c>
       <c r="O184" s="4" t="inlineStr">
@@ -14667,7 +14682,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G185" s="4" t="n">
+      <c r="G185" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H185" s="4" t="inlineStr">
@@ -14700,7 +14715,7 @@
           <t>Mujeres en parlamentos nacionales</t>
         </is>
       </c>
-      <c r="N185" s="4" t="n">
+      <c r="N185" s="8" t="n">
         <v>17.3652694610778</v>
       </c>
       <c r="O185" s="4" t="inlineStr">
@@ -14746,7 +14761,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G186" s="4" t="n">
+      <c r="G186" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H186" s="4" t="inlineStr">
@@ -14779,7 +14794,7 @@
           <t>Mujeres en parlamentos nacionales</t>
         </is>
       </c>
-      <c r="N186" s="4" t="n">
+      <c r="N186" s="8" t="n">
         <v>17.9640718562874</v>
       </c>
       <c r="O186" s="4" t="inlineStr">
@@ -14825,7 +14840,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G187" s="4" t="n">
+      <c r="G187" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H187" s="4" t="inlineStr">
@@ -14858,7 +14873,7 @@
           <t>Mujeres en parlamentos nacionales</t>
         </is>
       </c>
-      <c r="N187" s="4" t="n">
+      <c r="N187" s="8" t="n">
         <v>18.562874251497</v>
       </c>
       <c r="O187" s="4" t="inlineStr">
@@ -14904,7 +14919,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G188" s="4" t="n">
+      <c r="G188" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H188" s="4" t="inlineStr">
@@ -14937,7 +14952,7 @@
           <t>Mujeres en parlamentos nacionales</t>
         </is>
       </c>
-      <c r="N188" s="4" t="n">
+      <c r="N188" s="8" t="n">
         <v>18.562874251497</v>
       </c>
       <c r="O188" s="4" t="inlineStr">
@@ -14983,7 +14998,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G189" s="4" t="n">
+      <c r="G189" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H189" s="4" t="inlineStr">
@@ -15016,7 +15031,7 @@
           <t>Mujeres en parlamentos nacionales</t>
         </is>
       </c>
-      <c r="N189" s="4" t="n">
+      <c r="N189" s="8" t="n">
         <v>17.4698795180723</v>
       </c>
       <c r="O189" s="4" t="inlineStr">
@@ -15062,7 +15077,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G190" s="4" t="n">
+      <c r="G190" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H190" s="4" t="inlineStr">
@@ -15095,7 +15110,7 @@
           <t>Mujeres en parlamentos nacionales</t>
         </is>
       </c>
-      <c r="N190" s="4" t="n">
+      <c r="N190" s="8" t="n">
         <v>16.969696969697</v>
       </c>
       <c r="O190" s="4" t="inlineStr">
@@ -15141,7 +15156,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G191" s="4" t="n">
+      <c r="G191" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H191" s="4" t="inlineStr">
@@ -15174,7 +15189,7 @@
           <t>Mujeres en parlamentos nacionales</t>
         </is>
       </c>
-      <c r="N191" s="4" t="n">
+      <c r="N191" s="8" t="n">
         <v>16.969696969697</v>
       </c>
       <c r="O191" s="4" t="inlineStr">
@@ -15220,7 +15235,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G192" s="4" t="n">
+      <c r="G192" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H192" s="4" t="inlineStr">
@@ -15253,7 +15268,7 @@
           <t>Mujeres en parlamentos nacionales</t>
         </is>
       </c>
-      <c r="N192" s="4" t="n">
+      <c r="N192" s="8" t="n">
         <v>16.969696969697</v>
       </c>
       <c r="O192" s="4" t="inlineStr">
@@ -15299,7 +15314,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G193" s="4" t="n">
+      <c r="G193" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H193" s="4" t="inlineStr">
@@ -15332,7 +15347,7 @@
           <t>Mujeres en parlamentos nacionales</t>
         </is>
       </c>
-      <c r="N193" s="4" t="n">
+      <c r="N193" s="8" t="n">
         <v>16.969696969697</v>
       </c>
       <c r="O193" s="4" t="inlineStr">
@@ -15378,7 +15393,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G194" s="4" t="n">
+      <c r="G194" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H194" s="4" t="inlineStr">
@@ -15411,7 +15426,7 @@
           <t>Mujeres en parlamentos nacionales</t>
         </is>
       </c>
-      <c r="N194" s="4" t="n">
+      <c r="N194" s="8" t="n">
         <v>16.969696969697</v>
       </c>
       <c r="O194" s="4" t="inlineStr">
@@ -15457,7 +15472,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G195" s="4" t="n">
+      <c r="G195" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H195" s="4" t="inlineStr">
@@ -15490,7 +15505,7 @@
           <t>Mujeres en parlamentos nacionales</t>
         </is>
       </c>
-      <c r="N195" s="4" t="n">
+      <c r="N195" s="8" t="n">
         <v>16.969696969697</v>
       </c>
       <c r="O195" s="4" t="inlineStr">
@@ -15536,7 +15551,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G196" s="4" t="n">
+      <c r="G196" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H196" s="4" t="inlineStr">
@@ -15569,7 +15584,7 @@
           <t>Mujeres en parlamentos nacionales</t>
         </is>
       </c>
-      <c r="N196" s="4" t="n">
+      <c r="N196" s="8" t="n">
         <v>14.3712574850299</v>
       </c>
       <c r="O196" s="4" t="inlineStr">
@@ -15615,7 +15630,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G197" s="4" t="n">
+      <c r="G197" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H197" s="4" t="inlineStr">
@@ -15648,7 +15663,7 @@
           <t>Mujeres en parlamentos nacionales</t>
         </is>
       </c>
-      <c r="N197" s="4" t="n">
+      <c r="N197" s="8" t="n">
         <v>22.1556886227545</v>
       </c>
       <c r="O197" s="4" t="inlineStr">
@@ -15694,7 +15709,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G198" s="4" t="n">
+      <c r="G198" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H198" s="4" t="inlineStr">
@@ -15727,7 +15742,7 @@
           <t>Mujeres en parlamentos nacionales</t>
         </is>
       </c>
-      <c r="N198" s="4" t="n">
+      <c r="N198" s="8" t="n">
         <v>22.1556886227545</v>
       </c>
       <c r="O198" s="4" t="inlineStr">
@@ -15773,7 +15788,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G199" s="4" t="n">
+      <c r="G199" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H199" s="4" t="inlineStr">
@@ -15806,7 +15821,7 @@
           <t>Mujeres en parlamentos nacionales</t>
         </is>
       </c>
-      <c r="N199" s="4" t="n">
+      <c r="N199" s="8" t="n">
         <v>22.1556886227545</v>
       </c>
       <c r="O199" s="4" t="inlineStr">
@@ -15852,7 +15867,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G200" s="4" t="n">
+      <c r="G200" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H200" s="4" t="inlineStr">
@@ -15885,7 +15900,7 @@
           <t>Mujeres en parlamentos nacionales</t>
         </is>
       </c>
-      <c r="N200" s="4" t="n">
+      <c r="N200" s="8" t="n">
         <v>22.1556886227545</v>
       </c>
       <c r="O200" s="4" t="inlineStr">
@@ -15931,7 +15946,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G201" s="4" t="n">
+      <c r="G201" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H201" s="4" t="inlineStr">
@@ -15964,7 +15979,7 @@
           <t>Mujeres en parlamentos nacionales</t>
         </is>
       </c>
-      <c r="N201" s="4" t="n">
+      <c r="N201" s="8" t="n">
         <v>22.1556886227545</v>
       </c>
       <c r="O201" s="4" t="inlineStr">
@@ -16010,7 +16025,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G202" s="4" t="n">
+      <c r="G202" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H202" s="4" t="inlineStr">
@@ -16087,7 +16102,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G203" s="4" t="n">
+      <c r="G203" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H203" s="4" t="inlineStr">
@@ -16164,7 +16179,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G204" s="4" t="n">
+      <c r="G204" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H204" s="4" t="inlineStr">
@@ -16241,7 +16256,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G205" s="4" t="n">
+      <c r="G205" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H205" s="4" t="inlineStr">
@@ -16274,7 +16289,7 @@
           <t>Mujeres en parlamentos nacionales</t>
         </is>
       </c>
-      <c r="N205" s="4" t="n">
+      <c r="N205" s="8" t="n">
         <v>32.129963898917</v>
       </c>
       <c r="O205" s="4" t="inlineStr">
@@ -16320,7 +16335,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G206" s="4" t="n">
+      <c r="G206" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H206" s="4" t="inlineStr">
@@ -16397,7 +16412,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G207" s="4" t="n">
+      <c r="G207" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H207" s="4" t="inlineStr">
@@ -16474,7 +16489,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G208" s="4" t="n">
+      <c r="G208" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H208" s="4" t="inlineStr">
@@ -16551,7 +16566,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G209" s="4" t="n">
+      <c r="G209" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H209" s="4" t="inlineStr">
@@ -16628,7 +16643,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G210" s="4" t="n">
+      <c r="G210" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H210" s="4" t="inlineStr">
@@ -16705,7 +16720,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G211" s="4" t="n">
+      <c r="G211" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H211" s="4" t="inlineStr">
@@ -16782,7 +16797,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G212" s="4" t="n">
+      <c r="G212" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H212" s="4" t="inlineStr">
@@ -16859,7 +16874,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G213" s="4" t="n">
+      <c r="G213" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H213" s="4" t="inlineStr">
@@ -16936,7 +16951,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G214" s="4" t="n">
+      <c r="G214" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H214" s="4" t="inlineStr">
@@ -17013,7 +17028,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G215" s="4" t="n">
+      <c r="G215" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H215" s="4" t="inlineStr">
@@ -17090,7 +17105,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G216" s="4" t="n">
+      <c r="G216" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H216" s="4" t="inlineStr">
@@ -17167,7 +17182,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G217" s="4" t="n">
+      <c r="G217" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H217" s="4" t="inlineStr">
@@ -17244,7 +17259,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G218" s="4" t="n">
+      <c r="G218" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H218" s="4" t="inlineStr">
@@ -17321,7 +17336,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G219" s="4" t="n">
+      <c r="G219" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H219" s="4" t="inlineStr">
@@ -17398,7 +17413,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G220" s="4" t="n">
+      <c r="G220" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H220" s="4" t="inlineStr">
@@ -17475,7 +17490,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G221" s="4" t="n">
+      <c r="G221" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H221" s="4" t="inlineStr">
@@ -17552,7 +17567,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G222" s="4" t="n">
+      <c r="G222" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H222" s="4" t="inlineStr">
@@ -17629,7 +17644,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G223" s="4" t="n">
+      <c r="G223" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H223" s="4" t="inlineStr">
@@ -17706,7 +17721,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G224" s="4" t="n">
+      <c r="G224" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H224" s="4" t="inlineStr">
@@ -17783,7 +17798,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G225" s="4" t="n">
+      <c r="G225" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H225" s="4" t="inlineStr">
@@ -17860,7 +17875,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G226" s="4" t="n">
+      <c r="G226" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H226" s="4" t="inlineStr">
@@ -17937,7 +17952,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G227" s="4" t="n">
+      <c r="G227" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H227" s="4" t="inlineStr">
@@ -18014,7 +18029,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G228" s="4" t="n">
+      <c r="G228" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H228" s="4" t="inlineStr">
@@ -18091,7 +18106,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G229" s="4" t="n">
+      <c r="G229" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H229" s="4" t="inlineStr">
@@ -18168,7 +18183,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G230" s="4" t="n">
+      <c r="G230" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H230" s="4" t="inlineStr">
@@ -18245,7 +18260,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G231" s="4" t="n">
+      <c r="G231" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H231" s="4" t="inlineStr">
@@ -18322,7 +18337,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G232" s="4" t="n">
+      <c r="G232" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H232" s="4" t="inlineStr">
@@ -18399,7 +18414,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G233" s="4" t="n">
+      <c r="G233" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H233" s="4" t="inlineStr">
@@ -18476,7 +18491,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G234" s="4" t="n">
+      <c r="G234" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H234" s="4" t="inlineStr">
@@ -18553,7 +18568,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G235" s="4" t="n">
+      <c r="G235" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H235" s="4" t="inlineStr">
@@ -18630,7 +18645,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G236" s="4" t="n">
+      <c r="G236" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H236" s="4" t="inlineStr">
@@ -18663,7 +18678,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N236" s="4" t="n">
+      <c r="N236" s="8" t="n">
         <v>48.56</v>
       </c>
       <c r="O236" s="4" t="inlineStr">
@@ -18709,7 +18724,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G237" s="4" t="n">
+      <c r="G237" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H237" s="4" t="inlineStr">
@@ -18742,7 +18757,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N237" s="4" t="n">
+      <c r="N237" s="8" t="n">
         <v>49.027</v>
       </c>
       <c r="O237" s="4" t="inlineStr">
@@ -18788,7 +18803,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G238" s="4" t="n">
+      <c r="G238" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H238" s="4" t="inlineStr">
@@ -18821,7 +18836,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N238" s="4" t="n">
+      <c r="N238" s="8" t="n">
         <v>49.439</v>
       </c>
       <c r="O238" s="4" t="inlineStr">
@@ -18867,7 +18882,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G239" s="4" t="n">
+      <c r="G239" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H239" s="4" t="inlineStr">
@@ -18900,7 +18915,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N239" s="4" t="n">
+      <c r="N239" s="8" t="n">
         <v>49.121</v>
       </c>
       <c r="O239" s="4" t="inlineStr">
@@ -18946,7 +18961,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G240" s="4" t="n">
+      <c r="G240" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H240" s="4" t="inlineStr">
@@ -18979,7 +18994,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N240" s="4" t="n">
+      <c r="N240" s="8" t="n">
         <v>48.519</v>
       </c>
       <c r="O240" s="4" t="inlineStr">
@@ -19025,7 +19040,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G241" s="4" t="n">
+      <c r="G241" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H241" s="4" t="inlineStr">
@@ -19058,7 +19073,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N241" s="4" t="n">
+      <c r="N241" s="8" t="n">
         <v>48.502</v>
       </c>
       <c r="O241" s="4" t="inlineStr">
@@ -19104,7 +19119,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G242" s="4" t="n">
+      <c r="G242" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H242" s="4" t="inlineStr">
@@ -19137,7 +19152,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N242" s="4" t="n">
+      <c r="N242" s="8" t="n">
         <v>48.683</v>
       </c>
       <c r="O242" s="4" t="inlineStr">
@@ -19183,7 +19198,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G243" s="4" t="n">
+      <c r="G243" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H243" s="4" t="inlineStr">
@@ -19216,7 +19231,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N243" s="4" t="n">
+      <c r="N243" s="8" t="n">
         <v>48.743</v>
       </c>
       <c r="O243" s="4" t="inlineStr">
@@ -19262,7 +19277,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G244" s="4" t="n">
+      <c r="G244" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H244" s="4" t="inlineStr">
@@ -19295,7 +19310,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N244" s="4" t="n">
+      <c r="N244" s="8" t="n">
         <v>48.976</v>
       </c>
       <c r="O244" s="4" t="inlineStr">
@@ -19341,7 +19356,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G245" s="4" t="n">
+      <c r="G245" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H245" s="4" t="inlineStr">
@@ -19374,7 +19389,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N245" s="4" t="n">
+      <c r="N245" s="8" t="n">
         <v>48.119</v>
       </c>
       <c r="O245" s="4" t="inlineStr">
@@ -19420,7 +19435,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G246" s="4" t="n">
+      <c r="G246" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H246" s="4" t="inlineStr">
@@ -19453,7 +19468,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N246" s="4" t="n">
+      <c r="N246" s="8" t="n">
         <v>47.914</v>
       </c>
       <c r="O246" s="4" t="inlineStr">
@@ -19499,7 +19514,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G247" s="4" t="n">
+      <c r="G247" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H247" s="4" t="inlineStr">
@@ -19532,7 +19547,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N247" s="4" t="n">
+      <c r="N247" s="8" t="n">
         <v>48.527</v>
       </c>
       <c r="O247" s="4" t="inlineStr">
@@ -19578,7 +19593,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G248" s="4" t="n">
+      <c r="G248" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H248" s="4" t="inlineStr">
@@ -19611,7 +19626,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N248" s="4" t="n">
+      <c r="N248" s="8" t="n">
         <v>47.765</v>
       </c>
       <c r="O248" s="4" t="inlineStr">
@@ -19657,7 +19672,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G249" s="4" t="n">
+      <c r="G249" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H249" s="4" t="inlineStr">
@@ -19690,7 +19705,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N249" s="4" t="n">
+      <c r="N249" s="8" t="n">
         <v>46.462</v>
       </c>
       <c r="O249" s="4" t="inlineStr">
@@ -19736,7 +19751,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G250" s="4" t="n">
+      <c r="G250" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H250" s="4" t="inlineStr">
@@ -19769,7 +19784,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N250" s="4" t="n">
+      <c r="N250" s="8" t="n">
         <v>47.558</v>
       </c>
       <c r="O250" s="4" t="inlineStr">
@@ -19815,7 +19830,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G251" s="4" t="n">
+      <c r="G251" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H251" s="4" t="inlineStr">
@@ -19848,7 +19863,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N251" s="4" t="n">
+      <c r="N251" s="8" t="n">
         <v>49.457</v>
       </c>
       <c r="O251" s="4" t="inlineStr">
@@ -19894,7 +19909,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G252" s="4" t="n">
+      <c r="G252" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H252" s="4" t="inlineStr">
@@ -19927,7 +19942,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N252" s="4" t="n">
+      <c r="N252" s="8" t="n">
         <v>50.019</v>
       </c>
       <c r="O252" s="4" t="inlineStr">
@@ -19973,7 +19988,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G253" s="4" t="n">
+      <c r="G253" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H253" s="4" t="inlineStr">
@@ -20006,7 +20021,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N253" s="4" t="n">
+      <c r="N253" s="8" t="n">
         <v>49.726</v>
       </c>
       <c r="O253" s="4" t="inlineStr">
@@ -20052,7 +20067,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G254" s="4" t="n">
+      <c r="G254" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H254" s="4" t="inlineStr">
@@ -20085,7 +20100,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N254" s="4" t="n">
+      <c r="N254" s="8" t="n">
         <v>49.734</v>
       </c>
       <c r="O254" s="4" t="inlineStr">
@@ -20131,7 +20146,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G255" s="4" t="n">
+      <c r="G255" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H255" s="4" t="inlineStr">
@@ -20164,7 +20179,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N255" s="4" t="n">
+      <c r="N255" s="8" t="n">
         <v>50.004</v>
       </c>
       <c r="O255" s="4" t="inlineStr">
@@ -20210,7 +20225,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G256" s="4" t="n">
+      <c r="G256" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H256" s="4" t="inlineStr">
@@ -20243,7 +20258,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N256" s="4" t="n">
+      <c r="N256" s="8" t="n">
         <v>49.601</v>
       </c>
       <c r="O256" s="4" t="inlineStr">
@@ -20289,7 +20304,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G257" s="4" t="n">
+      <c r="G257" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H257" s="4" t="inlineStr">
@@ -20322,7 +20337,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N257" s="4" t="n">
+      <c r="N257" s="8" t="n">
         <v>49.643</v>
       </c>
       <c r="O257" s="4" t="inlineStr">
@@ -20368,7 +20383,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G258" s="4" t="n">
+      <c r="G258" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H258" s="4" t="inlineStr">
@@ -20401,7 +20416,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N258" s="4" t="n">
+      <c r="N258" s="8" t="n">
         <v>49.493</v>
       </c>
       <c r="O258" s="4" t="inlineStr">
@@ -20447,7 +20462,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G259" s="4" t="n">
+      <c r="G259" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H259" s="4" t="inlineStr">
@@ -20480,7 +20495,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N259" s="4" t="n">
+      <c r="N259" s="8" t="n">
         <v>49.084</v>
       </c>
       <c r="O259" s="4" t="inlineStr">
@@ -20526,7 +20541,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G260" s="4" t="n">
+      <c r="G260" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H260" s="4" t="inlineStr">
@@ -20559,7 +20574,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N260" s="4" t="n">
+      <c r="N260" s="8" t="n">
         <v>48.676</v>
       </c>
       <c r="O260" s="4" t="inlineStr">
@@ -20605,7 +20620,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G261" s="4" t="n">
+      <c r="G261" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H261" s="4" t="inlineStr">
@@ -20638,7 +20653,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N261" s="4" t="n">
+      <c r="N261" s="8" t="n">
         <v>48.27</v>
       </c>
       <c r="O261" s="4" t="inlineStr">
@@ -20684,7 +20699,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G262" s="4" t="n">
+      <c r="G262" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H262" s="4" t="inlineStr">
@@ -20717,7 +20732,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N262" s="4" t="n">
+      <c r="N262" s="8" t="n">
         <v>47.867</v>
       </c>
       <c r="O262" s="4" t="inlineStr">
@@ -20763,7 +20778,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G263" s="4" t="n">
+      <c r="G263" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H263" s="4" t="inlineStr">
@@ -20796,7 +20811,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N263" s="4" t="n">
+      <c r="N263" s="8" t="n">
         <v>46.185</v>
       </c>
       <c r="O263" s="4" t="inlineStr">
@@ -20842,7 +20857,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G264" s="4" t="n">
+      <c r="G264" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H264" s="4" t="inlineStr">
@@ -20875,7 +20890,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N264" s="4" t="n">
+      <c r="N264" s="8" t="n">
         <v>44.85</v>
       </c>
       <c r="O264" s="4" t="inlineStr">
@@ -20921,7 +20936,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G265" s="4" t="n">
+      <c r="G265" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H265" s="4" t="inlineStr">
@@ -20954,7 +20969,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N265" s="4" t="n">
+      <c r="N265" s="8" t="n">
         <v>42.344</v>
       </c>
       <c r="O265" s="4" t="inlineStr">
@@ -21000,7 +21015,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G266" s="4" t="n">
+      <c r="G266" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H266" s="4" t="inlineStr">
@@ -21033,7 +21048,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N266" s="4" t="n">
+      <c r="N266" s="8" t="n">
         <v>36.887</v>
       </c>
       <c r="O266" s="4" t="inlineStr">
@@ -21079,7 +21094,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G267" s="4" t="n">
+      <c r="G267" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H267" s="4" t="inlineStr">
@@ -21112,7 +21127,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N267" s="4" t="n">
+      <c r="N267" s="8" t="n">
         <v>37.368</v>
       </c>
       <c r="O267" s="4" t="inlineStr">
@@ -21158,7 +21173,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G268" s="4" t="n">
+      <c r="G268" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H268" s="4" t="inlineStr">
@@ -21191,7 +21206,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N268" s="4" t="n">
+      <c r="N268" s="8" t="n">
         <v>35.32</v>
       </c>
       <c r="O268" s="4" t="inlineStr">
@@ -21237,7 +21252,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G269" s="4" t="n">
+      <c r="G269" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H269" s="4" t="inlineStr">
@@ -21270,7 +21285,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N269" s="4" t="n">
+      <c r="N269" s="8" t="n">
         <v>36.158</v>
       </c>
       <c r="O269" s="4" t="inlineStr">
@@ -21316,7 +21331,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G270" s="4" t="n">
+      <c r="G270" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H270" s="4" t="inlineStr">
@@ -21349,7 +21364,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N270" s="4" t="n">
+      <c r="N270" s="8" t="n">
         <v>37.332</v>
       </c>
       <c r="O270" s="4" t="inlineStr">
@@ -21395,7 +21410,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G271" s="4" t="n">
+      <c r="G271" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H271" s="4" t="inlineStr">
@@ -21428,7 +21443,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N271" s="4" t="n">
+      <c r="N271" s="8" t="n">
         <v>37.098</v>
       </c>
       <c r="O271" s="4" t="inlineStr">
@@ -21474,7 +21489,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G272" s="4" t="n">
+      <c r="G272" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H272" s="4" t="inlineStr">
@@ -21551,7 +21566,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G273" s="4" t="n">
+      <c r="G273" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H273" s="4" t="inlineStr">
@@ -21628,7 +21643,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G274" s="4" t="n">
+      <c r="G274" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H274" s="4" t="inlineStr">
@@ -21705,7 +21720,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G275" s="4" t="n">
+      <c r="G275" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H275" s="4" t="inlineStr">
@@ -21782,7 +21797,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G276" s="4" t="n">
+      <c r="G276" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H276" s="4" t="inlineStr">
@@ -21859,7 +21874,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G277" s="4" t="n">
+      <c r="G277" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H277" s="4" t="inlineStr">
@@ -21936,7 +21951,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G278" s="4" t="n">
+      <c r="G278" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H278" s="4" t="inlineStr">
@@ -22013,7 +22028,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G279" s="4" t="n">
+      <c r="G279" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H279" s="4" t="inlineStr">
@@ -22090,7 +22105,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G280" s="4" t="n">
+      <c r="G280" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H280" s="4" t="inlineStr">
@@ -22167,7 +22182,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G281" s="4" t="n">
+      <c r="G281" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H281" s="4" t="inlineStr">
@@ -22244,7 +22259,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G282" s="4" t="n">
+      <c r="G282" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H282" s="4" t="inlineStr">
@@ -22321,7 +22336,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G283" s="4" t="n">
+      <c r="G283" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H283" s="4" t="inlineStr">
@@ -22398,7 +22413,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G284" s="4" t="n">
+      <c r="G284" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H284" s="4" t="inlineStr">
@@ -22475,7 +22490,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G285" s="4" t="n">
+      <c r="G285" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H285" s="4" t="inlineStr">
@@ -22552,7 +22567,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G286" s="4" t="n">
+      <c r="G286" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H286" s="4" t="inlineStr">
@@ -22629,7 +22644,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G287" s="4" t="n">
+      <c r="G287" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H287" s="4" t="inlineStr">
@@ -22706,7 +22721,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G288" s="4" t="n">
+      <c r="G288" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H288" s="4" t="inlineStr">
@@ -22783,7 +22798,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G289" s="4" t="n">
+      <c r="G289" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H289" s="4" t="inlineStr">
@@ -22860,7 +22875,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G290" s="4" t="n">
+      <c r="G290" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H290" s="4" t="inlineStr">
@@ -22937,7 +22952,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G291" s="4" t="n">
+      <c r="G291" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H291" s="4" t="inlineStr">
@@ -23014,7 +23029,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G292" s="4" t="n">
+      <c r="G292" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H292" s="4" t="inlineStr">
@@ -23091,7 +23106,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G293" s="4" t="n">
+      <c r="G293" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H293" s="4" t="inlineStr">
@@ -23168,7 +23183,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G294" s="4" t="n">
+      <c r="G294" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H294" s="4" t="inlineStr">
@@ -23245,7 +23260,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G295" s="4" t="n">
+      <c r="G295" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H295" s="4" t="inlineStr">
@@ -23322,7 +23337,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G296" s="4" t="n">
+      <c r="G296" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H296" s="4" t="inlineStr">
@@ -23399,7 +23414,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G297" s="4" t="n">
+      <c r="G297" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H297" s="4" t="inlineStr">
@@ -23476,7 +23491,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G298" s="4" t="n">
+      <c r="G298" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H298" s="4" t="inlineStr">
@@ -23553,7 +23568,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G299" s="4" t="n">
+      <c r="G299" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H299" s="4" t="inlineStr">
@@ -23630,7 +23645,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G300" s="4" t="n">
+      <c r="G300" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H300" s="4" t="inlineStr">
@@ -23707,7 +23722,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G301" s="4" t="n">
+      <c r="G301" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H301" s="4" t="inlineStr">
@@ -23784,7 +23799,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G302" s="4" t="n">
+      <c r="G302" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H302" s="4" t="inlineStr">
@@ -23861,7 +23876,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G303" s="4" t="n">
+      <c r="G303" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H303" s="4" t="inlineStr">
@@ -23894,7 +23909,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N303" s="4" t="n">
+      <c r="N303" s="8" t="n">
         <v>9.32</v>
       </c>
       <c r="O303" s="4" t="inlineStr">
@@ -23940,7 +23955,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G304" s="4" t="n">
+      <c r="G304" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H304" s="4" t="inlineStr">
@@ -23973,7 +23988,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N304" s="4" t="n">
+      <c r="N304" s="8" t="n">
         <v>6.925</v>
       </c>
       <c r="O304" s="4" t="inlineStr">
@@ -24019,7 +24034,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G305" s="4" t="n">
+      <c r="G305" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H305" s="4" t="inlineStr">
@@ -24052,7 +24067,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N305" s="4" t="n">
+      <c r="N305" s="8" t="n">
         <v>5.679</v>
       </c>
       <c r="O305" s="4" t="inlineStr">
@@ -24098,7 +24113,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G306" s="4" t="n">
+      <c r="G306" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H306" s="4" t="inlineStr">
@@ -24131,7 +24146,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N306" s="4" t="n">
+      <c r="N306" s="8" t="n">
         <v>9.557</v>
       </c>
       <c r="O306" s="4" t="inlineStr">
@@ -24177,7 +24192,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G307" s="4" t="n">
+      <c r="G307" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H307" s="4" t="inlineStr">
@@ -24210,7 +24225,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N307" s="4" t="n">
+      <c r="N307" s="8" t="n">
         <v>12.604</v>
       </c>
       <c r="O307" s="4" t="inlineStr">
@@ -24256,7 +24271,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G308" s="4" t="n">
+      <c r="G308" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H308" s="4" t="inlineStr">
@@ -24289,7 +24304,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N308" s="4" t="n">
+      <c r="N308" s="8" t="n">
         <v>14.345</v>
       </c>
       <c r="O308" s="4" t="inlineStr">
@@ -24335,7 +24350,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G309" s="4" t="n">
+      <c r="G309" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H309" s="4" t="inlineStr">
@@ -24368,7 +24383,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N309" s="4" t="n">
+      <c r="N309" s="8" t="n">
         <v>13.627</v>
       </c>
       <c r="O309" s="4" t="inlineStr">
@@ -24414,7 +24429,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G310" s="4" t="n">
+      <c r="G310" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H310" s="4" t="inlineStr">
@@ -24447,7 +24462,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N310" s="4" t="n">
+      <c r="N310" s="8" t="n">
         <v>13.306</v>
       </c>
       <c r="O310" s="4" t="inlineStr">
@@ -24493,7 +24508,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G311" s="4" t="n">
+      <c r="G311" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H311" s="4" t="inlineStr">
@@ -24526,7 +24541,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N311" s="4" t="n">
+      <c r="N311" s="8" t="n">
         <v>16.482</v>
       </c>
       <c r="O311" s="4" t="inlineStr">
@@ -24572,7 +24587,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G312" s="4" t="n">
+      <c r="G312" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H312" s="4" t="inlineStr">
@@ -24605,7 +24620,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N312" s="4" t="n">
+      <c r="N312" s="8" t="n">
         <v>14.605</v>
       </c>
       <c r="O312" s="4" t="inlineStr">
@@ -24651,7 +24666,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G313" s="4" t="n">
+      <c r="G313" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H313" s="4" t="inlineStr">
@@ -24684,7 +24699,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N313" s="4" t="n">
+      <c r="N313" s="8" t="n">
         <v>14.109</v>
       </c>
       <c r="O313" s="4" t="inlineStr">
@@ -24730,7 +24745,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G314" s="4" t="n">
+      <c r="G314" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H314" s="4" t="inlineStr">
@@ -24763,7 +24778,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N314" s="4" t="n">
+      <c r="N314" s="8" t="n">
         <v>18.895</v>
       </c>
       <c r="O314" s="4" t="inlineStr">
@@ -24809,7 +24824,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G315" s="4" t="n">
+      <c r="G315" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H315" s="4" t="inlineStr">
@@ -24842,7 +24857,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N315" s="4" t="n">
+      <c r="N315" s="8" t="n">
         <v>20.483</v>
       </c>
       <c r="O315" s="4" t="inlineStr">
@@ -24888,7 +24903,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G316" s="4" t="n">
+      <c r="G316" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H316" s="4" t="inlineStr">
@@ -24921,7 +24936,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N316" s="4" t="n">
+      <c r="N316" s="8" t="n">
         <v>17.974</v>
       </c>
       <c r="O316" s="4" t="inlineStr">
@@ -24967,7 +24982,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G317" s="4" t="n">
+      <c r="G317" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H317" s="4" t="inlineStr">
@@ -25000,7 +25015,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N317" s="4" t="n">
+      <c r="N317" s="8" t="n">
         <v>11.64</v>
       </c>
       <c r="O317" s="4" t="inlineStr">
@@ -25046,7 +25061,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G318" s="4" t="n">
+      <c r="G318" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H318" s="4" t="inlineStr">
@@ -25079,7 +25094,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N318" s="4" t="n">
+      <c r="N318" s="8" t="n">
         <v>9.380000000000001</v>
       </c>
       <c r="O318" s="4" t="inlineStr">
@@ -25125,7 +25140,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G319" s="4" t="n">
+      <c r="G319" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H319" s="4" t="inlineStr">
@@ -25158,7 +25173,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N319" s="4" t="n">
+      <c r="N319" s="8" t="n">
         <v>7.643</v>
       </c>
       <c r="O319" s="4" t="inlineStr">
@@ -25204,7 +25219,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G320" s="4" t="n">
+      <c r="G320" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H320" s="4" t="inlineStr">
@@ -25237,7 +25252,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N320" s="4" t="n">
+      <c r="N320" s="8" t="n">
         <v>6.218</v>
       </c>
       <c r="O320" s="4" t="inlineStr">
@@ -25283,7 +25298,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G321" s="4" t="n">
+      <c r="G321" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H321" s="4" t="inlineStr">
@@ -25316,7 +25331,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N321" s="4" t="n">
+      <c r="N321" s="8" t="n">
         <v>5.965</v>
       </c>
       <c r="O321" s="4" t="inlineStr">
@@ -25362,7 +25377,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G322" s="4" t="n">
+      <c r="G322" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H322" s="4" t="inlineStr">
@@ -25395,7 +25410,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N322" s="4" t="n">
+      <c r="N322" s="8" t="n">
         <v>6.952</v>
       </c>
       <c r="O322" s="4" t="inlineStr">
@@ -25441,7 +25456,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G323" s="4" t="n">
+      <c r="G323" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H323" s="4" t="inlineStr">
@@ -25474,7 +25489,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N323" s="4" t="n">
+      <c r="N323" s="8" t="n">
         <v>7.206</v>
       </c>
       <c r="O323" s="4" t="inlineStr">
@@ -25520,7 +25535,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G324" s="4" t="n">
+      <c r="G324" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H324" s="4" t="inlineStr">
@@ -25553,7 +25568,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N324" s="4" t="n">
+      <c r="N324" s="8" t="n">
         <v>7.109</v>
       </c>
       <c r="O324" s="4" t="inlineStr">
@@ -25599,7 +25614,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G325" s="4" t="n">
+      <c r="G325" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H325" s="4" t="inlineStr">
@@ -25632,7 +25647,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N325" s="4" t="n">
+      <c r="N325" s="8" t="n">
         <v>8.605</v>
       </c>
       <c r="O325" s="4" t="inlineStr">
@@ -25678,7 +25693,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G326" s="4" t="n">
+      <c r="G326" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H326" s="4" t="inlineStr">
@@ -25711,7 +25726,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N326" s="4" t="n">
+      <c r="N326" s="8" t="n">
         <v>7.578</v>
       </c>
       <c r="O326" s="4" t="inlineStr">
@@ -25757,7 +25772,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G327" s="4" t="n">
+      <c r="G327" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H327" s="4" t="inlineStr">
@@ -25790,7 +25805,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N327" s="4" t="n">
+      <c r="N327" s="8" t="n">
         <v>6.572</v>
       </c>
       <c r="O327" s="4" t="inlineStr">
@@ -25836,7 +25851,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G328" s="4" t="n">
+      <c r="G328" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H328" s="4" t="inlineStr">
@@ -25869,7 +25884,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N328" s="4" t="n">
+      <c r="N328" s="8" t="n">
         <v>5.413</v>
       </c>
       <c r="O328" s="4" t="inlineStr">
@@ -25915,7 +25930,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G329" s="4" t="n">
+      <c r="G329" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H329" s="4" t="inlineStr">
@@ -25948,7 +25963,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N329" s="4" t="n">
+      <c r="N329" s="8" t="n">
         <v>5.858</v>
       </c>
       <c r="O329" s="4" t="inlineStr">
@@ -25994,7 +26009,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G330" s="4" t="n">
+      <c r="G330" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H330" s="4" t="inlineStr">
@@ -26027,7 +26042,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N330" s="4" t="n">
+      <c r="N330" s="8" t="n">
         <v>6.178</v>
       </c>
       <c r="O330" s="4" t="inlineStr">
@@ -26073,7 +26088,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G331" s="4" t="n">
+      <c r="G331" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H331" s="4" t="inlineStr">
@@ -26106,7 +26121,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N331" s="4" t="n">
+      <c r="N331" s="8" t="n">
         <v>6.497</v>
       </c>
       <c r="O331" s="4" t="inlineStr">
@@ -26152,7 +26167,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G332" s="4" t="n">
+      <c r="G332" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H332" s="4" t="inlineStr">
@@ -26185,7 +26200,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N332" s="4" t="n">
+      <c r="N332" s="8" t="n">
         <v>7.907</v>
       </c>
       <c r="O332" s="4" t="inlineStr">
@@ -26231,7 +26246,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G333" s="4" t="n">
+      <c r="G333" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H333" s="4" t="inlineStr">
@@ -26264,7 +26279,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N333" s="4" t="n">
+      <c r="N333" s="8" t="n">
         <v>7.541</v>
       </c>
       <c r="O333" s="4" t="inlineStr">
@@ -26310,7 +26325,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G334" s="4" t="n">
+      <c r="G334" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H334" s="4" t="inlineStr">
@@ -26343,7 +26358,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N334" s="4" t="n">
+      <c r="N334" s="8" t="n">
         <v>6.179</v>
       </c>
       <c r="O334" s="4" t="inlineStr">
@@ -26389,7 +26404,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G335" s="4" t="n">
+      <c r="G335" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H335" s="4" t="inlineStr">
@@ -26422,7 +26437,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N335" s="4" t="n">
+      <c r="N335" s="8" t="n">
         <v>5.937</v>
       </c>
       <c r="O335" s="4" t="inlineStr">
@@ -26468,7 +26483,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G336" s="4" t="n">
+      <c r="G336" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H336" s="4" t="inlineStr">
@@ -26501,7 +26516,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N336" s="4" t="n">
+      <c r="N336" s="8" t="n">
         <v>5.845</v>
       </c>
       <c r="O336" s="4" t="inlineStr">
@@ -26547,7 +26562,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G337" s="4" t="n">
+      <c r="G337" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H337" s="4" t="inlineStr">
@@ -26580,7 +26595,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N337" s="4" t="n">
+      <c r="N337" s="8" t="n">
         <v>5.835</v>
       </c>
       <c r="O337" s="4" t="inlineStr">
@@ -26685,7 +26700,7 @@
           <t>Número de indicadores</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B10" s="7" t="n">
         <v>5</v>
       </c>
     </row>
@@ -26695,7 +26710,7 @@
           <t>Número de registros</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B11" s="7" t="n">
         <v>331</v>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_genero.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_genero.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="datos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metadatos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="datos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="metadatos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -82,26 +82,94 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -116,16 +184,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -134,7 +199,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -149,16 +214,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -455,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q337"/>
+  <dimension ref="A1:Q336"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -480,14 +542,14 @@
     <row r="1" ht="28" customHeight="1">
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Banco Mundial - Venezuela - Género</t>
+          <t>Banco Mundial - Género</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>World Development Indicators</t>
+          <t>Venezuela</t>
         </is>
       </c>
     </row>
@@ -612,7 +674,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G7" s="7" t="n">
+      <c r="G7" s="5" t="n">
         <v>1960</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -653,7 +715,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -689,7 +751,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G8" s="7" t="n">
+      <c r="G8" s="5" t="n">
         <v>1961</v>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -730,7 +792,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -766,7 +828,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G9" s="7" t="n">
+      <c r="G9" s="5" t="n">
         <v>1962</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -807,7 +869,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -843,7 +905,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G10" s="7" t="n">
+      <c r="G10" s="5" t="n">
         <v>1963</v>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -884,7 +946,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -920,7 +982,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G11" s="7" t="n">
+      <c r="G11" s="5" t="n">
         <v>1964</v>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -961,7 +1023,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -997,7 +1059,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G12" s="7" t="n">
+      <c r="G12" s="5" t="n">
         <v>1965</v>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -1038,7 +1100,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1074,7 +1136,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G13" s="7" t="n">
+      <c r="G13" s="5" t="n">
         <v>1966</v>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1115,7 +1177,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1151,7 +1213,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G14" s="7" t="n">
+      <c r="G14" s="5" t="n">
         <v>1967</v>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -1192,7 +1254,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1228,7 +1290,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G15" s="7" t="n">
+      <c r="G15" s="5" t="n">
         <v>1968</v>
       </c>
       <c r="H15" s="4" t="inlineStr">
@@ -1269,7 +1331,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1305,7 +1367,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G16" s="7" t="n">
+      <c r="G16" s="5" t="n">
         <v>1969</v>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -1346,7 +1408,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1382,7 +1444,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G17" s="7" t="n">
+      <c r="G17" s="5" t="n">
         <v>1970</v>
       </c>
       <c r="H17" s="4" t="inlineStr">
@@ -1423,7 +1485,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1459,7 +1521,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G18" s="7" t="n">
+      <c r="G18" s="5" t="n">
         <v>1971</v>
       </c>
       <c r="H18" s="4" t="inlineStr">
@@ -1492,7 +1554,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N18" s="8" t="n">
+      <c r="N18" s="6" t="n">
         <v>1.02354001998901</v>
       </c>
       <c r="O18" s="4" t="inlineStr">
@@ -1502,7 +1564,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1538,7 +1600,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G19" s="7" t="n">
+      <c r="G19" s="5" t="n">
         <v>1972</v>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -1571,7 +1633,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N19" s="8" t="n">
+      <c r="N19" s="6" t="n">
         <v>1.02113997936249</v>
       </c>
       <c r="O19" s="4" t="inlineStr">
@@ -1581,7 +1643,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1617,7 +1679,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G20" s="7" t="n">
+      <c r="G20" s="5" t="n">
         <v>1973</v>
       </c>
       <c r="H20" s="4" t="inlineStr">
@@ -1650,7 +1712,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N20" s="8" t="n">
+      <c r="N20" s="6" t="n">
         <v>1.01996004581451</v>
       </c>
       <c r="O20" s="4" t="inlineStr">
@@ -1660,7 +1722,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1696,7 +1758,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G21" s="7" t="n">
+      <c r="G21" s="5" t="n">
         <v>1974</v>
       </c>
       <c r="H21" s="4" t="inlineStr">
@@ -1729,7 +1791,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N21" s="8" t="n">
+      <c r="N21" s="6" t="n">
         <v>1.01884996891022</v>
       </c>
       <c r="O21" s="4" t="inlineStr">
@@ -1739,7 +1801,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1775,7 +1837,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G22" s="7" t="n">
+      <c r="G22" s="5" t="n">
         <v>1975</v>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -1808,7 +1870,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N22" s="8" t="n">
+      <c r="N22" s="6" t="n">
         <v>1.01637005805969</v>
       </c>
       <c r="O22" s="4" t="inlineStr">
@@ -1818,7 +1880,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1854,7 +1916,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G23" s="7" t="n">
+      <c r="G23" s="5" t="n">
         <v>1976</v>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -1887,7 +1949,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N23" s="8" t="n">
+      <c r="N23" s="6" t="n">
         <v>1.01276004314423</v>
       </c>
       <c r="O23" s="4" t="inlineStr">
@@ -1897,7 +1959,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -1933,7 +1995,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G24" s="7" t="n">
+      <c r="G24" s="5" t="n">
         <v>1977</v>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -1966,7 +2028,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N24" s="8" t="n">
+      <c r="N24" s="6" t="n">
         <v>1.00941002368927</v>
       </c>
       <c r="O24" s="4" t="inlineStr">
@@ -1976,7 +2038,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2012,7 +2074,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G25" s="7" t="n">
+      <c r="G25" s="5" t="n">
         <v>1978</v>
       </c>
       <c r="H25" s="4" t="inlineStr">
@@ -2045,7 +2107,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N25" s="8" t="n">
+      <c r="N25" s="6" t="n">
         <v>1.01135003566742</v>
       </c>
       <c r="O25" s="4" t="inlineStr">
@@ -2055,7 +2117,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2091,7 +2153,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G26" s="7" t="n">
+      <c r="G26" s="5" t="n">
         <v>1979</v>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -2124,7 +2186,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N26" s="8" t="n">
+      <c r="N26" s="6" t="n">
         <v>1.01270997524261</v>
       </c>
       <c r="O26" s="4" t="inlineStr">
@@ -2134,7 +2196,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2170,7 +2232,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G27" s="7" t="n">
+      <c r="G27" s="5" t="n">
         <v>1980</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -2203,7 +2265,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N27" s="8" t="n">
+      <c r="N27" s="6" t="n">
         <v>1.0116800069809</v>
       </c>
       <c r="O27" s="4" t="inlineStr">
@@ -2213,7 +2275,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2249,7 +2311,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G28" s="7" t="n">
+      <c r="G28" s="5" t="n">
         <v>1981</v>
       </c>
       <c r="H28" s="4" t="inlineStr">
@@ -2290,7 +2352,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2326,7 +2388,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G29" s="7" t="n">
+      <c r="G29" s="5" t="n">
         <v>1982</v>
       </c>
       <c r="H29" s="4" t="inlineStr">
@@ -2367,7 +2429,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2403,7 +2465,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G30" s="7" t="n">
+      <c r="G30" s="5" t="n">
         <v>1983</v>
       </c>
       <c r="H30" s="4" t="inlineStr">
@@ -2436,7 +2498,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N30" s="8" t="n">
+      <c r="N30" s="6" t="n">
         <v>1.0331699848175</v>
       </c>
       <c r="O30" s="4" t="inlineStr">
@@ -2446,7 +2508,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2482,7 +2544,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G31" s="7" t="n">
+      <c r="G31" s="5" t="n">
         <v>1984</v>
       </c>
       <c r="H31" s="4" t="inlineStr">
@@ -2515,7 +2577,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N31" s="8" t="n">
+      <c r="N31" s="6" t="n">
         <v>0.99974000453949</v>
       </c>
       <c r="O31" s="4" t="inlineStr">
@@ -2525,7 +2587,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2561,7 +2623,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G32" s="7" t="n">
+      <c r="G32" s="5" t="n">
         <v>1985</v>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -2594,7 +2656,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N32" s="8" t="n">
+      <c r="N32" s="6" t="n">
         <v>0.9933900237083439</v>
       </c>
       <c r="O32" s="4" t="inlineStr">
@@ -2604,7 +2666,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2640,7 +2702,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G33" s="7" t="n">
+      <c r="G33" s="5" t="n">
         <v>1986</v>
       </c>
       <c r="H33" s="4" t="inlineStr">
@@ -2673,7 +2735,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N33" s="8" t="n">
+      <c r="N33" s="6" t="n">
         <v>0.9947800040245059</v>
       </c>
       <c r="O33" s="4" t="inlineStr">
@@ -2683,7 +2745,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2719,7 +2781,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G34" s="7" t="n">
+      <c r="G34" s="5" t="n">
         <v>1987</v>
       </c>
       <c r="H34" s="4" t="inlineStr">
@@ -2752,7 +2814,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N34" s="8" t="n">
+      <c r="N34" s="6" t="n">
         <v>0.995450019836426</v>
       </c>
       <c r="O34" s="4" t="inlineStr">
@@ -2762,7 +2824,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2798,7 +2860,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G35" s="7" t="n">
+      <c r="G35" s="5" t="n">
         <v>1988</v>
       </c>
       <c r="H35" s="4" t="inlineStr">
@@ -2831,7 +2893,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N35" s="8" t="n">
+      <c r="N35" s="6" t="n">
         <v>0.997699975967407</v>
       </c>
       <c r="O35" s="4" t="inlineStr">
@@ -2841,7 +2903,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2877,7 +2939,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G36" s="7" t="n">
+      <c r="G36" s="5" t="n">
         <v>1989</v>
       </c>
       <c r="H36" s="4" t="inlineStr">
@@ -2910,7 +2972,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N36" s="8" t="n">
+      <c r="N36" s="6" t="n">
         <v>1.00051999092102</v>
       </c>
       <c r="O36" s="4" t="inlineStr">
@@ -2920,7 +2982,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -2956,7 +3018,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G37" s="7" t="n">
+      <c r="G37" s="5" t="n">
         <v>1990</v>
       </c>
       <c r="H37" s="4" t="inlineStr">
@@ -2997,7 +3059,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3033,7 +3095,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G38" s="7" t="n">
+      <c r="G38" s="5" t="n">
         <v>1991</v>
       </c>
       <c r="H38" s="4" t="inlineStr">
@@ -3066,7 +3128,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N38" s="8" t="n">
+      <c r="N38" s="6" t="n">
         <v>0.989409983158112</v>
       </c>
       <c r="O38" s="4" t="inlineStr">
@@ -3076,7 +3138,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3112,7 +3174,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G39" s="7" t="n">
+      <c r="G39" s="5" t="n">
         <v>1992</v>
       </c>
       <c r="H39" s="4" t="inlineStr">
@@ -3145,7 +3207,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N39" s="8" t="n">
+      <c r="N39" s="6" t="n">
         <v>0.98183000087738</v>
       </c>
       <c r="O39" s="4" t="inlineStr">
@@ -3155,7 +3217,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3191,7 +3253,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G40" s="7" t="n">
+      <c r="G40" s="5" t="n">
         <v>1993</v>
       </c>
       <c r="H40" s="4" t="inlineStr">
@@ -3224,7 +3286,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N40" s="8" t="n">
+      <c r="N40" s="6" t="n">
         <v>0.978500008583069</v>
       </c>
       <c r="O40" s="4" t="inlineStr">
@@ -3234,7 +3296,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3270,7 +3332,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G41" s="7" t="n">
+      <c r="G41" s="5" t="n">
         <v>1994</v>
       </c>
       <c r="H41" s="4" t="inlineStr">
@@ -3311,7 +3373,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3347,7 +3409,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G42" s="7" t="n">
+      <c r="G42" s="5" t="n">
         <v>1995</v>
       </c>
       <c r="H42" s="4" t="inlineStr">
@@ -3388,7 +3450,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3424,7 +3486,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G43" s="7" t="n">
+      <c r="G43" s="5" t="n">
         <v>1996</v>
       </c>
       <c r="H43" s="4" t="inlineStr">
@@ -3457,7 +3519,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N43" s="8" t="n">
+      <c r="N43" s="6" t="n">
         <v>0.986720025539398</v>
       </c>
       <c r="O43" s="4" t="inlineStr">
@@ -3467,7 +3529,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3503,7 +3565,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G44" s="7" t="n">
+      <c r="G44" s="5" t="n">
         <v>1997</v>
       </c>
       <c r="H44" s="4" t="inlineStr">
@@ -3536,7 +3598,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N44" s="8" t="n">
+      <c r="N44" s="6" t="n">
         <v>0.97969001531601</v>
       </c>
       <c r="O44" s="4" t="inlineStr">
@@ -3546,7 +3608,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3582,7 +3644,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G45" s="7" t="n">
+      <c r="G45" s="5" t="n">
         <v>1998</v>
       </c>
       <c r="H45" s="4" t="inlineStr">
@@ -3623,7 +3685,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3659,7 +3721,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G46" s="7" t="n">
+      <c r="G46" s="5" t="n">
         <v>1999</v>
       </c>
       <c r="H46" s="4" t="inlineStr">
@@ -3692,7 +3754,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N46" s="8" t="n">
+      <c r="N46" s="6" t="n">
         <v>0.983089983463287</v>
       </c>
       <c r="O46" s="4" t="inlineStr">
@@ -3702,7 +3764,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3738,7 +3800,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G47" s="7" t="n">
+      <c r="G47" s="5" t="n">
         <v>2000</v>
       </c>
       <c r="H47" s="4" t="inlineStr">
@@ -3771,7 +3833,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N47" s="8" t="n">
+      <c r="N47" s="6" t="n">
         <v>0.983439981937408</v>
       </c>
       <c r="O47" s="4" t="inlineStr">
@@ -3781,7 +3843,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3817,7 +3879,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G48" s="7" t="n">
+      <c r="G48" s="5" t="n">
         <v>2001</v>
       </c>
       <c r="H48" s="4" t="inlineStr">
@@ -3850,7 +3912,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N48" s="8" t="n">
+      <c r="N48" s="6" t="n">
         <v>0.982729971408844</v>
       </c>
       <c r="O48" s="4" t="inlineStr">
@@ -3860,7 +3922,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -3896,7 +3958,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G49" s="7" t="n">
+      <c r="G49" s="5" t="n">
         <v>2002</v>
       </c>
       <c r="H49" s="4" t="inlineStr">
@@ -3929,7 +3991,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N49" s="8" t="n">
+      <c r="N49" s="6" t="n">
         <v>0.98131000995636</v>
       </c>
       <c r="O49" s="4" t="inlineStr">
@@ -3939,7 +4001,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -3975,7 +4037,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G50" s="7" t="n">
+      <c r="G50" s="5" t="n">
         <v>2003</v>
       </c>
       <c r="H50" s="4" t="inlineStr">
@@ -4008,7 +4070,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N50" s="8" t="n">
+      <c r="N50" s="6" t="n">
         <v>0.980359971523285</v>
       </c>
       <c r="O50" s="4" t="inlineStr">
@@ -4018,7 +4080,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4054,7 +4116,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G51" s="7" t="n">
+      <c r="G51" s="5" t="n">
         <v>2004</v>
       </c>
       <c r="H51" s="4" t="inlineStr">
@@ -4087,7 +4149,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N51" s="8" t="n">
+      <c r="N51" s="6" t="n">
         <v>0.979730010032654</v>
       </c>
       <c r="O51" s="4" t="inlineStr">
@@ -4097,7 +4159,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4133,7 +4195,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G52" s="7" t="n">
+      <c r="G52" s="5" t="n">
         <v>2005</v>
       </c>
       <c r="H52" s="4" t="inlineStr">
@@ -4166,7 +4228,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N52" s="8" t="n">
+      <c r="N52" s="6" t="n">
         <v>0.981199979782104</v>
       </c>
       <c r="O52" s="4" t="inlineStr">
@@ -4176,7 +4238,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4212,7 +4274,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G53" s="7" t="n">
+      <c r="G53" s="5" t="n">
         <v>2006</v>
       </c>
       <c r="H53" s="4" t="inlineStr">
@@ -4245,7 +4307,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N53" s="8" t="n">
+      <c r="N53" s="6" t="n">
         <v>0.977609992027283</v>
       </c>
       <c r="O53" s="4" t="inlineStr">
@@ -4255,7 +4317,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4291,7 +4353,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G54" s="7" t="n">
+      <c r="G54" s="5" t="n">
         <v>2007</v>
       </c>
       <c r="H54" s="4" t="inlineStr">
@@ -4324,7 +4386,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N54" s="8" t="n">
+      <c r="N54" s="6" t="n">
         <v>0.974629998207092</v>
       </c>
       <c r="O54" s="4" t="inlineStr">
@@ -4334,7 +4396,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4370,7 +4432,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G55" s="7" t="n">
+      <c r="G55" s="5" t="n">
         <v>2008</v>
       </c>
       <c r="H55" s="4" t="inlineStr">
@@ -4403,7 +4465,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N55" s="8" t="n">
+      <c r="N55" s="6" t="n">
         <v>0.974510014057159</v>
       </c>
       <c r="O55" s="4" t="inlineStr">
@@ -4413,7 +4475,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4449,7 +4511,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G56" s="7" t="n">
+      <c r="G56" s="5" t="n">
         <v>2009</v>
       </c>
       <c r="H56" s="4" t="inlineStr">
@@ -4482,7 +4544,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N56" s="8" t="n">
+      <c r="N56" s="6" t="n">
         <v>0.974039971828461</v>
       </c>
       <c r="O56" s="4" t="inlineStr">
@@ -4492,7 +4554,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4528,7 +4590,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G57" s="7" t="n">
+      <c r="G57" s="5" t="n">
         <v>2010</v>
       </c>
       <c r="H57" s="4" t="inlineStr">
@@ -4561,7 +4623,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N57" s="8" t="n">
+      <c r="N57" s="6" t="n">
         <v>0.972440004348755</v>
       </c>
       <c r="O57" s="4" t="inlineStr">
@@ -4571,7 +4633,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4607,7 +4669,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G58" s="7" t="n">
+      <c r="G58" s="5" t="n">
         <v>2011</v>
       </c>
       <c r="H58" s="4" t="inlineStr">
@@ -4640,7 +4702,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N58" s="8" t="n">
+      <c r="N58" s="6" t="n">
         <v>0.975350022315979</v>
       </c>
       <c r="O58" s="4" t="inlineStr">
@@ -4650,7 +4712,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4686,7 +4748,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G59" s="7" t="n">
+      <c r="G59" s="5" t="n">
         <v>2012</v>
       </c>
       <c r="H59" s="4" t="inlineStr">
@@ -4719,7 +4781,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N59" s="8" t="n">
+      <c r="N59" s="6" t="n">
         <v>0.98063999414444</v>
       </c>
       <c r="O59" s="4" t="inlineStr">
@@ -4729,7 +4791,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4765,7 +4827,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G60" s="7" t="n">
+      <c r="G60" s="5" t="n">
         <v>2013</v>
       </c>
       <c r="H60" s="4" t="inlineStr">
@@ -4798,7 +4860,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N60" s="8" t="n">
+      <c r="N60" s="6" t="n">
         <v>0.9868900179862981</v>
       </c>
       <c r="O60" s="4" t="inlineStr">
@@ -4808,7 +4870,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4844,7 +4906,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G61" s="7" t="n">
+      <c r="G61" s="5" t="n">
         <v>2014</v>
       </c>
       <c r="H61" s="4" t="inlineStr">
@@ -4877,7 +4939,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N61" s="8" t="n">
+      <c r="N61" s="6" t="n">
         <v>0.9825199842453</v>
       </c>
       <c r="O61" s="4" t="inlineStr">
@@ -4887,7 +4949,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -4923,7 +4985,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G62" s="7" t="n">
+      <c r="G62" s="5" t="n">
         <v>2015</v>
       </c>
       <c r="H62" s="4" t="inlineStr">
@@ -4956,7 +5018,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N62" s="8" t="n">
+      <c r="N62" s="6" t="n">
         <v>0.977729976177216</v>
       </c>
       <c r="O62" s="4" t="inlineStr">
@@ -4966,7 +5028,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5002,7 +5064,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G63" s="7" t="n">
+      <c r="G63" s="5" t="n">
         <v>2016</v>
       </c>
       <c r="H63" s="4" t="inlineStr">
@@ -5035,7 +5097,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N63" s="8" t="n">
+      <c r="N63" s="6" t="n">
         <v>0.976989984512329</v>
       </c>
       <c r="O63" s="4" t="inlineStr">
@@ -5045,7 +5107,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5081,7 +5143,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G64" s="7" t="n">
+      <c r="G64" s="5" t="n">
         <v>2017</v>
       </c>
       <c r="H64" s="4" t="inlineStr">
@@ -5114,7 +5176,7 @@
           <t>Ratio niñas-niños en educación primaria</t>
         </is>
       </c>
-      <c r="N64" s="8" t="n">
+      <c r="N64" s="6" t="n">
         <v>0.9770799875259401</v>
       </c>
       <c r="O64" s="4" t="inlineStr">
@@ -5124,7 +5186,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5160,7 +5222,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G65" s="7" t="n">
+      <c r="G65" s="5" t="n">
         <v>2018</v>
       </c>
       <c r="H65" s="4" t="inlineStr">
@@ -5201,7 +5263,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5237,7 +5299,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G66" s="7" t="n">
+      <c r="G66" s="5" t="n">
         <v>2019</v>
       </c>
       <c r="H66" s="4" t="inlineStr">
@@ -5278,7 +5340,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5314,7 +5376,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G67" s="7" t="n">
+      <c r="G67" s="5" t="n">
         <v>2020</v>
       </c>
       <c r="H67" s="4" t="inlineStr">
@@ -5355,7 +5417,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5391,7 +5453,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G68" s="7" t="n">
+      <c r="G68" s="5" t="n">
         <v>2021</v>
       </c>
       <c r="H68" s="4" t="inlineStr">
@@ -5432,7 +5494,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5468,7 +5530,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G69" s="7" t="n">
+      <c r="G69" s="5" t="n">
         <v>2022</v>
       </c>
       <c r="H69" s="4" t="inlineStr">
@@ -5509,7 +5571,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5545,7 +5607,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G70" s="7" t="n">
+      <c r="G70" s="5" t="n">
         <v>2023</v>
       </c>
       <c r="H70" s="4" t="inlineStr">
@@ -5586,7 +5648,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5622,7 +5684,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G71" s="7" t="n">
+      <c r="G71" s="5" t="n">
         <v>2024</v>
       </c>
       <c r="H71" s="4" t="inlineStr">
@@ -5663,7 +5725,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5699,7 +5761,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G72" s="7" t="n">
+      <c r="G72" s="5" t="n">
         <v>2025</v>
       </c>
       <c r="H72" s="4" t="inlineStr">
@@ -5740,7 +5802,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5776,7 +5838,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G73" s="7" t="n">
+      <c r="G73" s="5" t="n">
         <v>1960</v>
       </c>
       <c r="H73" s="4" t="inlineStr">
@@ -5817,14 +5879,10 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q73" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q73" s="4" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
@@ -5857,7 +5915,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G74" s="7" t="n">
+      <c r="G74" s="5" t="n">
         <v>1961</v>
       </c>
       <c r="H74" s="4" t="inlineStr">
@@ -5898,14 +5956,10 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q74" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q74" s="4" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
@@ -5938,7 +5992,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G75" s="7" t="n">
+      <c r="G75" s="5" t="n">
         <v>1962</v>
       </c>
       <c r="H75" s="4" t="inlineStr">
@@ -5979,14 +6033,10 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q75" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q75" s="4" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
@@ -6019,7 +6069,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G76" s="7" t="n">
+      <c r="G76" s="5" t="n">
         <v>1963</v>
       </c>
       <c r="H76" s="4" t="inlineStr">
@@ -6060,14 +6110,10 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q76" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q76" s="4" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
@@ -6100,7 +6146,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G77" s="7" t="n">
+      <c r="G77" s="5" t="n">
         <v>1964</v>
       </c>
       <c r="H77" s="4" t="inlineStr">
@@ -6141,14 +6187,10 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q77" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q77" s="4" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
@@ -6181,7 +6223,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G78" s="7" t="n">
+      <c r="G78" s="5" t="n">
         <v>1965</v>
       </c>
       <c r="H78" s="4" t="inlineStr">
@@ -6222,14 +6264,10 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q78" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q78" s="4" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
@@ -6262,7 +6300,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G79" s="7" t="n">
+      <c r="G79" s="5" t="n">
         <v>1966</v>
       </c>
       <c r="H79" s="4" t="inlineStr">
@@ -6303,14 +6341,10 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q79" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q79" s="4" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
@@ -6343,7 +6377,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G80" s="7" t="n">
+      <c r="G80" s="5" t="n">
         <v>1967</v>
       </c>
       <c r="H80" s="4" t="inlineStr">
@@ -6384,14 +6418,10 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q80" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q80" s="4" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
@@ -6424,7 +6454,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G81" s="7" t="n">
+      <c r="G81" s="5" t="n">
         <v>1968</v>
       </c>
       <c r="H81" s="4" t="inlineStr">
@@ -6465,14 +6495,10 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q81" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q81" s="4" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
@@ -6505,7 +6531,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G82" s="7" t="n">
+      <c r="G82" s="5" t="n">
         <v>1969</v>
       </c>
       <c r="H82" s="4" t="inlineStr">
@@ -6546,14 +6572,10 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q82" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q82" s="4" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
@@ -6586,7 +6608,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G83" s="7" t="n">
+      <c r="G83" s="5" t="n">
         <v>1970</v>
       </c>
       <c r="H83" s="4" t="inlineStr">
@@ -6627,14 +6649,10 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q83" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q83" s="4" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
@@ -6667,7 +6685,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G84" s="7" t="n">
+      <c r="G84" s="5" t="n">
         <v>1971</v>
       </c>
       <c r="H84" s="4" t="inlineStr">
@@ -6700,7 +6718,9 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N84" s="4" t="n"/>
+      <c r="N84" s="6" t="n">
+        <v>1.06591999530792</v>
+      </c>
       <c r="O84" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -6708,14 +6728,10 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q84" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q84" s="4" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
@@ -6748,7 +6764,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G85" s="7" t="n">
+      <c r="G85" s="5" t="n">
         <v>1972</v>
       </c>
       <c r="H85" s="4" t="inlineStr">
@@ -6781,7 +6797,9 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N85" s="4" t="n"/>
+      <c r="N85" s="6" t="n">
+        <v>1.07165002822876</v>
+      </c>
       <c r="O85" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -6789,14 +6807,10 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q85" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q85" s="4" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
@@ -6829,7 +6843,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G86" s="7" t="n">
+      <c r="G86" s="5" t="n">
         <v>1973</v>
       </c>
       <c r="H86" s="4" t="inlineStr">
@@ -6862,7 +6876,9 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N86" s="4" t="n"/>
+      <c r="N86" s="6" t="n">
+        <v>1.09589004516602</v>
+      </c>
       <c r="O86" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -6870,14 +6886,10 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q86" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q86" s="4" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
@@ -6910,7 +6922,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G87" s="7" t="n">
+      <c r="G87" s="5" t="n">
         <v>1974</v>
       </c>
       <c r="H87" s="4" t="inlineStr">
@@ -6943,7 +6955,9 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N87" s="4" t="n"/>
+      <c r="N87" s="6" t="n">
+        <v>1.13256001472473</v>
+      </c>
       <c r="O87" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -6951,14 +6965,10 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q87" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q87" s="4" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
@@ -6991,7 +7001,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G88" s="7" t="n">
+      <c r="G88" s="5" t="n">
         <v>1975</v>
       </c>
       <c r="H88" s="4" t="inlineStr">
@@ -7024,7 +7034,9 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N88" s="4" t="n"/>
+      <c r="N88" s="6" t="n">
+        <v>1.13680994510651</v>
+      </c>
       <c r="O88" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -7032,14 +7044,10 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q88" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q88" s="4" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
@@ -7072,7 +7080,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G89" s="7" t="n">
+      <c r="G89" s="5" t="n">
         <v>1976</v>
       </c>
       <c r="H89" s="4" t="inlineStr">
@@ -7113,14 +7121,10 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q89" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q89" s="4" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
@@ -7153,7 +7157,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G90" s="7" t="n">
+      <c r="G90" s="5" t="n">
         <v>1977</v>
       </c>
       <c r="H90" s="4" t="inlineStr">
@@ -7194,14 +7198,10 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q90" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q90" s="4" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
@@ -7234,7 +7234,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G91" s="7" t="n">
+      <c r="G91" s="5" t="n">
         <v>1978</v>
       </c>
       <c r="H91" s="4" t="inlineStr">
@@ -7275,14 +7275,10 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q91" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q91" s="4" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
@@ -7315,7 +7311,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G92" s="7" t="n">
+      <c r="G92" s="5" t="n">
         <v>1979</v>
       </c>
       <c r="H92" s="4" t="inlineStr">
@@ -7356,14 +7352,10 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q92" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q92" s="4" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
@@ -7396,7 +7388,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G93" s="7" t="n">
+      <c r="G93" s="5" t="n">
         <v>1980</v>
       </c>
       <c r="H93" s="4" t="inlineStr">
@@ -7437,14 +7429,10 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q93" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q93" s="4" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
@@ -7477,7 +7465,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G94" s="7" t="n">
+      <c r="G94" s="5" t="n">
         <v>1981</v>
       </c>
       <c r="H94" s="4" t="inlineStr">
@@ -7518,14 +7506,10 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q94" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q94" s="4" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
@@ -7558,7 +7542,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G95" s="7" t="n">
+      <c r="G95" s="5" t="n">
         <v>1982</v>
       </c>
       <c r="H95" s="4" t="inlineStr">
@@ -7599,14 +7583,10 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q95" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q95" s="4" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
@@ -7639,7 +7619,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G96" s="7" t="n">
+      <c r="G96" s="5" t="n">
         <v>1983</v>
       </c>
       <c r="H96" s="4" t="inlineStr">
@@ -7680,14 +7660,10 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q96" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q96" s="4" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
@@ -7720,7 +7696,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G97" s="7" t="n">
+      <c r="G97" s="5" t="n">
         <v>1984</v>
       </c>
       <c r="H97" s="4" t="inlineStr">
@@ -7753,7 +7729,9 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N97" s="4" t="n"/>
+      <c r="N97" s="6" t="n">
+        <v>1.24408996105194</v>
+      </c>
       <c r="O97" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -7761,14 +7739,10 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q97" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q97" s="4" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
@@ -7801,7 +7775,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G98" s="7" t="n">
+      <c r="G98" s="5" t="n">
         <v>1985</v>
       </c>
       <c r="H98" s="4" t="inlineStr">
@@ -7834,7 +7808,9 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N98" s="4" t="n"/>
+      <c r="N98" s="6" t="n">
+        <v>1.25617003440857</v>
+      </c>
       <c r="O98" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -7842,14 +7818,10 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q98" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q98" s="4" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
@@ -7882,7 +7854,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G99" s="7" t="n">
+      <c r="G99" s="5" t="n">
         <v>1986</v>
       </c>
       <c r="H99" s="4" t="inlineStr">
@@ -7915,7 +7887,9 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N99" s="4" t="n"/>
+      <c r="N99" s="6" t="n">
+        <v>1.23227000236511</v>
+      </c>
       <c r="O99" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -7923,14 +7897,10 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q99" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q99" s="4" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
@@ -7963,7 +7933,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G100" s="7" t="n">
+      <c r="G100" s="5" t="n">
         <v>1987</v>
       </c>
       <c r="H100" s="4" t="inlineStr">
@@ -7996,7 +7966,9 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N100" s="4" t="n"/>
+      <c r="N100" s="6" t="n">
+        <v>1.23520004749298</v>
+      </c>
       <c r="O100" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8004,14 +7976,10 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q100" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q100" s="4" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
@@ -8044,7 +8012,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G101" s="7" t="n">
+      <c r="G101" s="5" t="n">
         <v>1988</v>
       </c>
       <c r="H101" s="4" t="inlineStr">
@@ -8077,7 +8045,9 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N101" s="4" t="n"/>
+      <c r="N101" s="6" t="n">
+        <v>1.23055994510651</v>
+      </c>
       <c r="O101" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8085,14 +8055,10 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q101" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q101" s="4" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
@@ -8125,7 +8091,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G102" s="7" t="n">
+      <c r="G102" s="5" t="n">
         <v>1989</v>
       </c>
       <c r="H102" s="4" t="inlineStr">
@@ -8158,7 +8124,9 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N102" s="4" t="n"/>
+      <c r="N102" s="6" t="n">
+        <v>1.23713004589081</v>
+      </c>
       <c r="O102" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8166,14 +8134,10 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q102" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q102" s="4" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
@@ -8206,7 +8170,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G103" s="7" t="n">
+      <c r="G103" s="5" t="n">
         <v>1990</v>
       </c>
       <c r="H103" s="4" t="inlineStr">
@@ -8247,14 +8211,10 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q103" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q103" s="4" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
@@ -8287,7 +8247,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G104" s="7" t="n">
+      <c r="G104" s="5" t="n">
         <v>1991</v>
       </c>
       <c r="H104" s="4" t="inlineStr">
@@ -8320,7 +8280,9 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N104" s="4" t="n"/>
+      <c r="N104" s="6" t="n">
+        <v>1.24015998840332</v>
+      </c>
       <c r="O104" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8328,14 +8290,10 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q104" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q104" s="4" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
@@ -8368,7 +8326,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G105" s="7" t="n">
+      <c r="G105" s="5" t="n">
         <v>1992</v>
       </c>
       <c r="H105" s="4" t="inlineStr">
@@ -8401,7 +8359,9 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N105" s="4" t="n"/>
+      <c r="N105" s="6" t="n">
+        <v>1.2406200170517</v>
+      </c>
       <c r="O105" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8409,14 +8369,10 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q105" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q105" s="4" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
@@ -8449,7 +8405,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G106" s="7" t="n">
+      <c r="G106" s="5" t="n">
         <v>1993</v>
       </c>
       <c r="H106" s="4" t="inlineStr">
@@ -8482,7 +8438,9 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N106" s="4" t="n"/>
+      <c r="N106" s="6" t="n">
+        <v>1.24875998497009</v>
+      </c>
       <c r="O106" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8490,14 +8448,10 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q106" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q106" s="4" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
@@ -8530,7 +8484,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G107" s="7" t="n">
+      <c r="G107" s="5" t="n">
         <v>1994</v>
       </c>
       <c r="H107" s="4" t="inlineStr">
@@ -8571,14 +8525,10 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q107" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q107" s="4" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
@@ -8611,7 +8561,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G108" s="7" t="n">
+      <c r="G108" s="5" t="n">
         <v>1995</v>
       </c>
       <c r="H108" s="4" t="inlineStr">
@@ -8652,14 +8602,10 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q108" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q108" s="4" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
@@ -8692,7 +8638,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G109" s="7" t="n">
+      <c r="G109" s="5" t="n">
         <v>1996</v>
       </c>
       <c r="H109" s="4" t="inlineStr">
@@ -8733,14 +8679,10 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q109" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q109" s="4" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
@@ -8773,7 +8715,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G110" s="7" t="n">
+      <c r="G110" s="5" t="n">
         <v>1997</v>
       </c>
       <c r="H110" s="4" t="inlineStr">
@@ -8814,14 +8756,10 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q110" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q110" s="4" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
@@ -8854,7 +8792,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G111" s="7" t="n">
+      <c r="G111" s="5" t="n">
         <v>1998</v>
       </c>
       <c r="H111" s="4" t="inlineStr">
@@ -8895,14 +8833,10 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q111" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q111" s="4" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
@@ -8935,7 +8869,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G112" s="7" t="n">
+      <c r="G112" s="5" t="n">
         <v>1999</v>
       </c>
       <c r="H112" s="4" t="inlineStr">
@@ -8968,7 +8902,9 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N112" s="4" t="n"/>
+      <c r="N112" s="6" t="n">
+        <v>1.22622001171112</v>
+      </c>
       <c r="O112" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8976,14 +8912,10 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q112" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q112" s="4" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
@@ -9016,7 +8948,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G113" s="7" t="n">
+      <c r="G113" s="5" t="n">
         <v>2000</v>
       </c>
       <c r="H113" s="4" t="inlineStr">
@@ -9049,7 +8981,9 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N113" s="4" t="n"/>
+      <c r="N113" s="6" t="n">
+        <v>1.19964003562927</v>
+      </c>
       <c r="O113" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9057,14 +8991,10 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q113" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q113" s="4" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
@@ -9097,7 +9027,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G114" s="7" t="n">
+      <c r="G114" s="5" t="n">
         <v>2001</v>
       </c>
       <c r="H114" s="4" t="inlineStr">
@@ -9130,7 +9060,9 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N114" s="4" t="n"/>
+      <c r="N114" s="6" t="n">
+        <v>1.17510998249054</v>
+      </c>
       <c r="O114" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9138,14 +9070,10 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q114" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q114" s="4" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
@@ -9178,7 +9106,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G115" s="7" t="n">
+      <c r="G115" s="5" t="n">
         <v>2002</v>
       </c>
       <c r="H115" s="4" t="inlineStr">
@@ -9211,7 +9139,9 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N115" s="4" t="n"/>
+      <c r="N115" s="6" t="n">
+        <v>1.16194999217987</v>
+      </c>
       <c r="O115" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9219,14 +9149,10 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q115" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q115" s="4" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
@@ -9259,7 +9185,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G116" s="7" t="n">
+      <c r="G116" s="5" t="n">
         <v>2003</v>
       </c>
       <c r="H116" s="4" t="inlineStr">
@@ -9292,7 +9218,9 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N116" s="4" t="n"/>
+      <c r="N116" s="6" t="n">
+        <v>1.15086996555328</v>
+      </c>
       <c r="O116" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9300,14 +9228,10 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q116" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q116" s="4" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
@@ -9340,7 +9264,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G117" s="7" t="n">
+      <c r="G117" s="5" t="n">
         <v>2004</v>
       </c>
       <c r="H117" s="4" t="inlineStr">
@@ -9373,7 +9297,9 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N117" s="4" t="n"/>
+      <c r="N117" s="6" t="n">
+        <v>1.13995003700256</v>
+      </c>
       <c r="O117" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9381,14 +9307,10 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q117" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q117" s="4" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
@@ -9421,7 +9343,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G118" s="7" t="n">
+      <c r="G118" s="5" t="n">
         <v>2005</v>
       </c>
       <c r="H118" s="4" t="inlineStr">
@@ -9454,7 +9376,9 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N118" s="4" t="n"/>
+      <c r="N118" s="6" t="n">
+        <v>1.13028001785278</v>
+      </c>
       <c r="O118" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9462,14 +9386,10 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q118" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q118" s="4" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
@@ -9502,7 +9422,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G119" s="7" t="n">
+      <c r="G119" s="5" t="n">
         <v>2006</v>
       </c>
       <c r="H119" s="4" t="inlineStr">
@@ -9535,7 +9455,9 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N119" s="4" t="n"/>
+      <c r="N119" s="6" t="n">
+        <v>1.12556004524231</v>
+      </c>
       <c r="O119" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9543,14 +9465,10 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q119" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q119" s="4" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
@@ -9583,7 +9501,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G120" s="7" t="n">
+      <c r="G120" s="5" t="n">
         <v>2007</v>
       </c>
       <c r="H120" s="4" t="inlineStr">
@@ -9616,7 +9534,9 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N120" s="4" t="n"/>
+      <c r="N120" s="6" t="n">
+        <v>1.11647999286652</v>
+      </c>
       <c r="O120" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9624,14 +9544,10 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q120" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q120" s="4" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
@@ -9664,7 +9580,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G121" s="7" t="n">
+      <c r="G121" s="5" t="n">
         <v>2008</v>
       </c>
       <c r="H121" s="4" t="inlineStr">
@@ -9697,7 +9613,9 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N121" s="4" t="n"/>
+      <c r="N121" s="6" t="n">
+        <v>1.10140001773834</v>
+      </c>
       <c r="O121" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9705,14 +9623,10 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q121" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q121" s="4" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
@@ -9745,7 +9659,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G122" s="7" t="n">
+      <c r="G122" s="5" t="n">
         <v>2009</v>
       </c>
       <c r="H122" s="4" t="inlineStr">
@@ -9778,7 +9692,9 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N122" s="4" t="n"/>
+      <c r="N122" s="6" t="n">
+        <v>1.09311997890472</v>
+      </c>
       <c r="O122" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9786,14 +9702,10 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q122" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q122" s="4" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
@@ -9826,7 +9738,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G123" s="7" t="n">
+      <c r="G123" s="5" t="n">
         <v>2010</v>
       </c>
       <c r="H123" s="4" t="inlineStr">
@@ -9859,7 +9771,9 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N123" s="4" t="n"/>
+      <c r="N123" s="6" t="n">
+        <v>1.09621000289917</v>
+      </c>
       <c r="O123" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9867,14 +9781,10 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q123" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q123" s="4" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
@@ -9907,7 +9817,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G124" s="7" t="n">
+      <c r="G124" s="5" t="n">
         <v>2011</v>
       </c>
       <c r="H124" s="4" t="inlineStr">
@@ -9940,7 +9850,9 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N124" s="4" t="n"/>
+      <c r="N124" s="6" t="n">
+        <v>1.09371995925903</v>
+      </c>
       <c r="O124" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9948,14 +9860,10 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q124" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q124" s="4" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
@@ -9988,7 +9896,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G125" s="7" t="n">
+      <c r="G125" s="5" t="n">
         <v>2012</v>
       </c>
       <c r="H125" s="4" t="inlineStr">
@@ -10021,7 +9929,9 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N125" s="4" t="n"/>
+      <c r="N125" s="6" t="n">
+        <v>1.09325003623962</v>
+      </c>
       <c r="O125" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -10029,14 +9939,10 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q125" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q125" s="4" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
@@ -10069,7 +9975,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G126" s="7" t="n">
+      <c r="G126" s="5" t="n">
         <v>2013</v>
       </c>
       <c r="H126" s="4" t="inlineStr">
@@ -10102,7 +10008,9 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N126" s="4" t="n"/>
+      <c r="N126" s="6" t="n">
+        <v>1.09049999713898</v>
+      </c>
       <c r="O126" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -10110,14 +10018,10 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q126" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q126" s="4" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
@@ -10150,7 +10054,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G127" s="7" t="n">
+      <c r="G127" s="5" t="n">
         <v>2014</v>
       </c>
       <c r="H127" s="4" t="inlineStr">
@@ -10183,7 +10087,9 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N127" s="4" t="n"/>
+      <c r="N127" s="6" t="n">
+        <v>1.07729995250702</v>
+      </c>
       <c r="O127" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -10191,14 +10097,10 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q127" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q127" s="4" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
@@ -10231,7 +10133,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G128" s="7" t="n">
+      <c r="G128" s="5" t="n">
         <v>2015</v>
       </c>
       <c r="H128" s="4" t="inlineStr">
@@ -10264,7 +10166,9 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N128" s="4" t="n"/>
+      <c r="N128" s="6" t="n">
+        <v>1.07729005813599</v>
+      </c>
       <c r="O128" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -10272,14 +10176,10 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q128" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q128" s="4" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
@@ -10312,7 +10212,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G129" s="7" t="n">
+      <c r="G129" s="5" t="n">
         <v>2016</v>
       </c>
       <c r="H129" s="4" t="inlineStr">
@@ -10345,7 +10245,9 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N129" s="4" t="n"/>
+      <c r="N129" s="6" t="n">
+        <v>1.07924997806549</v>
+      </c>
       <c r="O129" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -10353,14 +10255,10 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q129" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q129" s="4" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
@@ -10393,7 +10291,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G130" s="7" t="n">
+      <c r="G130" s="5" t="n">
         <v>2017</v>
       </c>
       <c r="H130" s="4" t="inlineStr">
@@ -10426,7 +10324,9 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N130" s="4" t="n"/>
+      <c r="N130" s="6" t="n">
+        <v>1.0806200504303</v>
+      </c>
       <c r="O130" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -10434,14 +10334,10 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q130" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q130" s="4" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
@@ -10474,7 +10370,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G131" s="7" t="n">
+      <c r="G131" s="5" t="n">
         <v>2018</v>
       </c>
       <c r="H131" s="4" t="inlineStr">
@@ -10515,14 +10411,10 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q131" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q131" s="4" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
@@ -10555,7 +10447,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G132" s="7" t="n">
+      <c r="G132" s="5" t="n">
         <v>2019</v>
       </c>
       <c r="H132" s="4" t="inlineStr">
@@ -10596,14 +10488,10 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q132" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q132" s="4" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
@@ -10636,7 +10524,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G133" s="7" t="n">
+      <c r="G133" s="5" t="n">
         <v>2020</v>
       </c>
       <c r="H133" s="4" t="inlineStr">
@@ -10677,14 +10565,10 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q133" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q133" s="4" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
@@ -10717,7 +10601,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G134" s="7" t="n">
+      <c r="G134" s="5" t="n">
         <v>2021</v>
       </c>
       <c r="H134" s="4" t="inlineStr">
@@ -10758,14 +10642,10 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q134" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q134" s="4" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
@@ -10798,7 +10678,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G135" s="7" t="n">
+      <c r="G135" s="5" t="n">
         <v>2022</v>
       </c>
       <c r="H135" s="4" t="inlineStr">
@@ -10839,14 +10719,10 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q135" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q135" s="4" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
@@ -10879,7 +10755,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G136" s="7" t="n">
+      <c r="G136" s="5" t="n">
         <v>2023</v>
       </c>
       <c r="H136" s="4" t="inlineStr">
@@ -10920,14 +10796,10 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q136" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q136" s="4" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
@@ -10960,7 +10832,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G137" s="7" t="n">
+      <c r="G137" s="5" t="n">
         <v>2024</v>
       </c>
       <c r="H137" s="4" t="inlineStr">
@@ -11001,14 +10873,10 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q137" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q137" s="4" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
@@ -11041,7 +10909,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G138" s="7" t="n">
+      <c r="G138" s="5" t="n">
         <v>2025</v>
       </c>
       <c r="H138" s="4" t="inlineStr">
@@ -11082,14 +10950,10 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q138" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q138" s="4" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
@@ -11122,8 +10986,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G139" s="7" t="n">
-        <v>2026</v>
+      <c r="G139" s="5" t="n">
+        <v>1960</v>
       </c>
       <c r="H139" s="4" t="inlineStr">
         <is>
@@ -11137,22 +11001,22 @@
       </c>
       <c r="J139" s="4" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Participación política</t>
         </is>
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>educacion</t>
+          <t>participacion_politica</t>
         </is>
       </c>
       <c r="L139" s="4" t="inlineStr">
         <is>
-          <t>SE.ENR.SECO.FM.ZS</t>
+          <t>SG.GEN.PARL.ZS</t>
         </is>
       </c>
       <c r="M139" s="4" t="inlineStr">
         <is>
-          <t>Ratio niñas-niños en educación secundaria</t>
+          <t>Mujeres en parlamentos nacionales</t>
         </is>
       </c>
       <c r="N139" s="4" t="n"/>
@@ -11163,14 +11027,10 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q139" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q139" s="4" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
@@ -11203,8 +11063,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G140" s="7" t="n">
-        <v>1960</v>
+      <c r="G140" s="5" t="n">
+        <v>1961</v>
       </c>
       <c r="H140" s="4" t="inlineStr">
         <is>
@@ -11244,7 +11104,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11280,8 +11140,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G141" s="7" t="n">
-        <v>1961</v>
+      <c r="G141" s="5" t="n">
+        <v>1962</v>
       </c>
       <c r="H141" s="4" t="inlineStr">
         <is>
@@ -11321,7 +11181,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11357,8 +11217,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G142" s="7" t="n">
-        <v>1962</v>
+      <c r="G142" s="5" t="n">
+        <v>1963</v>
       </c>
       <c r="H142" s="4" t="inlineStr">
         <is>
@@ -11398,7 +11258,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11434,8 +11294,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G143" s="7" t="n">
-        <v>1963</v>
+      <c r="G143" s="5" t="n">
+        <v>1964</v>
       </c>
       <c r="H143" s="4" t="inlineStr">
         <is>
@@ -11475,7 +11335,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11511,8 +11371,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G144" s="7" t="n">
-        <v>1964</v>
+      <c r="G144" s="5" t="n">
+        <v>1965</v>
       </c>
       <c r="H144" s="4" t="inlineStr">
         <is>
@@ -11552,7 +11412,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11588,8 +11448,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G145" s="7" t="n">
-        <v>1965</v>
+      <c r="G145" s="5" t="n">
+        <v>1966</v>
       </c>
       <c r="H145" s="4" t="inlineStr">
         <is>
@@ -11629,7 +11489,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11665,8 +11525,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G146" s="7" t="n">
-        <v>1966</v>
+      <c r="G146" s="5" t="n">
+        <v>1967</v>
       </c>
       <c r="H146" s="4" t="inlineStr">
         <is>
@@ -11706,7 +11566,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11742,8 +11602,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G147" s="7" t="n">
-        <v>1967</v>
+      <c r="G147" s="5" t="n">
+        <v>1968</v>
       </c>
       <c r="H147" s="4" t="inlineStr">
         <is>
@@ -11783,7 +11643,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11819,8 +11679,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G148" s="7" t="n">
-        <v>1968</v>
+      <c r="G148" s="5" t="n">
+        <v>1969</v>
       </c>
       <c r="H148" s="4" t="inlineStr">
         <is>
@@ -11860,7 +11720,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11896,8 +11756,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G149" s="7" t="n">
-        <v>1969</v>
+      <c r="G149" s="5" t="n">
+        <v>1970</v>
       </c>
       <c r="H149" s="4" t="inlineStr">
         <is>
@@ -11937,7 +11797,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11973,8 +11833,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G150" s="7" t="n">
-        <v>1970</v>
+      <c r="G150" s="5" t="n">
+        <v>1971</v>
       </c>
       <c r="H150" s="4" t="inlineStr">
         <is>
@@ -12014,7 +11874,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -12050,8 +11910,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G151" s="7" t="n">
-        <v>1971</v>
+      <c r="G151" s="5" t="n">
+        <v>1972</v>
       </c>
       <c r="H151" s="4" t="inlineStr">
         <is>
@@ -12091,7 +11951,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12127,8 +11987,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G152" s="7" t="n">
-        <v>1972</v>
+      <c r="G152" s="5" t="n">
+        <v>1973</v>
       </c>
       <c r="H152" s="4" t="inlineStr">
         <is>
@@ -12168,7 +12028,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12204,8 +12064,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G153" s="7" t="n">
-        <v>1973</v>
+      <c r="G153" s="5" t="n">
+        <v>1974</v>
       </c>
       <c r="H153" s="4" t="inlineStr">
         <is>
@@ -12245,7 +12105,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12281,8 +12141,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G154" s="7" t="n">
-        <v>1974</v>
+      <c r="G154" s="5" t="n">
+        <v>1975</v>
       </c>
       <c r="H154" s="4" t="inlineStr">
         <is>
@@ -12322,7 +12182,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12358,8 +12218,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G155" s="7" t="n">
-        <v>1975</v>
+      <c r="G155" s="5" t="n">
+        <v>1976</v>
       </c>
       <c r="H155" s="4" t="inlineStr">
         <is>
@@ -12399,7 +12259,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12435,8 +12295,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G156" s="7" t="n">
-        <v>1976</v>
+      <c r="G156" s="5" t="n">
+        <v>1977</v>
       </c>
       <c r="H156" s="4" t="inlineStr">
         <is>
@@ -12476,7 +12336,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12512,8 +12372,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G157" s="7" t="n">
-        <v>1977</v>
+      <c r="G157" s="5" t="n">
+        <v>1978</v>
       </c>
       <c r="H157" s="4" t="inlineStr">
         <is>
@@ -12553,7 +12413,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12589,8 +12449,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G158" s="7" t="n">
-        <v>1978</v>
+      <c r="G158" s="5" t="n">
+        <v>1979</v>
       </c>
       <c r="H158" s="4" t="inlineStr">
         <is>
@@ -12630,7 +12490,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12666,8 +12526,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G159" s="7" t="n">
-        <v>1979</v>
+      <c r="G159" s="5" t="n">
+        <v>1980</v>
       </c>
       <c r="H159" s="4" t="inlineStr">
         <is>
@@ -12707,7 +12567,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12743,8 +12603,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G160" s="7" t="n">
-        <v>1980</v>
+      <c r="G160" s="5" t="n">
+        <v>1981</v>
       </c>
       <c r="H160" s="4" t="inlineStr">
         <is>
@@ -12784,7 +12644,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12820,8 +12680,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G161" s="7" t="n">
-        <v>1981</v>
+      <c r="G161" s="5" t="n">
+        <v>1982</v>
       </c>
       <c r="H161" s="4" t="inlineStr">
         <is>
@@ -12861,7 +12721,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12897,8 +12757,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G162" s="7" t="n">
-        <v>1982</v>
+      <c r="G162" s="5" t="n">
+        <v>1983</v>
       </c>
       <c r="H162" s="4" t="inlineStr">
         <is>
@@ -12938,7 +12798,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12974,8 +12834,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G163" s="7" t="n">
-        <v>1983</v>
+      <c r="G163" s="5" t="n">
+        <v>1984</v>
       </c>
       <c r="H163" s="4" t="inlineStr">
         <is>
@@ -13015,7 +12875,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -13051,8 +12911,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G164" s="7" t="n">
-        <v>1984</v>
+      <c r="G164" s="5" t="n">
+        <v>1985</v>
       </c>
       <c r="H164" s="4" t="inlineStr">
         <is>
@@ -13092,7 +12952,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13128,8 +12988,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G165" s="7" t="n">
-        <v>1985</v>
+      <c r="G165" s="5" t="n">
+        <v>1986</v>
       </c>
       <c r="H165" s="4" t="inlineStr">
         <is>
@@ -13169,7 +13029,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13205,8 +13065,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G166" s="7" t="n">
-        <v>1986</v>
+      <c r="G166" s="5" t="n">
+        <v>1987</v>
       </c>
       <c r="H166" s="4" t="inlineStr">
         <is>
@@ -13246,7 +13106,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13282,8 +13142,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G167" s="7" t="n">
-        <v>1987</v>
+      <c r="G167" s="5" t="n">
+        <v>1988</v>
       </c>
       <c r="H167" s="4" t="inlineStr">
         <is>
@@ -13323,7 +13183,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13359,8 +13219,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G168" s="7" t="n">
-        <v>1988</v>
+      <c r="G168" s="5" t="n">
+        <v>1989</v>
       </c>
       <c r="H168" s="4" t="inlineStr">
         <is>
@@ -13400,7 +13260,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13436,8 +13296,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G169" s="7" t="n">
-        <v>1989</v>
+      <c r="G169" s="5" t="n">
+        <v>1990</v>
       </c>
       <c r="H169" s="4" t="inlineStr">
         <is>
@@ -13477,7 +13337,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13513,8 +13373,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G170" s="7" t="n">
-        <v>1990</v>
+      <c r="G170" s="5" t="n">
+        <v>1991</v>
       </c>
       <c r="H170" s="4" t="inlineStr">
         <is>
@@ -13554,7 +13414,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13590,8 +13450,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G171" s="7" t="n">
-        <v>1991</v>
+      <c r="G171" s="5" t="n">
+        <v>1992</v>
       </c>
       <c r="H171" s="4" t="inlineStr">
         <is>
@@ -13631,7 +13491,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13667,8 +13527,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G172" s="7" t="n">
-        <v>1992</v>
+      <c r="G172" s="5" t="n">
+        <v>1993</v>
       </c>
       <c r="H172" s="4" t="inlineStr">
         <is>
@@ -13708,7 +13568,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13744,8 +13604,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G173" s="7" t="n">
-        <v>1993</v>
+      <c r="G173" s="5" t="n">
+        <v>1994</v>
       </c>
       <c r="H173" s="4" t="inlineStr">
         <is>
@@ -13785,7 +13645,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13821,8 +13681,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G174" s="7" t="n">
-        <v>1994</v>
+      <c r="G174" s="5" t="n">
+        <v>1995</v>
       </c>
       <c r="H174" s="4" t="inlineStr">
         <is>
@@ -13862,7 +13722,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13898,8 +13758,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G175" s="7" t="n">
-        <v>1995</v>
+      <c r="G175" s="5" t="n">
+        <v>1996</v>
       </c>
       <c r="H175" s="4" t="inlineStr">
         <is>
@@ -13939,7 +13799,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13975,8 +13835,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G176" s="7" t="n">
-        <v>1996</v>
+      <c r="G176" s="5" t="n">
+        <v>1997</v>
       </c>
       <c r="H176" s="4" t="inlineStr">
         <is>
@@ -14008,7 +13868,9 @@
           <t>Mujeres en parlamentos nacionales</t>
         </is>
       </c>
-      <c r="N176" s="4" t="n"/>
+      <c r="N176" s="6" t="n">
+        <v>5.91133004926108</v>
+      </c>
       <c r="O176" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -14016,7 +13878,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -14052,8 +13914,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G177" s="7" t="n">
-        <v>1997</v>
+      <c r="G177" s="5" t="n">
+        <v>1998</v>
       </c>
       <c r="H177" s="4" t="inlineStr">
         <is>
@@ -14085,7 +13947,7 @@
           <t>Mujeres en parlamentos nacionales</t>
         </is>
       </c>
-      <c r="N177" s="8" t="n">
+      <c r="N177" s="6" t="n">
         <v>5.91133004926108</v>
       </c>
       <c r="O177" s="4" t="inlineStr">
@@ -14095,7 +13957,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14131,8 +13993,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G178" s="7" t="n">
-        <v>1998</v>
+      <c r="G178" s="5" t="n">
+        <v>1999</v>
       </c>
       <c r="H178" s="4" t="inlineStr">
         <is>
@@ -14164,8 +14026,8 @@
           <t>Mujeres en parlamentos nacionales</t>
         </is>
       </c>
-      <c r="N178" s="8" t="n">
-        <v>5.91133004926108</v>
+      <c r="N178" s="6" t="n">
+        <v>12.1359223300971</v>
       </c>
       <c r="O178" s="4" t="inlineStr">
         <is>
@@ -14174,7 +14036,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14210,8 +14072,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G179" s="7" t="n">
-        <v>1999</v>
+      <c r="G179" s="5" t="n">
+        <v>2000</v>
       </c>
       <c r="H179" s="4" t="inlineStr">
         <is>
@@ -14243,9 +14105,7 @@
           <t>Mujeres en parlamentos nacionales</t>
         </is>
       </c>
-      <c r="N179" s="8" t="n">
-        <v>12.1359223300971</v>
-      </c>
+      <c r="N179" s="4" t="n"/>
       <c r="O179" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -14253,7 +14113,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14289,8 +14149,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G180" s="7" t="n">
-        <v>2000</v>
+      <c r="G180" s="5" t="n">
+        <v>2001</v>
       </c>
       <c r="H180" s="4" t="inlineStr">
         <is>
@@ -14322,7 +14182,9 @@
           <t>Mujeres en parlamentos nacionales</t>
         </is>
       </c>
-      <c r="N180" s="4" t="n"/>
+      <c r="N180" s="6" t="n">
+        <v>9.696969696969701</v>
+      </c>
       <c r="O180" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -14330,7 +14192,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14366,8 +14228,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G181" s="7" t="n">
-        <v>2001</v>
+      <c r="G181" s="5" t="n">
+        <v>2002</v>
       </c>
       <c r="H181" s="4" t="inlineStr">
         <is>
@@ -14399,7 +14261,7 @@
           <t>Mujeres en parlamentos nacionales</t>
         </is>
       </c>
-      <c r="N181" s="8" t="n">
+      <c r="N181" s="6" t="n">
         <v>9.696969696969701</v>
       </c>
       <c r="O181" s="4" t="inlineStr">
@@ -14409,7 +14271,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14445,8 +14307,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G182" s="7" t="n">
-        <v>2002</v>
+      <c r="G182" s="5" t="n">
+        <v>2003</v>
       </c>
       <c r="H182" s="4" t="inlineStr">
         <is>
@@ -14478,7 +14340,7 @@
           <t>Mujeres en parlamentos nacionales</t>
         </is>
       </c>
-      <c r="N182" s="8" t="n">
+      <c r="N182" s="6" t="n">
         <v>9.696969696969701</v>
       </c>
       <c r="O182" s="4" t="inlineStr">
@@ -14488,7 +14350,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14524,8 +14386,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G183" s="7" t="n">
-        <v>2003</v>
+      <c r="G183" s="5" t="n">
+        <v>2004</v>
       </c>
       <c r="H183" s="4" t="inlineStr">
         <is>
@@ -14557,7 +14419,7 @@
           <t>Mujeres en parlamentos nacionales</t>
         </is>
       </c>
-      <c r="N183" s="8" t="n">
+      <c r="N183" s="6" t="n">
         <v>9.696969696969701</v>
       </c>
       <c r="O183" s="4" t="inlineStr">
@@ -14567,7 +14429,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14603,8 +14465,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G184" s="7" t="n">
-        <v>2004</v>
+      <c r="G184" s="5" t="n">
+        <v>2005</v>
       </c>
       <c r="H184" s="4" t="inlineStr">
         <is>
@@ -14636,8 +14498,8 @@
           <t>Mujeres en parlamentos nacionales</t>
         </is>
       </c>
-      <c r="N184" s="8" t="n">
-        <v>9.696969696969701</v>
+      <c r="N184" s="6" t="n">
+        <v>17.3652694610778</v>
       </c>
       <c r="O184" s="4" t="inlineStr">
         <is>
@@ -14646,7 +14508,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14682,8 +14544,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G185" s="7" t="n">
-        <v>2005</v>
+      <c r="G185" s="5" t="n">
+        <v>2006</v>
       </c>
       <c r="H185" s="4" t="inlineStr">
         <is>
@@ -14715,8 +14577,8 @@
           <t>Mujeres en parlamentos nacionales</t>
         </is>
       </c>
-      <c r="N185" s="8" t="n">
-        <v>17.3652694610778</v>
+      <c r="N185" s="6" t="n">
+        <v>17.9640718562874</v>
       </c>
       <c r="O185" s="4" t="inlineStr">
         <is>
@@ -14725,7 +14587,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14761,8 +14623,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G186" s="7" t="n">
-        <v>2006</v>
+      <c r="G186" s="5" t="n">
+        <v>2007</v>
       </c>
       <c r="H186" s="4" t="inlineStr">
         <is>
@@ -14794,8 +14656,8 @@
           <t>Mujeres en parlamentos nacionales</t>
         </is>
       </c>
-      <c r="N186" s="8" t="n">
-        <v>17.9640718562874</v>
+      <c r="N186" s="6" t="n">
+        <v>18.562874251497</v>
       </c>
       <c r="O186" s="4" t="inlineStr">
         <is>
@@ -14804,7 +14666,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14840,8 +14702,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G187" s="7" t="n">
-        <v>2007</v>
+      <c r="G187" s="5" t="n">
+        <v>2008</v>
       </c>
       <c r="H187" s="4" t="inlineStr">
         <is>
@@ -14873,7 +14735,7 @@
           <t>Mujeres en parlamentos nacionales</t>
         </is>
       </c>
-      <c r="N187" s="8" t="n">
+      <c r="N187" s="6" t="n">
         <v>18.562874251497</v>
       </c>
       <c r="O187" s="4" t="inlineStr">
@@ -14883,7 +14745,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14919,8 +14781,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G188" s="7" t="n">
-        <v>2008</v>
+      <c r="G188" s="5" t="n">
+        <v>2009</v>
       </c>
       <c r="H188" s="4" t="inlineStr">
         <is>
@@ -14952,8 +14814,8 @@
           <t>Mujeres en parlamentos nacionales</t>
         </is>
       </c>
-      <c r="N188" s="8" t="n">
-        <v>18.562874251497</v>
+      <c r="N188" s="6" t="n">
+        <v>17.4698795180723</v>
       </c>
       <c r="O188" s="4" t="inlineStr">
         <is>
@@ -14962,7 +14824,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14998,8 +14860,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G189" s="7" t="n">
-        <v>2009</v>
+      <c r="G189" s="5" t="n">
+        <v>2010</v>
       </c>
       <c r="H189" s="4" t="inlineStr">
         <is>
@@ -15031,8 +14893,8 @@
           <t>Mujeres en parlamentos nacionales</t>
         </is>
       </c>
-      <c r="N189" s="8" t="n">
-        <v>17.4698795180723</v>
+      <c r="N189" s="6" t="n">
+        <v>16.969696969697</v>
       </c>
       <c r="O189" s="4" t="inlineStr">
         <is>
@@ -15041,7 +14903,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15077,8 +14939,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G190" s="7" t="n">
-        <v>2010</v>
+      <c r="G190" s="5" t="n">
+        <v>2011</v>
       </c>
       <c r="H190" s="4" t="inlineStr">
         <is>
@@ -15110,7 +14972,7 @@
           <t>Mujeres en parlamentos nacionales</t>
         </is>
       </c>
-      <c r="N190" s="8" t="n">
+      <c r="N190" s="6" t="n">
         <v>16.969696969697</v>
       </c>
       <c r="O190" s="4" t="inlineStr">
@@ -15120,7 +14982,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15156,8 +15018,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G191" s="7" t="n">
-        <v>2011</v>
+      <c r="G191" s="5" t="n">
+        <v>2012</v>
       </c>
       <c r="H191" s="4" t="inlineStr">
         <is>
@@ -15189,7 +15051,7 @@
           <t>Mujeres en parlamentos nacionales</t>
         </is>
       </c>
-      <c r="N191" s="8" t="n">
+      <c r="N191" s="6" t="n">
         <v>16.969696969697</v>
       </c>
       <c r="O191" s="4" t="inlineStr">
@@ -15199,7 +15061,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15235,8 +15097,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G192" s="7" t="n">
-        <v>2012</v>
+      <c r="G192" s="5" t="n">
+        <v>2013</v>
       </c>
       <c r="H192" s="4" t="inlineStr">
         <is>
@@ -15268,7 +15130,7 @@
           <t>Mujeres en parlamentos nacionales</t>
         </is>
       </c>
-      <c r="N192" s="8" t="n">
+      <c r="N192" s="6" t="n">
         <v>16.969696969697</v>
       </c>
       <c r="O192" s="4" t="inlineStr">
@@ -15278,7 +15140,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15314,8 +15176,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G193" s="7" t="n">
-        <v>2013</v>
+      <c r="G193" s="5" t="n">
+        <v>2014</v>
       </c>
       <c r="H193" s="4" t="inlineStr">
         <is>
@@ -15347,7 +15209,7 @@
           <t>Mujeres en parlamentos nacionales</t>
         </is>
       </c>
-      <c r="N193" s="8" t="n">
+      <c r="N193" s="6" t="n">
         <v>16.969696969697</v>
       </c>
       <c r="O193" s="4" t="inlineStr">
@@ -15357,7 +15219,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15393,8 +15255,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G194" s="7" t="n">
-        <v>2014</v>
+      <c r="G194" s="5" t="n">
+        <v>2015</v>
       </c>
       <c r="H194" s="4" t="inlineStr">
         <is>
@@ -15426,7 +15288,7 @@
           <t>Mujeres en parlamentos nacionales</t>
         </is>
       </c>
-      <c r="N194" s="8" t="n">
+      <c r="N194" s="6" t="n">
         <v>16.969696969697</v>
       </c>
       <c r="O194" s="4" t="inlineStr">
@@ -15436,7 +15298,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15472,8 +15334,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G195" s="7" t="n">
-        <v>2015</v>
+      <c r="G195" s="5" t="n">
+        <v>2016</v>
       </c>
       <c r="H195" s="4" t="inlineStr">
         <is>
@@ -15505,8 +15367,8 @@
           <t>Mujeres en parlamentos nacionales</t>
         </is>
       </c>
-      <c r="N195" s="8" t="n">
-        <v>16.969696969697</v>
+      <c r="N195" s="6" t="n">
+        <v>14.3712574850299</v>
       </c>
       <c r="O195" s="4" t="inlineStr">
         <is>
@@ -15515,7 +15377,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15551,8 +15413,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G196" s="7" t="n">
-        <v>2016</v>
+      <c r="G196" s="5" t="n">
+        <v>2017</v>
       </c>
       <c r="H196" s="4" t="inlineStr">
         <is>
@@ -15584,8 +15446,8 @@
           <t>Mujeres en parlamentos nacionales</t>
         </is>
       </c>
-      <c r="N196" s="8" t="n">
-        <v>14.3712574850299</v>
+      <c r="N196" s="6" t="n">
+        <v>22.1556886227545</v>
       </c>
       <c r="O196" s="4" t="inlineStr">
         <is>
@@ -15594,7 +15456,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15630,8 +15492,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G197" s="7" t="n">
-        <v>2017</v>
+      <c r="G197" s="5" t="n">
+        <v>2018</v>
       </c>
       <c r="H197" s="4" t="inlineStr">
         <is>
@@ -15663,7 +15525,7 @@
           <t>Mujeres en parlamentos nacionales</t>
         </is>
       </c>
-      <c r="N197" s="8" t="n">
+      <c r="N197" s="6" t="n">
         <v>22.1556886227545</v>
       </c>
       <c r="O197" s="4" t="inlineStr">
@@ -15673,7 +15535,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15709,8 +15571,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G198" s="7" t="n">
-        <v>2018</v>
+      <c r="G198" s="5" t="n">
+        <v>2019</v>
       </c>
       <c r="H198" s="4" t="inlineStr">
         <is>
@@ -15742,7 +15604,7 @@
           <t>Mujeres en parlamentos nacionales</t>
         </is>
       </c>
-      <c r="N198" s="8" t="n">
+      <c r="N198" s="6" t="n">
         <v>22.1556886227545</v>
       </c>
       <c r="O198" s="4" t="inlineStr">
@@ -15752,7 +15614,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15788,8 +15650,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G199" s="7" t="n">
-        <v>2019</v>
+      <c r="G199" s="5" t="n">
+        <v>2020</v>
       </c>
       <c r="H199" s="4" t="inlineStr">
         <is>
@@ -15821,7 +15683,7 @@
           <t>Mujeres en parlamentos nacionales</t>
         </is>
       </c>
-      <c r="N199" s="8" t="n">
+      <c r="N199" s="6" t="n">
         <v>22.1556886227545</v>
       </c>
       <c r="O199" s="4" t="inlineStr">
@@ -15831,7 +15693,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15867,8 +15729,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G200" s="7" t="n">
-        <v>2020</v>
+      <c r="G200" s="5" t="n">
+        <v>2021</v>
       </c>
       <c r="H200" s="4" t="inlineStr">
         <is>
@@ -15900,7 +15762,7 @@
           <t>Mujeres en parlamentos nacionales</t>
         </is>
       </c>
-      <c r="N200" s="8" t="n">
+      <c r="N200" s="6" t="n">
         <v>22.1556886227545</v>
       </c>
       <c r="O200" s="4" t="inlineStr">
@@ -15910,7 +15772,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15946,8 +15808,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G201" s="7" t="n">
-        <v>2021</v>
+      <c r="G201" s="5" t="n">
+        <v>2022</v>
       </c>
       <c r="H201" s="4" t="inlineStr">
         <is>
@@ -15979,9 +15841,7 @@
           <t>Mujeres en parlamentos nacionales</t>
         </is>
       </c>
-      <c r="N201" s="8" t="n">
-        <v>22.1556886227545</v>
-      </c>
+      <c r="N201" s="4" t="n"/>
       <c r="O201" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -15989,7 +15849,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -16025,8 +15885,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G202" s="7" t="n">
-        <v>2022</v>
+      <c r="G202" s="5" t="n">
+        <v>2023</v>
       </c>
       <c r="H202" s="4" t="inlineStr">
         <is>
@@ -16066,7 +15926,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16102,8 +15962,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G203" s="7" t="n">
-        <v>2023</v>
+      <c r="G203" s="5" t="n">
+        <v>2024</v>
       </c>
       <c r="H203" s="4" t="inlineStr">
         <is>
@@ -16143,7 +16003,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16179,8 +16039,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G204" s="7" t="n">
-        <v>2024</v>
+      <c r="G204" s="5" t="n">
+        <v>2025</v>
       </c>
       <c r="H204" s="4" t="inlineStr">
         <is>
@@ -16212,7 +16072,9 @@
           <t>Mujeres en parlamentos nacionales</t>
         </is>
       </c>
-      <c r="N204" s="4" t="n"/>
+      <c r="N204" s="6" t="n">
+        <v>32.129963898917</v>
+      </c>
       <c r="O204" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -16220,7 +16082,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16256,8 +16118,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G205" s="7" t="n">
-        <v>2025</v>
+      <c r="G205" s="5" t="n">
+        <v>1960</v>
       </c>
       <c r="H205" s="4" t="inlineStr">
         <is>
@@ -16271,27 +16133,25 @@
       </c>
       <c r="J205" s="4" t="inlineStr">
         <is>
-          <t>Participación política</t>
+          <t>Mercado laboral</t>
         </is>
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>participacion_politica</t>
+          <t>mercado_laboral</t>
         </is>
       </c>
       <c r="L205" s="4" t="inlineStr">
         <is>
-          <t>SG.GEN.PARL.ZS</t>
+          <t>SL.TLF.CACT.FE.ZS</t>
         </is>
       </c>
       <c r="M205" s="4" t="inlineStr">
         <is>
-          <t>Mujeres en parlamentos nacionales</t>
-        </is>
-      </c>
-      <c r="N205" s="8" t="n">
-        <v>32.129963898917</v>
-      </c>
+          <t>Participación laboral femenina</t>
+        </is>
+      </c>
+      <c r="N205" s="4" t="n"/>
       <c r="O205" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -16299,7 +16159,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16335,8 +16195,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G206" s="7" t="n">
-        <v>1960</v>
+      <c r="G206" s="5" t="n">
+        <v>1961</v>
       </c>
       <c r="H206" s="4" t="inlineStr">
         <is>
@@ -16376,7 +16236,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16412,8 +16272,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G207" s="7" t="n">
-        <v>1961</v>
+      <c r="G207" s="5" t="n">
+        <v>1962</v>
       </c>
       <c r="H207" s="4" t="inlineStr">
         <is>
@@ -16453,7 +16313,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16489,8 +16349,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G208" s="7" t="n">
-        <v>1962</v>
+      <c r="G208" s="5" t="n">
+        <v>1963</v>
       </c>
       <c r="H208" s="4" t="inlineStr">
         <is>
@@ -16530,7 +16390,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16566,8 +16426,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G209" s="7" t="n">
-        <v>1963</v>
+      <c r="G209" s="5" t="n">
+        <v>1964</v>
       </c>
       <c r="H209" s="4" t="inlineStr">
         <is>
@@ -16607,7 +16467,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16643,8 +16503,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G210" s="7" t="n">
-        <v>1964</v>
+      <c r="G210" s="5" t="n">
+        <v>1965</v>
       </c>
       <c r="H210" s="4" t="inlineStr">
         <is>
@@ -16684,7 +16544,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16720,8 +16580,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G211" s="7" t="n">
-        <v>1965</v>
+      <c r="G211" s="5" t="n">
+        <v>1966</v>
       </c>
       <c r="H211" s="4" t="inlineStr">
         <is>
@@ -16761,7 +16621,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16797,8 +16657,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G212" s="7" t="n">
-        <v>1966</v>
+      <c r="G212" s="5" t="n">
+        <v>1967</v>
       </c>
       <c r="H212" s="4" t="inlineStr">
         <is>
@@ -16838,7 +16698,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16874,8 +16734,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G213" s="7" t="n">
-        <v>1967</v>
+      <c r="G213" s="5" t="n">
+        <v>1968</v>
       </c>
       <c r="H213" s="4" t="inlineStr">
         <is>
@@ -16915,7 +16775,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16951,8 +16811,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G214" s="7" t="n">
-        <v>1968</v>
+      <c r="G214" s="5" t="n">
+        <v>1969</v>
       </c>
       <c r="H214" s="4" t="inlineStr">
         <is>
@@ -16992,7 +16852,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -17028,8 +16888,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G215" s="7" t="n">
-        <v>1969</v>
+      <c r="G215" s="5" t="n">
+        <v>1970</v>
       </c>
       <c r="H215" s="4" t="inlineStr">
         <is>
@@ -17069,7 +16929,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17105,8 +16965,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G216" s="7" t="n">
-        <v>1970</v>
+      <c r="G216" s="5" t="n">
+        <v>1971</v>
       </c>
       <c r="H216" s="4" t="inlineStr">
         <is>
@@ -17146,7 +17006,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17182,8 +17042,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G217" s="7" t="n">
-        <v>1971</v>
+      <c r="G217" s="5" t="n">
+        <v>1972</v>
       </c>
       <c r="H217" s="4" t="inlineStr">
         <is>
@@ -17223,7 +17083,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17259,8 +17119,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G218" s="7" t="n">
-        <v>1972</v>
+      <c r="G218" s="5" t="n">
+        <v>1973</v>
       </c>
       <c r="H218" s="4" t="inlineStr">
         <is>
@@ -17300,7 +17160,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17336,8 +17196,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G219" s="7" t="n">
-        <v>1973</v>
+      <c r="G219" s="5" t="n">
+        <v>1974</v>
       </c>
       <c r="H219" s="4" t="inlineStr">
         <is>
@@ -17377,7 +17237,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17413,8 +17273,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G220" s="7" t="n">
-        <v>1974</v>
+      <c r="G220" s="5" t="n">
+        <v>1975</v>
       </c>
       <c r="H220" s="4" t="inlineStr">
         <is>
@@ -17454,7 +17314,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17490,8 +17350,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G221" s="7" t="n">
-        <v>1975</v>
+      <c r="G221" s="5" t="n">
+        <v>1976</v>
       </c>
       <c r="H221" s="4" t="inlineStr">
         <is>
@@ -17531,7 +17391,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17567,8 +17427,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G222" s="7" t="n">
-        <v>1976</v>
+      <c r="G222" s="5" t="n">
+        <v>1977</v>
       </c>
       <c r="H222" s="4" t="inlineStr">
         <is>
@@ -17608,7 +17468,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17644,8 +17504,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G223" s="7" t="n">
-        <v>1977</v>
+      <c r="G223" s="5" t="n">
+        <v>1978</v>
       </c>
       <c r="H223" s="4" t="inlineStr">
         <is>
@@ -17685,7 +17545,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17721,8 +17581,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G224" s="7" t="n">
-        <v>1978</v>
+      <c r="G224" s="5" t="n">
+        <v>1979</v>
       </c>
       <c r="H224" s="4" t="inlineStr">
         <is>
@@ -17762,7 +17622,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17798,8 +17658,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G225" s="7" t="n">
-        <v>1979</v>
+      <c r="G225" s="5" t="n">
+        <v>1980</v>
       </c>
       <c r="H225" s="4" t="inlineStr">
         <is>
@@ -17839,7 +17699,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17875,8 +17735,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G226" s="7" t="n">
-        <v>1980</v>
+      <c r="G226" s="5" t="n">
+        <v>1981</v>
       </c>
       <c r="H226" s="4" t="inlineStr">
         <is>
@@ -17916,7 +17776,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17952,8 +17812,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G227" s="7" t="n">
-        <v>1981</v>
+      <c r="G227" s="5" t="n">
+        <v>1982</v>
       </c>
       <c r="H227" s="4" t="inlineStr">
         <is>
@@ -17993,7 +17853,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -18029,8 +17889,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G228" s="7" t="n">
-        <v>1982</v>
+      <c r="G228" s="5" t="n">
+        <v>1983</v>
       </c>
       <c r="H228" s="4" t="inlineStr">
         <is>
@@ -18070,7 +17930,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18106,8 +17966,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G229" s="7" t="n">
-        <v>1983</v>
+      <c r="G229" s="5" t="n">
+        <v>1984</v>
       </c>
       <c r="H229" s="4" t="inlineStr">
         <is>
@@ -18147,7 +18007,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18183,8 +18043,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G230" s="7" t="n">
-        <v>1984</v>
+      <c r="G230" s="5" t="n">
+        <v>1985</v>
       </c>
       <c r="H230" s="4" t="inlineStr">
         <is>
@@ -18224,7 +18084,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18260,8 +18120,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G231" s="7" t="n">
-        <v>1985</v>
+      <c r="G231" s="5" t="n">
+        <v>1986</v>
       </c>
       <c r="H231" s="4" t="inlineStr">
         <is>
@@ -18301,7 +18161,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18337,8 +18197,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G232" s="7" t="n">
-        <v>1986</v>
+      <c r="G232" s="5" t="n">
+        <v>1987</v>
       </c>
       <c r="H232" s="4" t="inlineStr">
         <is>
@@ -18378,7 +18238,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18414,8 +18274,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G233" s="7" t="n">
-        <v>1987</v>
+      <c r="G233" s="5" t="n">
+        <v>1988</v>
       </c>
       <c r="H233" s="4" t="inlineStr">
         <is>
@@ -18455,7 +18315,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18491,8 +18351,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G234" s="7" t="n">
-        <v>1988</v>
+      <c r="G234" s="5" t="n">
+        <v>1989</v>
       </c>
       <c r="H234" s="4" t="inlineStr">
         <is>
@@ -18532,7 +18392,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18568,8 +18428,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G235" s="7" t="n">
-        <v>1989</v>
+      <c r="G235" s="5" t="n">
+        <v>1990</v>
       </c>
       <c r="H235" s="4" t="inlineStr">
         <is>
@@ -18601,7 +18461,9 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N235" s="4" t="n"/>
+      <c r="N235" s="6" t="n">
+        <v>48.56</v>
+      </c>
       <c r="O235" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -18609,7 +18471,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18645,8 +18507,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G236" s="7" t="n">
-        <v>1990</v>
+      <c r="G236" s="5" t="n">
+        <v>1991</v>
       </c>
       <c r="H236" s="4" t="inlineStr">
         <is>
@@ -18678,8 +18540,8 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N236" s="8" t="n">
-        <v>48.56</v>
+      <c r="N236" s="6" t="n">
+        <v>49.027</v>
       </c>
       <c r="O236" s="4" t="inlineStr">
         <is>
@@ -18688,7 +18550,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18724,8 +18586,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G237" s="7" t="n">
-        <v>1991</v>
+      <c r="G237" s="5" t="n">
+        <v>1992</v>
       </c>
       <c r="H237" s="4" t="inlineStr">
         <is>
@@ -18757,8 +18619,8 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N237" s="8" t="n">
-        <v>49.027</v>
+      <c r="N237" s="6" t="n">
+        <v>49.439</v>
       </c>
       <c r="O237" s="4" t="inlineStr">
         <is>
@@ -18767,7 +18629,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18803,8 +18665,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G238" s="7" t="n">
-        <v>1992</v>
+      <c r="G238" s="5" t="n">
+        <v>1993</v>
       </c>
       <c r="H238" s="4" t="inlineStr">
         <is>
@@ -18836,8 +18698,8 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N238" s="8" t="n">
-        <v>49.439</v>
+      <c r="N238" s="6" t="n">
+        <v>49.121</v>
       </c>
       <c r="O238" s="4" t="inlineStr">
         <is>
@@ -18846,7 +18708,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18882,8 +18744,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G239" s="7" t="n">
-        <v>1993</v>
+      <c r="G239" s="5" t="n">
+        <v>1994</v>
       </c>
       <c r="H239" s="4" t="inlineStr">
         <is>
@@ -18915,8 +18777,8 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N239" s="8" t="n">
-        <v>49.121</v>
+      <c r="N239" s="6" t="n">
+        <v>48.519</v>
       </c>
       <c r="O239" s="4" t="inlineStr">
         <is>
@@ -18925,7 +18787,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18961,8 +18823,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G240" s="7" t="n">
-        <v>1994</v>
+      <c r="G240" s="5" t="n">
+        <v>1995</v>
       </c>
       <c r="H240" s="4" t="inlineStr">
         <is>
@@ -18994,8 +18856,8 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N240" s="8" t="n">
-        <v>48.519</v>
+      <c r="N240" s="6" t="n">
+        <v>48.502</v>
       </c>
       <c r="O240" s="4" t="inlineStr">
         <is>
@@ -19004,7 +18866,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -19040,8 +18902,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G241" s="7" t="n">
-        <v>1995</v>
+      <c r="G241" s="5" t="n">
+        <v>1996</v>
       </c>
       <c r="H241" s="4" t="inlineStr">
         <is>
@@ -19073,8 +18935,8 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N241" s="8" t="n">
-        <v>48.502</v>
+      <c r="N241" s="6" t="n">
+        <v>48.683</v>
       </c>
       <c r="O241" s="4" t="inlineStr">
         <is>
@@ -19083,7 +18945,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19119,8 +18981,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G242" s="7" t="n">
-        <v>1996</v>
+      <c r="G242" s="5" t="n">
+        <v>1997</v>
       </c>
       <c r="H242" s="4" t="inlineStr">
         <is>
@@ -19152,8 +19014,8 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N242" s="8" t="n">
-        <v>48.683</v>
+      <c r="N242" s="6" t="n">
+        <v>48.743</v>
       </c>
       <c r="O242" s="4" t="inlineStr">
         <is>
@@ -19162,7 +19024,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19198,8 +19060,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G243" s="7" t="n">
-        <v>1997</v>
+      <c r="G243" s="5" t="n">
+        <v>1998</v>
       </c>
       <c r="H243" s="4" t="inlineStr">
         <is>
@@ -19231,8 +19093,8 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N243" s="8" t="n">
-        <v>48.743</v>
+      <c r="N243" s="6" t="n">
+        <v>48.976</v>
       </c>
       <c r="O243" s="4" t="inlineStr">
         <is>
@@ -19241,7 +19103,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19277,8 +19139,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G244" s="7" t="n">
-        <v>1998</v>
+      <c r="G244" s="5" t="n">
+        <v>1999</v>
       </c>
       <c r="H244" s="4" t="inlineStr">
         <is>
@@ -19310,8 +19172,8 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N244" s="8" t="n">
-        <v>48.976</v>
+      <c r="N244" s="6" t="n">
+        <v>48.119</v>
       </c>
       <c r="O244" s="4" t="inlineStr">
         <is>
@@ -19320,7 +19182,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19356,8 +19218,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G245" s="7" t="n">
-        <v>1999</v>
+      <c r="G245" s="5" t="n">
+        <v>2000</v>
       </c>
       <c r="H245" s="4" t="inlineStr">
         <is>
@@ -19389,8 +19251,8 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N245" s="8" t="n">
-        <v>48.119</v>
+      <c r="N245" s="6" t="n">
+        <v>47.914</v>
       </c>
       <c r="O245" s="4" t="inlineStr">
         <is>
@@ -19399,7 +19261,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19435,8 +19297,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G246" s="7" t="n">
-        <v>2000</v>
+      <c r="G246" s="5" t="n">
+        <v>2001</v>
       </c>
       <c r="H246" s="4" t="inlineStr">
         <is>
@@ -19468,8 +19330,8 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N246" s="8" t="n">
-        <v>47.914</v>
+      <c r="N246" s="6" t="n">
+        <v>48.527</v>
       </c>
       <c r="O246" s="4" t="inlineStr">
         <is>
@@ -19478,7 +19340,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19514,8 +19376,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G247" s="7" t="n">
-        <v>2001</v>
+      <c r="G247" s="5" t="n">
+        <v>2002</v>
       </c>
       <c r="H247" s="4" t="inlineStr">
         <is>
@@ -19547,8 +19409,8 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N247" s="8" t="n">
-        <v>48.527</v>
+      <c r="N247" s="6" t="n">
+        <v>47.765</v>
       </c>
       <c r="O247" s="4" t="inlineStr">
         <is>
@@ -19557,7 +19419,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19593,8 +19455,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G248" s="7" t="n">
-        <v>2002</v>
+      <c r="G248" s="5" t="n">
+        <v>2003</v>
       </c>
       <c r="H248" s="4" t="inlineStr">
         <is>
@@ -19626,8 +19488,8 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N248" s="8" t="n">
-        <v>47.765</v>
+      <c r="N248" s="6" t="n">
+        <v>46.462</v>
       </c>
       <c r="O248" s="4" t="inlineStr">
         <is>
@@ -19636,7 +19498,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19672,8 +19534,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G249" s="7" t="n">
-        <v>2003</v>
+      <c r="G249" s="5" t="n">
+        <v>2004</v>
       </c>
       <c r="H249" s="4" t="inlineStr">
         <is>
@@ -19705,8 +19567,8 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N249" s="8" t="n">
-        <v>46.462</v>
+      <c r="N249" s="6" t="n">
+        <v>47.558</v>
       </c>
       <c r="O249" s="4" t="inlineStr">
         <is>
@@ -19715,7 +19577,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19751,8 +19613,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G250" s="7" t="n">
-        <v>2004</v>
+      <c r="G250" s="5" t="n">
+        <v>2005</v>
       </c>
       <c r="H250" s="4" t="inlineStr">
         <is>
@@ -19784,8 +19646,8 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N250" s="8" t="n">
-        <v>47.558</v>
+      <c r="N250" s="6" t="n">
+        <v>49.457</v>
       </c>
       <c r="O250" s="4" t="inlineStr">
         <is>
@@ -19794,7 +19656,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19830,8 +19692,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G251" s="7" t="n">
-        <v>2005</v>
+      <c r="G251" s="5" t="n">
+        <v>2006</v>
       </c>
       <c r="H251" s="4" t="inlineStr">
         <is>
@@ -19863,8 +19725,8 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N251" s="8" t="n">
-        <v>49.457</v>
+      <c r="N251" s="6" t="n">
+        <v>50.019</v>
       </c>
       <c r="O251" s="4" t="inlineStr">
         <is>
@@ -19873,7 +19735,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19909,8 +19771,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G252" s="7" t="n">
-        <v>2006</v>
+      <c r="G252" s="5" t="n">
+        <v>2007</v>
       </c>
       <c r="H252" s="4" t="inlineStr">
         <is>
@@ -19942,8 +19804,8 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N252" s="8" t="n">
-        <v>50.019</v>
+      <c r="N252" s="6" t="n">
+        <v>49.726</v>
       </c>
       <c r="O252" s="4" t="inlineStr">
         <is>
@@ -19952,7 +19814,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19988,8 +19850,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G253" s="7" t="n">
-        <v>2007</v>
+      <c r="G253" s="5" t="n">
+        <v>2008</v>
       </c>
       <c r="H253" s="4" t="inlineStr">
         <is>
@@ -20021,8 +19883,8 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N253" s="8" t="n">
-        <v>49.726</v>
+      <c r="N253" s="6" t="n">
+        <v>49.734</v>
       </c>
       <c r="O253" s="4" t="inlineStr">
         <is>
@@ -20031,7 +19893,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -20067,8 +19929,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G254" s="7" t="n">
-        <v>2008</v>
+      <c r="G254" s="5" t="n">
+        <v>2009</v>
       </c>
       <c r="H254" s="4" t="inlineStr">
         <is>
@@ -20100,8 +19962,8 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N254" s="8" t="n">
-        <v>49.734</v>
+      <c r="N254" s="6" t="n">
+        <v>50.004</v>
       </c>
       <c r="O254" s="4" t="inlineStr">
         <is>
@@ -20110,7 +19972,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20146,8 +20008,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G255" s="7" t="n">
-        <v>2009</v>
+      <c r="G255" s="5" t="n">
+        <v>2010</v>
       </c>
       <c r="H255" s="4" t="inlineStr">
         <is>
@@ -20179,8 +20041,8 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N255" s="8" t="n">
-        <v>50.004</v>
+      <c r="N255" s="6" t="n">
+        <v>49.601</v>
       </c>
       <c r="O255" s="4" t="inlineStr">
         <is>
@@ -20189,7 +20051,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20225,8 +20087,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G256" s="7" t="n">
-        <v>2010</v>
+      <c r="G256" s="5" t="n">
+        <v>2011</v>
       </c>
       <c r="H256" s="4" t="inlineStr">
         <is>
@@ -20258,8 +20120,8 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N256" s="8" t="n">
-        <v>49.601</v>
+      <c r="N256" s="6" t="n">
+        <v>49.643</v>
       </c>
       <c r="O256" s="4" t="inlineStr">
         <is>
@@ -20268,7 +20130,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20304,8 +20166,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G257" s="7" t="n">
-        <v>2011</v>
+      <c r="G257" s="5" t="n">
+        <v>2012</v>
       </c>
       <c r="H257" s="4" t="inlineStr">
         <is>
@@ -20337,8 +20199,8 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N257" s="8" t="n">
-        <v>49.643</v>
+      <c r="N257" s="6" t="n">
+        <v>49.493</v>
       </c>
       <c r="O257" s="4" t="inlineStr">
         <is>
@@ -20347,7 +20209,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20383,8 +20245,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G258" s="7" t="n">
-        <v>2012</v>
+      <c r="G258" s="5" t="n">
+        <v>2013</v>
       </c>
       <c r="H258" s="4" t="inlineStr">
         <is>
@@ -20416,8 +20278,8 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N258" s="8" t="n">
-        <v>49.493</v>
+      <c r="N258" s="6" t="n">
+        <v>49.084</v>
       </c>
       <c r="O258" s="4" t="inlineStr">
         <is>
@@ -20426,7 +20288,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20462,8 +20324,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G259" s="7" t="n">
-        <v>2013</v>
+      <c r="G259" s="5" t="n">
+        <v>2014</v>
       </c>
       <c r="H259" s="4" t="inlineStr">
         <is>
@@ -20495,8 +20357,8 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N259" s="8" t="n">
-        <v>49.084</v>
+      <c r="N259" s="6" t="n">
+        <v>48.676</v>
       </c>
       <c r="O259" s="4" t="inlineStr">
         <is>
@@ -20505,7 +20367,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20541,8 +20403,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G260" s="7" t="n">
-        <v>2014</v>
+      <c r="G260" s="5" t="n">
+        <v>2015</v>
       </c>
       <c r="H260" s="4" t="inlineStr">
         <is>
@@ -20574,8 +20436,8 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N260" s="8" t="n">
-        <v>48.676</v>
+      <c r="N260" s="6" t="n">
+        <v>48.27</v>
       </c>
       <c r="O260" s="4" t="inlineStr">
         <is>
@@ -20584,7 +20446,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20620,8 +20482,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G261" s="7" t="n">
-        <v>2015</v>
+      <c r="G261" s="5" t="n">
+        <v>2016</v>
       </c>
       <c r="H261" s="4" t="inlineStr">
         <is>
@@ -20653,8 +20515,8 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N261" s="8" t="n">
-        <v>48.27</v>
+      <c r="N261" s="6" t="n">
+        <v>47.867</v>
       </c>
       <c r="O261" s="4" t="inlineStr">
         <is>
@@ -20663,7 +20525,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20699,8 +20561,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G262" s="7" t="n">
-        <v>2016</v>
+      <c r="G262" s="5" t="n">
+        <v>2017</v>
       </c>
       <c r="H262" s="4" t="inlineStr">
         <is>
@@ -20732,8 +20594,8 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N262" s="8" t="n">
-        <v>47.867</v>
+      <c r="N262" s="6" t="n">
+        <v>46.185</v>
       </c>
       <c r="O262" s="4" t="inlineStr">
         <is>
@@ -20742,7 +20604,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20778,8 +20640,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G263" s="7" t="n">
-        <v>2017</v>
+      <c r="G263" s="5" t="n">
+        <v>2018</v>
       </c>
       <c r="H263" s="4" t="inlineStr">
         <is>
@@ -20811,8 +20673,8 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N263" s="8" t="n">
-        <v>46.185</v>
+      <c r="N263" s="6" t="n">
+        <v>44.85</v>
       </c>
       <c r="O263" s="4" t="inlineStr">
         <is>
@@ -20821,7 +20683,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20857,8 +20719,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G264" s="7" t="n">
-        <v>2018</v>
+      <c r="G264" s="5" t="n">
+        <v>2019</v>
       </c>
       <c r="H264" s="4" t="inlineStr">
         <is>
@@ -20890,8 +20752,8 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N264" s="8" t="n">
-        <v>44.85</v>
+      <c r="N264" s="6" t="n">
+        <v>42.344</v>
       </c>
       <c r="O264" s="4" t="inlineStr">
         <is>
@@ -20900,7 +20762,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20936,8 +20798,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G265" s="7" t="n">
-        <v>2019</v>
+      <c r="G265" s="5" t="n">
+        <v>2020</v>
       </c>
       <c r="H265" s="4" t="inlineStr">
         <is>
@@ -20969,8 +20831,8 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N265" s="8" t="n">
-        <v>42.344</v>
+      <c r="N265" s="6" t="n">
+        <v>36.887</v>
       </c>
       <c r="O265" s="4" t="inlineStr">
         <is>
@@ -20979,7 +20841,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -21015,8 +20877,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G266" s="7" t="n">
-        <v>2020</v>
+      <c r="G266" s="5" t="n">
+        <v>2021</v>
       </c>
       <c r="H266" s="4" t="inlineStr">
         <is>
@@ -21048,8 +20910,8 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N266" s="8" t="n">
-        <v>36.887</v>
+      <c r="N266" s="6" t="n">
+        <v>37.368</v>
       </c>
       <c r="O266" s="4" t="inlineStr">
         <is>
@@ -21058,7 +20920,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21094,8 +20956,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G267" s="7" t="n">
-        <v>2021</v>
+      <c r="G267" s="5" t="n">
+        <v>2022</v>
       </c>
       <c r="H267" s="4" t="inlineStr">
         <is>
@@ -21127,8 +20989,8 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N267" s="8" t="n">
-        <v>37.368</v>
+      <c r="N267" s="6" t="n">
+        <v>35.32</v>
       </c>
       <c r="O267" s="4" t="inlineStr">
         <is>
@@ -21137,7 +20999,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21173,8 +21035,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G268" s="7" t="n">
-        <v>2022</v>
+      <c r="G268" s="5" t="n">
+        <v>2023</v>
       </c>
       <c r="H268" s="4" t="inlineStr">
         <is>
@@ -21206,8 +21068,8 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N268" s="8" t="n">
-        <v>35.32</v>
+      <c r="N268" s="6" t="n">
+        <v>36.158</v>
       </c>
       <c r="O268" s="4" t="inlineStr">
         <is>
@@ -21216,7 +21078,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21252,8 +21114,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G269" s="7" t="n">
-        <v>2023</v>
+      <c r="G269" s="5" t="n">
+        <v>2024</v>
       </c>
       <c r="H269" s="4" t="inlineStr">
         <is>
@@ -21285,8 +21147,8 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N269" s="8" t="n">
-        <v>36.158</v>
+      <c r="N269" s="6" t="n">
+        <v>37.332</v>
       </c>
       <c r="O269" s="4" t="inlineStr">
         <is>
@@ -21295,7 +21157,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21331,8 +21193,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G270" s="7" t="n">
-        <v>2024</v>
+      <c r="G270" s="5" t="n">
+        <v>2025</v>
       </c>
       <c r="H270" s="4" t="inlineStr">
         <is>
@@ -21364,8 +21226,8 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N270" s="8" t="n">
-        <v>37.332</v>
+      <c r="N270" s="6" t="n">
+        <v>37.098</v>
       </c>
       <c r="O270" s="4" t="inlineStr">
         <is>
@@ -21374,7 +21236,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21410,8 +21272,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G271" s="7" t="n">
-        <v>2025</v>
+      <c r="G271" s="5" t="n">
+        <v>1960</v>
       </c>
       <c r="H271" s="4" t="inlineStr">
         <is>
@@ -21435,17 +21297,15 @@
       </c>
       <c r="L271" s="4" t="inlineStr">
         <is>
-          <t>SL.TLF.CACT.FE.ZS</t>
+          <t>SL.UEM.TOTL.FE.ZS</t>
         </is>
       </c>
       <c r="M271" s="4" t="inlineStr">
         <is>
-          <t>Participación laboral femenina</t>
-        </is>
-      </c>
-      <c r="N271" s="8" t="n">
-        <v>37.098</v>
-      </c>
+          <t>Desempleo femenino</t>
+        </is>
+      </c>
+      <c r="N271" s="4" t="n"/>
       <c r="O271" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -21453,7 +21313,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21489,8 +21349,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G272" s="7" t="n">
-        <v>1960</v>
+      <c r="G272" s="5" t="n">
+        <v>1961</v>
       </c>
       <c r="H272" s="4" t="inlineStr">
         <is>
@@ -21530,7 +21390,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21566,8 +21426,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G273" s="7" t="n">
-        <v>1961</v>
+      <c r="G273" s="5" t="n">
+        <v>1962</v>
       </c>
       <c r="H273" s="4" t="inlineStr">
         <is>
@@ -21607,7 +21467,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21643,8 +21503,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G274" s="7" t="n">
-        <v>1962</v>
+      <c r="G274" s="5" t="n">
+        <v>1963</v>
       </c>
       <c r="H274" s="4" t="inlineStr">
         <is>
@@ -21684,7 +21544,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21720,8 +21580,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G275" s="7" t="n">
-        <v>1963</v>
+      <c r="G275" s="5" t="n">
+        <v>1964</v>
       </c>
       <c r="H275" s="4" t="inlineStr">
         <is>
@@ -21761,7 +21621,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21797,8 +21657,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G276" s="7" t="n">
-        <v>1964</v>
+      <c r="G276" s="5" t="n">
+        <v>1965</v>
       </c>
       <c r="H276" s="4" t="inlineStr">
         <is>
@@ -21838,7 +21698,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21874,8 +21734,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G277" s="7" t="n">
-        <v>1965</v>
+      <c r="G277" s="5" t="n">
+        <v>1966</v>
       </c>
       <c r="H277" s="4" t="inlineStr">
         <is>
@@ -21915,7 +21775,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -21951,8 +21811,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G278" s="7" t="n">
-        <v>1966</v>
+      <c r="G278" s="5" t="n">
+        <v>1967</v>
       </c>
       <c r="H278" s="4" t="inlineStr">
         <is>
@@ -21992,7 +21852,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -22028,8 +21888,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G279" s="7" t="n">
-        <v>1967</v>
+      <c r="G279" s="5" t="n">
+        <v>1968</v>
       </c>
       <c r="H279" s="4" t="inlineStr">
         <is>
@@ -22069,7 +21929,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -22105,8 +21965,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G280" s="7" t="n">
-        <v>1968</v>
+      <c r="G280" s="5" t="n">
+        <v>1969</v>
       </c>
       <c r="H280" s="4" t="inlineStr">
         <is>
@@ -22146,7 +22006,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22182,8 +22042,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G281" s="7" t="n">
-        <v>1969</v>
+      <c r="G281" s="5" t="n">
+        <v>1970</v>
       </c>
       <c r="H281" s="4" t="inlineStr">
         <is>
@@ -22223,7 +22083,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22259,8 +22119,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G282" s="7" t="n">
-        <v>1970</v>
+      <c r="G282" s="5" t="n">
+        <v>1971</v>
       </c>
       <c r="H282" s="4" t="inlineStr">
         <is>
@@ -22300,7 +22160,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22336,8 +22196,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G283" s="7" t="n">
-        <v>1971</v>
+      <c r="G283" s="5" t="n">
+        <v>1972</v>
       </c>
       <c r="H283" s="4" t="inlineStr">
         <is>
@@ -22377,7 +22237,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22413,8 +22273,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G284" s="7" t="n">
-        <v>1972</v>
+      <c r="G284" s="5" t="n">
+        <v>1973</v>
       </c>
       <c r="H284" s="4" t="inlineStr">
         <is>
@@ -22454,7 +22314,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22490,8 +22350,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G285" s="7" t="n">
-        <v>1973</v>
+      <c r="G285" s="5" t="n">
+        <v>1974</v>
       </c>
       <c r="H285" s="4" t="inlineStr">
         <is>
@@ -22531,7 +22391,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22567,8 +22427,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G286" s="7" t="n">
-        <v>1974</v>
+      <c r="G286" s="5" t="n">
+        <v>1975</v>
       </c>
       <c r="H286" s="4" t="inlineStr">
         <is>
@@ -22608,7 +22468,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22644,8 +22504,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G287" s="7" t="n">
-        <v>1975</v>
+      <c r="G287" s="5" t="n">
+        <v>1976</v>
       </c>
       <c r="H287" s="4" t="inlineStr">
         <is>
@@ -22685,7 +22545,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22721,8 +22581,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G288" s="7" t="n">
-        <v>1976</v>
+      <c r="G288" s="5" t="n">
+        <v>1977</v>
       </c>
       <c r="H288" s="4" t="inlineStr">
         <is>
@@ -22762,7 +22622,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22798,8 +22658,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G289" s="7" t="n">
-        <v>1977</v>
+      <c r="G289" s="5" t="n">
+        <v>1978</v>
       </c>
       <c r="H289" s="4" t="inlineStr">
         <is>
@@ -22839,7 +22699,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22875,8 +22735,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G290" s="7" t="n">
-        <v>1978</v>
+      <c r="G290" s="5" t="n">
+        <v>1979</v>
       </c>
       <c r="H290" s="4" t="inlineStr">
         <is>
@@ -22916,7 +22776,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -22952,8 +22812,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G291" s="7" t="n">
-        <v>1979</v>
+      <c r="G291" s="5" t="n">
+        <v>1980</v>
       </c>
       <c r="H291" s="4" t="inlineStr">
         <is>
@@ -22993,7 +22853,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -23029,8 +22889,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G292" s="7" t="n">
-        <v>1980</v>
+      <c r="G292" s="5" t="n">
+        <v>1981</v>
       </c>
       <c r="H292" s="4" t="inlineStr">
         <is>
@@ -23070,7 +22930,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -23106,8 +22966,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G293" s="7" t="n">
-        <v>1981</v>
+      <c r="G293" s="5" t="n">
+        <v>1982</v>
       </c>
       <c r="H293" s="4" t="inlineStr">
         <is>
@@ -23147,7 +23007,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23183,8 +23043,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G294" s="7" t="n">
-        <v>1982</v>
+      <c r="G294" s="5" t="n">
+        <v>1983</v>
       </c>
       <c r="H294" s="4" t="inlineStr">
         <is>
@@ -23224,7 +23084,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23260,8 +23120,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G295" s="7" t="n">
-        <v>1983</v>
+      <c r="G295" s="5" t="n">
+        <v>1984</v>
       </c>
       <c r="H295" s="4" t="inlineStr">
         <is>
@@ -23301,7 +23161,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23337,8 +23197,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G296" s="7" t="n">
-        <v>1984</v>
+      <c r="G296" s="5" t="n">
+        <v>1985</v>
       </c>
       <c r="H296" s="4" t="inlineStr">
         <is>
@@ -23378,7 +23238,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23414,8 +23274,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G297" s="7" t="n">
-        <v>1985</v>
+      <c r="G297" s="5" t="n">
+        <v>1986</v>
       </c>
       <c r="H297" s="4" t="inlineStr">
         <is>
@@ -23455,7 +23315,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23491,8 +23351,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G298" s="7" t="n">
-        <v>1986</v>
+      <c r="G298" s="5" t="n">
+        <v>1987</v>
       </c>
       <c r="H298" s="4" t="inlineStr">
         <is>
@@ -23532,7 +23392,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23568,8 +23428,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G299" s="7" t="n">
-        <v>1987</v>
+      <c r="G299" s="5" t="n">
+        <v>1988</v>
       </c>
       <c r="H299" s="4" t="inlineStr">
         <is>
@@ -23609,7 +23469,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23645,8 +23505,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G300" s="7" t="n">
-        <v>1988</v>
+      <c r="G300" s="5" t="n">
+        <v>1989</v>
       </c>
       <c r="H300" s="4" t="inlineStr">
         <is>
@@ -23686,7 +23546,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23722,8 +23582,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G301" s="7" t="n">
-        <v>1989</v>
+      <c r="G301" s="5" t="n">
+        <v>1990</v>
       </c>
       <c r="H301" s="4" t="inlineStr">
         <is>
@@ -23763,7 +23623,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23799,8 +23659,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G302" s="7" t="n">
-        <v>1990</v>
+      <c r="G302" s="5" t="n">
+        <v>1991</v>
       </c>
       <c r="H302" s="4" t="inlineStr">
         <is>
@@ -23832,7 +23692,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N302" s="4" t="n"/>
+      <c r="N302" s="6" t="n">
+        <v>9.32</v>
+      </c>
       <c r="O302" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -23840,7 +23702,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23876,8 +23738,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G303" s="7" t="n">
-        <v>1991</v>
+      <c r="G303" s="5" t="n">
+        <v>1992</v>
       </c>
       <c r="H303" s="4" t="inlineStr">
         <is>
@@ -23909,8 +23771,8 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N303" s="8" t="n">
-        <v>9.32</v>
+      <c r="N303" s="6" t="n">
+        <v>6.925</v>
       </c>
       <c r="O303" s="4" t="inlineStr">
         <is>
@@ -23919,7 +23781,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -23955,8 +23817,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G304" s="7" t="n">
-        <v>1992</v>
+      <c r="G304" s="5" t="n">
+        <v>1993</v>
       </c>
       <c r="H304" s="4" t="inlineStr">
         <is>
@@ -23988,8 +23850,8 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N304" s="8" t="n">
-        <v>6.925</v>
+      <c r="N304" s="6" t="n">
+        <v>5.679</v>
       </c>
       <c r="O304" s="4" t="inlineStr">
         <is>
@@ -23998,7 +23860,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -24034,8 +23896,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G305" s="7" t="n">
-        <v>1993</v>
+      <c r="G305" s="5" t="n">
+        <v>1994</v>
       </c>
       <c r="H305" s="4" t="inlineStr">
         <is>
@@ -24067,8 +23929,8 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N305" s="8" t="n">
-        <v>5.679</v>
+      <c r="N305" s="6" t="n">
+        <v>9.557</v>
       </c>
       <c r="O305" s="4" t="inlineStr">
         <is>
@@ -24077,7 +23939,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24113,8 +23975,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G306" s="7" t="n">
-        <v>1994</v>
+      <c r="G306" s="5" t="n">
+        <v>1995</v>
       </c>
       <c r="H306" s="4" t="inlineStr">
         <is>
@@ -24146,8 +24008,8 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N306" s="8" t="n">
-        <v>9.557</v>
+      <c r="N306" s="6" t="n">
+        <v>12.604</v>
       </c>
       <c r="O306" s="4" t="inlineStr">
         <is>
@@ -24156,7 +24018,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24192,8 +24054,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G307" s="7" t="n">
-        <v>1995</v>
+      <c r="G307" s="5" t="n">
+        <v>1996</v>
       </c>
       <c r="H307" s="4" t="inlineStr">
         <is>
@@ -24225,8 +24087,8 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N307" s="8" t="n">
-        <v>12.604</v>
+      <c r="N307" s="6" t="n">
+        <v>14.345</v>
       </c>
       <c r="O307" s="4" t="inlineStr">
         <is>
@@ -24235,7 +24097,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24271,8 +24133,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G308" s="7" t="n">
-        <v>1996</v>
+      <c r="G308" s="5" t="n">
+        <v>1997</v>
       </c>
       <c r="H308" s="4" t="inlineStr">
         <is>
@@ -24304,8 +24166,8 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N308" s="8" t="n">
-        <v>14.345</v>
+      <c r="N308" s="6" t="n">
+        <v>13.627</v>
       </c>
       <c r="O308" s="4" t="inlineStr">
         <is>
@@ -24314,7 +24176,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24350,8 +24212,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G309" s="7" t="n">
-        <v>1997</v>
+      <c r="G309" s="5" t="n">
+        <v>1998</v>
       </c>
       <c r="H309" s="4" t="inlineStr">
         <is>
@@ -24383,8 +24245,8 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N309" s="8" t="n">
-        <v>13.627</v>
+      <c r="N309" s="6" t="n">
+        <v>13.306</v>
       </c>
       <c r="O309" s="4" t="inlineStr">
         <is>
@@ -24393,7 +24255,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24429,8 +24291,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G310" s="7" t="n">
-        <v>1998</v>
+      <c r="G310" s="5" t="n">
+        <v>1999</v>
       </c>
       <c r="H310" s="4" t="inlineStr">
         <is>
@@ -24462,8 +24324,8 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N310" s="8" t="n">
-        <v>13.306</v>
+      <c r="N310" s="6" t="n">
+        <v>16.482</v>
       </c>
       <c r="O310" s="4" t="inlineStr">
         <is>
@@ -24472,7 +24334,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24508,8 +24370,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G311" s="7" t="n">
-        <v>1999</v>
+      <c r="G311" s="5" t="n">
+        <v>2000</v>
       </c>
       <c r="H311" s="4" t="inlineStr">
         <is>
@@ -24541,8 +24403,8 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N311" s="8" t="n">
-        <v>16.482</v>
+      <c r="N311" s="6" t="n">
+        <v>14.605</v>
       </c>
       <c r="O311" s="4" t="inlineStr">
         <is>
@@ -24551,7 +24413,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24587,8 +24449,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G312" s="7" t="n">
-        <v>2000</v>
+      <c r="G312" s="5" t="n">
+        <v>2001</v>
       </c>
       <c r="H312" s="4" t="inlineStr">
         <is>
@@ -24620,8 +24482,8 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N312" s="8" t="n">
-        <v>14.605</v>
+      <c r="N312" s="6" t="n">
+        <v>14.109</v>
       </c>
       <c r="O312" s="4" t="inlineStr">
         <is>
@@ -24630,7 +24492,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24666,8 +24528,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G313" s="7" t="n">
-        <v>2001</v>
+      <c r="G313" s="5" t="n">
+        <v>2002</v>
       </c>
       <c r="H313" s="4" t="inlineStr">
         <is>
@@ -24699,8 +24561,8 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N313" s="8" t="n">
-        <v>14.109</v>
+      <c r="N313" s="6" t="n">
+        <v>18.895</v>
       </c>
       <c r="O313" s="4" t="inlineStr">
         <is>
@@ -24709,7 +24571,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24745,8 +24607,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G314" s="7" t="n">
-        <v>2002</v>
+      <c r="G314" s="5" t="n">
+        <v>2003</v>
       </c>
       <c r="H314" s="4" t="inlineStr">
         <is>
@@ -24778,8 +24640,8 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N314" s="8" t="n">
-        <v>18.895</v>
+      <c r="N314" s="6" t="n">
+        <v>20.483</v>
       </c>
       <c r="O314" s="4" t="inlineStr">
         <is>
@@ -24788,7 +24650,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24824,8 +24686,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G315" s="7" t="n">
-        <v>2003</v>
+      <c r="G315" s="5" t="n">
+        <v>2004</v>
       </c>
       <c r="H315" s="4" t="inlineStr">
         <is>
@@ -24857,8 +24719,8 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N315" s="8" t="n">
-        <v>20.483</v>
+      <c r="N315" s="6" t="n">
+        <v>17.974</v>
       </c>
       <c r="O315" s="4" t="inlineStr">
         <is>
@@ -24867,7 +24729,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24903,8 +24765,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G316" s="7" t="n">
-        <v>2004</v>
+      <c r="G316" s="5" t="n">
+        <v>2005</v>
       </c>
       <c r="H316" s="4" t="inlineStr">
         <is>
@@ -24936,8 +24798,8 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N316" s="8" t="n">
-        <v>17.974</v>
+      <c r="N316" s="6" t="n">
+        <v>11.64</v>
       </c>
       <c r="O316" s="4" t="inlineStr">
         <is>
@@ -24946,7 +24808,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -24982,8 +24844,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G317" s="7" t="n">
-        <v>2005</v>
+      <c r="G317" s="5" t="n">
+        <v>2006</v>
       </c>
       <c r="H317" s="4" t="inlineStr">
         <is>
@@ -25015,8 +24877,8 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N317" s="8" t="n">
-        <v>11.64</v>
+      <c r="N317" s="6" t="n">
+        <v>9.380000000000001</v>
       </c>
       <c r="O317" s="4" t="inlineStr">
         <is>
@@ -25025,7 +24887,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -25061,8 +24923,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G318" s="7" t="n">
-        <v>2006</v>
+      <c r="G318" s="5" t="n">
+        <v>2007</v>
       </c>
       <c r="H318" s="4" t="inlineStr">
         <is>
@@ -25094,8 +24956,8 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N318" s="8" t="n">
-        <v>9.380000000000001</v>
+      <c r="N318" s="6" t="n">
+        <v>7.643</v>
       </c>
       <c r="O318" s="4" t="inlineStr">
         <is>
@@ -25104,7 +24966,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25140,8 +25002,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G319" s="7" t="n">
-        <v>2007</v>
+      <c r="G319" s="5" t="n">
+        <v>2008</v>
       </c>
       <c r="H319" s="4" t="inlineStr">
         <is>
@@ -25173,8 +25035,8 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N319" s="8" t="n">
-        <v>7.643</v>
+      <c r="N319" s="6" t="n">
+        <v>6.218</v>
       </c>
       <c r="O319" s="4" t="inlineStr">
         <is>
@@ -25183,7 +25045,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25219,8 +25081,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G320" s="7" t="n">
-        <v>2008</v>
+      <c r="G320" s="5" t="n">
+        <v>2009</v>
       </c>
       <c r="H320" s="4" t="inlineStr">
         <is>
@@ -25252,8 +25114,8 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N320" s="8" t="n">
-        <v>6.218</v>
+      <c r="N320" s="6" t="n">
+        <v>5.965</v>
       </c>
       <c r="O320" s="4" t="inlineStr">
         <is>
@@ -25262,7 +25124,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25298,8 +25160,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G321" s="7" t="n">
-        <v>2009</v>
+      <c r="G321" s="5" t="n">
+        <v>2010</v>
       </c>
       <c r="H321" s="4" t="inlineStr">
         <is>
@@ -25331,8 +25193,8 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N321" s="8" t="n">
-        <v>5.965</v>
+      <c r="N321" s="6" t="n">
+        <v>6.952</v>
       </c>
       <c r="O321" s="4" t="inlineStr">
         <is>
@@ -25341,7 +25203,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25377,8 +25239,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G322" s="7" t="n">
-        <v>2010</v>
+      <c r="G322" s="5" t="n">
+        <v>2011</v>
       </c>
       <c r="H322" s="4" t="inlineStr">
         <is>
@@ -25410,8 +25272,8 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N322" s="8" t="n">
-        <v>6.952</v>
+      <c r="N322" s="6" t="n">
+        <v>7.206</v>
       </c>
       <c r="O322" s="4" t="inlineStr">
         <is>
@@ -25420,7 +25282,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25456,8 +25318,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G323" s="7" t="n">
-        <v>2011</v>
+      <c r="G323" s="5" t="n">
+        <v>2012</v>
       </c>
       <c r="H323" s="4" t="inlineStr">
         <is>
@@ -25489,8 +25351,8 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N323" s="8" t="n">
-        <v>7.206</v>
+      <c r="N323" s="6" t="n">
+        <v>7.109</v>
       </c>
       <c r="O323" s="4" t="inlineStr">
         <is>
@@ -25499,7 +25361,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25535,8 +25397,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G324" s="7" t="n">
-        <v>2012</v>
+      <c r="G324" s="5" t="n">
+        <v>2013</v>
       </c>
       <c r="H324" s="4" t="inlineStr">
         <is>
@@ -25568,8 +25430,8 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N324" s="8" t="n">
-        <v>7.109</v>
+      <c r="N324" s="6" t="n">
+        <v>8.605</v>
       </c>
       <c r="O324" s="4" t="inlineStr">
         <is>
@@ -25578,7 +25440,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25614,8 +25476,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G325" s="7" t="n">
-        <v>2013</v>
+      <c r="G325" s="5" t="n">
+        <v>2014</v>
       </c>
       <c r="H325" s="4" t="inlineStr">
         <is>
@@ -25647,8 +25509,8 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N325" s="8" t="n">
-        <v>8.605</v>
+      <c r="N325" s="6" t="n">
+        <v>7.578</v>
       </c>
       <c r="O325" s="4" t="inlineStr">
         <is>
@@ -25657,7 +25519,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25693,8 +25555,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G326" s="7" t="n">
-        <v>2014</v>
+      <c r="G326" s="5" t="n">
+        <v>2015</v>
       </c>
       <c r="H326" s="4" t="inlineStr">
         <is>
@@ -25726,8 +25588,8 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N326" s="8" t="n">
-        <v>7.578</v>
+      <c r="N326" s="6" t="n">
+        <v>6.572</v>
       </c>
       <c r="O326" s="4" t="inlineStr">
         <is>
@@ -25736,7 +25598,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25772,8 +25634,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G327" s="7" t="n">
-        <v>2015</v>
+      <c r="G327" s="5" t="n">
+        <v>2016</v>
       </c>
       <c r="H327" s="4" t="inlineStr">
         <is>
@@ -25805,8 +25667,8 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N327" s="8" t="n">
-        <v>6.572</v>
+      <c r="N327" s="6" t="n">
+        <v>5.413</v>
       </c>
       <c r="O327" s="4" t="inlineStr">
         <is>
@@ -25815,7 +25677,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25851,8 +25713,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G328" s="7" t="n">
-        <v>2016</v>
+      <c r="G328" s="5" t="n">
+        <v>2017</v>
       </c>
       <c r="H328" s="4" t="inlineStr">
         <is>
@@ -25884,8 +25746,8 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N328" s="8" t="n">
-        <v>5.413</v>
+      <c r="N328" s="6" t="n">
+        <v>5.858</v>
       </c>
       <c r="O328" s="4" t="inlineStr">
         <is>
@@ -25894,7 +25756,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25930,8 +25792,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G329" s="7" t="n">
-        <v>2017</v>
+      <c r="G329" s="5" t="n">
+        <v>2018</v>
       </c>
       <c r="H329" s="4" t="inlineStr">
         <is>
@@ -25963,8 +25825,8 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N329" s="8" t="n">
-        <v>5.858</v>
+      <c r="N329" s="6" t="n">
+        <v>6.178</v>
       </c>
       <c r="O329" s="4" t="inlineStr">
         <is>
@@ -25973,7 +25835,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -26009,8 +25871,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G330" s="7" t="n">
-        <v>2018</v>
+      <c r="G330" s="5" t="n">
+        <v>2019</v>
       </c>
       <c r="H330" s="4" t="inlineStr">
         <is>
@@ -26042,8 +25904,8 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N330" s="8" t="n">
-        <v>6.178</v>
+      <c r="N330" s="6" t="n">
+        <v>6.497</v>
       </c>
       <c r="O330" s="4" t="inlineStr">
         <is>
@@ -26052,7 +25914,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -26088,8 +25950,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G331" s="7" t="n">
-        <v>2019</v>
+      <c r="G331" s="5" t="n">
+        <v>2020</v>
       </c>
       <c r="H331" s="4" t="inlineStr">
         <is>
@@ -26121,8 +25983,8 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N331" s="8" t="n">
-        <v>6.497</v>
+      <c r="N331" s="6" t="n">
+        <v>7.907</v>
       </c>
       <c r="O331" s="4" t="inlineStr">
         <is>
@@ -26131,7 +25993,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26167,8 +26029,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G332" s="7" t="n">
-        <v>2020</v>
+      <c r="G332" s="5" t="n">
+        <v>2021</v>
       </c>
       <c r="H332" s="4" t="inlineStr">
         <is>
@@ -26200,8 +26062,8 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N332" s="8" t="n">
-        <v>7.907</v>
+      <c r="N332" s="6" t="n">
+        <v>7.541</v>
       </c>
       <c r="O332" s="4" t="inlineStr">
         <is>
@@ -26210,7 +26072,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26246,8 +26108,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G333" s="7" t="n">
-        <v>2021</v>
+      <c r="G333" s="5" t="n">
+        <v>2022</v>
       </c>
       <c r="H333" s="4" t="inlineStr">
         <is>
@@ -26279,8 +26141,8 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N333" s="8" t="n">
-        <v>7.541</v>
+      <c r="N333" s="6" t="n">
+        <v>6.179</v>
       </c>
       <c r="O333" s="4" t="inlineStr">
         <is>
@@ -26289,7 +26151,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26325,8 +26187,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G334" s="7" t="n">
-        <v>2022</v>
+      <c r="G334" s="5" t="n">
+        <v>2023</v>
       </c>
       <c r="H334" s="4" t="inlineStr">
         <is>
@@ -26358,8 +26220,8 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N334" s="8" t="n">
-        <v>6.179</v>
+      <c r="N334" s="6" t="n">
+        <v>5.937</v>
       </c>
       <c r="O334" s="4" t="inlineStr">
         <is>
@@ -26368,7 +26230,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26404,8 +26266,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G335" s="7" t="n">
-        <v>2023</v>
+      <c r="G335" s="5" t="n">
+        <v>2024</v>
       </c>
       <c r="H335" s="4" t="inlineStr">
         <is>
@@ -26437,8 +26299,8 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N335" s="8" t="n">
-        <v>5.937</v>
+      <c r="N335" s="6" t="n">
+        <v>5.845</v>
       </c>
       <c r="O335" s="4" t="inlineStr">
         <is>
@@ -26447,7 +26309,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26483,8 +26345,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G336" s="7" t="n">
-        <v>2024</v>
+      <c r="G336" s="5" t="n">
+        <v>2025</v>
       </c>
       <c r="H336" s="4" t="inlineStr">
         <is>
@@ -26516,8 +26378,8 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N336" s="8" t="n">
-        <v>5.845</v>
+      <c r="N336" s="6" t="n">
+        <v>5.835</v>
       </c>
       <c r="O336" s="4" t="inlineStr">
         <is>
@@ -26526,89 +26388,10 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
-    </row>
-    <row r="337">
-      <c r="A337" s="4" t="inlineStr">
-        <is>
-          <t>Venezuela</t>
-        </is>
-      </c>
-      <c r="B337" s="4" t="inlineStr">
-        <is>
-          <t>Venezuela, RB</t>
-        </is>
-      </c>
-      <c r="C337" s="4" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D337" s="4" t="inlineStr">
-        <is>
-          <t>VEN</t>
-        </is>
-      </c>
-      <c r="E337" s="4" t="inlineStr">
-        <is>
-          <t>Latin America &amp; Caribbean</t>
-        </is>
-      </c>
-      <c r="F337" s="4" t="inlineStr">
-        <is>
-          <t>Not classified</t>
-        </is>
-      </c>
-      <c r="G337" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="H337" s="4" t="inlineStr">
-        <is>
-          <t>Género</t>
-        </is>
-      </c>
-      <c r="I337" s="4" t="inlineStr">
-        <is>
-          <t>genero</t>
-        </is>
-      </c>
-      <c r="J337" s="4" t="inlineStr">
-        <is>
-          <t>Mercado laboral</t>
-        </is>
-      </c>
-      <c r="K337" s="4" t="inlineStr">
-        <is>
-          <t>mercado_laboral</t>
-        </is>
-      </c>
-      <c r="L337" s="4" t="inlineStr">
-        <is>
-          <t>SL.UEM.TOTL.FE.ZS</t>
-        </is>
-      </c>
-      <c r="M337" s="4" t="inlineStr">
-        <is>
-          <t>Desempleo femenino</t>
-        </is>
-      </c>
-      <c r="N337" s="8" t="n">
-        <v>5.835</v>
-      </c>
-      <c r="O337" s="4" t="inlineStr">
-        <is>
-          <t>Banco Mundial - World Development Indicators</t>
-        </is>
-      </c>
-      <c r="P337" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q337" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -26639,7 +26422,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Banco Mundial - Venezuela - Género</t>
+          <t>Banco Mundial - Género</t>
         </is>
       </c>
     </row>
@@ -26647,19 +26430,19 @@
     <row r="4" ht="16" customHeight="1"/>
     <row r="5" ht="8" customHeight="1"/>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Campo</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Organización</t>
         </is>
@@ -26671,7 +26454,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Dataset</t>
         </is>
@@ -26683,35 +26466,35 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Fecha generación</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>Número de indicadores</t>
         </is>
       </c>
-      <c r="B10" s="7" t="n">
+      <c r="B10" s="5" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>Número de registros</t>
         </is>
       </c>
-      <c r="B11" s="7" t="n">
-        <v>331</v>
+      <c r="B11" s="5" t="n">
+        <v>330</v>
       </c>
     </row>
   </sheetData>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_genero.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_genero.xlsx
@@ -517,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q336"/>
+  <dimension ref="A1:Q337"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -715,7 +715,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2745,7 +2745,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3217,7 +3217,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3685,7 +3685,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3764,7 +3764,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3843,7 +3843,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4159,7 +4159,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4238,7 +4238,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4317,7 +4317,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4554,7 +4554,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4633,7 +4633,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4712,7 +4712,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4791,7 +4791,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4870,7 +4870,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5107,7 +5107,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5186,7 +5186,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5263,7 +5263,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5417,7 +5417,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5571,7 +5571,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5725,7 +5725,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5879,7 +5879,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6033,7 +6033,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6110,7 +6110,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6264,7 +6264,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6495,7 +6495,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6572,7 +6572,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6649,7 +6649,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6728,7 +6728,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6807,7 +6807,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6886,7 +6886,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6965,7 +6965,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7044,7 +7044,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7121,7 +7121,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7275,7 +7275,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7352,7 +7352,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7429,7 +7429,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7506,7 +7506,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7583,7 +7583,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7739,7 +7739,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7818,7 +7818,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7897,7 +7897,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -7976,7 +7976,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8055,7 +8055,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8134,7 +8134,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8211,7 +8211,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8290,7 +8290,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8369,7 +8369,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8448,7 +8448,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8525,7 +8525,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8602,7 +8602,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8679,7 +8679,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8756,7 +8756,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8912,7 +8912,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -8991,7 +8991,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9070,7 +9070,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9149,7 +9149,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9228,7 +9228,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9307,7 +9307,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9386,7 +9386,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9465,7 +9465,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9544,7 +9544,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9623,7 +9623,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9702,7 +9702,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9781,7 +9781,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9860,7 +9860,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9939,7 +9939,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -10018,7 +10018,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10097,7 +10097,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10176,7 +10176,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10255,7 +10255,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10334,7 +10334,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10411,7 +10411,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10488,7 +10488,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10565,7 +10565,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10642,7 +10642,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10719,7 +10719,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10796,7 +10796,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10873,7 +10873,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -10950,7 +10950,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11027,7 +11027,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11104,7 +11104,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11181,7 +11181,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11258,7 +11258,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11335,7 +11335,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11412,7 +11412,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11489,7 +11489,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11566,7 +11566,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11643,7 +11643,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11720,7 +11720,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11797,7 +11797,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11874,7 +11874,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -11951,7 +11951,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12028,7 +12028,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12105,7 +12105,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12182,7 +12182,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12259,7 +12259,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12336,7 +12336,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12413,7 +12413,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12490,7 +12490,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12567,7 +12567,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12644,7 +12644,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12721,7 +12721,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12798,7 +12798,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12875,7 +12875,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -12952,7 +12952,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13029,7 +13029,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13106,7 +13106,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13183,7 +13183,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13260,7 +13260,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13337,7 +13337,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13414,7 +13414,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13491,7 +13491,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13568,7 +13568,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13645,7 +13645,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13722,7 +13722,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13799,7 +13799,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13878,7 +13878,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -13957,7 +13957,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14036,7 +14036,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14113,7 +14113,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14192,7 +14192,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14271,7 +14271,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14350,7 +14350,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14429,7 +14429,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14508,7 +14508,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14587,7 +14587,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14666,7 +14666,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14745,7 +14745,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14824,7 +14824,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -14982,7 +14982,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15061,7 +15061,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15140,7 +15140,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15219,7 +15219,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15298,7 +15298,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15377,7 +15377,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15456,7 +15456,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15535,7 +15535,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15614,7 +15614,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15693,7 +15693,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15772,7 +15772,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15849,7 +15849,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15926,7 +15926,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16003,7 +16003,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16082,7 +16082,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16159,7 +16159,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16236,7 +16236,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16313,7 +16313,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16390,7 +16390,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16467,7 +16467,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16544,7 +16544,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16621,7 +16621,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16698,7 +16698,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16775,7 +16775,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16852,7 +16852,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16929,7 +16929,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17006,7 +17006,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17083,7 +17083,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17160,7 +17160,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17237,7 +17237,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17314,7 +17314,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17391,7 +17391,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17468,7 +17468,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17545,7 +17545,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17622,7 +17622,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17699,7 +17699,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17776,7 +17776,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17853,7 +17853,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17930,7 +17930,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18007,7 +18007,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18084,7 +18084,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18161,7 +18161,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18238,7 +18238,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18315,7 +18315,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18392,7 +18392,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18471,7 +18471,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18550,7 +18550,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18629,7 +18629,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18708,7 +18708,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18787,7 +18787,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18866,7 +18866,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18945,7 +18945,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19024,7 +19024,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19103,7 +19103,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19182,7 +19182,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19261,7 +19261,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19340,7 +19340,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19419,7 +19419,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19498,7 +19498,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19577,7 +19577,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19656,7 +19656,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19735,7 +19735,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19893,7 +19893,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -19972,7 +19972,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20051,7 +20051,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20130,7 +20130,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20209,7 +20209,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20288,7 +20288,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20367,7 +20367,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20446,7 +20446,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20525,7 +20525,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20604,7 +20604,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20683,7 +20683,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20762,7 +20762,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20841,7 +20841,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20920,7 +20920,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -20999,7 +20999,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21078,7 +21078,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21157,7 +21157,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21236,7 +21236,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21313,10 +21313,14 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q271" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q271" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="4" t="inlineStr">
@@ -21390,10 +21394,14 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q272" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q272" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="4" t="inlineStr">
@@ -21467,10 +21475,14 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q273" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q273" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="4" t="inlineStr">
@@ -21544,10 +21556,14 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q274" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q274" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="4" t="inlineStr">
@@ -21621,10 +21637,14 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q275" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q275" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="4" t="inlineStr">
@@ -21698,10 +21718,14 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q276" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q276" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="4" t="inlineStr">
@@ -21775,10 +21799,14 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q277" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q277" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="4" t="inlineStr">
@@ -21852,10 +21880,14 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q278" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q278" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="4" t="inlineStr">
@@ -21929,10 +21961,14 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q279" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q279" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="4" t="inlineStr">
@@ -22006,10 +22042,14 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q280" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q280" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="4" t="inlineStr">
@@ -22083,10 +22123,14 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q281" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q281" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="4" t="inlineStr">
@@ -22160,10 +22204,14 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q282" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q282" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="4" t="inlineStr">
@@ -22237,10 +22285,14 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q283" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q283" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="4" t="inlineStr">
@@ -22314,10 +22366,14 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q284" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q284" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="4" t="inlineStr">
@@ -22391,10 +22447,14 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q285" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q285" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="4" t="inlineStr">
@@ -22468,10 +22528,14 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q286" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q286" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="4" t="inlineStr">
@@ -22545,10 +22609,14 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q287" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q287" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="4" t="inlineStr">
@@ -22622,10 +22690,14 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q288" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q288" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="4" t="inlineStr">
@@ -22699,10 +22771,14 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q289" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q289" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="4" t="inlineStr">
@@ -22776,10 +22852,14 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q290" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q290" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="4" t="inlineStr">
@@ -22853,10 +22933,14 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q291" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q291" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="4" t="inlineStr">
@@ -22930,10 +23014,14 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q292" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q292" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="4" t="inlineStr">
@@ -23007,10 +23095,14 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q293" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q293" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="4" t="inlineStr">
@@ -23084,10 +23176,14 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q294" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q294" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="4" t="inlineStr">
@@ -23161,10 +23257,14 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q295" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q295" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="4" t="inlineStr">
@@ -23238,10 +23338,14 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q296" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q296" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="4" t="inlineStr">
@@ -23315,10 +23419,14 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q297" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q297" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="4" t="inlineStr">
@@ -23392,10 +23500,14 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q298" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q298" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="4" t="inlineStr">
@@ -23469,10 +23581,14 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q299" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q299" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="4" t="inlineStr">
@@ -23546,10 +23662,14 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q300" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q300" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="4" t="inlineStr">
@@ -23623,10 +23743,14 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q301" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q301" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" s="4" t="inlineStr">
@@ -23692,9 +23816,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N302" s="6" t="n">
-        <v>9.32</v>
-      </c>
+      <c r="N302" s="4" t="n"/>
       <c r="O302" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -23702,10 +23824,14 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q302" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q302" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" s="4" t="inlineStr">
@@ -23771,9 +23897,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N303" s="6" t="n">
-        <v>6.925</v>
-      </c>
+      <c r="N303" s="4" t="n"/>
       <c r="O303" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -23781,10 +23905,14 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q303" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q303" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="4" t="inlineStr">
@@ -23850,9 +23978,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N304" s="6" t="n">
-        <v>5.679</v>
-      </c>
+      <c r="N304" s="4" t="n"/>
       <c r="O304" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -23860,10 +23986,14 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q304" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q304" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" s="4" t="inlineStr">
@@ -23929,9 +24059,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N305" s="6" t="n">
-        <v>9.557</v>
-      </c>
+      <c r="N305" s="4" t="n"/>
       <c r="O305" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -23939,10 +24067,14 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q305" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q305" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="4" t="inlineStr">
@@ -24008,9 +24140,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N306" s="6" t="n">
-        <v>12.604</v>
-      </c>
+      <c r="N306" s="4" t="n"/>
       <c r="O306" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24018,10 +24148,14 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q306" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q306" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="4" t="inlineStr">
@@ -24087,9 +24221,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N307" s="6" t="n">
-        <v>14.345</v>
-      </c>
+      <c r="N307" s="4" t="n"/>
       <c r="O307" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24097,10 +24229,14 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q307" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q307" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="4" t="inlineStr">
@@ -24166,9 +24302,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N308" s="6" t="n">
-        <v>13.627</v>
-      </c>
+      <c r="N308" s="4" t="n"/>
       <c r="O308" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24176,10 +24310,14 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q308" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q308" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" s="4" t="inlineStr">
@@ -24245,9 +24383,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N309" s="6" t="n">
-        <v>13.306</v>
-      </c>
+      <c r="N309" s="4" t="n"/>
       <c r="O309" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24255,10 +24391,14 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q309" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q309" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" s="4" t="inlineStr">
@@ -24324,9 +24464,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N310" s="6" t="n">
-        <v>16.482</v>
-      </c>
+      <c r="N310" s="4" t="n"/>
       <c r="O310" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24334,10 +24472,14 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q310" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q310" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" s="4" t="inlineStr">
@@ -24403,9 +24545,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N311" s="6" t="n">
-        <v>14.605</v>
-      </c>
+      <c r="N311" s="4" t="n"/>
       <c r="O311" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24413,10 +24553,14 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q311" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q311" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" s="4" t="inlineStr">
@@ -24482,9 +24626,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N312" s="6" t="n">
-        <v>14.109</v>
-      </c>
+      <c r="N312" s="4" t="n"/>
       <c r="O312" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24492,10 +24634,14 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q312" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q312" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" s="4" t="inlineStr">
@@ -24561,9 +24707,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N313" s="6" t="n">
-        <v>18.895</v>
-      </c>
+      <c r="N313" s="4" t="n"/>
       <c r="O313" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24571,10 +24715,14 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q313" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q313" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" s="4" t="inlineStr">
@@ -24640,9 +24788,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N314" s="6" t="n">
-        <v>20.483</v>
-      </c>
+      <c r="N314" s="4" t="n"/>
       <c r="O314" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24650,10 +24796,14 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q314" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q314" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" s="4" t="inlineStr">
@@ -24719,9 +24869,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N315" s="6" t="n">
-        <v>17.974</v>
-      </c>
+      <c r="N315" s="4" t="n"/>
       <c r="O315" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24729,10 +24877,14 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q315" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q315" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" s="4" t="inlineStr">
@@ -24798,9 +24950,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N316" s="6" t="n">
-        <v>11.64</v>
-      </c>
+      <c r="N316" s="4" t="n"/>
       <c r="O316" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24808,10 +24958,14 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q316" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q316" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" s="4" t="inlineStr">
@@ -24877,9 +25031,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N317" s="6" t="n">
-        <v>9.380000000000001</v>
-      </c>
+      <c r="N317" s="4" t="n"/>
       <c r="O317" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24887,10 +25039,14 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q317" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q317" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" s="4" t="inlineStr">
@@ -24956,9 +25112,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N318" s="6" t="n">
-        <v>7.643</v>
-      </c>
+      <c r="N318" s="4" t="n"/>
       <c r="O318" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24966,10 +25120,14 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q318" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q318" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" s="4" t="inlineStr">
@@ -25035,9 +25193,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N319" s="6" t="n">
-        <v>6.218</v>
-      </c>
+      <c r="N319" s="4" t="n"/>
       <c r="O319" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25045,10 +25201,14 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q319" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q319" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" s="4" t="inlineStr">
@@ -25114,9 +25274,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N320" s="6" t="n">
-        <v>5.965</v>
-      </c>
+      <c r="N320" s="4" t="n"/>
       <c r="O320" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25124,10 +25282,14 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q320" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q320" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" s="4" t="inlineStr">
@@ -25193,9 +25355,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N321" s="6" t="n">
-        <v>6.952</v>
-      </c>
+      <c r="N321" s="4" t="n"/>
       <c r="O321" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25203,10 +25363,14 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q321" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q321" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" s="4" t="inlineStr">
@@ -25272,9 +25436,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N322" s="6" t="n">
-        <v>7.206</v>
-      </c>
+      <c r="N322" s="4" t="n"/>
       <c r="O322" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25282,10 +25444,14 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q322" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q322" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" s="4" t="inlineStr">
@@ -25351,9 +25517,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N323" s="6" t="n">
-        <v>7.109</v>
-      </c>
+      <c r="N323" s="4" t="n"/>
       <c r="O323" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25361,10 +25525,14 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q323" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q323" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" s="4" t="inlineStr">
@@ -25430,9 +25598,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N324" s="6" t="n">
-        <v>8.605</v>
-      </c>
+      <c r="N324" s="4" t="n"/>
       <c r="O324" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25440,10 +25606,14 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q324" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q324" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" s="4" t="inlineStr">
@@ -25509,9 +25679,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N325" s="6" t="n">
-        <v>7.578</v>
-      </c>
+      <c r="N325" s="4" t="n"/>
       <c r="O325" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25519,10 +25687,14 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q325" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q325" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" s="4" t="inlineStr">
@@ -25588,9 +25760,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N326" s="6" t="n">
-        <v>6.572</v>
-      </c>
+      <c r="N326" s="4" t="n"/>
       <c r="O326" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25598,10 +25768,14 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q326" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q326" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" s="4" t="inlineStr">
@@ -25667,9 +25841,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N327" s="6" t="n">
-        <v>5.413</v>
-      </c>
+      <c r="N327" s="4" t="n"/>
       <c r="O327" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25677,10 +25849,14 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q327" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q327" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" s="4" t="inlineStr">
@@ -25746,9 +25922,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N328" s="6" t="n">
-        <v>5.858</v>
-      </c>
+      <c r="N328" s="4" t="n"/>
       <c r="O328" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25756,10 +25930,14 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q328" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q328" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" s="4" t="inlineStr">
@@ -25825,9 +26003,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N329" s="6" t="n">
-        <v>6.178</v>
-      </c>
+      <c r="N329" s="4" t="n"/>
       <c r="O329" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25835,10 +26011,14 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q329" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q329" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" s="4" t="inlineStr">
@@ -25904,9 +26084,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N330" s="6" t="n">
-        <v>6.497</v>
-      </c>
+      <c r="N330" s="4" t="n"/>
       <c r="O330" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25914,10 +26092,14 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q330" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q330" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" s="4" t="inlineStr">
@@ -25983,9 +26165,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N331" s="6" t="n">
-        <v>7.907</v>
-      </c>
+      <c r="N331" s="4" t="n"/>
       <c r="O331" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25993,10 +26173,14 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q331" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q331" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" s="4" t="inlineStr">
@@ -26062,9 +26246,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N332" s="6" t="n">
-        <v>7.541</v>
-      </c>
+      <c r="N332" s="4" t="n"/>
       <c r="O332" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -26072,10 +26254,14 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q332" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q332" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" s="4" t="inlineStr">
@@ -26141,9 +26327,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N333" s="6" t="n">
-        <v>6.179</v>
-      </c>
+      <c r="N333" s="4" t="n"/>
       <c r="O333" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -26151,10 +26335,14 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q333" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q333" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" s="4" t="inlineStr">
@@ -26220,9 +26408,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N334" s="6" t="n">
-        <v>5.937</v>
-      </c>
+      <c r="N334" s="4" t="n"/>
       <c r="O334" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -26230,10 +26416,14 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q334" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q334" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" s="4" t="inlineStr">
@@ -26299,9 +26489,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N335" s="6" t="n">
-        <v>5.845</v>
-      </c>
+      <c r="N335" s="4" t="n"/>
       <c r="O335" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -26309,10 +26497,14 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q335" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q335" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" s="4" t="inlineStr">
@@ -26378,9 +26570,7 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N336" s="6" t="n">
-        <v>5.835</v>
-      </c>
+      <c r="N336" s="4" t="n"/>
       <c r="O336" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -26388,10 +26578,95 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q336" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q336" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="4" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="B337" s="4" t="inlineStr">
+        <is>
+          <t>Venezuela, RB</t>
+        </is>
+      </c>
+      <c r="C337" s="4" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="D337" s="4" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="E337" s="4" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="F337" s="4" t="inlineStr">
+        <is>
+          <t>Not classified</t>
+        </is>
+      </c>
+      <c r="G337" s="5" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H337" s="4" t="inlineStr">
+        <is>
+          <t>Género</t>
+        </is>
+      </c>
+      <c r="I337" s="4" t="inlineStr">
+        <is>
+          <t>genero</t>
+        </is>
+      </c>
+      <c r="J337" s="4" t="inlineStr">
+        <is>
+          <t>Mercado laboral</t>
+        </is>
+      </c>
+      <c r="K337" s="4" t="inlineStr">
+        <is>
+          <t>mercado_laboral</t>
+        </is>
+      </c>
+      <c r="L337" s="4" t="inlineStr">
+        <is>
+          <t>SL.UEM.TOTL.FE.ZS</t>
+        </is>
+      </c>
+      <c r="M337" s="4" t="inlineStr">
+        <is>
+          <t>Desempleo femenino</t>
+        </is>
+      </c>
+      <c r="N337" s="4" t="n"/>
+      <c r="O337" s="4" t="inlineStr">
+        <is>
+          <t>Banco Mundial - World Development Indicators</t>
+        </is>
+      </c>
+      <c r="P337" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q337" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -26473,7 +26748,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
@@ -26494,7 +26769,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
   </sheetData>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_genero.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_genero.xlsx
@@ -715,7 +715,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2745,7 +2745,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3217,7 +3217,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3685,7 +3685,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3764,7 +3764,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3843,7 +3843,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4159,7 +4159,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4238,7 +4238,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4317,7 +4317,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4554,7 +4554,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4633,7 +4633,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4712,7 +4712,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4791,7 +4791,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4870,7 +4870,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5107,7 +5107,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5186,7 +5186,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5263,7 +5263,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5417,7 +5417,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5571,7 +5571,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5725,7 +5725,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5879,10 +5879,14 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q73" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q73" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
@@ -5956,10 +5960,14 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q74" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q74" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
@@ -6033,10 +6041,14 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q75" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q75" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
@@ -6110,10 +6122,14 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q76" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q76" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
@@ -6187,10 +6203,14 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q77" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q77" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
@@ -6264,10 +6284,14 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q78" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q78" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
@@ -6341,10 +6365,14 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q79" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q79" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
@@ -6418,10 +6446,14 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q80" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q80" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
@@ -6495,10 +6527,14 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q81" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q81" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
@@ -6572,10 +6608,14 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q82" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q82" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
@@ -6649,10 +6689,14 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q83" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q83" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
@@ -6718,9 +6762,7 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N84" s="6" t="n">
-        <v>1.06591999530792</v>
-      </c>
+      <c r="N84" s="4" t="n"/>
       <c r="O84" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -6728,10 +6770,14 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q84" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q84" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
@@ -6797,9 +6843,7 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N85" s="6" t="n">
-        <v>1.07165002822876</v>
-      </c>
+      <c r="N85" s="4" t="n"/>
       <c r="O85" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -6807,10 +6851,14 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q85" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q85" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
@@ -6876,9 +6924,7 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N86" s="6" t="n">
-        <v>1.09589004516602</v>
-      </c>
+      <c r="N86" s="4" t="n"/>
       <c r="O86" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -6886,10 +6932,14 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q86" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q86" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
@@ -6955,9 +7005,7 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N87" s="6" t="n">
-        <v>1.13256001472473</v>
-      </c>
+      <c r="N87" s="4" t="n"/>
       <c r="O87" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -6965,10 +7013,14 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q87" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q87" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
@@ -7034,9 +7086,7 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N88" s="6" t="n">
-        <v>1.13680994510651</v>
-      </c>
+      <c r="N88" s="4" t="n"/>
       <c r="O88" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -7044,10 +7094,14 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q88" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q88" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
@@ -7121,10 +7175,14 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q89" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q89" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
@@ -7198,10 +7256,14 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q90" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q90" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
@@ -7275,10 +7337,14 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q91" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q91" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
@@ -7352,10 +7418,14 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q92" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q92" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
@@ -7429,10 +7499,14 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q93" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q93" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
@@ -7506,10 +7580,14 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q94" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q94" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
@@ -7583,10 +7661,14 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q95" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q95" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
@@ -7660,10 +7742,14 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q96" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q96" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
@@ -7729,9 +7815,7 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N97" s="6" t="n">
-        <v>1.24408996105194</v>
-      </c>
+      <c r="N97" s="4" t="n"/>
       <c r="O97" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -7739,10 +7823,14 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q97" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q97" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
@@ -7808,9 +7896,7 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N98" s="6" t="n">
-        <v>1.25617003440857</v>
-      </c>
+      <c r="N98" s="4" t="n"/>
       <c r="O98" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -7818,10 +7904,14 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q98" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q98" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
@@ -7887,9 +7977,7 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N99" s="6" t="n">
-        <v>1.23227000236511</v>
-      </c>
+      <c r="N99" s="4" t="n"/>
       <c r="O99" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -7897,10 +7985,14 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q99" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q99" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
@@ -7966,9 +8058,7 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N100" s="6" t="n">
-        <v>1.23520004749298</v>
-      </c>
+      <c r="N100" s="4" t="n"/>
       <c r="O100" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -7976,10 +8066,14 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q100" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q100" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
@@ -8045,9 +8139,7 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N101" s="6" t="n">
-        <v>1.23055994510651</v>
-      </c>
+      <c r="N101" s="4" t="n"/>
       <c r="O101" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8055,10 +8147,14 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q101" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q101" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
@@ -8124,9 +8220,7 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N102" s="6" t="n">
-        <v>1.23713004589081</v>
-      </c>
+      <c r="N102" s="4" t="n"/>
       <c r="O102" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8134,10 +8228,14 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q102" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q102" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
@@ -8211,10 +8309,14 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q103" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q103" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
@@ -8280,9 +8382,7 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N104" s="6" t="n">
-        <v>1.24015998840332</v>
-      </c>
+      <c r="N104" s="4" t="n"/>
       <c r="O104" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8290,10 +8390,14 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q104" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q104" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
@@ -8359,9 +8463,7 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N105" s="6" t="n">
-        <v>1.2406200170517</v>
-      </c>
+      <c r="N105" s="4" t="n"/>
       <c r="O105" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8369,10 +8471,14 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q105" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q105" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
@@ -8438,9 +8544,7 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N106" s="6" t="n">
-        <v>1.24875998497009</v>
-      </c>
+      <c r="N106" s="4" t="n"/>
       <c r="O106" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8448,10 +8552,14 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q106" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q106" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
@@ -8525,10 +8633,14 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q107" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q107" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
@@ -8602,10 +8714,14 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q108" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q108" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
@@ -8679,10 +8795,14 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q109" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q109" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
@@ -8756,10 +8876,14 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q110" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q110" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
@@ -8833,10 +8957,14 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q111" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q111" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
@@ -8902,9 +9030,7 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N112" s="6" t="n">
-        <v>1.22622001171112</v>
-      </c>
+      <c r="N112" s="4" t="n"/>
       <c r="O112" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8912,10 +9038,14 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q112" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q112" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
@@ -8981,9 +9111,7 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N113" s="6" t="n">
-        <v>1.19964003562927</v>
-      </c>
+      <c r="N113" s="4" t="n"/>
       <c r="O113" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8991,10 +9119,14 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q113" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q113" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
@@ -9060,9 +9192,7 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N114" s="6" t="n">
-        <v>1.17510998249054</v>
-      </c>
+      <c r="N114" s="4" t="n"/>
       <c r="O114" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9070,10 +9200,14 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q114" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q114" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
@@ -9139,9 +9273,7 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N115" s="6" t="n">
-        <v>1.16194999217987</v>
-      </c>
+      <c r="N115" s="4" t="n"/>
       <c r="O115" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9149,10 +9281,14 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q115" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q115" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
@@ -9218,9 +9354,7 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N116" s="6" t="n">
-        <v>1.15086996555328</v>
-      </c>
+      <c r="N116" s="4" t="n"/>
       <c r="O116" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9228,10 +9362,14 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q116" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q116" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
@@ -9297,9 +9435,7 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N117" s="6" t="n">
-        <v>1.13995003700256</v>
-      </c>
+      <c r="N117" s="4" t="n"/>
       <c r="O117" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9307,10 +9443,14 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q117" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q117" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
@@ -9376,9 +9516,7 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N118" s="6" t="n">
-        <v>1.13028001785278</v>
-      </c>
+      <c r="N118" s="4" t="n"/>
       <c r="O118" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9386,10 +9524,14 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q118" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q118" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
@@ -9455,9 +9597,7 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N119" s="6" t="n">
-        <v>1.12556004524231</v>
-      </c>
+      <c r="N119" s="4" t="n"/>
       <c r="O119" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9465,10 +9605,14 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q119" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q119" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
@@ -9534,9 +9678,7 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N120" s="6" t="n">
-        <v>1.11647999286652</v>
-      </c>
+      <c r="N120" s="4" t="n"/>
       <c r="O120" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9544,10 +9686,14 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q120" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q120" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
@@ -9613,9 +9759,7 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N121" s="6" t="n">
-        <v>1.10140001773834</v>
-      </c>
+      <c r="N121" s="4" t="n"/>
       <c r="O121" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9623,10 +9767,14 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q121" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q121" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
@@ -9692,9 +9840,7 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N122" s="6" t="n">
-        <v>1.09311997890472</v>
-      </c>
+      <c r="N122" s="4" t="n"/>
       <c r="O122" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9702,10 +9848,14 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q122" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q122" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
@@ -9771,9 +9921,7 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N123" s="6" t="n">
-        <v>1.09621000289917</v>
-      </c>
+      <c r="N123" s="4" t="n"/>
       <c r="O123" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9781,10 +9929,14 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q123" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q123" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
@@ -9850,9 +10002,7 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N124" s="6" t="n">
-        <v>1.09371995925903</v>
-      </c>
+      <c r="N124" s="4" t="n"/>
       <c r="O124" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9860,10 +10010,14 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q124" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q124" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
@@ -9929,9 +10083,7 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N125" s="6" t="n">
-        <v>1.09325003623962</v>
-      </c>
+      <c r="N125" s="4" t="n"/>
       <c r="O125" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9939,10 +10091,14 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q125" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q125" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
@@ -10008,9 +10164,7 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N126" s="6" t="n">
-        <v>1.09049999713898</v>
-      </c>
+      <c r="N126" s="4" t="n"/>
       <c r="O126" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -10018,10 +10172,14 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q126" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q126" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
@@ -10087,9 +10245,7 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N127" s="6" t="n">
-        <v>1.07729995250702</v>
-      </c>
+      <c r="N127" s="4" t="n"/>
       <c r="O127" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -10097,10 +10253,14 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q127" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q127" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
@@ -10166,9 +10326,7 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N128" s="6" t="n">
-        <v>1.07729005813599</v>
-      </c>
+      <c r="N128" s="4" t="n"/>
       <c r="O128" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -10176,10 +10334,14 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q128" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q128" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
@@ -10245,9 +10407,7 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N129" s="6" t="n">
-        <v>1.07924997806549</v>
-      </c>
+      <c r="N129" s="4" t="n"/>
       <c r="O129" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -10255,10 +10415,14 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q129" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q129" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
@@ -10324,9 +10488,7 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N130" s="6" t="n">
-        <v>1.0806200504303</v>
-      </c>
+      <c r="N130" s="4" t="n"/>
       <c r="O130" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -10334,10 +10496,14 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q130" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q130" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
@@ -10411,10 +10577,14 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q131" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q131" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
@@ -10488,10 +10658,14 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q132" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q132" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
@@ -10565,10 +10739,14 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q133" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q133" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
@@ -10642,10 +10820,14 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q134" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q134" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
@@ -10719,10 +10901,14 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q135" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q135" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
@@ -10796,10 +10982,14 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q136" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q136" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
@@ -10873,10 +11063,14 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q137" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q137" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
@@ -10950,10 +11144,14 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q138" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q138" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
@@ -10987,7 +11185,7 @@
         </is>
       </c>
       <c r="G139" s="5" t="n">
-        <v>1960</v>
+        <v>2026</v>
       </c>
       <c r="H139" s="4" t="inlineStr">
         <is>
@@ -11001,22 +11199,22 @@
       </c>
       <c r="J139" s="4" t="inlineStr">
         <is>
-          <t>Participación política</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>participacion_politica</t>
+          <t>educacion</t>
         </is>
       </c>
       <c r="L139" s="4" t="inlineStr">
         <is>
-          <t>SG.GEN.PARL.ZS</t>
+          <t>SE.ENR.SECO.FM.ZS</t>
         </is>
       </c>
       <c r="M139" s="4" t="inlineStr">
         <is>
-          <t>Mujeres en parlamentos nacionales</t>
+          <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
       <c r="N139" s="4" t="n"/>
@@ -11027,10 +11225,14 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q139" s="4" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q139" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
@@ -11064,7 +11266,7 @@
         </is>
       </c>
       <c r="G140" s="5" t="n">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="H140" s="4" t="inlineStr">
         <is>
@@ -11104,7 +11306,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11141,7 +11343,7 @@
         </is>
       </c>
       <c r="G141" s="5" t="n">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="H141" s="4" t="inlineStr">
         <is>
@@ -11181,7 +11383,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11218,7 +11420,7 @@
         </is>
       </c>
       <c r="G142" s="5" t="n">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="H142" s="4" t="inlineStr">
         <is>
@@ -11258,7 +11460,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11295,7 +11497,7 @@
         </is>
       </c>
       <c r="G143" s="5" t="n">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="H143" s="4" t="inlineStr">
         <is>
@@ -11335,7 +11537,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11372,7 +11574,7 @@
         </is>
       </c>
       <c r="G144" s="5" t="n">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="H144" s="4" t="inlineStr">
         <is>
@@ -11412,7 +11614,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11449,7 +11651,7 @@
         </is>
       </c>
       <c r="G145" s="5" t="n">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="H145" s="4" t="inlineStr">
         <is>
@@ -11489,7 +11691,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11526,7 +11728,7 @@
         </is>
       </c>
       <c r="G146" s="5" t="n">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="H146" s="4" t="inlineStr">
         <is>
@@ -11566,7 +11768,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11603,7 +11805,7 @@
         </is>
       </c>
       <c r="G147" s="5" t="n">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="H147" s="4" t="inlineStr">
         <is>
@@ -11643,7 +11845,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11680,7 +11882,7 @@
         </is>
       </c>
       <c r="G148" s="5" t="n">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="H148" s="4" t="inlineStr">
         <is>
@@ -11720,7 +11922,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11757,7 +11959,7 @@
         </is>
       </c>
       <c r="G149" s="5" t="n">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="H149" s="4" t="inlineStr">
         <is>
@@ -11797,7 +11999,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11834,7 +12036,7 @@
         </is>
       </c>
       <c r="G150" s="5" t="n">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="H150" s="4" t="inlineStr">
         <is>
@@ -11874,7 +12076,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -11911,7 +12113,7 @@
         </is>
       </c>
       <c r="G151" s="5" t="n">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="H151" s="4" t="inlineStr">
         <is>
@@ -11951,7 +12153,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -11988,7 +12190,7 @@
         </is>
       </c>
       <c r="G152" s="5" t="n">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="H152" s="4" t="inlineStr">
         <is>
@@ -12028,7 +12230,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12065,7 +12267,7 @@
         </is>
       </c>
       <c r="G153" s="5" t="n">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="H153" s="4" t="inlineStr">
         <is>
@@ -12105,7 +12307,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12142,7 +12344,7 @@
         </is>
       </c>
       <c r="G154" s="5" t="n">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="H154" s="4" t="inlineStr">
         <is>
@@ -12182,7 +12384,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12219,7 +12421,7 @@
         </is>
       </c>
       <c r="G155" s="5" t="n">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="H155" s="4" t="inlineStr">
         <is>
@@ -12259,7 +12461,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12296,7 +12498,7 @@
         </is>
       </c>
       <c r="G156" s="5" t="n">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="H156" s="4" t="inlineStr">
         <is>
@@ -12336,7 +12538,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12373,7 +12575,7 @@
         </is>
       </c>
       <c r="G157" s="5" t="n">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="H157" s="4" t="inlineStr">
         <is>
@@ -12413,7 +12615,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12450,7 +12652,7 @@
         </is>
       </c>
       <c r="G158" s="5" t="n">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="H158" s="4" t="inlineStr">
         <is>
@@ -12490,7 +12692,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12527,7 +12729,7 @@
         </is>
       </c>
       <c r="G159" s="5" t="n">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="H159" s="4" t="inlineStr">
         <is>
@@ -12567,7 +12769,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12604,7 +12806,7 @@
         </is>
       </c>
       <c r="G160" s="5" t="n">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="H160" s="4" t="inlineStr">
         <is>
@@ -12644,7 +12846,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12681,7 +12883,7 @@
         </is>
       </c>
       <c r="G161" s="5" t="n">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="H161" s="4" t="inlineStr">
         <is>
@@ -12721,7 +12923,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12758,7 +12960,7 @@
         </is>
       </c>
       <c r="G162" s="5" t="n">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="H162" s="4" t="inlineStr">
         <is>
@@ -12798,7 +13000,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12835,7 +13037,7 @@
         </is>
       </c>
       <c r="G163" s="5" t="n">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="H163" s="4" t="inlineStr">
         <is>
@@ -12875,7 +13077,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -12912,7 +13114,7 @@
         </is>
       </c>
       <c r="G164" s="5" t="n">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="H164" s="4" t="inlineStr">
         <is>
@@ -12952,7 +13154,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -12989,7 +13191,7 @@
         </is>
       </c>
       <c r="G165" s="5" t="n">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="H165" s="4" t="inlineStr">
         <is>
@@ -13029,7 +13231,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13066,7 +13268,7 @@
         </is>
       </c>
       <c r="G166" s="5" t="n">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="H166" s="4" t="inlineStr">
         <is>
@@ -13106,7 +13308,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13143,7 +13345,7 @@
         </is>
       </c>
       <c r="G167" s="5" t="n">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="H167" s="4" t="inlineStr">
         <is>
@@ -13183,7 +13385,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13220,7 +13422,7 @@
         </is>
       </c>
       <c r="G168" s="5" t="n">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="H168" s="4" t="inlineStr">
         <is>
@@ -13260,7 +13462,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13297,7 +13499,7 @@
         </is>
       </c>
       <c r="G169" s="5" t="n">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="H169" s="4" t="inlineStr">
         <is>
@@ -13337,7 +13539,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13374,7 +13576,7 @@
         </is>
       </c>
       <c r="G170" s="5" t="n">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="H170" s="4" t="inlineStr">
         <is>
@@ -13414,7 +13616,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13451,7 +13653,7 @@
         </is>
       </c>
       <c r="G171" s="5" t="n">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="H171" s="4" t="inlineStr">
         <is>
@@ -13491,7 +13693,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13528,7 +13730,7 @@
         </is>
       </c>
       <c r="G172" s="5" t="n">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="H172" s="4" t="inlineStr">
         <is>
@@ -13568,7 +13770,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13605,7 +13807,7 @@
         </is>
       </c>
       <c r="G173" s="5" t="n">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="H173" s="4" t="inlineStr">
         <is>
@@ -13645,7 +13847,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13682,7 +13884,7 @@
         </is>
       </c>
       <c r="G174" s="5" t="n">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="H174" s="4" t="inlineStr">
         <is>
@@ -13722,7 +13924,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13759,7 +13961,7 @@
         </is>
       </c>
       <c r="G175" s="5" t="n">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="H175" s="4" t="inlineStr">
         <is>
@@ -13799,7 +14001,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13836,7 +14038,7 @@
         </is>
       </c>
       <c r="G176" s="5" t="n">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="H176" s="4" t="inlineStr">
         <is>
@@ -13868,9 +14070,7 @@
           <t>Mujeres en parlamentos nacionales</t>
         </is>
       </c>
-      <c r="N176" s="6" t="n">
-        <v>5.91133004926108</v>
-      </c>
+      <c r="N176" s="4" t="n"/>
       <c r="O176" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -13878,7 +14078,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -13915,7 +14115,7 @@
         </is>
       </c>
       <c r="G177" s="5" t="n">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="H177" s="4" t="inlineStr">
         <is>
@@ -13957,7 +14157,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -13994,7 +14194,7 @@
         </is>
       </c>
       <c r="G178" s="5" t="n">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="H178" s="4" t="inlineStr">
         <is>
@@ -14027,7 +14227,7 @@
         </is>
       </c>
       <c r="N178" s="6" t="n">
-        <v>12.1359223300971</v>
+        <v>5.91133004926108</v>
       </c>
       <c r="O178" s="4" t="inlineStr">
         <is>
@@ -14036,7 +14236,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14073,7 +14273,7 @@
         </is>
       </c>
       <c r="G179" s="5" t="n">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="H179" s="4" t="inlineStr">
         <is>
@@ -14105,7 +14305,9 @@
           <t>Mujeres en parlamentos nacionales</t>
         </is>
       </c>
-      <c r="N179" s="4" t="n"/>
+      <c r="N179" s="6" t="n">
+        <v>12.1359223300971</v>
+      </c>
       <c r="O179" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -14113,7 +14315,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14150,7 +14352,7 @@
         </is>
       </c>
       <c r="G180" s="5" t="n">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="H180" s="4" t="inlineStr">
         <is>
@@ -14182,9 +14384,7 @@
           <t>Mujeres en parlamentos nacionales</t>
         </is>
       </c>
-      <c r="N180" s="6" t="n">
-        <v>9.696969696969701</v>
-      </c>
+      <c r="N180" s="4" t="n"/>
       <c r="O180" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -14192,7 +14392,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14229,7 +14429,7 @@
         </is>
       </c>
       <c r="G181" s="5" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="H181" s="4" t="inlineStr">
         <is>
@@ -14271,7 +14471,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14308,7 +14508,7 @@
         </is>
       </c>
       <c r="G182" s="5" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="H182" s="4" t="inlineStr">
         <is>
@@ -14350,7 +14550,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14387,7 +14587,7 @@
         </is>
       </c>
       <c r="G183" s="5" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="H183" s="4" t="inlineStr">
         <is>
@@ -14429,7 +14629,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14466,7 +14666,7 @@
         </is>
       </c>
       <c r="G184" s="5" t="n">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="H184" s="4" t="inlineStr">
         <is>
@@ -14499,7 +14699,7 @@
         </is>
       </c>
       <c r="N184" s="6" t="n">
-        <v>17.3652694610778</v>
+        <v>9.696969696969701</v>
       </c>
       <c r="O184" s="4" t="inlineStr">
         <is>
@@ -14508,7 +14708,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14545,7 +14745,7 @@
         </is>
       </c>
       <c r="G185" s="5" t="n">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="H185" s="4" t="inlineStr">
         <is>
@@ -14578,7 +14778,7 @@
         </is>
       </c>
       <c r="N185" s="6" t="n">
-        <v>17.9640718562874</v>
+        <v>17.3652694610778</v>
       </c>
       <c r="O185" s="4" t="inlineStr">
         <is>
@@ -14587,7 +14787,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14624,7 +14824,7 @@
         </is>
       </c>
       <c r="G186" s="5" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="H186" s="4" t="inlineStr">
         <is>
@@ -14657,7 +14857,7 @@
         </is>
       </c>
       <c r="N186" s="6" t="n">
-        <v>18.562874251497</v>
+        <v>17.9640718562874</v>
       </c>
       <c r="O186" s="4" t="inlineStr">
         <is>
@@ -14666,7 +14866,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14703,7 +14903,7 @@
         </is>
       </c>
       <c r="G187" s="5" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="H187" s="4" t="inlineStr">
         <is>
@@ -14745,7 +14945,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14782,7 +14982,7 @@
         </is>
       </c>
       <c r="G188" s="5" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="H188" s="4" t="inlineStr">
         <is>
@@ -14815,7 +15015,7 @@
         </is>
       </c>
       <c r="N188" s="6" t="n">
-        <v>17.4698795180723</v>
+        <v>18.562874251497</v>
       </c>
       <c r="O188" s="4" t="inlineStr">
         <is>
@@ -14824,7 +15024,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14861,7 +15061,7 @@
         </is>
       </c>
       <c r="G189" s="5" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="H189" s="4" t="inlineStr">
         <is>
@@ -14894,7 +15094,7 @@
         </is>
       </c>
       <c r="N189" s="6" t="n">
-        <v>16.969696969697</v>
+        <v>17.4698795180723</v>
       </c>
       <c r="O189" s="4" t="inlineStr">
         <is>
@@ -14903,7 +15103,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -14940,7 +15140,7 @@
         </is>
       </c>
       <c r="G190" s="5" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="H190" s="4" t="inlineStr">
         <is>
@@ -14982,7 +15182,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15019,7 +15219,7 @@
         </is>
       </c>
       <c r="G191" s="5" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="H191" s="4" t="inlineStr">
         <is>
@@ -15061,7 +15261,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15098,7 +15298,7 @@
         </is>
       </c>
       <c r="G192" s="5" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="H192" s="4" t="inlineStr">
         <is>
@@ -15140,7 +15340,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15177,7 +15377,7 @@
         </is>
       </c>
       <c r="G193" s="5" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="H193" s="4" t="inlineStr">
         <is>
@@ -15219,7 +15419,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15256,7 +15456,7 @@
         </is>
       </c>
       <c r="G194" s="5" t="n">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="H194" s="4" t="inlineStr">
         <is>
@@ -15298,7 +15498,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15335,7 +15535,7 @@
         </is>
       </c>
       <c r="G195" s="5" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="H195" s="4" t="inlineStr">
         <is>
@@ -15368,7 +15568,7 @@
         </is>
       </c>
       <c r="N195" s="6" t="n">
-        <v>14.3712574850299</v>
+        <v>16.969696969697</v>
       </c>
       <c r="O195" s="4" t="inlineStr">
         <is>
@@ -15377,7 +15577,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15414,7 +15614,7 @@
         </is>
       </c>
       <c r="G196" s="5" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="H196" s="4" t="inlineStr">
         <is>
@@ -15447,7 +15647,7 @@
         </is>
       </c>
       <c r="N196" s="6" t="n">
-        <v>22.1556886227545</v>
+        <v>14.3712574850299</v>
       </c>
       <c r="O196" s="4" t="inlineStr">
         <is>
@@ -15456,7 +15656,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15493,7 +15693,7 @@
         </is>
       </c>
       <c r="G197" s="5" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="H197" s="4" t="inlineStr">
         <is>
@@ -15535,7 +15735,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15572,7 +15772,7 @@
         </is>
       </c>
       <c r="G198" s="5" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="H198" s="4" t="inlineStr">
         <is>
@@ -15614,7 +15814,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15651,7 +15851,7 @@
         </is>
       </c>
       <c r="G199" s="5" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="H199" s="4" t="inlineStr">
         <is>
@@ -15693,7 +15893,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15730,7 +15930,7 @@
         </is>
       </c>
       <c r="G200" s="5" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="H200" s="4" t="inlineStr">
         <is>
@@ -15772,7 +15972,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15809,7 +16009,7 @@
         </is>
       </c>
       <c r="G201" s="5" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H201" s="4" t="inlineStr">
         <is>
@@ -15841,7 +16041,9 @@
           <t>Mujeres en parlamentos nacionales</t>
         </is>
       </c>
-      <c r="N201" s="4" t="n"/>
+      <c r="N201" s="6" t="n">
+        <v>22.1556886227545</v>
+      </c>
       <c r="O201" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -15849,7 +16051,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15886,7 +16088,7 @@
         </is>
       </c>
       <c r="G202" s="5" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="H202" s="4" t="inlineStr">
         <is>
@@ -15926,7 +16128,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -15963,7 +16165,7 @@
         </is>
       </c>
       <c r="G203" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="H203" s="4" t="inlineStr">
         <is>
@@ -16003,7 +16205,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16040,7 +16242,7 @@
         </is>
       </c>
       <c r="G204" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="H204" s="4" t="inlineStr">
         <is>
@@ -16072,9 +16274,7 @@
           <t>Mujeres en parlamentos nacionales</t>
         </is>
       </c>
-      <c r="N204" s="6" t="n">
-        <v>32.129963898917</v>
-      </c>
+      <c r="N204" s="4" t="n"/>
       <c r="O204" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -16082,7 +16282,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16119,7 +16319,7 @@
         </is>
       </c>
       <c r="G205" s="5" t="n">
-        <v>1960</v>
+        <v>2025</v>
       </c>
       <c r="H205" s="4" t="inlineStr">
         <is>
@@ -16133,25 +16333,27 @@
       </c>
       <c r="J205" s="4" t="inlineStr">
         <is>
-          <t>Mercado laboral</t>
+          <t>Participación política</t>
         </is>
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>mercado_laboral</t>
+          <t>participacion_politica</t>
         </is>
       </c>
       <c r="L205" s="4" t="inlineStr">
         <is>
-          <t>SL.TLF.CACT.FE.ZS</t>
+          <t>SG.GEN.PARL.ZS</t>
         </is>
       </c>
       <c r="M205" s="4" t="inlineStr">
         <is>
-          <t>Participación laboral femenina</t>
-        </is>
-      </c>
-      <c r="N205" s="4" t="n"/>
+          <t>Mujeres en parlamentos nacionales</t>
+        </is>
+      </c>
+      <c r="N205" s="6" t="n">
+        <v>32.129963898917</v>
+      </c>
       <c r="O205" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -16159,7 +16361,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16196,7 +16398,7 @@
         </is>
       </c>
       <c r="G206" s="5" t="n">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="H206" s="4" t="inlineStr">
         <is>
@@ -16236,7 +16438,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16273,7 +16475,7 @@
         </is>
       </c>
       <c r="G207" s="5" t="n">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="H207" s="4" t="inlineStr">
         <is>
@@ -16313,7 +16515,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16350,7 +16552,7 @@
         </is>
       </c>
       <c r="G208" s="5" t="n">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="H208" s="4" t="inlineStr">
         <is>
@@ -16390,7 +16592,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16427,7 +16629,7 @@
         </is>
       </c>
       <c r="G209" s="5" t="n">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="H209" s="4" t="inlineStr">
         <is>
@@ -16467,7 +16669,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16504,7 +16706,7 @@
         </is>
       </c>
       <c r="G210" s="5" t="n">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="H210" s="4" t="inlineStr">
         <is>
@@ -16544,7 +16746,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16581,7 +16783,7 @@
         </is>
       </c>
       <c r="G211" s="5" t="n">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="H211" s="4" t="inlineStr">
         <is>
@@ -16621,7 +16823,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16658,7 +16860,7 @@
         </is>
       </c>
       <c r="G212" s="5" t="n">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="H212" s="4" t="inlineStr">
         <is>
@@ -16698,7 +16900,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16735,7 +16937,7 @@
         </is>
       </c>
       <c r="G213" s="5" t="n">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="H213" s="4" t="inlineStr">
         <is>
@@ -16775,7 +16977,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16812,7 +17014,7 @@
         </is>
       </c>
       <c r="G214" s="5" t="n">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="H214" s="4" t="inlineStr">
         <is>
@@ -16852,7 +17054,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16889,7 +17091,7 @@
         </is>
       </c>
       <c r="G215" s="5" t="n">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="H215" s="4" t="inlineStr">
         <is>
@@ -16929,7 +17131,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -16966,7 +17168,7 @@
         </is>
       </c>
       <c r="G216" s="5" t="n">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="H216" s="4" t="inlineStr">
         <is>
@@ -17006,7 +17208,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17043,7 +17245,7 @@
         </is>
       </c>
       <c r="G217" s="5" t="n">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="H217" s="4" t="inlineStr">
         <is>
@@ -17083,7 +17285,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17120,7 +17322,7 @@
         </is>
       </c>
       <c r="G218" s="5" t="n">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="H218" s="4" t="inlineStr">
         <is>
@@ -17160,7 +17362,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17197,7 +17399,7 @@
         </is>
       </c>
       <c r="G219" s="5" t="n">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="H219" s="4" t="inlineStr">
         <is>
@@ -17237,7 +17439,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17274,7 +17476,7 @@
         </is>
       </c>
       <c r="G220" s="5" t="n">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="H220" s="4" t="inlineStr">
         <is>
@@ -17314,7 +17516,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17351,7 +17553,7 @@
         </is>
       </c>
       <c r="G221" s="5" t="n">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="H221" s="4" t="inlineStr">
         <is>
@@ -17391,7 +17593,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17428,7 +17630,7 @@
         </is>
       </c>
       <c r="G222" s="5" t="n">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="H222" s="4" t="inlineStr">
         <is>
@@ -17468,7 +17670,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17505,7 +17707,7 @@
         </is>
       </c>
       <c r="G223" s="5" t="n">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="H223" s="4" t="inlineStr">
         <is>
@@ -17545,7 +17747,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17582,7 +17784,7 @@
         </is>
       </c>
       <c r="G224" s="5" t="n">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="H224" s="4" t="inlineStr">
         <is>
@@ -17622,7 +17824,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17659,7 +17861,7 @@
         </is>
       </c>
       <c r="G225" s="5" t="n">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="H225" s="4" t="inlineStr">
         <is>
@@ -17699,7 +17901,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17736,7 +17938,7 @@
         </is>
       </c>
       <c r="G226" s="5" t="n">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="H226" s="4" t="inlineStr">
         <is>
@@ -17776,7 +17978,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17813,7 +18015,7 @@
         </is>
       </c>
       <c r="G227" s="5" t="n">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="H227" s="4" t="inlineStr">
         <is>
@@ -17853,7 +18055,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17890,7 +18092,7 @@
         </is>
       </c>
       <c r="G228" s="5" t="n">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="H228" s="4" t="inlineStr">
         <is>
@@ -17930,7 +18132,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -17967,7 +18169,7 @@
         </is>
       </c>
       <c r="G229" s="5" t="n">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="H229" s="4" t="inlineStr">
         <is>
@@ -18007,7 +18209,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18044,7 +18246,7 @@
         </is>
       </c>
       <c r="G230" s="5" t="n">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="H230" s="4" t="inlineStr">
         <is>
@@ -18084,7 +18286,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18121,7 +18323,7 @@
         </is>
       </c>
       <c r="G231" s="5" t="n">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="H231" s="4" t="inlineStr">
         <is>
@@ -18161,7 +18363,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18198,7 +18400,7 @@
         </is>
       </c>
       <c r="G232" s="5" t="n">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="H232" s="4" t="inlineStr">
         <is>
@@ -18238,7 +18440,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18275,7 +18477,7 @@
         </is>
       </c>
       <c r="G233" s="5" t="n">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="H233" s="4" t="inlineStr">
         <is>
@@ -18315,7 +18517,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18352,7 +18554,7 @@
         </is>
       </c>
       <c r="G234" s="5" t="n">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="H234" s="4" t="inlineStr">
         <is>
@@ -18392,7 +18594,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18429,7 +18631,7 @@
         </is>
       </c>
       <c r="G235" s="5" t="n">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="H235" s="4" t="inlineStr">
         <is>
@@ -18461,9 +18663,7 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N235" s="6" t="n">
-        <v>48.56</v>
-      </c>
+      <c r="N235" s="4" t="n"/>
       <c r="O235" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -18471,7 +18671,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18508,7 +18708,7 @@
         </is>
       </c>
       <c r="G236" s="5" t="n">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="H236" s="4" t="inlineStr">
         <is>
@@ -18541,7 +18741,7 @@
         </is>
       </c>
       <c r="N236" s="6" t="n">
-        <v>49.027</v>
+        <v>48.56</v>
       </c>
       <c r="O236" s="4" t="inlineStr">
         <is>
@@ -18550,7 +18750,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18587,7 +18787,7 @@
         </is>
       </c>
       <c r="G237" s="5" t="n">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="H237" s="4" t="inlineStr">
         <is>
@@ -18620,7 +18820,7 @@
         </is>
       </c>
       <c r="N237" s="6" t="n">
-        <v>49.439</v>
+        <v>49.027</v>
       </c>
       <c r="O237" s="4" t="inlineStr">
         <is>
@@ -18629,7 +18829,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18666,7 +18866,7 @@
         </is>
       </c>
       <c r="G238" s="5" t="n">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="H238" s="4" t="inlineStr">
         <is>
@@ -18699,7 +18899,7 @@
         </is>
       </c>
       <c r="N238" s="6" t="n">
-        <v>49.121</v>
+        <v>49.439</v>
       </c>
       <c r="O238" s="4" t="inlineStr">
         <is>
@@ -18708,7 +18908,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18745,7 +18945,7 @@
         </is>
       </c>
       <c r="G239" s="5" t="n">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="H239" s="4" t="inlineStr">
         <is>
@@ -18778,7 +18978,7 @@
         </is>
       </c>
       <c r="N239" s="6" t="n">
-        <v>48.519</v>
+        <v>49.121</v>
       </c>
       <c r="O239" s="4" t="inlineStr">
         <is>
@@ -18787,7 +18987,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18824,7 +19024,7 @@
         </is>
       </c>
       <c r="G240" s="5" t="n">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="H240" s="4" t="inlineStr">
         <is>
@@ -18857,7 +19057,7 @@
         </is>
       </c>
       <c r="N240" s="6" t="n">
-        <v>48.502</v>
+        <v>48.519</v>
       </c>
       <c r="O240" s="4" t="inlineStr">
         <is>
@@ -18866,7 +19066,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18903,7 +19103,7 @@
         </is>
       </c>
       <c r="G241" s="5" t="n">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="H241" s="4" t="inlineStr">
         <is>
@@ -18936,7 +19136,7 @@
         </is>
       </c>
       <c r="N241" s="6" t="n">
-        <v>48.683</v>
+        <v>48.502</v>
       </c>
       <c r="O241" s="4" t="inlineStr">
         <is>
@@ -18945,7 +19145,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -18982,7 +19182,7 @@
         </is>
       </c>
       <c r="G242" s="5" t="n">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="H242" s="4" t="inlineStr">
         <is>
@@ -19015,7 +19215,7 @@
         </is>
       </c>
       <c r="N242" s="6" t="n">
-        <v>48.743</v>
+        <v>48.683</v>
       </c>
       <c r="O242" s="4" t="inlineStr">
         <is>
@@ -19024,7 +19224,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19061,7 +19261,7 @@
         </is>
       </c>
       <c r="G243" s="5" t="n">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="H243" s="4" t="inlineStr">
         <is>
@@ -19094,7 +19294,7 @@
         </is>
       </c>
       <c r="N243" s="6" t="n">
-        <v>48.976</v>
+        <v>48.743</v>
       </c>
       <c r="O243" s="4" t="inlineStr">
         <is>
@@ -19103,7 +19303,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19140,7 +19340,7 @@
         </is>
       </c>
       <c r="G244" s="5" t="n">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="H244" s="4" t="inlineStr">
         <is>
@@ -19173,7 +19373,7 @@
         </is>
       </c>
       <c r="N244" s="6" t="n">
-        <v>48.119</v>
+        <v>48.976</v>
       </c>
       <c r="O244" s="4" t="inlineStr">
         <is>
@@ -19182,7 +19382,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19219,7 +19419,7 @@
         </is>
       </c>
       <c r="G245" s="5" t="n">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="H245" s="4" t="inlineStr">
         <is>
@@ -19252,7 +19452,7 @@
         </is>
       </c>
       <c r="N245" s="6" t="n">
-        <v>47.914</v>
+        <v>48.119</v>
       </c>
       <c r="O245" s="4" t="inlineStr">
         <is>
@@ -19261,7 +19461,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19298,7 +19498,7 @@
         </is>
       </c>
       <c r="G246" s="5" t="n">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="H246" s="4" t="inlineStr">
         <is>
@@ -19331,7 +19531,7 @@
         </is>
       </c>
       <c r="N246" s="6" t="n">
-        <v>48.527</v>
+        <v>47.914</v>
       </c>
       <c r="O246" s="4" t="inlineStr">
         <is>
@@ -19340,7 +19540,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19377,7 +19577,7 @@
         </is>
       </c>
       <c r="G247" s="5" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="H247" s="4" t="inlineStr">
         <is>
@@ -19410,7 +19610,7 @@
         </is>
       </c>
       <c r="N247" s="6" t="n">
-        <v>47.765</v>
+        <v>48.527</v>
       </c>
       <c r="O247" s="4" t="inlineStr">
         <is>
@@ -19419,7 +19619,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19456,7 +19656,7 @@
         </is>
       </c>
       <c r="G248" s="5" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="H248" s="4" t="inlineStr">
         <is>
@@ -19489,7 +19689,7 @@
         </is>
       </c>
       <c r="N248" s="6" t="n">
-        <v>46.462</v>
+        <v>47.765</v>
       </c>
       <c r="O248" s="4" t="inlineStr">
         <is>
@@ -19498,7 +19698,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19535,7 +19735,7 @@
         </is>
       </c>
       <c r="G249" s="5" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="H249" s="4" t="inlineStr">
         <is>
@@ -19568,7 +19768,7 @@
         </is>
       </c>
       <c r="N249" s="6" t="n">
-        <v>47.558</v>
+        <v>46.462</v>
       </c>
       <c r="O249" s="4" t="inlineStr">
         <is>
@@ -19577,7 +19777,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19614,7 +19814,7 @@
         </is>
       </c>
       <c r="G250" s="5" t="n">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="H250" s="4" t="inlineStr">
         <is>
@@ -19647,7 +19847,7 @@
         </is>
       </c>
       <c r="N250" s="6" t="n">
-        <v>49.457</v>
+        <v>47.558</v>
       </c>
       <c r="O250" s="4" t="inlineStr">
         <is>
@@ -19656,7 +19856,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19693,7 +19893,7 @@
         </is>
       </c>
       <c r="G251" s="5" t="n">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="H251" s="4" t="inlineStr">
         <is>
@@ -19726,7 +19926,7 @@
         </is>
       </c>
       <c r="N251" s="6" t="n">
-        <v>50.019</v>
+        <v>49.457</v>
       </c>
       <c r="O251" s="4" t="inlineStr">
         <is>
@@ -19735,7 +19935,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19772,7 +19972,7 @@
         </is>
       </c>
       <c r="G252" s="5" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="H252" s="4" t="inlineStr">
         <is>
@@ -19805,7 +20005,7 @@
         </is>
       </c>
       <c r="N252" s="6" t="n">
-        <v>49.726</v>
+        <v>50.019</v>
       </c>
       <c r="O252" s="4" t="inlineStr">
         <is>
@@ -19814,7 +20014,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19851,7 +20051,7 @@
         </is>
       </c>
       <c r="G253" s="5" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="H253" s="4" t="inlineStr">
         <is>
@@ -19884,7 +20084,7 @@
         </is>
       </c>
       <c r="N253" s="6" t="n">
-        <v>49.734</v>
+        <v>49.726</v>
       </c>
       <c r="O253" s="4" t="inlineStr">
         <is>
@@ -19893,7 +20093,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -19930,7 +20130,7 @@
         </is>
       </c>
       <c r="G254" s="5" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="H254" s="4" t="inlineStr">
         <is>
@@ -19963,7 +20163,7 @@
         </is>
       </c>
       <c r="N254" s="6" t="n">
-        <v>50.004</v>
+        <v>49.734</v>
       </c>
       <c r="O254" s="4" t="inlineStr">
         <is>
@@ -19972,7 +20172,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20009,7 +20209,7 @@
         </is>
       </c>
       <c r="G255" s="5" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="H255" s="4" t="inlineStr">
         <is>
@@ -20042,7 +20242,7 @@
         </is>
       </c>
       <c r="N255" s="6" t="n">
-        <v>49.601</v>
+        <v>50.004</v>
       </c>
       <c r="O255" s="4" t="inlineStr">
         <is>
@@ -20051,7 +20251,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20088,7 +20288,7 @@
         </is>
       </c>
       <c r="G256" s="5" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="H256" s="4" t="inlineStr">
         <is>
@@ -20121,7 +20321,7 @@
         </is>
       </c>
       <c r="N256" s="6" t="n">
-        <v>49.643</v>
+        <v>49.601</v>
       </c>
       <c r="O256" s="4" t="inlineStr">
         <is>
@@ -20130,7 +20330,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20167,7 +20367,7 @@
         </is>
       </c>
       <c r="G257" s="5" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="H257" s="4" t="inlineStr">
         <is>
@@ -20200,7 +20400,7 @@
         </is>
       </c>
       <c r="N257" s="6" t="n">
-        <v>49.493</v>
+        <v>49.643</v>
       </c>
       <c r="O257" s="4" t="inlineStr">
         <is>
@@ -20209,7 +20409,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20246,7 +20446,7 @@
         </is>
       </c>
       <c r="G258" s="5" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="H258" s="4" t="inlineStr">
         <is>
@@ -20279,7 +20479,7 @@
         </is>
       </c>
       <c r="N258" s="6" t="n">
-        <v>49.084</v>
+        <v>49.493</v>
       </c>
       <c r="O258" s="4" t="inlineStr">
         <is>
@@ -20288,7 +20488,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20325,7 +20525,7 @@
         </is>
       </c>
       <c r="G259" s="5" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="H259" s="4" t="inlineStr">
         <is>
@@ -20358,7 +20558,7 @@
         </is>
       </c>
       <c r="N259" s="6" t="n">
-        <v>48.676</v>
+        <v>49.084</v>
       </c>
       <c r="O259" s="4" t="inlineStr">
         <is>
@@ -20367,7 +20567,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20404,7 +20604,7 @@
         </is>
       </c>
       <c r="G260" s="5" t="n">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="H260" s="4" t="inlineStr">
         <is>
@@ -20437,7 +20637,7 @@
         </is>
       </c>
       <c r="N260" s="6" t="n">
-        <v>48.27</v>
+        <v>48.676</v>
       </c>
       <c r="O260" s="4" t="inlineStr">
         <is>
@@ -20446,7 +20646,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20483,7 +20683,7 @@
         </is>
       </c>
       <c r="G261" s="5" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="H261" s="4" t="inlineStr">
         <is>
@@ -20516,7 +20716,7 @@
         </is>
       </c>
       <c r="N261" s="6" t="n">
-        <v>47.867</v>
+        <v>48.27</v>
       </c>
       <c r="O261" s="4" t="inlineStr">
         <is>
@@ -20525,7 +20725,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20562,7 +20762,7 @@
         </is>
       </c>
       <c r="G262" s="5" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="H262" s="4" t="inlineStr">
         <is>
@@ -20595,7 +20795,7 @@
         </is>
       </c>
       <c r="N262" s="6" t="n">
-        <v>46.185</v>
+        <v>47.867</v>
       </c>
       <c r="O262" s="4" t="inlineStr">
         <is>
@@ -20604,7 +20804,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20641,7 +20841,7 @@
         </is>
       </c>
       <c r="G263" s="5" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="H263" s="4" t="inlineStr">
         <is>
@@ -20674,7 +20874,7 @@
         </is>
       </c>
       <c r="N263" s="6" t="n">
-        <v>44.85</v>
+        <v>46.185</v>
       </c>
       <c r="O263" s="4" t="inlineStr">
         <is>
@@ -20683,7 +20883,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20720,7 +20920,7 @@
         </is>
       </c>
       <c r="G264" s="5" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="H264" s="4" t="inlineStr">
         <is>
@@ -20753,7 +20953,7 @@
         </is>
       </c>
       <c r="N264" s="6" t="n">
-        <v>42.344</v>
+        <v>44.85</v>
       </c>
       <c r="O264" s="4" t="inlineStr">
         <is>
@@ -20762,7 +20962,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20799,7 +20999,7 @@
         </is>
       </c>
       <c r="G265" s="5" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="H265" s="4" t="inlineStr">
         <is>
@@ -20832,7 +21032,7 @@
         </is>
       </c>
       <c r="N265" s="6" t="n">
-        <v>36.887</v>
+        <v>42.344</v>
       </c>
       <c r="O265" s="4" t="inlineStr">
         <is>
@@ -20841,7 +21041,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20878,7 +21078,7 @@
         </is>
       </c>
       <c r="G266" s="5" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="H266" s="4" t="inlineStr">
         <is>
@@ -20911,7 +21111,7 @@
         </is>
       </c>
       <c r="N266" s="6" t="n">
-        <v>37.368</v>
+        <v>36.887</v>
       </c>
       <c r="O266" s="4" t="inlineStr">
         <is>
@@ -20920,7 +21120,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -20957,7 +21157,7 @@
         </is>
       </c>
       <c r="G267" s="5" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H267" s="4" t="inlineStr">
         <is>
@@ -20990,7 +21190,7 @@
         </is>
       </c>
       <c r="N267" s="6" t="n">
-        <v>35.32</v>
+        <v>37.368</v>
       </c>
       <c r="O267" s="4" t="inlineStr">
         <is>
@@ -20999,7 +21199,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21036,7 +21236,7 @@
         </is>
       </c>
       <c r="G268" s="5" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="H268" s="4" t="inlineStr">
         <is>
@@ -21069,7 +21269,7 @@
         </is>
       </c>
       <c r="N268" s="6" t="n">
-        <v>36.158</v>
+        <v>35.32</v>
       </c>
       <c r="O268" s="4" t="inlineStr">
         <is>
@@ -21078,7 +21278,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21115,7 +21315,7 @@
         </is>
       </c>
       <c r="G269" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="H269" s="4" t="inlineStr">
         <is>
@@ -21148,7 +21348,7 @@
         </is>
       </c>
       <c r="N269" s="6" t="n">
-        <v>37.332</v>
+        <v>36.158</v>
       </c>
       <c r="O269" s="4" t="inlineStr">
         <is>
@@ -21157,7 +21357,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21194,7 +21394,7 @@
         </is>
       </c>
       <c r="G270" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="H270" s="4" t="inlineStr">
         <is>
@@ -21227,7 +21427,7 @@
         </is>
       </c>
       <c r="N270" s="6" t="n">
-        <v>37.098</v>
+        <v>37.332</v>
       </c>
       <c r="O270" s="4" t="inlineStr">
         <is>
@@ -21236,7 +21436,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21273,7 +21473,7 @@
         </is>
       </c>
       <c r="G271" s="5" t="n">
-        <v>1960</v>
+        <v>2025</v>
       </c>
       <c r="H271" s="4" t="inlineStr">
         <is>
@@ -21297,15 +21497,17 @@
       </c>
       <c r="L271" s="4" t="inlineStr">
         <is>
-          <t>SL.UEM.TOTL.FE.ZS</t>
+          <t>SL.TLF.CACT.FE.ZS</t>
         </is>
       </c>
       <c r="M271" s="4" t="inlineStr">
         <is>
-          <t>Desempleo femenino</t>
-        </is>
-      </c>
-      <c r="N271" s="4" t="n"/>
+          <t>Participación laboral femenina</t>
+        </is>
+      </c>
+      <c r="N271" s="6" t="n">
+        <v>37.098</v>
+      </c>
       <c r="O271" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -21313,14 +21515,10 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q271" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q271" s="4" t="n"/>
     </row>
     <row r="272">
       <c r="A272" s="4" t="inlineStr">
@@ -21354,7 +21552,7 @@
         </is>
       </c>
       <c r="G272" s="5" t="n">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="H272" s="4" t="inlineStr">
         <is>
@@ -21394,14 +21592,10 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q272" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q272" s="4" t="n"/>
     </row>
     <row r="273">
       <c r="A273" s="4" t="inlineStr">
@@ -21435,7 +21629,7 @@
         </is>
       </c>
       <c r="G273" s="5" t="n">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="H273" s="4" t="inlineStr">
         <is>
@@ -21475,14 +21669,10 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q273" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q273" s="4" t="n"/>
     </row>
     <row r="274">
       <c r="A274" s="4" t="inlineStr">
@@ -21516,7 +21706,7 @@
         </is>
       </c>
       <c r="G274" s="5" t="n">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="H274" s="4" t="inlineStr">
         <is>
@@ -21556,14 +21746,10 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q274" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q274" s="4" t="n"/>
     </row>
     <row r="275">
       <c r="A275" s="4" t="inlineStr">
@@ -21597,7 +21783,7 @@
         </is>
       </c>
       <c r="G275" s="5" t="n">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="H275" s="4" t="inlineStr">
         <is>
@@ -21637,14 +21823,10 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q275" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q275" s="4" t="n"/>
     </row>
     <row r="276">
       <c r="A276" s="4" t="inlineStr">
@@ -21678,7 +21860,7 @@
         </is>
       </c>
       <c r="G276" s="5" t="n">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="H276" s="4" t="inlineStr">
         <is>
@@ -21718,14 +21900,10 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q276" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q276" s="4" t="n"/>
     </row>
     <row r="277">
       <c r="A277" s="4" t="inlineStr">
@@ -21759,7 +21937,7 @@
         </is>
       </c>
       <c r="G277" s="5" t="n">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="H277" s="4" t="inlineStr">
         <is>
@@ -21799,14 +21977,10 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q277" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q277" s="4" t="n"/>
     </row>
     <row r="278">
       <c r="A278" s="4" t="inlineStr">
@@ -21840,7 +22014,7 @@
         </is>
       </c>
       <c r="G278" s="5" t="n">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="H278" s="4" t="inlineStr">
         <is>
@@ -21880,14 +22054,10 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q278" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q278" s="4" t="n"/>
     </row>
     <row r="279">
       <c r="A279" s="4" t="inlineStr">
@@ -21921,7 +22091,7 @@
         </is>
       </c>
       <c r="G279" s="5" t="n">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="H279" s="4" t="inlineStr">
         <is>
@@ -21961,14 +22131,10 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q279" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q279" s="4" t="n"/>
     </row>
     <row r="280">
       <c r="A280" s="4" t="inlineStr">
@@ -22002,7 +22168,7 @@
         </is>
       </c>
       <c r="G280" s="5" t="n">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="H280" s="4" t="inlineStr">
         <is>
@@ -22042,14 +22208,10 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q280" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q280" s="4" t="n"/>
     </row>
     <row r="281">
       <c r="A281" s="4" t="inlineStr">
@@ -22083,7 +22245,7 @@
         </is>
       </c>
       <c r="G281" s="5" t="n">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="H281" s="4" t="inlineStr">
         <is>
@@ -22123,14 +22285,10 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q281" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q281" s="4" t="n"/>
     </row>
     <row r="282">
       <c r="A282" s="4" t="inlineStr">
@@ -22164,7 +22322,7 @@
         </is>
       </c>
       <c r="G282" s="5" t="n">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="H282" s="4" t="inlineStr">
         <is>
@@ -22204,14 +22362,10 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q282" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q282" s="4" t="n"/>
     </row>
     <row r="283">
       <c r="A283" s="4" t="inlineStr">
@@ -22245,7 +22399,7 @@
         </is>
       </c>
       <c r="G283" s="5" t="n">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="H283" s="4" t="inlineStr">
         <is>
@@ -22285,14 +22439,10 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q283" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q283" s="4" t="n"/>
     </row>
     <row r="284">
       <c r="A284" s="4" t="inlineStr">
@@ -22326,7 +22476,7 @@
         </is>
       </c>
       <c r="G284" s="5" t="n">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="H284" s="4" t="inlineStr">
         <is>
@@ -22366,14 +22516,10 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q284" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q284" s="4" t="n"/>
     </row>
     <row r="285">
       <c r="A285" s="4" t="inlineStr">
@@ -22407,7 +22553,7 @@
         </is>
       </c>
       <c r="G285" s="5" t="n">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="H285" s="4" t="inlineStr">
         <is>
@@ -22447,14 +22593,10 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q285" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q285" s="4" t="n"/>
     </row>
     <row r="286">
       <c r="A286" s="4" t="inlineStr">
@@ -22488,7 +22630,7 @@
         </is>
       </c>
       <c r="G286" s="5" t="n">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="H286" s="4" t="inlineStr">
         <is>
@@ -22528,14 +22670,10 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q286" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q286" s="4" t="n"/>
     </row>
     <row r="287">
       <c r="A287" s="4" t="inlineStr">
@@ -22569,7 +22707,7 @@
         </is>
       </c>
       <c r="G287" s="5" t="n">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="H287" s="4" t="inlineStr">
         <is>
@@ -22609,14 +22747,10 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q287" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q287" s="4" t="n"/>
     </row>
     <row r="288">
       <c r="A288" s="4" t="inlineStr">
@@ -22650,7 +22784,7 @@
         </is>
       </c>
       <c r="G288" s="5" t="n">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="H288" s="4" t="inlineStr">
         <is>
@@ -22690,14 +22824,10 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q288" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q288" s="4" t="n"/>
     </row>
     <row r="289">
       <c r="A289" s="4" t="inlineStr">
@@ -22731,7 +22861,7 @@
         </is>
       </c>
       <c r="G289" s="5" t="n">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="H289" s="4" t="inlineStr">
         <is>
@@ -22771,14 +22901,10 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q289" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q289" s="4" t="n"/>
     </row>
     <row r="290">
       <c r="A290" s="4" t="inlineStr">
@@ -22812,7 +22938,7 @@
         </is>
       </c>
       <c r="G290" s="5" t="n">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="H290" s="4" t="inlineStr">
         <is>
@@ -22852,14 +22978,10 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q290" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q290" s="4" t="n"/>
     </row>
     <row r="291">
       <c r="A291" s="4" t="inlineStr">
@@ -22893,7 +23015,7 @@
         </is>
       </c>
       <c r="G291" s="5" t="n">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="H291" s="4" t="inlineStr">
         <is>
@@ -22933,14 +23055,10 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q291" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q291" s="4" t="n"/>
     </row>
     <row r="292">
       <c r="A292" s="4" t="inlineStr">
@@ -22974,7 +23092,7 @@
         </is>
       </c>
       <c r="G292" s="5" t="n">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="H292" s="4" t="inlineStr">
         <is>
@@ -23014,14 +23132,10 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q292" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q292" s="4" t="n"/>
     </row>
     <row r="293">
       <c r="A293" s="4" t="inlineStr">
@@ -23055,7 +23169,7 @@
         </is>
       </c>
       <c r="G293" s="5" t="n">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="H293" s="4" t="inlineStr">
         <is>
@@ -23095,14 +23209,10 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q293" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q293" s="4" t="n"/>
     </row>
     <row r="294">
       <c r="A294" s="4" t="inlineStr">
@@ -23136,7 +23246,7 @@
         </is>
       </c>
       <c r="G294" s="5" t="n">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="H294" s="4" t="inlineStr">
         <is>
@@ -23176,14 +23286,10 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q294" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q294" s="4" t="n"/>
     </row>
     <row r="295">
       <c r="A295" s="4" t="inlineStr">
@@ -23217,7 +23323,7 @@
         </is>
       </c>
       <c r="G295" s="5" t="n">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="H295" s="4" t="inlineStr">
         <is>
@@ -23257,14 +23363,10 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q295" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q295" s="4" t="n"/>
     </row>
     <row r="296">
       <c r="A296" s="4" t="inlineStr">
@@ -23298,7 +23400,7 @@
         </is>
       </c>
       <c r="G296" s="5" t="n">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="H296" s="4" t="inlineStr">
         <is>
@@ -23338,14 +23440,10 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q296" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q296" s="4" t="n"/>
     </row>
     <row r="297">
       <c r="A297" s="4" t="inlineStr">
@@ -23379,7 +23477,7 @@
         </is>
       </c>
       <c r="G297" s="5" t="n">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="H297" s="4" t="inlineStr">
         <is>
@@ -23419,14 +23517,10 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q297" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q297" s="4" t="n"/>
     </row>
     <row r="298">
       <c r="A298" s="4" t="inlineStr">
@@ -23460,7 +23554,7 @@
         </is>
       </c>
       <c r="G298" s="5" t="n">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="H298" s="4" t="inlineStr">
         <is>
@@ -23500,14 +23594,10 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q298" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q298" s="4" t="n"/>
     </row>
     <row r="299">
       <c r="A299" s="4" t="inlineStr">
@@ -23541,7 +23631,7 @@
         </is>
       </c>
       <c r="G299" s="5" t="n">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="H299" s="4" t="inlineStr">
         <is>
@@ -23581,14 +23671,10 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q299" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q299" s="4" t="n"/>
     </row>
     <row r="300">
       <c r="A300" s="4" t="inlineStr">
@@ -23622,7 +23708,7 @@
         </is>
       </c>
       <c r="G300" s="5" t="n">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="H300" s="4" t="inlineStr">
         <is>
@@ -23662,14 +23748,10 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q300" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q300" s="4" t="n"/>
     </row>
     <row r="301">
       <c r="A301" s="4" t="inlineStr">
@@ -23703,7 +23785,7 @@
         </is>
       </c>
       <c r="G301" s="5" t="n">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="H301" s="4" t="inlineStr">
         <is>
@@ -23743,14 +23825,10 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q301" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q301" s="4" t="n"/>
     </row>
     <row r="302">
       <c r="A302" s="4" t="inlineStr">
@@ -23784,7 +23862,7 @@
         </is>
       </c>
       <c r="G302" s="5" t="n">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="H302" s="4" t="inlineStr">
         <is>
@@ -23824,14 +23902,10 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q302" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q302" s="4" t="n"/>
     </row>
     <row r="303">
       <c r="A303" s="4" t="inlineStr">
@@ -23865,7 +23939,7 @@
         </is>
       </c>
       <c r="G303" s="5" t="n">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="H303" s="4" t="inlineStr">
         <is>
@@ -23897,7 +23971,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N303" s="4" t="n"/>
+      <c r="N303" s="6" t="n">
+        <v>9.32</v>
+      </c>
       <c r="O303" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -23905,14 +23981,10 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q303" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q303" s="4" t="n"/>
     </row>
     <row r="304">
       <c r="A304" s="4" t="inlineStr">
@@ -23946,7 +24018,7 @@
         </is>
       </c>
       <c r="G304" s="5" t="n">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="H304" s="4" t="inlineStr">
         <is>
@@ -23978,7 +24050,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N304" s="4" t="n"/>
+      <c r="N304" s="6" t="n">
+        <v>6.925</v>
+      </c>
       <c r="O304" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -23986,14 +24060,10 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q304" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q304" s="4" t="n"/>
     </row>
     <row r="305">
       <c r="A305" s="4" t="inlineStr">
@@ -24027,7 +24097,7 @@
         </is>
       </c>
       <c r="G305" s="5" t="n">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="H305" s="4" t="inlineStr">
         <is>
@@ -24059,7 +24129,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N305" s="4" t="n"/>
+      <c r="N305" s="6" t="n">
+        <v>5.679</v>
+      </c>
       <c r="O305" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24067,14 +24139,10 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q305" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q305" s="4" t="n"/>
     </row>
     <row r="306">
       <c r="A306" s="4" t="inlineStr">
@@ -24108,7 +24176,7 @@
         </is>
       </c>
       <c r="G306" s="5" t="n">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="H306" s="4" t="inlineStr">
         <is>
@@ -24140,7 +24208,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N306" s="4" t="n"/>
+      <c r="N306" s="6" t="n">
+        <v>9.557</v>
+      </c>
       <c r="O306" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24148,14 +24218,10 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q306" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q306" s="4" t="n"/>
     </row>
     <row r="307">
       <c r="A307" s="4" t="inlineStr">
@@ -24189,7 +24255,7 @@
         </is>
       </c>
       <c r="G307" s="5" t="n">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="H307" s="4" t="inlineStr">
         <is>
@@ -24221,7 +24287,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N307" s="4" t="n"/>
+      <c r="N307" s="6" t="n">
+        <v>12.604</v>
+      </c>
       <c r="O307" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24229,14 +24297,10 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q307" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q307" s="4" t="n"/>
     </row>
     <row r="308">
       <c r="A308" s="4" t="inlineStr">
@@ -24270,7 +24334,7 @@
         </is>
       </c>
       <c r="G308" s="5" t="n">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="H308" s="4" t="inlineStr">
         <is>
@@ -24302,7 +24366,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N308" s="4" t="n"/>
+      <c r="N308" s="6" t="n">
+        <v>14.345</v>
+      </c>
       <c r="O308" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24310,14 +24376,10 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q308" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q308" s="4" t="n"/>
     </row>
     <row r="309">
       <c r="A309" s="4" t="inlineStr">
@@ -24351,7 +24413,7 @@
         </is>
       </c>
       <c r="G309" s="5" t="n">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="H309" s="4" t="inlineStr">
         <is>
@@ -24383,7 +24445,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N309" s="4" t="n"/>
+      <c r="N309" s="6" t="n">
+        <v>13.627</v>
+      </c>
       <c r="O309" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24391,14 +24455,10 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q309" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q309" s="4" t="n"/>
     </row>
     <row r="310">
       <c r="A310" s="4" t="inlineStr">
@@ -24432,7 +24492,7 @@
         </is>
       </c>
       <c r="G310" s="5" t="n">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="H310" s="4" t="inlineStr">
         <is>
@@ -24464,7 +24524,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N310" s="4" t="n"/>
+      <c r="N310" s="6" t="n">
+        <v>13.306</v>
+      </c>
       <c r="O310" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24472,14 +24534,10 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q310" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q310" s="4" t="n"/>
     </row>
     <row r="311">
       <c r="A311" s="4" t="inlineStr">
@@ -24513,7 +24571,7 @@
         </is>
       </c>
       <c r="G311" s="5" t="n">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="H311" s="4" t="inlineStr">
         <is>
@@ -24545,7 +24603,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N311" s="4" t="n"/>
+      <c r="N311" s="6" t="n">
+        <v>16.482</v>
+      </c>
       <c r="O311" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24553,14 +24613,10 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q311" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q311" s="4" t="n"/>
     </row>
     <row r="312">
       <c r="A312" s="4" t="inlineStr">
@@ -24594,7 +24650,7 @@
         </is>
       </c>
       <c r="G312" s="5" t="n">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="H312" s="4" t="inlineStr">
         <is>
@@ -24626,7 +24682,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N312" s="4" t="n"/>
+      <c r="N312" s="6" t="n">
+        <v>14.605</v>
+      </c>
       <c r="O312" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24634,14 +24692,10 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q312" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q312" s="4" t="n"/>
     </row>
     <row r="313">
       <c r="A313" s="4" t="inlineStr">
@@ -24675,7 +24729,7 @@
         </is>
       </c>
       <c r="G313" s="5" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="H313" s="4" t="inlineStr">
         <is>
@@ -24707,7 +24761,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N313" s="4" t="n"/>
+      <c r="N313" s="6" t="n">
+        <v>14.109</v>
+      </c>
       <c r="O313" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24715,14 +24771,10 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q313" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q313" s="4" t="n"/>
     </row>
     <row r="314">
       <c r="A314" s="4" t="inlineStr">
@@ -24756,7 +24808,7 @@
         </is>
       </c>
       <c r="G314" s="5" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="H314" s="4" t="inlineStr">
         <is>
@@ -24788,7 +24840,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N314" s="4" t="n"/>
+      <c r="N314" s="6" t="n">
+        <v>18.895</v>
+      </c>
       <c r="O314" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24796,14 +24850,10 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q314" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q314" s="4" t="n"/>
     </row>
     <row r="315">
       <c r="A315" s="4" t="inlineStr">
@@ -24837,7 +24887,7 @@
         </is>
       </c>
       <c r="G315" s="5" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="H315" s="4" t="inlineStr">
         <is>
@@ -24869,7 +24919,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N315" s="4" t="n"/>
+      <c r="N315" s="6" t="n">
+        <v>20.483</v>
+      </c>
       <c r="O315" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24877,14 +24929,10 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q315" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q315" s="4" t="n"/>
     </row>
     <row r="316">
       <c r="A316" s="4" t="inlineStr">
@@ -24918,7 +24966,7 @@
         </is>
       </c>
       <c r="G316" s="5" t="n">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="H316" s="4" t="inlineStr">
         <is>
@@ -24950,7 +24998,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N316" s="4" t="n"/>
+      <c r="N316" s="6" t="n">
+        <v>17.974</v>
+      </c>
       <c r="O316" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -24958,14 +25008,10 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q316" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q316" s="4" t="n"/>
     </row>
     <row r="317">
       <c r="A317" s="4" t="inlineStr">
@@ -24999,7 +25045,7 @@
         </is>
       </c>
       <c r="G317" s="5" t="n">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="H317" s="4" t="inlineStr">
         <is>
@@ -25031,7 +25077,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N317" s="4" t="n"/>
+      <c r="N317" s="6" t="n">
+        <v>11.64</v>
+      </c>
       <c r="O317" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25039,14 +25087,10 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q317" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q317" s="4" t="n"/>
     </row>
     <row r="318">
       <c r="A318" s="4" t="inlineStr">
@@ -25080,7 +25124,7 @@
         </is>
       </c>
       <c r="G318" s="5" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="H318" s="4" t="inlineStr">
         <is>
@@ -25112,7 +25156,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N318" s="4" t="n"/>
+      <c r="N318" s="6" t="n">
+        <v>9.380000000000001</v>
+      </c>
       <c r="O318" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25120,14 +25166,10 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q318" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q318" s="4" t="n"/>
     </row>
     <row r="319">
       <c r="A319" s="4" t="inlineStr">
@@ -25161,7 +25203,7 @@
         </is>
       </c>
       <c r="G319" s="5" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="H319" s="4" t="inlineStr">
         <is>
@@ -25193,7 +25235,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N319" s="4" t="n"/>
+      <c r="N319" s="6" t="n">
+        <v>7.643</v>
+      </c>
       <c r="O319" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25201,14 +25245,10 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q319" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q319" s="4" t="n"/>
     </row>
     <row r="320">
       <c r="A320" s="4" t="inlineStr">
@@ -25242,7 +25282,7 @@
         </is>
       </c>
       <c r="G320" s="5" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="H320" s="4" t="inlineStr">
         <is>
@@ -25274,7 +25314,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N320" s="4" t="n"/>
+      <c r="N320" s="6" t="n">
+        <v>6.218</v>
+      </c>
       <c r="O320" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25282,14 +25324,10 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q320" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q320" s="4" t="n"/>
     </row>
     <row r="321">
       <c r="A321" s="4" t="inlineStr">
@@ -25323,7 +25361,7 @@
         </is>
       </c>
       <c r="G321" s="5" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="H321" s="4" t="inlineStr">
         <is>
@@ -25355,7 +25393,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N321" s="4" t="n"/>
+      <c r="N321" s="6" t="n">
+        <v>5.965</v>
+      </c>
       <c r="O321" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25363,14 +25403,10 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q321" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q321" s="4" t="n"/>
     </row>
     <row r="322">
       <c r="A322" s="4" t="inlineStr">
@@ -25404,7 +25440,7 @@
         </is>
       </c>
       <c r="G322" s="5" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="H322" s="4" t="inlineStr">
         <is>
@@ -25436,7 +25472,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N322" s="4" t="n"/>
+      <c r="N322" s="6" t="n">
+        <v>6.952</v>
+      </c>
       <c r="O322" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25444,14 +25482,10 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q322" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q322" s="4" t="n"/>
     </row>
     <row r="323">
       <c r="A323" s="4" t="inlineStr">
@@ -25485,7 +25519,7 @@
         </is>
       </c>
       <c r="G323" s="5" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="H323" s="4" t="inlineStr">
         <is>
@@ -25517,7 +25551,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N323" s="4" t="n"/>
+      <c r="N323" s="6" t="n">
+        <v>7.206</v>
+      </c>
       <c r="O323" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25525,14 +25561,10 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q323" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q323" s="4" t="n"/>
     </row>
     <row r="324">
       <c r="A324" s="4" t="inlineStr">
@@ -25566,7 +25598,7 @@
         </is>
       </c>
       <c r="G324" s="5" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="H324" s="4" t="inlineStr">
         <is>
@@ -25598,7 +25630,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N324" s="4" t="n"/>
+      <c r="N324" s="6" t="n">
+        <v>7.109</v>
+      </c>
       <c r="O324" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25606,14 +25640,10 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q324" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q324" s="4" t="n"/>
     </row>
     <row r="325">
       <c r="A325" s="4" t="inlineStr">
@@ -25647,7 +25677,7 @@
         </is>
       </c>
       <c r="G325" s="5" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="H325" s="4" t="inlineStr">
         <is>
@@ -25679,7 +25709,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N325" s="4" t="n"/>
+      <c r="N325" s="6" t="n">
+        <v>8.605</v>
+      </c>
       <c r="O325" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25687,14 +25719,10 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q325" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q325" s="4" t="n"/>
     </row>
     <row r="326">
       <c r="A326" s="4" t="inlineStr">
@@ -25728,7 +25756,7 @@
         </is>
       </c>
       <c r="G326" s="5" t="n">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="H326" s="4" t="inlineStr">
         <is>
@@ -25760,7 +25788,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N326" s="4" t="n"/>
+      <c r="N326" s="6" t="n">
+        <v>7.578</v>
+      </c>
       <c r="O326" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25768,14 +25798,10 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q326" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q326" s="4" t="n"/>
     </row>
     <row r="327">
       <c r="A327" s="4" t="inlineStr">
@@ -25809,7 +25835,7 @@
         </is>
       </c>
       <c r="G327" s="5" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="H327" s="4" t="inlineStr">
         <is>
@@ -25841,7 +25867,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N327" s="4" t="n"/>
+      <c r="N327" s="6" t="n">
+        <v>6.572</v>
+      </c>
       <c r="O327" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25849,14 +25877,10 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q327" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q327" s="4" t="n"/>
     </row>
     <row r="328">
       <c r="A328" s="4" t="inlineStr">
@@ -25890,7 +25914,7 @@
         </is>
       </c>
       <c r="G328" s="5" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="H328" s="4" t="inlineStr">
         <is>
@@ -25922,7 +25946,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N328" s="4" t="n"/>
+      <c r="N328" s="6" t="n">
+        <v>5.413</v>
+      </c>
       <c r="O328" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25930,14 +25956,10 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q328" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q328" s="4" t="n"/>
     </row>
     <row r="329">
       <c r="A329" s="4" t="inlineStr">
@@ -25971,7 +25993,7 @@
         </is>
       </c>
       <c r="G329" s="5" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="H329" s="4" t="inlineStr">
         <is>
@@ -26003,7 +26025,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N329" s="4" t="n"/>
+      <c r="N329" s="6" t="n">
+        <v>5.858</v>
+      </c>
       <c r="O329" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -26011,14 +26035,10 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q329" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q329" s="4" t="n"/>
     </row>
     <row r="330">
       <c r="A330" s="4" t="inlineStr">
@@ -26052,7 +26072,7 @@
         </is>
       </c>
       <c r="G330" s="5" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="H330" s="4" t="inlineStr">
         <is>
@@ -26084,7 +26104,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N330" s="4" t="n"/>
+      <c r="N330" s="6" t="n">
+        <v>6.178</v>
+      </c>
       <c r="O330" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -26092,14 +26114,10 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q330" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q330" s="4" t="n"/>
     </row>
     <row r="331">
       <c r="A331" s="4" t="inlineStr">
@@ -26133,7 +26151,7 @@
         </is>
       </c>
       <c r="G331" s="5" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="H331" s="4" t="inlineStr">
         <is>
@@ -26165,7 +26183,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N331" s="4" t="n"/>
+      <c r="N331" s="6" t="n">
+        <v>6.497</v>
+      </c>
       <c r="O331" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -26173,14 +26193,10 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q331" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q331" s="4" t="n"/>
     </row>
     <row r="332">
       <c r="A332" s="4" t="inlineStr">
@@ -26214,7 +26230,7 @@
         </is>
       </c>
       <c r="G332" s="5" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="H332" s="4" t="inlineStr">
         <is>
@@ -26246,7 +26262,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N332" s="4" t="n"/>
+      <c r="N332" s="6" t="n">
+        <v>7.907</v>
+      </c>
       <c r="O332" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -26254,14 +26272,10 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q332" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q332" s="4" t="n"/>
     </row>
     <row r="333">
       <c r="A333" s="4" t="inlineStr">
@@ -26295,7 +26309,7 @@
         </is>
       </c>
       <c r="G333" s="5" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H333" s="4" t="inlineStr">
         <is>
@@ -26327,7 +26341,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N333" s="4" t="n"/>
+      <c r="N333" s="6" t="n">
+        <v>7.541</v>
+      </c>
       <c r="O333" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -26335,14 +26351,10 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q333" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q333" s="4" t="n"/>
     </row>
     <row r="334">
       <c r="A334" s="4" t="inlineStr">
@@ -26376,7 +26388,7 @@
         </is>
       </c>
       <c r="G334" s="5" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="H334" s="4" t="inlineStr">
         <is>
@@ -26408,7 +26420,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N334" s="4" t="n"/>
+      <c r="N334" s="6" t="n">
+        <v>6.179</v>
+      </c>
       <c r="O334" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -26416,14 +26430,10 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q334" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q334" s="4" t="n"/>
     </row>
     <row r="335">
       <c r="A335" s="4" t="inlineStr">
@@ -26457,7 +26467,7 @@
         </is>
       </c>
       <c r="G335" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="H335" s="4" t="inlineStr">
         <is>
@@ -26489,7 +26499,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N335" s="4" t="n"/>
+      <c r="N335" s="6" t="n">
+        <v>5.937</v>
+      </c>
       <c r="O335" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -26497,14 +26509,10 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q335" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q335" s="4" t="n"/>
     </row>
     <row r="336">
       <c r="A336" s="4" t="inlineStr">
@@ -26538,7 +26546,7 @@
         </is>
       </c>
       <c r="G336" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="H336" s="4" t="inlineStr">
         <is>
@@ -26570,7 +26578,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N336" s="4" t="n"/>
+      <c r="N336" s="6" t="n">
+        <v>5.845</v>
+      </c>
       <c r="O336" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -26578,14 +26588,10 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q336" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q336" s="4" t="n"/>
     </row>
     <row r="337">
       <c r="A337" s="4" t="inlineStr">
@@ -26619,7 +26625,7 @@
         </is>
       </c>
       <c r="G337" s="5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="H337" s="4" t="inlineStr">
         <is>
@@ -26651,7 +26657,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N337" s="4" t="n"/>
+      <c r="N337" s="6" t="n">
+        <v>5.835</v>
+      </c>
       <c r="O337" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -26659,14 +26667,10 @@
       </c>
       <c r="P337" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q337" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q337" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -26748,7 +26752,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_genero.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_genero.xlsx
@@ -517,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q337"/>
+  <dimension ref="A1:Q336"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -715,7 +715,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2745,7 +2745,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3217,7 +3217,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3685,7 +3685,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3764,7 +3764,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3843,7 +3843,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4159,7 +4159,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4238,7 +4238,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4317,7 +4317,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4554,7 +4554,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4633,7 +4633,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4712,7 +4712,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4791,7 +4791,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4870,7 +4870,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5107,7 +5107,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5186,7 +5186,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5263,7 +5263,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5417,7 +5417,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5571,7 +5571,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5725,7 +5725,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5879,14 +5879,10 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q73" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q73" s="4" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
@@ -5960,14 +5956,10 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q74" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q74" s="4" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
@@ -6041,14 +6033,10 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q75" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q75" s="4" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
@@ -6122,14 +6110,10 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q76" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q76" s="4" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
@@ -6203,14 +6187,10 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q77" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q77" s="4" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
@@ -6284,14 +6264,10 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q78" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q78" s="4" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
@@ -6365,14 +6341,10 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q79" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q79" s="4" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
@@ -6446,14 +6418,10 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q80" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q80" s="4" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
@@ -6527,14 +6495,10 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q81" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q81" s="4" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
@@ -6608,14 +6572,10 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q82" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q82" s="4" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
@@ -6689,14 +6649,10 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q83" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q83" s="4" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
@@ -6762,7 +6718,9 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N84" s="4" t="n"/>
+      <c r="N84" s="6" t="n">
+        <v>1.06591999530792</v>
+      </c>
       <c r="O84" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -6770,14 +6728,10 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q84" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q84" s="4" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
@@ -6843,7 +6797,9 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N85" s="4" t="n"/>
+      <c r="N85" s="6" t="n">
+        <v>1.07165002822876</v>
+      </c>
       <c r="O85" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -6851,14 +6807,10 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q85" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q85" s="4" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
@@ -6924,7 +6876,9 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N86" s="4" t="n"/>
+      <c r="N86" s="6" t="n">
+        <v>1.09589004516602</v>
+      </c>
       <c r="O86" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -6932,14 +6886,10 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q86" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q86" s="4" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
@@ -7005,7 +6955,9 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N87" s="4" t="n"/>
+      <c r="N87" s="6" t="n">
+        <v>1.13256001472473</v>
+      </c>
       <c r="O87" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -7013,14 +6965,10 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q87" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q87" s="4" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
@@ -7086,7 +7034,9 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N88" s="4" t="n"/>
+      <c r="N88" s="6" t="n">
+        <v>1.13680994510651</v>
+      </c>
       <c r="O88" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -7094,14 +7044,10 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q88" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q88" s="4" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
@@ -7175,14 +7121,10 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q89" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q89" s="4" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
@@ -7256,14 +7198,10 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q90" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q90" s="4" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
@@ -7337,14 +7275,10 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q91" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q91" s="4" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
@@ -7418,14 +7352,10 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q92" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q92" s="4" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
@@ -7499,14 +7429,10 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q93" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q93" s="4" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
@@ -7580,14 +7506,10 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q94" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q94" s="4" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
@@ -7661,14 +7583,10 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q95" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q95" s="4" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
@@ -7742,14 +7660,10 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q96" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q96" s="4" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
@@ -7815,7 +7729,9 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N97" s="4" t="n"/>
+      <c r="N97" s="6" t="n">
+        <v>1.24408996105194</v>
+      </c>
       <c r="O97" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -7823,14 +7739,10 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q97" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q97" s="4" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
@@ -7896,7 +7808,9 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N98" s="4" t="n"/>
+      <c r="N98" s="6" t="n">
+        <v>1.25617003440857</v>
+      </c>
       <c r="O98" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -7904,14 +7818,10 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q98" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q98" s="4" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
@@ -7977,7 +7887,9 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N99" s="4" t="n"/>
+      <c r="N99" s="6" t="n">
+        <v>1.23227000236511</v>
+      </c>
       <c r="O99" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -7985,14 +7897,10 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q99" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q99" s="4" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
@@ -8058,7 +7966,9 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N100" s="4" t="n"/>
+      <c r="N100" s="6" t="n">
+        <v>1.23520004749298</v>
+      </c>
       <c r="O100" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8066,14 +7976,10 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q100" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q100" s="4" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
@@ -8139,7 +8045,9 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N101" s="4" t="n"/>
+      <c r="N101" s="6" t="n">
+        <v>1.23055994510651</v>
+      </c>
       <c r="O101" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8147,14 +8055,10 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q101" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q101" s="4" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
@@ -8220,7 +8124,9 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N102" s="4" t="n"/>
+      <c r="N102" s="6" t="n">
+        <v>1.23713004589081</v>
+      </c>
       <c r="O102" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8228,14 +8134,10 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q102" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q102" s="4" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
@@ -8309,14 +8211,10 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q103" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q103" s="4" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
@@ -8382,7 +8280,9 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N104" s="4" t="n"/>
+      <c r="N104" s="6" t="n">
+        <v>1.24015998840332</v>
+      </c>
       <c r="O104" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8390,14 +8290,10 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q104" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q104" s="4" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
@@ -8463,7 +8359,9 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N105" s="4" t="n"/>
+      <c r="N105" s="6" t="n">
+        <v>1.2406200170517</v>
+      </c>
       <c r="O105" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8471,14 +8369,10 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q105" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q105" s="4" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
@@ -8544,7 +8438,9 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N106" s="4" t="n"/>
+      <c r="N106" s="6" t="n">
+        <v>1.24875998497009</v>
+      </c>
       <c r="O106" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8552,14 +8448,10 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q106" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q106" s="4" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
@@ -8633,14 +8525,10 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q107" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q107" s="4" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
@@ -8714,14 +8602,10 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q108" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q108" s="4" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
@@ -8795,14 +8679,10 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q109" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q109" s="4" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
@@ -8876,14 +8756,10 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q110" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q110" s="4" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
@@ -8957,14 +8833,10 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q111" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q111" s="4" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
@@ -9030,7 +8902,9 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N112" s="4" t="n"/>
+      <c r="N112" s="6" t="n">
+        <v>1.22622001171112</v>
+      </c>
       <c r="O112" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9038,14 +8912,10 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q112" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q112" s="4" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
@@ -9111,7 +8981,9 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N113" s="4" t="n"/>
+      <c r="N113" s="6" t="n">
+        <v>1.19964003562927</v>
+      </c>
       <c r="O113" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9119,14 +8991,10 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q113" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q113" s="4" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
@@ -9192,7 +9060,9 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N114" s="4" t="n"/>
+      <c r="N114" s="6" t="n">
+        <v>1.17510998249054</v>
+      </c>
       <c r="O114" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9200,14 +9070,10 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q114" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q114" s="4" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
@@ -9273,7 +9139,9 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N115" s="4" t="n"/>
+      <c r="N115" s="6" t="n">
+        <v>1.16194999217987</v>
+      </c>
       <c r="O115" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9281,14 +9149,10 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q115" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q115" s="4" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
@@ -9354,7 +9218,9 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N116" s="4" t="n"/>
+      <c r="N116" s="6" t="n">
+        <v>1.15086996555328</v>
+      </c>
       <c r="O116" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9362,14 +9228,10 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q116" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q116" s="4" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
@@ -9435,7 +9297,9 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N117" s="4" t="n"/>
+      <c r="N117" s="6" t="n">
+        <v>1.13995003700256</v>
+      </c>
       <c r="O117" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9443,14 +9307,10 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q117" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q117" s="4" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
@@ -9516,7 +9376,9 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N118" s="4" t="n"/>
+      <c r="N118" s="6" t="n">
+        <v>1.13028001785278</v>
+      </c>
       <c r="O118" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9524,14 +9386,10 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q118" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q118" s="4" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
@@ -9597,7 +9455,9 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N119" s="4" t="n"/>
+      <c r="N119" s="6" t="n">
+        <v>1.12556004524231</v>
+      </c>
       <c r="O119" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9605,14 +9465,10 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q119" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q119" s="4" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
@@ -9678,7 +9534,9 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N120" s="4" t="n"/>
+      <c r="N120" s="6" t="n">
+        <v>1.11647999286652</v>
+      </c>
       <c r="O120" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9686,14 +9544,10 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q120" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q120" s="4" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
@@ -9759,7 +9613,9 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N121" s="4" t="n"/>
+      <c r="N121" s="6" t="n">
+        <v>1.10140001773834</v>
+      </c>
       <c r="O121" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9767,14 +9623,10 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q121" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q121" s="4" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
@@ -9840,7 +9692,9 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N122" s="4" t="n"/>
+      <c r="N122" s="6" t="n">
+        <v>1.09311997890472</v>
+      </c>
       <c r="O122" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9848,14 +9702,10 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q122" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q122" s="4" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
@@ -9921,7 +9771,9 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N123" s="4" t="n"/>
+      <c r="N123" s="6" t="n">
+        <v>1.09621000289917</v>
+      </c>
       <c r="O123" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -9929,14 +9781,10 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q123" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q123" s="4" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
@@ -10002,7 +9850,9 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N124" s="4" t="n"/>
+      <c r="N124" s="6" t="n">
+        <v>1.09371995925903</v>
+      </c>
       <c r="O124" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -10010,14 +9860,10 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q124" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q124" s="4" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
@@ -10083,7 +9929,9 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N125" s="4" t="n"/>
+      <c r="N125" s="6" t="n">
+        <v>1.09325003623962</v>
+      </c>
       <c r="O125" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -10091,14 +9939,10 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q125" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q125" s="4" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
@@ -10164,7 +10008,9 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N126" s="4" t="n"/>
+      <c r="N126" s="6" t="n">
+        <v>1.09049999713898</v>
+      </c>
       <c r="O126" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -10172,14 +10018,10 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q126" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q126" s="4" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
@@ -10245,7 +10087,9 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N127" s="4" t="n"/>
+      <c r="N127" s="6" t="n">
+        <v>1.07729995250702</v>
+      </c>
       <c r="O127" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -10253,14 +10097,10 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q127" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q127" s="4" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
@@ -10326,7 +10166,9 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N128" s="4" t="n"/>
+      <c r="N128" s="6" t="n">
+        <v>1.07729005813599</v>
+      </c>
       <c r="O128" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -10334,14 +10176,10 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q128" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q128" s="4" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
@@ -10407,7 +10245,9 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N129" s="4" t="n"/>
+      <c r="N129" s="6" t="n">
+        <v>1.07924997806549</v>
+      </c>
       <c r="O129" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -10415,14 +10255,10 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q129" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q129" s="4" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
@@ -10488,7 +10324,9 @@
           <t>Ratio niñas-niños en educación secundaria</t>
         </is>
       </c>
-      <c r="N130" s="4" t="n"/>
+      <c r="N130" s="6" t="n">
+        <v>1.0806200504303</v>
+      </c>
       <c r="O130" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -10496,14 +10334,10 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q130" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q130" s="4" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
@@ -10577,14 +10411,10 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q131" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q131" s="4" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
@@ -10658,14 +10488,10 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q132" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q132" s="4" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
@@ -10739,14 +10565,10 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q133" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q133" s="4" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
@@ -10820,14 +10642,10 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q134" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q134" s="4" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
@@ -10901,14 +10719,10 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q135" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q135" s="4" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
@@ -10982,14 +10796,10 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q136" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q136" s="4" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
@@ -11063,14 +10873,10 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q137" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q137" s="4" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
@@ -11144,14 +10950,10 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q138" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q138" s="4" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
@@ -11185,7 +10987,7 @@
         </is>
       </c>
       <c r="G139" s="5" t="n">
-        <v>2026</v>
+        <v>1960</v>
       </c>
       <c r="H139" s="4" t="inlineStr">
         <is>
@@ -11199,22 +11001,22 @@
       </c>
       <c r="J139" s="4" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Participación política</t>
         </is>
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>educacion</t>
+          <t>participacion_politica</t>
         </is>
       </c>
       <c r="L139" s="4" t="inlineStr">
         <is>
-          <t>SE.ENR.SECO.FM.ZS</t>
+          <t>SG.GEN.PARL.ZS</t>
         </is>
       </c>
       <c r="M139" s="4" t="inlineStr">
         <is>
-          <t>Ratio niñas-niños en educación secundaria</t>
+          <t>Mujeres en parlamentos nacionales</t>
         </is>
       </c>
       <c r="N139" s="4" t="n"/>
@@ -11225,14 +11027,10 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q139" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q139" s="4" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
@@ -11266,7 +11064,7 @@
         </is>
       </c>
       <c r="G140" s="5" t="n">
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="H140" s="4" t="inlineStr">
         <is>
@@ -11306,7 +11104,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11343,7 +11141,7 @@
         </is>
       </c>
       <c r="G141" s="5" t="n">
-        <v>1961</v>
+        <v>1962</v>
       </c>
       <c r="H141" s="4" t="inlineStr">
         <is>
@@ -11383,7 +11181,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11420,7 +11218,7 @@
         </is>
       </c>
       <c r="G142" s="5" t="n">
-        <v>1962</v>
+        <v>1963</v>
       </c>
       <c r="H142" s="4" t="inlineStr">
         <is>
@@ -11460,7 +11258,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11497,7 +11295,7 @@
         </is>
       </c>
       <c r="G143" s="5" t="n">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="H143" s="4" t="inlineStr">
         <is>
@@ -11537,7 +11335,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11574,7 +11372,7 @@
         </is>
       </c>
       <c r="G144" s="5" t="n">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="H144" s="4" t="inlineStr">
         <is>
@@ -11614,7 +11412,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11651,7 +11449,7 @@
         </is>
       </c>
       <c r="G145" s="5" t="n">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="H145" s="4" t="inlineStr">
         <is>
@@ -11691,7 +11489,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11728,7 +11526,7 @@
         </is>
       </c>
       <c r="G146" s="5" t="n">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="H146" s="4" t="inlineStr">
         <is>
@@ -11768,7 +11566,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11805,7 +11603,7 @@
         </is>
       </c>
       <c r="G147" s="5" t="n">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="H147" s="4" t="inlineStr">
         <is>
@@ -11845,7 +11643,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11882,7 +11680,7 @@
         </is>
       </c>
       <c r="G148" s="5" t="n">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="H148" s="4" t="inlineStr">
         <is>
@@ -11922,7 +11720,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11959,7 +11757,7 @@
         </is>
       </c>
       <c r="G149" s="5" t="n">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="H149" s="4" t="inlineStr">
         <is>
@@ -11999,7 +11797,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -12036,7 +11834,7 @@
         </is>
       </c>
       <c r="G150" s="5" t="n">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="H150" s="4" t="inlineStr">
         <is>
@@ -12076,7 +11874,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -12113,7 +11911,7 @@
         </is>
       </c>
       <c r="G151" s="5" t="n">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="H151" s="4" t="inlineStr">
         <is>
@@ -12153,7 +11951,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12190,7 +11988,7 @@
         </is>
       </c>
       <c r="G152" s="5" t="n">
-        <v>1972</v>
+        <v>1973</v>
       </c>
       <c r="H152" s="4" t="inlineStr">
         <is>
@@ -12230,7 +12028,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12267,7 +12065,7 @@
         </is>
       </c>
       <c r="G153" s="5" t="n">
-        <v>1973</v>
+        <v>1974</v>
       </c>
       <c r="H153" s="4" t="inlineStr">
         <is>
@@ -12307,7 +12105,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12344,7 +12142,7 @@
         </is>
       </c>
       <c r="G154" s="5" t="n">
-        <v>1974</v>
+        <v>1975</v>
       </c>
       <c r="H154" s="4" t="inlineStr">
         <is>
@@ -12384,7 +12182,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12421,7 +12219,7 @@
         </is>
       </c>
       <c r="G155" s="5" t="n">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="H155" s="4" t="inlineStr">
         <is>
@@ -12461,7 +12259,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12498,7 +12296,7 @@
         </is>
       </c>
       <c r="G156" s="5" t="n">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="H156" s="4" t="inlineStr">
         <is>
@@ -12538,7 +12336,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12575,7 +12373,7 @@
         </is>
       </c>
       <c r="G157" s="5" t="n">
-        <v>1977</v>
+        <v>1978</v>
       </c>
       <c r="H157" s="4" t="inlineStr">
         <is>
@@ -12615,7 +12413,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12652,7 +12450,7 @@
         </is>
       </c>
       <c r="G158" s="5" t="n">
-        <v>1978</v>
+        <v>1979</v>
       </c>
       <c r="H158" s="4" t="inlineStr">
         <is>
@@ -12692,7 +12490,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12729,7 +12527,7 @@
         </is>
       </c>
       <c r="G159" s="5" t="n">
-        <v>1979</v>
+        <v>1980</v>
       </c>
       <c r="H159" s="4" t="inlineStr">
         <is>
@@ -12769,7 +12567,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12806,7 +12604,7 @@
         </is>
       </c>
       <c r="G160" s="5" t="n">
-        <v>1980</v>
+        <v>1981</v>
       </c>
       <c r="H160" s="4" t="inlineStr">
         <is>
@@ -12846,7 +12644,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12883,7 +12681,7 @@
         </is>
       </c>
       <c r="G161" s="5" t="n">
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="H161" s="4" t="inlineStr">
         <is>
@@ -12923,7 +12721,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12960,7 +12758,7 @@
         </is>
       </c>
       <c r="G162" s="5" t="n">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="H162" s="4" t="inlineStr">
         <is>
@@ -13000,7 +12798,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -13037,7 +12835,7 @@
         </is>
       </c>
       <c r="G163" s="5" t="n">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="H163" s="4" t="inlineStr">
         <is>
@@ -13077,7 +12875,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -13114,7 +12912,7 @@
         </is>
       </c>
       <c r="G164" s="5" t="n">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="H164" s="4" t="inlineStr">
         <is>
@@ -13154,7 +12952,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13191,7 +12989,7 @@
         </is>
       </c>
       <c r="G165" s="5" t="n">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="H165" s="4" t="inlineStr">
         <is>
@@ -13231,7 +13029,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13268,7 +13066,7 @@
         </is>
       </c>
       <c r="G166" s="5" t="n">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="H166" s="4" t="inlineStr">
         <is>
@@ -13308,7 +13106,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13345,7 +13143,7 @@
         </is>
       </c>
       <c r="G167" s="5" t="n">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="H167" s="4" t="inlineStr">
         <is>
@@ -13385,7 +13183,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13422,7 +13220,7 @@
         </is>
       </c>
       <c r="G168" s="5" t="n">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="H168" s="4" t="inlineStr">
         <is>
@@ -13462,7 +13260,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13499,7 +13297,7 @@
         </is>
       </c>
       <c r="G169" s="5" t="n">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="H169" s="4" t="inlineStr">
         <is>
@@ -13539,7 +13337,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13576,7 +13374,7 @@
         </is>
       </c>
       <c r="G170" s="5" t="n">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="H170" s="4" t="inlineStr">
         <is>
@@ -13616,7 +13414,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13653,7 +13451,7 @@
         </is>
       </c>
       <c r="G171" s="5" t="n">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="H171" s="4" t="inlineStr">
         <is>
@@ -13693,7 +13491,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13730,7 +13528,7 @@
         </is>
       </c>
       <c r="G172" s="5" t="n">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="H172" s="4" t="inlineStr">
         <is>
@@ -13770,7 +13568,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13807,7 +13605,7 @@
         </is>
       </c>
       <c r="G173" s="5" t="n">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="H173" s="4" t="inlineStr">
         <is>
@@ -13847,7 +13645,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13884,7 +13682,7 @@
         </is>
       </c>
       <c r="G174" s="5" t="n">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="H174" s="4" t="inlineStr">
         <is>
@@ -13924,7 +13722,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13961,7 +13759,7 @@
         </is>
       </c>
       <c r="G175" s="5" t="n">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="H175" s="4" t="inlineStr">
         <is>
@@ -14001,7 +13799,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -14038,7 +13836,7 @@
         </is>
       </c>
       <c r="G176" s="5" t="n">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="H176" s="4" t="inlineStr">
         <is>
@@ -14070,7 +13868,9 @@
           <t>Mujeres en parlamentos nacionales</t>
         </is>
       </c>
-      <c r="N176" s="4" t="n"/>
+      <c r="N176" s="6" t="n">
+        <v>5.91133004926108</v>
+      </c>
       <c r="O176" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -14078,7 +13878,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -14115,7 +13915,7 @@
         </is>
       </c>
       <c r="G177" s="5" t="n">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="H177" s="4" t="inlineStr">
         <is>
@@ -14157,7 +13957,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14194,7 +13994,7 @@
         </is>
       </c>
       <c r="G178" s="5" t="n">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="H178" s="4" t="inlineStr">
         <is>
@@ -14227,7 +14027,7 @@
         </is>
       </c>
       <c r="N178" s="6" t="n">
-        <v>5.91133004926108</v>
+        <v>12.1359223300971</v>
       </c>
       <c r="O178" s="4" t="inlineStr">
         <is>
@@ -14236,7 +14036,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14273,7 +14073,7 @@
         </is>
       </c>
       <c r="G179" s="5" t="n">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="H179" s="4" t="inlineStr">
         <is>
@@ -14305,9 +14105,7 @@
           <t>Mujeres en parlamentos nacionales</t>
         </is>
       </c>
-      <c r="N179" s="6" t="n">
-        <v>12.1359223300971</v>
-      </c>
+      <c r="N179" s="4" t="n"/>
       <c r="O179" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -14315,7 +14113,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14352,7 +14150,7 @@
         </is>
       </c>
       <c r="G180" s="5" t="n">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="H180" s="4" t="inlineStr">
         <is>
@@ -14384,7 +14182,9 @@
           <t>Mujeres en parlamentos nacionales</t>
         </is>
       </c>
-      <c r="N180" s="4" t="n"/>
+      <c r="N180" s="6" t="n">
+        <v>9.696969696969701</v>
+      </c>
       <c r="O180" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -14392,7 +14192,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14429,7 +14229,7 @@
         </is>
       </c>
       <c r="G181" s="5" t="n">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="H181" s="4" t="inlineStr">
         <is>
@@ -14471,7 +14271,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14508,7 +14308,7 @@
         </is>
       </c>
       <c r="G182" s="5" t="n">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="H182" s="4" t="inlineStr">
         <is>
@@ -14550,7 +14350,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14587,7 +14387,7 @@
         </is>
       </c>
       <c r="G183" s="5" t="n">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="H183" s="4" t="inlineStr">
         <is>
@@ -14629,7 +14429,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14666,7 +14466,7 @@
         </is>
       </c>
       <c r="G184" s="5" t="n">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="H184" s="4" t="inlineStr">
         <is>
@@ -14699,7 +14499,7 @@
         </is>
       </c>
       <c r="N184" s="6" t="n">
-        <v>9.696969696969701</v>
+        <v>17.3652694610778</v>
       </c>
       <c r="O184" s="4" t="inlineStr">
         <is>
@@ -14708,7 +14508,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14745,7 +14545,7 @@
         </is>
       </c>
       <c r="G185" s="5" t="n">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="H185" s="4" t="inlineStr">
         <is>
@@ -14778,7 +14578,7 @@
         </is>
       </c>
       <c r="N185" s="6" t="n">
-        <v>17.3652694610778</v>
+        <v>17.9640718562874</v>
       </c>
       <c r="O185" s="4" t="inlineStr">
         <is>
@@ -14787,7 +14587,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14824,7 +14624,7 @@
         </is>
       </c>
       <c r="G186" s="5" t="n">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="H186" s="4" t="inlineStr">
         <is>
@@ -14857,7 +14657,7 @@
         </is>
       </c>
       <c r="N186" s="6" t="n">
-        <v>17.9640718562874</v>
+        <v>18.562874251497</v>
       </c>
       <c r="O186" s="4" t="inlineStr">
         <is>
@@ -14866,7 +14666,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14903,7 +14703,7 @@
         </is>
       </c>
       <c r="G187" s="5" t="n">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="H187" s="4" t="inlineStr">
         <is>
@@ -14945,7 +14745,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14982,7 +14782,7 @@
         </is>
       </c>
       <c r="G188" s="5" t="n">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="H188" s="4" t="inlineStr">
         <is>
@@ -15015,7 +14815,7 @@
         </is>
       </c>
       <c r="N188" s="6" t="n">
-        <v>18.562874251497</v>
+        <v>17.4698795180723</v>
       </c>
       <c r="O188" s="4" t="inlineStr">
         <is>
@@ -15024,7 +14824,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -15061,7 +14861,7 @@
         </is>
       </c>
       <c r="G189" s="5" t="n">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="H189" s="4" t="inlineStr">
         <is>
@@ -15094,7 +14894,7 @@
         </is>
       </c>
       <c r="N189" s="6" t="n">
-        <v>17.4698795180723</v>
+        <v>16.969696969697</v>
       </c>
       <c r="O189" s="4" t="inlineStr">
         <is>
@@ -15103,7 +14903,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15140,7 +14940,7 @@
         </is>
       </c>
       <c r="G190" s="5" t="n">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="H190" s="4" t="inlineStr">
         <is>
@@ -15182,7 +14982,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15219,7 +15019,7 @@
         </is>
       </c>
       <c r="G191" s="5" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="H191" s="4" t="inlineStr">
         <is>
@@ -15261,7 +15061,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15298,7 +15098,7 @@
         </is>
       </c>
       <c r="G192" s="5" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="H192" s="4" t="inlineStr">
         <is>
@@ -15340,7 +15140,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15377,7 +15177,7 @@
         </is>
       </c>
       <c r="G193" s="5" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="H193" s="4" t="inlineStr">
         <is>
@@ -15419,7 +15219,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15456,7 +15256,7 @@
         </is>
       </c>
       <c r="G194" s="5" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="H194" s="4" t="inlineStr">
         <is>
@@ -15498,7 +15298,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15535,7 +15335,7 @@
         </is>
       </c>
       <c r="G195" s="5" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="H195" s="4" t="inlineStr">
         <is>
@@ -15568,7 +15368,7 @@
         </is>
       </c>
       <c r="N195" s="6" t="n">
-        <v>16.969696969697</v>
+        <v>14.3712574850299</v>
       </c>
       <c r="O195" s="4" t="inlineStr">
         <is>
@@ -15577,7 +15377,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15614,7 +15414,7 @@
         </is>
       </c>
       <c r="G196" s="5" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="H196" s="4" t="inlineStr">
         <is>
@@ -15647,7 +15447,7 @@
         </is>
       </c>
       <c r="N196" s="6" t="n">
-        <v>14.3712574850299</v>
+        <v>22.1556886227545</v>
       </c>
       <c r="O196" s="4" t="inlineStr">
         <is>
@@ -15656,7 +15456,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15693,7 +15493,7 @@
         </is>
       </c>
       <c r="G197" s="5" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="H197" s="4" t="inlineStr">
         <is>
@@ -15735,7 +15535,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15772,7 +15572,7 @@
         </is>
       </c>
       <c r="G198" s="5" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="H198" s="4" t="inlineStr">
         <is>
@@ -15814,7 +15614,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15851,7 +15651,7 @@
         </is>
       </c>
       <c r="G199" s="5" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="H199" s="4" t="inlineStr">
         <is>
@@ -15893,7 +15693,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15930,7 +15730,7 @@
         </is>
       </c>
       <c r="G200" s="5" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="H200" s="4" t="inlineStr">
         <is>
@@ -15972,7 +15772,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -16009,7 +15809,7 @@
         </is>
       </c>
       <c r="G201" s="5" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="H201" s="4" t="inlineStr">
         <is>
@@ -16041,9 +15841,7 @@
           <t>Mujeres en parlamentos nacionales</t>
         </is>
       </c>
-      <c r="N201" s="6" t="n">
-        <v>22.1556886227545</v>
-      </c>
+      <c r="N201" s="4" t="n"/>
       <c r="O201" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -16051,7 +15849,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -16088,7 +15886,7 @@
         </is>
       </c>
       <c r="G202" s="5" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="H202" s="4" t="inlineStr">
         <is>
@@ -16128,7 +15926,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16165,7 +15963,7 @@
         </is>
       </c>
       <c r="G203" s="5" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="H203" s="4" t="inlineStr">
         <is>
@@ -16205,7 +16003,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16242,7 +16040,7 @@
         </is>
       </c>
       <c r="G204" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="H204" s="4" t="inlineStr">
         <is>
@@ -16274,7 +16072,9 @@
           <t>Mujeres en parlamentos nacionales</t>
         </is>
       </c>
-      <c r="N204" s="4" t="n"/>
+      <c r="N204" s="6" t="n">
+        <v>32.129963898917</v>
+      </c>
       <c r="O204" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -16282,7 +16082,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16319,7 +16119,7 @@
         </is>
       </c>
       <c r="G205" s="5" t="n">
-        <v>2025</v>
+        <v>1960</v>
       </c>
       <c r="H205" s="4" t="inlineStr">
         <is>
@@ -16333,27 +16133,25 @@
       </c>
       <c r="J205" s="4" t="inlineStr">
         <is>
-          <t>Participación política</t>
+          <t>Mercado laboral</t>
         </is>
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>participacion_politica</t>
+          <t>mercado_laboral</t>
         </is>
       </c>
       <c r="L205" s="4" t="inlineStr">
         <is>
-          <t>SG.GEN.PARL.ZS</t>
+          <t>SL.TLF.CACT.FE.ZS</t>
         </is>
       </c>
       <c r="M205" s="4" t="inlineStr">
         <is>
-          <t>Mujeres en parlamentos nacionales</t>
-        </is>
-      </c>
-      <c r="N205" s="6" t="n">
-        <v>32.129963898917</v>
-      </c>
+          <t>Participación laboral femenina</t>
+        </is>
+      </c>
+      <c r="N205" s="4" t="n"/>
       <c r="O205" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -16361,7 +16159,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16398,7 +16196,7 @@
         </is>
       </c>
       <c r="G206" s="5" t="n">
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="H206" s="4" t="inlineStr">
         <is>
@@ -16438,7 +16236,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16475,7 +16273,7 @@
         </is>
       </c>
       <c r="G207" s="5" t="n">
-        <v>1961</v>
+        <v>1962</v>
       </c>
       <c r="H207" s="4" t="inlineStr">
         <is>
@@ -16515,7 +16313,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16552,7 +16350,7 @@
         </is>
       </c>
       <c r="G208" s="5" t="n">
-        <v>1962</v>
+        <v>1963</v>
       </c>
       <c r="H208" s="4" t="inlineStr">
         <is>
@@ -16592,7 +16390,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16629,7 +16427,7 @@
         </is>
       </c>
       <c r="G209" s="5" t="n">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="H209" s="4" t="inlineStr">
         <is>
@@ -16669,7 +16467,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16706,7 +16504,7 @@
         </is>
       </c>
       <c r="G210" s="5" t="n">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="H210" s="4" t="inlineStr">
         <is>
@@ -16746,7 +16544,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16783,7 +16581,7 @@
         </is>
       </c>
       <c r="G211" s="5" t="n">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="H211" s="4" t="inlineStr">
         <is>
@@ -16823,7 +16621,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16860,7 +16658,7 @@
         </is>
       </c>
       <c r="G212" s="5" t="n">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="H212" s="4" t="inlineStr">
         <is>
@@ -16900,7 +16698,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16937,7 +16735,7 @@
         </is>
       </c>
       <c r="G213" s="5" t="n">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="H213" s="4" t="inlineStr">
         <is>
@@ -16977,7 +16775,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -17014,7 +16812,7 @@
         </is>
       </c>
       <c r="G214" s="5" t="n">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="H214" s="4" t="inlineStr">
         <is>
@@ -17054,7 +16852,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -17091,7 +16889,7 @@
         </is>
       </c>
       <c r="G215" s="5" t="n">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="H215" s="4" t="inlineStr">
         <is>
@@ -17131,7 +16929,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17168,7 +16966,7 @@
         </is>
       </c>
       <c r="G216" s="5" t="n">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="H216" s="4" t="inlineStr">
         <is>
@@ -17208,7 +17006,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17245,7 +17043,7 @@
         </is>
       </c>
       <c r="G217" s="5" t="n">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="H217" s="4" t="inlineStr">
         <is>
@@ -17285,7 +17083,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17322,7 +17120,7 @@
         </is>
       </c>
       <c r="G218" s="5" t="n">
-        <v>1972</v>
+        <v>1973</v>
       </c>
       <c r="H218" s="4" t="inlineStr">
         <is>
@@ -17362,7 +17160,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17399,7 +17197,7 @@
         </is>
       </c>
       <c r="G219" s="5" t="n">
-        <v>1973</v>
+        <v>1974</v>
       </c>
       <c r="H219" s="4" t="inlineStr">
         <is>
@@ -17439,7 +17237,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17476,7 +17274,7 @@
         </is>
       </c>
       <c r="G220" s="5" t="n">
-        <v>1974</v>
+        <v>1975</v>
       </c>
       <c r="H220" s="4" t="inlineStr">
         <is>
@@ -17516,7 +17314,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17553,7 +17351,7 @@
         </is>
       </c>
       <c r="G221" s="5" t="n">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="H221" s="4" t="inlineStr">
         <is>
@@ -17593,7 +17391,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17630,7 +17428,7 @@
         </is>
       </c>
       <c r="G222" s="5" t="n">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="H222" s="4" t="inlineStr">
         <is>
@@ -17670,7 +17468,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17707,7 +17505,7 @@
         </is>
       </c>
       <c r="G223" s="5" t="n">
-        <v>1977</v>
+        <v>1978</v>
       </c>
       <c r="H223" s="4" t="inlineStr">
         <is>
@@ -17747,7 +17545,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17784,7 +17582,7 @@
         </is>
       </c>
       <c r="G224" s="5" t="n">
-        <v>1978</v>
+        <v>1979</v>
       </c>
       <c r="H224" s="4" t="inlineStr">
         <is>
@@ -17824,7 +17622,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17861,7 +17659,7 @@
         </is>
       </c>
       <c r="G225" s="5" t="n">
-        <v>1979</v>
+        <v>1980</v>
       </c>
       <c r="H225" s="4" t="inlineStr">
         <is>
@@ -17901,7 +17699,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17938,7 +17736,7 @@
         </is>
       </c>
       <c r="G226" s="5" t="n">
-        <v>1980</v>
+        <v>1981</v>
       </c>
       <c r="H226" s="4" t="inlineStr">
         <is>
@@ -17978,7 +17776,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -18015,7 +17813,7 @@
         </is>
       </c>
       <c r="G227" s="5" t="n">
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="H227" s="4" t="inlineStr">
         <is>
@@ -18055,7 +17853,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -18092,7 +17890,7 @@
         </is>
       </c>
       <c r="G228" s="5" t="n">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="H228" s="4" t="inlineStr">
         <is>
@@ -18132,7 +17930,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18169,7 +17967,7 @@
         </is>
       </c>
       <c r="G229" s="5" t="n">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="H229" s="4" t="inlineStr">
         <is>
@@ -18209,7 +18007,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18246,7 +18044,7 @@
         </is>
       </c>
       <c r="G230" s="5" t="n">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="H230" s="4" t="inlineStr">
         <is>
@@ -18286,7 +18084,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18323,7 +18121,7 @@
         </is>
       </c>
       <c r="G231" s="5" t="n">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="H231" s="4" t="inlineStr">
         <is>
@@ -18363,7 +18161,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18400,7 +18198,7 @@
         </is>
       </c>
       <c r="G232" s="5" t="n">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="H232" s="4" t="inlineStr">
         <is>
@@ -18440,7 +18238,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18477,7 +18275,7 @@
         </is>
       </c>
       <c r="G233" s="5" t="n">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="H233" s="4" t="inlineStr">
         <is>
@@ -18517,7 +18315,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18554,7 +18352,7 @@
         </is>
       </c>
       <c r="G234" s="5" t="n">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="H234" s="4" t="inlineStr">
         <is>
@@ -18594,7 +18392,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18631,7 +18429,7 @@
         </is>
       </c>
       <c r="G235" s="5" t="n">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="H235" s="4" t="inlineStr">
         <is>
@@ -18663,7 +18461,9 @@
           <t>Participación laboral femenina</t>
         </is>
       </c>
-      <c r="N235" s="4" t="n"/>
+      <c r="N235" s="6" t="n">
+        <v>48.56</v>
+      </c>
       <c r="O235" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -18671,7 +18471,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18708,7 +18508,7 @@
         </is>
       </c>
       <c r="G236" s="5" t="n">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="H236" s="4" t="inlineStr">
         <is>
@@ -18741,7 +18541,7 @@
         </is>
       </c>
       <c r="N236" s="6" t="n">
-        <v>48.56</v>
+        <v>49.027</v>
       </c>
       <c r="O236" s="4" t="inlineStr">
         <is>
@@ -18750,7 +18550,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18787,7 +18587,7 @@
         </is>
       </c>
       <c r="G237" s="5" t="n">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="H237" s="4" t="inlineStr">
         <is>
@@ -18820,7 +18620,7 @@
         </is>
       </c>
       <c r="N237" s="6" t="n">
-        <v>49.027</v>
+        <v>49.439</v>
       </c>
       <c r="O237" s="4" t="inlineStr">
         <is>
@@ -18829,7 +18629,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18866,7 +18666,7 @@
         </is>
       </c>
       <c r="G238" s="5" t="n">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="H238" s="4" t="inlineStr">
         <is>
@@ -18899,7 +18699,7 @@
         </is>
       </c>
       <c r="N238" s="6" t="n">
-        <v>49.439</v>
+        <v>49.121</v>
       </c>
       <c r="O238" s="4" t="inlineStr">
         <is>
@@ -18908,7 +18708,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18945,7 +18745,7 @@
         </is>
       </c>
       <c r="G239" s="5" t="n">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="H239" s="4" t="inlineStr">
         <is>
@@ -18978,7 +18778,7 @@
         </is>
       </c>
       <c r="N239" s="6" t="n">
-        <v>49.121</v>
+        <v>48.519</v>
       </c>
       <c r="O239" s="4" t="inlineStr">
         <is>
@@ -18987,7 +18787,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -19024,7 +18824,7 @@
         </is>
       </c>
       <c r="G240" s="5" t="n">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="H240" s="4" t="inlineStr">
         <is>
@@ -19057,7 +18857,7 @@
         </is>
       </c>
       <c r="N240" s="6" t="n">
-        <v>48.519</v>
+        <v>48.502</v>
       </c>
       <c r="O240" s="4" t="inlineStr">
         <is>
@@ -19066,7 +18866,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -19103,7 +18903,7 @@
         </is>
       </c>
       <c r="G241" s="5" t="n">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="H241" s="4" t="inlineStr">
         <is>
@@ -19136,7 +18936,7 @@
         </is>
       </c>
       <c r="N241" s="6" t="n">
-        <v>48.502</v>
+        <v>48.683</v>
       </c>
       <c r="O241" s="4" t="inlineStr">
         <is>
@@ -19145,7 +18945,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19182,7 +18982,7 @@
         </is>
       </c>
       <c r="G242" s="5" t="n">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="H242" s="4" t="inlineStr">
         <is>
@@ -19215,7 +19015,7 @@
         </is>
       </c>
       <c r="N242" s="6" t="n">
-        <v>48.683</v>
+        <v>48.743</v>
       </c>
       <c r="O242" s="4" t="inlineStr">
         <is>
@@ -19224,7 +19024,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19261,7 +19061,7 @@
         </is>
       </c>
       <c r="G243" s="5" t="n">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="H243" s="4" t="inlineStr">
         <is>
@@ -19294,7 +19094,7 @@
         </is>
       </c>
       <c r="N243" s="6" t="n">
-        <v>48.743</v>
+        <v>48.976</v>
       </c>
       <c r="O243" s="4" t="inlineStr">
         <is>
@@ -19303,7 +19103,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19340,7 +19140,7 @@
         </is>
       </c>
       <c r="G244" s="5" t="n">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="H244" s="4" t="inlineStr">
         <is>
@@ -19373,7 +19173,7 @@
         </is>
       </c>
       <c r="N244" s="6" t="n">
-        <v>48.976</v>
+        <v>48.119</v>
       </c>
       <c r="O244" s="4" t="inlineStr">
         <is>
@@ -19382,7 +19182,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19419,7 +19219,7 @@
         </is>
       </c>
       <c r="G245" s="5" t="n">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="H245" s="4" t="inlineStr">
         <is>
@@ -19452,7 +19252,7 @@
         </is>
       </c>
       <c r="N245" s="6" t="n">
-        <v>48.119</v>
+        <v>47.914</v>
       </c>
       <c r="O245" s="4" t="inlineStr">
         <is>
@@ -19461,7 +19261,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19498,7 +19298,7 @@
         </is>
       </c>
       <c r="G246" s="5" t="n">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="H246" s="4" t="inlineStr">
         <is>
@@ -19531,7 +19331,7 @@
         </is>
       </c>
       <c r="N246" s="6" t="n">
-        <v>47.914</v>
+        <v>48.527</v>
       </c>
       <c r="O246" s="4" t="inlineStr">
         <is>
@@ -19540,7 +19340,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19577,7 +19377,7 @@
         </is>
       </c>
       <c r="G247" s="5" t="n">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="H247" s="4" t="inlineStr">
         <is>
@@ -19610,7 +19410,7 @@
         </is>
       </c>
       <c r="N247" s="6" t="n">
-        <v>48.527</v>
+        <v>47.765</v>
       </c>
       <c r="O247" s="4" t="inlineStr">
         <is>
@@ -19619,7 +19419,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19656,7 +19456,7 @@
         </is>
       </c>
       <c r="G248" s="5" t="n">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="H248" s="4" t="inlineStr">
         <is>
@@ -19689,7 +19489,7 @@
         </is>
       </c>
       <c r="N248" s="6" t="n">
-        <v>47.765</v>
+        <v>46.462</v>
       </c>
       <c r="O248" s="4" t="inlineStr">
         <is>
@@ -19698,7 +19498,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19735,7 +19535,7 @@
         </is>
       </c>
       <c r="G249" s="5" t="n">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="H249" s="4" t="inlineStr">
         <is>
@@ -19768,7 +19568,7 @@
         </is>
       </c>
       <c r="N249" s="6" t="n">
-        <v>46.462</v>
+        <v>47.558</v>
       </c>
       <c r="O249" s="4" t="inlineStr">
         <is>
@@ -19777,7 +19577,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19814,7 +19614,7 @@
         </is>
       </c>
       <c r="G250" s="5" t="n">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="H250" s="4" t="inlineStr">
         <is>
@@ -19847,7 +19647,7 @@
         </is>
       </c>
       <c r="N250" s="6" t="n">
-        <v>47.558</v>
+        <v>49.457</v>
       </c>
       <c r="O250" s="4" t="inlineStr">
         <is>
@@ -19856,7 +19656,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19893,7 +19693,7 @@
         </is>
       </c>
       <c r="G251" s="5" t="n">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="H251" s="4" t="inlineStr">
         <is>
@@ -19926,7 +19726,7 @@
         </is>
       </c>
       <c r="N251" s="6" t="n">
-        <v>49.457</v>
+        <v>50.019</v>
       </c>
       <c r="O251" s="4" t="inlineStr">
         <is>
@@ -19935,7 +19735,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19972,7 +19772,7 @@
         </is>
       </c>
       <c r="G252" s="5" t="n">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="H252" s="4" t="inlineStr">
         <is>
@@ -20005,7 +19805,7 @@
         </is>
       </c>
       <c r="N252" s="6" t="n">
-        <v>50.019</v>
+        <v>49.726</v>
       </c>
       <c r="O252" s="4" t="inlineStr">
         <is>
@@ -20014,7 +19814,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -20051,7 +19851,7 @@
         </is>
       </c>
       <c r="G253" s="5" t="n">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="H253" s="4" t="inlineStr">
         <is>
@@ -20084,7 +19884,7 @@
         </is>
       </c>
       <c r="N253" s="6" t="n">
-        <v>49.726</v>
+        <v>49.734</v>
       </c>
       <c r="O253" s="4" t="inlineStr">
         <is>
@@ -20093,7 +19893,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -20130,7 +19930,7 @@
         </is>
       </c>
       <c r="G254" s="5" t="n">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="H254" s="4" t="inlineStr">
         <is>
@@ -20163,7 +19963,7 @@
         </is>
       </c>
       <c r="N254" s="6" t="n">
-        <v>49.734</v>
+        <v>50.004</v>
       </c>
       <c r="O254" s="4" t="inlineStr">
         <is>
@@ -20172,7 +19972,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20209,7 +20009,7 @@
         </is>
       </c>
       <c r="G255" s="5" t="n">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="H255" s="4" t="inlineStr">
         <is>
@@ -20242,7 +20042,7 @@
         </is>
       </c>
       <c r="N255" s="6" t="n">
-        <v>50.004</v>
+        <v>49.601</v>
       </c>
       <c r="O255" s="4" t="inlineStr">
         <is>
@@ -20251,7 +20051,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20288,7 +20088,7 @@
         </is>
       </c>
       <c r="G256" s="5" t="n">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="H256" s="4" t="inlineStr">
         <is>
@@ -20321,7 +20121,7 @@
         </is>
       </c>
       <c r="N256" s="6" t="n">
-        <v>49.601</v>
+        <v>49.643</v>
       </c>
       <c r="O256" s="4" t="inlineStr">
         <is>
@@ -20330,7 +20130,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20367,7 +20167,7 @@
         </is>
       </c>
       <c r="G257" s="5" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="H257" s="4" t="inlineStr">
         <is>
@@ -20400,7 +20200,7 @@
         </is>
       </c>
       <c r="N257" s="6" t="n">
-        <v>49.643</v>
+        <v>49.493</v>
       </c>
       <c r="O257" s="4" t="inlineStr">
         <is>
@@ -20409,7 +20209,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20446,7 +20246,7 @@
         </is>
       </c>
       <c r="G258" s="5" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="H258" s="4" t="inlineStr">
         <is>
@@ -20479,7 +20279,7 @@
         </is>
       </c>
       <c r="N258" s="6" t="n">
-        <v>49.493</v>
+        <v>49.084</v>
       </c>
       <c r="O258" s="4" t="inlineStr">
         <is>
@@ -20488,7 +20288,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20525,7 +20325,7 @@
         </is>
       </c>
       <c r="G259" s="5" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="H259" s="4" t="inlineStr">
         <is>
@@ -20558,7 +20358,7 @@
         </is>
       </c>
       <c r="N259" s="6" t="n">
-        <v>49.084</v>
+        <v>48.676</v>
       </c>
       <c r="O259" s="4" t="inlineStr">
         <is>
@@ -20567,7 +20367,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20604,7 +20404,7 @@
         </is>
       </c>
       <c r="G260" s="5" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="H260" s="4" t="inlineStr">
         <is>
@@ -20637,7 +20437,7 @@
         </is>
       </c>
       <c r="N260" s="6" t="n">
-        <v>48.676</v>
+        <v>48.27</v>
       </c>
       <c r="O260" s="4" t="inlineStr">
         <is>
@@ -20646,7 +20446,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20683,7 +20483,7 @@
         </is>
       </c>
       <c r="G261" s="5" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="H261" s="4" t="inlineStr">
         <is>
@@ -20716,7 +20516,7 @@
         </is>
       </c>
       <c r="N261" s="6" t="n">
-        <v>48.27</v>
+        <v>47.867</v>
       </c>
       <c r="O261" s="4" t="inlineStr">
         <is>
@@ -20725,7 +20525,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20762,7 +20562,7 @@
         </is>
       </c>
       <c r="G262" s="5" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="H262" s="4" t="inlineStr">
         <is>
@@ -20795,7 +20595,7 @@
         </is>
       </c>
       <c r="N262" s="6" t="n">
-        <v>47.867</v>
+        <v>46.185</v>
       </c>
       <c r="O262" s="4" t="inlineStr">
         <is>
@@ -20804,7 +20604,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20841,7 +20641,7 @@
         </is>
       </c>
       <c r="G263" s="5" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="H263" s="4" t="inlineStr">
         <is>
@@ -20874,7 +20674,7 @@
         </is>
       </c>
       <c r="N263" s="6" t="n">
-        <v>46.185</v>
+        <v>44.85</v>
       </c>
       <c r="O263" s="4" t="inlineStr">
         <is>
@@ -20883,7 +20683,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20920,7 +20720,7 @@
         </is>
       </c>
       <c r="G264" s="5" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="H264" s="4" t="inlineStr">
         <is>
@@ -20953,7 +20753,7 @@
         </is>
       </c>
       <c r="N264" s="6" t="n">
-        <v>44.85</v>
+        <v>42.344</v>
       </c>
       <c r="O264" s="4" t="inlineStr">
         <is>
@@ -20962,7 +20762,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20999,7 +20799,7 @@
         </is>
       </c>
       <c r="G265" s="5" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="H265" s="4" t="inlineStr">
         <is>
@@ -21032,7 +20832,7 @@
         </is>
       </c>
       <c r="N265" s="6" t="n">
-        <v>42.344</v>
+        <v>36.887</v>
       </c>
       <c r="O265" s="4" t="inlineStr">
         <is>
@@ -21041,7 +20841,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -21078,7 +20878,7 @@
         </is>
       </c>
       <c r="G266" s="5" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="H266" s="4" t="inlineStr">
         <is>
@@ -21111,7 +20911,7 @@
         </is>
       </c>
       <c r="N266" s="6" t="n">
-        <v>36.887</v>
+        <v>37.368</v>
       </c>
       <c r="O266" s="4" t="inlineStr">
         <is>
@@ -21120,7 +20920,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21157,7 +20957,7 @@
         </is>
       </c>
       <c r="G267" s="5" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="H267" s="4" t="inlineStr">
         <is>
@@ -21190,7 +20990,7 @@
         </is>
       </c>
       <c r="N267" s="6" t="n">
-        <v>37.368</v>
+        <v>35.32</v>
       </c>
       <c r="O267" s="4" t="inlineStr">
         <is>
@@ -21199,7 +20999,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21236,7 +21036,7 @@
         </is>
       </c>
       <c r="G268" s="5" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="H268" s="4" t="inlineStr">
         <is>
@@ -21269,7 +21069,7 @@
         </is>
       </c>
       <c r="N268" s="6" t="n">
-        <v>35.32</v>
+        <v>36.158</v>
       </c>
       <c r="O268" s="4" t="inlineStr">
         <is>
@@ -21278,7 +21078,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21315,7 +21115,7 @@
         </is>
       </c>
       <c r="G269" s="5" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="H269" s="4" t="inlineStr">
         <is>
@@ -21348,7 +21148,7 @@
         </is>
       </c>
       <c r="N269" s="6" t="n">
-        <v>36.158</v>
+        <v>37.332</v>
       </c>
       <c r="O269" s="4" t="inlineStr">
         <is>
@@ -21357,7 +21157,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21394,7 +21194,7 @@
         </is>
       </c>
       <c r="G270" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="H270" s="4" t="inlineStr">
         <is>
@@ -21427,7 +21227,7 @@
         </is>
       </c>
       <c r="N270" s="6" t="n">
-        <v>37.332</v>
+        <v>37.098</v>
       </c>
       <c r="O270" s="4" t="inlineStr">
         <is>
@@ -21436,7 +21236,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21473,7 +21273,7 @@
         </is>
       </c>
       <c r="G271" s="5" t="n">
-        <v>2025</v>
+        <v>1960</v>
       </c>
       <c r="H271" s="4" t="inlineStr">
         <is>
@@ -21497,17 +21297,15 @@
       </c>
       <c r="L271" s="4" t="inlineStr">
         <is>
-          <t>SL.TLF.CACT.FE.ZS</t>
+          <t>SL.UEM.TOTL.FE.ZS</t>
         </is>
       </c>
       <c r="M271" s="4" t="inlineStr">
         <is>
-          <t>Participación laboral femenina</t>
-        </is>
-      </c>
-      <c r="N271" s="6" t="n">
-        <v>37.098</v>
-      </c>
+          <t>Desempleo femenino</t>
+        </is>
+      </c>
+      <c r="N271" s="4" t="n"/>
       <c r="O271" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -21515,7 +21313,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21552,7 +21350,7 @@
         </is>
       </c>
       <c r="G272" s="5" t="n">
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="H272" s="4" t="inlineStr">
         <is>
@@ -21592,7 +21390,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21629,7 +21427,7 @@
         </is>
       </c>
       <c r="G273" s="5" t="n">
-        <v>1961</v>
+        <v>1962</v>
       </c>
       <c r="H273" s="4" t="inlineStr">
         <is>
@@ -21669,7 +21467,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21706,7 +21504,7 @@
         </is>
       </c>
       <c r="G274" s="5" t="n">
-        <v>1962</v>
+        <v>1963</v>
       </c>
       <c r="H274" s="4" t="inlineStr">
         <is>
@@ -21746,7 +21544,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21783,7 +21581,7 @@
         </is>
       </c>
       <c r="G275" s="5" t="n">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="H275" s="4" t="inlineStr">
         <is>
@@ -21823,7 +21621,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21860,7 +21658,7 @@
         </is>
       </c>
       <c r="G276" s="5" t="n">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="H276" s="4" t="inlineStr">
         <is>
@@ -21900,7 +21698,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21937,7 +21735,7 @@
         </is>
       </c>
       <c r="G277" s="5" t="n">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="H277" s="4" t="inlineStr">
         <is>
@@ -21977,7 +21775,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -22014,7 +21812,7 @@
         </is>
       </c>
       <c r="G278" s="5" t="n">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="H278" s="4" t="inlineStr">
         <is>
@@ -22054,7 +21852,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -22091,7 +21889,7 @@
         </is>
       </c>
       <c r="G279" s="5" t="n">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="H279" s="4" t="inlineStr">
         <is>
@@ -22131,7 +21929,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -22168,7 +21966,7 @@
         </is>
       </c>
       <c r="G280" s="5" t="n">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="H280" s="4" t="inlineStr">
         <is>
@@ -22208,7 +22006,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22245,7 +22043,7 @@
         </is>
       </c>
       <c r="G281" s="5" t="n">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="H281" s="4" t="inlineStr">
         <is>
@@ -22285,7 +22083,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22322,7 +22120,7 @@
         </is>
       </c>
       <c r="G282" s="5" t="n">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="H282" s="4" t="inlineStr">
         <is>
@@ -22362,7 +22160,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22399,7 +22197,7 @@
         </is>
       </c>
       <c r="G283" s="5" t="n">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="H283" s="4" t="inlineStr">
         <is>
@@ -22439,7 +22237,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22476,7 +22274,7 @@
         </is>
       </c>
       <c r="G284" s="5" t="n">
-        <v>1972</v>
+        <v>1973</v>
       </c>
       <c r="H284" s="4" t="inlineStr">
         <is>
@@ -22516,7 +22314,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22553,7 +22351,7 @@
         </is>
       </c>
       <c r="G285" s="5" t="n">
-        <v>1973</v>
+        <v>1974</v>
       </c>
       <c r="H285" s="4" t="inlineStr">
         <is>
@@ -22593,7 +22391,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22630,7 +22428,7 @@
         </is>
       </c>
       <c r="G286" s="5" t="n">
-        <v>1974</v>
+        <v>1975</v>
       </c>
       <c r="H286" s="4" t="inlineStr">
         <is>
@@ -22670,7 +22468,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22707,7 +22505,7 @@
         </is>
       </c>
       <c r="G287" s="5" t="n">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="H287" s="4" t="inlineStr">
         <is>
@@ -22747,7 +22545,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22784,7 +22582,7 @@
         </is>
       </c>
       <c r="G288" s="5" t="n">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="H288" s="4" t="inlineStr">
         <is>
@@ -22824,7 +22622,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22861,7 +22659,7 @@
         </is>
       </c>
       <c r="G289" s="5" t="n">
-        <v>1977</v>
+        <v>1978</v>
       </c>
       <c r="H289" s="4" t="inlineStr">
         <is>
@@ -22901,7 +22699,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22938,7 +22736,7 @@
         </is>
       </c>
       <c r="G290" s="5" t="n">
-        <v>1978</v>
+        <v>1979</v>
       </c>
       <c r="H290" s="4" t="inlineStr">
         <is>
@@ -22978,7 +22776,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -23015,7 +22813,7 @@
         </is>
       </c>
       <c r="G291" s="5" t="n">
-        <v>1979</v>
+        <v>1980</v>
       </c>
       <c r="H291" s="4" t="inlineStr">
         <is>
@@ -23055,7 +22853,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -23092,7 +22890,7 @@
         </is>
       </c>
       <c r="G292" s="5" t="n">
-        <v>1980</v>
+        <v>1981</v>
       </c>
       <c r="H292" s="4" t="inlineStr">
         <is>
@@ -23132,7 +22930,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -23169,7 +22967,7 @@
         </is>
       </c>
       <c r="G293" s="5" t="n">
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="H293" s="4" t="inlineStr">
         <is>
@@ -23209,7 +23007,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23246,7 +23044,7 @@
         </is>
       </c>
       <c r="G294" s="5" t="n">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="H294" s="4" t="inlineStr">
         <is>
@@ -23286,7 +23084,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23323,7 +23121,7 @@
         </is>
       </c>
       <c r="G295" s="5" t="n">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="H295" s="4" t="inlineStr">
         <is>
@@ -23363,7 +23161,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23400,7 +23198,7 @@
         </is>
       </c>
       <c r="G296" s="5" t="n">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="H296" s="4" t="inlineStr">
         <is>
@@ -23440,7 +23238,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23477,7 +23275,7 @@
         </is>
       </c>
       <c r="G297" s="5" t="n">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="H297" s="4" t="inlineStr">
         <is>
@@ -23517,7 +23315,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23554,7 +23352,7 @@
         </is>
       </c>
       <c r="G298" s="5" t="n">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="H298" s="4" t="inlineStr">
         <is>
@@ -23594,7 +23392,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23631,7 +23429,7 @@
         </is>
       </c>
       <c r="G299" s="5" t="n">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="H299" s="4" t="inlineStr">
         <is>
@@ -23671,7 +23469,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23708,7 +23506,7 @@
         </is>
       </c>
       <c r="G300" s="5" t="n">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="H300" s="4" t="inlineStr">
         <is>
@@ -23748,7 +23546,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23785,7 +23583,7 @@
         </is>
       </c>
       <c r="G301" s="5" t="n">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="H301" s="4" t="inlineStr">
         <is>
@@ -23825,7 +23623,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23862,7 +23660,7 @@
         </is>
       </c>
       <c r="G302" s="5" t="n">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="H302" s="4" t="inlineStr">
         <is>
@@ -23894,7 +23692,9 @@
           <t>Desempleo femenino</t>
         </is>
       </c>
-      <c r="N302" s="4" t="n"/>
+      <c r="N302" s="6" t="n">
+        <v>9.32</v>
+      </c>
       <c r="O302" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -23902,7 +23702,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23939,7 +23739,7 @@
         </is>
       </c>
       <c r="G303" s="5" t="n">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="H303" s="4" t="inlineStr">
         <is>
@@ -23972,7 +23772,7 @@
         </is>
       </c>
       <c r="N303" s="6" t="n">
-        <v>9.32</v>
+        <v>6.925</v>
       </c>
       <c r="O303" s="4" t="inlineStr">
         <is>
@@ -23981,7 +23781,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -24018,7 +23818,7 @@
         </is>
       </c>
       <c r="G304" s="5" t="n">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="H304" s="4" t="inlineStr">
         <is>
@@ -24051,7 +23851,7 @@
         </is>
       </c>
       <c r="N304" s="6" t="n">
-        <v>6.925</v>
+        <v>5.679</v>
       </c>
       <c r="O304" s="4" t="inlineStr">
         <is>
@@ -24060,7 +23860,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -24097,7 +23897,7 @@
         </is>
       </c>
       <c r="G305" s="5" t="n">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="H305" s="4" t="inlineStr">
         <is>
@@ -24130,7 +23930,7 @@
         </is>
       </c>
       <c r="N305" s="6" t="n">
-        <v>5.679</v>
+        <v>9.557</v>
       </c>
       <c r="O305" s="4" t="inlineStr">
         <is>
@@ -24139,7 +23939,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24176,7 +23976,7 @@
         </is>
       </c>
       <c r="G306" s="5" t="n">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="H306" s="4" t="inlineStr">
         <is>
@@ -24209,7 +24009,7 @@
         </is>
       </c>
       <c r="N306" s="6" t="n">
-        <v>9.557</v>
+        <v>12.604</v>
       </c>
       <c r="O306" s="4" t="inlineStr">
         <is>
@@ -24218,7 +24018,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24255,7 +24055,7 @@
         </is>
       </c>
       <c r="G307" s="5" t="n">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="H307" s="4" t="inlineStr">
         <is>
@@ -24288,7 +24088,7 @@
         </is>
       </c>
       <c r="N307" s="6" t="n">
-        <v>12.604</v>
+        <v>14.345</v>
       </c>
       <c r="O307" s="4" t="inlineStr">
         <is>
@@ -24297,7 +24097,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24334,7 +24134,7 @@
         </is>
       </c>
       <c r="G308" s="5" t="n">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="H308" s="4" t="inlineStr">
         <is>
@@ -24367,7 +24167,7 @@
         </is>
       </c>
       <c r="N308" s="6" t="n">
-        <v>14.345</v>
+        <v>13.627</v>
       </c>
       <c r="O308" s="4" t="inlineStr">
         <is>
@@ -24376,7 +24176,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24413,7 +24213,7 @@
         </is>
       </c>
       <c r="G309" s="5" t="n">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="H309" s="4" t="inlineStr">
         <is>
@@ -24446,7 +24246,7 @@
         </is>
       </c>
       <c r="N309" s="6" t="n">
-        <v>13.627</v>
+        <v>13.306</v>
       </c>
       <c r="O309" s="4" t="inlineStr">
         <is>
@@ -24455,7 +24255,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24492,7 +24292,7 @@
         </is>
       </c>
       <c r="G310" s="5" t="n">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="H310" s="4" t="inlineStr">
         <is>
@@ -24525,7 +24325,7 @@
         </is>
       </c>
       <c r="N310" s="6" t="n">
-        <v>13.306</v>
+        <v>16.482</v>
       </c>
       <c r="O310" s="4" t="inlineStr">
         <is>
@@ -24534,7 +24334,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24571,7 +24371,7 @@
         </is>
       </c>
       <c r="G311" s="5" t="n">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="H311" s="4" t="inlineStr">
         <is>
@@ -24604,7 +24404,7 @@
         </is>
       </c>
       <c r="N311" s="6" t="n">
-        <v>16.482</v>
+        <v>14.605</v>
       </c>
       <c r="O311" s="4" t="inlineStr">
         <is>
@@ -24613,7 +24413,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24650,7 +24450,7 @@
         </is>
       </c>
       <c r="G312" s="5" t="n">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="H312" s="4" t="inlineStr">
         <is>
@@ -24683,7 +24483,7 @@
         </is>
       </c>
       <c r="N312" s="6" t="n">
-        <v>14.605</v>
+        <v>14.109</v>
       </c>
       <c r="O312" s="4" t="inlineStr">
         <is>
@@ -24692,7 +24492,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24729,7 +24529,7 @@
         </is>
       </c>
       <c r="G313" s="5" t="n">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="H313" s="4" t="inlineStr">
         <is>
@@ -24762,7 +24562,7 @@
         </is>
       </c>
       <c r="N313" s="6" t="n">
-        <v>14.109</v>
+        <v>18.895</v>
       </c>
       <c r="O313" s="4" t="inlineStr">
         <is>
@@ -24771,7 +24571,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24808,7 +24608,7 @@
         </is>
       </c>
       <c r="G314" s="5" t="n">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="H314" s="4" t="inlineStr">
         <is>
@@ -24841,7 +24641,7 @@
         </is>
       </c>
       <c r="N314" s="6" t="n">
-        <v>18.895</v>
+        <v>20.483</v>
       </c>
       <c r="O314" s="4" t="inlineStr">
         <is>
@@ -24850,7 +24650,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24887,7 +24687,7 @@
         </is>
       </c>
       <c r="G315" s="5" t="n">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="H315" s="4" t="inlineStr">
         <is>
@@ -24920,7 +24720,7 @@
         </is>
       </c>
       <c r="N315" s="6" t="n">
-        <v>20.483</v>
+        <v>17.974</v>
       </c>
       <c r="O315" s="4" t="inlineStr">
         <is>
@@ -24929,7 +24729,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24966,7 +24766,7 @@
         </is>
       </c>
       <c r="G316" s="5" t="n">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="H316" s="4" t="inlineStr">
         <is>
@@ -24999,7 +24799,7 @@
         </is>
       </c>
       <c r="N316" s="6" t="n">
-        <v>17.974</v>
+        <v>11.64</v>
       </c>
       <c r="O316" s="4" t="inlineStr">
         <is>
@@ -25008,7 +24808,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -25045,7 +24845,7 @@
         </is>
       </c>
       <c r="G317" s="5" t="n">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="H317" s="4" t="inlineStr">
         <is>
@@ -25078,7 +24878,7 @@
         </is>
       </c>
       <c r="N317" s="6" t="n">
-        <v>11.64</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="O317" s="4" t="inlineStr">
         <is>
@@ -25087,7 +24887,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -25124,7 +24924,7 @@
         </is>
       </c>
       <c r="G318" s="5" t="n">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="H318" s="4" t="inlineStr">
         <is>
@@ -25157,7 +24957,7 @@
         </is>
       </c>
       <c r="N318" s="6" t="n">
-        <v>9.380000000000001</v>
+        <v>7.643</v>
       </c>
       <c r="O318" s="4" t="inlineStr">
         <is>
@@ -25166,7 +24966,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25203,7 +25003,7 @@
         </is>
       </c>
       <c r="G319" s="5" t="n">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="H319" s="4" t="inlineStr">
         <is>
@@ -25236,7 +25036,7 @@
         </is>
       </c>
       <c r="N319" s="6" t="n">
-        <v>7.643</v>
+        <v>6.218</v>
       </c>
       <c r="O319" s="4" t="inlineStr">
         <is>
@@ -25245,7 +25045,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25282,7 +25082,7 @@
         </is>
       </c>
       <c r="G320" s="5" t="n">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="H320" s="4" t="inlineStr">
         <is>
@@ -25315,7 +25115,7 @@
         </is>
       </c>
       <c r="N320" s="6" t="n">
-        <v>6.218</v>
+        <v>5.965</v>
       </c>
       <c r="O320" s="4" t="inlineStr">
         <is>
@@ -25324,7 +25124,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25361,7 +25161,7 @@
         </is>
       </c>
       <c r="G321" s="5" t="n">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="H321" s="4" t="inlineStr">
         <is>
@@ -25394,7 +25194,7 @@
         </is>
       </c>
       <c r="N321" s="6" t="n">
-        <v>5.965</v>
+        <v>6.952</v>
       </c>
       <c r="O321" s="4" t="inlineStr">
         <is>
@@ -25403,7 +25203,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25440,7 +25240,7 @@
         </is>
       </c>
       <c r="G322" s="5" t="n">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="H322" s="4" t="inlineStr">
         <is>
@@ -25473,7 +25273,7 @@
         </is>
       </c>
       <c r="N322" s="6" t="n">
-        <v>6.952</v>
+        <v>7.206</v>
       </c>
       <c r="O322" s="4" t="inlineStr">
         <is>
@@ -25482,7 +25282,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25519,7 +25319,7 @@
         </is>
       </c>
       <c r="G323" s="5" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="H323" s="4" t="inlineStr">
         <is>
@@ -25552,7 +25352,7 @@
         </is>
       </c>
       <c r="N323" s="6" t="n">
-        <v>7.206</v>
+        <v>7.109</v>
       </c>
       <c r="O323" s="4" t="inlineStr">
         <is>
@@ -25561,7 +25361,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25598,7 +25398,7 @@
         </is>
       </c>
       <c r="G324" s="5" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="H324" s="4" t="inlineStr">
         <is>
@@ -25631,7 +25431,7 @@
         </is>
       </c>
       <c r="N324" s="6" t="n">
-        <v>7.109</v>
+        <v>8.605</v>
       </c>
       <c r="O324" s="4" t="inlineStr">
         <is>
@@ -25640,7 +25440,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25677,7 +25477,7 @@
         </is>
       </c>
       <c r="G325" s="5" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="H325" s="4" t="inlineStr">
         <is>
@@ -25710,7 +25510,7 @@
         </is>
       </c>
       <c r="N325" s="6" t="n">
-        <v>8.605</v>
+        <v>7.578</v>
       </c>
       <c r="O325" s="4" t="inlineStr">
         <is>
@@ -25719,7 +25519,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25756,7 +25556,7 @@
         </is>
       </c>
       <c r="G326" s="5" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="H326" s="4" t="inlineStr">
         <is>
@@ -25789,7 +25589,7 @@
         </is>
       </c>
       <c r="N326" s="6" t="n">
-        <v>7.578</v>
+        <v>6.572</v>
       </c>
       <c r="O326" s="4" t="inlineStr">
         <is>
@@ -25798,7 +25598,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25835,7 +25635,7 @@
         </is>
       </c>
       <c r="G327" s="5" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="H327" s="4" t="inlineStr">
         <is>
@@ -25868,7 +25668,7 @@
         </is>
       </c>
       <c r="N327" s="6" t="n">
-        <v>6.572</v>
+        <v>5.413</v>
       </c>
       <c r="O327" s="4" t="inlineStr">
         <is>
@@ -25877,7 +25677,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25914,7 +25714,7 @@
         </is>
       </c>
       <c r="G328" s="5" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="H328" s="4" t="inlineStr">
         <is>
@@ -25947,7 +25747,7 @@
         </is>
       </c>
       <c r="N328" s="6" t="n">
-        <v>5.413</v>
+        <v>5.858</v>
       </c>
       <c r="O328" s="4" t="inlineStr">
         <is>
@@ -25956,7 +25756,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25993,7 +25793,7 @@
         </is>
       </c>
       <c r="G329" s="5" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="H329" s="4" t="inlineStr">
         <is>
@@ -26026,7 +25826,7 @@
         </is>
       </c>
       <c r="N329" s="6" t="n">
-        <v>5.858</v>
+        <v>6.178</v>
       </c>
       <c r="O329" s="4" t="inlineStr">
         <is>
@@ -26035,7 +25835,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -26072,7 +25872,7 @@
         </is>
       </c>
       <c r="G330" s="5" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="H330" s="4" t="inlineStr">
         <is>
@@ -26105,7 +25905,7 @@
         </is>
       </c>
       <c r="N330" s="6" t="n">
-        <v>6.178</v>
+        <v>6.497</v>
       </c>
       <c r="O330" s="4" t="inlineStr">
         <is>
@@ -26114,7 +25914,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -26151,7 +25951,7 @@
         </is>
       </c>
       <c r="G331" s="5" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="H331" s="4" t="inlineStr">
         <is>
@@ -26184,7 +25984,7 @@
         </is>
       </c>
       <c r="N331" s="6" t="n">
-        <v>6.497</v>
+        <v>7.907</v>
       </c>
       <c r="O331" s="4" t="inlineStr">
         <is>
@@ -26193,7 +25993,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26230,7 +26030,7 @@
         </is>
       </c>
       <c r="G332" s="5" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="H332" s="4" t="inlineStr">
         <is>
@@ -26263,7 +26063,7 @@
         </is>
       </c>
       <c r="N332" s="6" t="n">
-        <v>7.907</v>
+        <v>7.541</v>
       </c>
       <c r="O332" s="4" t="inlineStr">
         <is>
@@ -26272,7 +26072,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26309,7 +26109,7 @@
         </is>
       </c>
       <c r="G333" s="5" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="H333" s="4" t="inlineStr">
         <is>
@@ -26342,7 +26142,7 @@
         </is>
       </c>
       <c r="N333" s="6" t="n">
-        <v>7.541</v>
+        <v>6.179</v>
       </c>
       <c r="O333" s="4" t="inlineStr">
         <is>
@@ -26351,7 +26151,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26388,7 +26188,7 @@
         </is>
       </c>
       <c r="G334" s="5" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="H334" s="4" t="inlineStr">
         <is>
@@ -26421,7 +26221,7 @@
         </is>
       </c>
       <c r="N334" s="6" t="n">
-        <v>6.179</v>
+        <v>5.937</v>
       </c>
       <c r="O334" s="4" t="inlineStr">
         <is>
@@ -26430,7 +26230,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26467,7 +26267,7 @@
         </is>
       </c>
       <c r="G335" s="5" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="H335" s="4" t="inlineStr">
         <is>
@@ -26500,7 +26300,7 @@
         </is>
       </c>
       <c r="N335" s="6" t="n">
-        <v>5.937</v>
+        <v>5.845</v>
       </c>
       <c r="O335" s="4" t="inlineStr">
         <is>
@@ -26509,7 +26309,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26546,7 +26346,7 @@
         </is>
       </c>
       <c r="G336" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="H336" s="4" t="inlineStr">
         <is>
@@ -26579,7 +26379,7 @@
         </is>
       </c>
       <c r="N336" s="6" t="n">
-        <v>5.845</v>
+        <v>5.835</v>
       </c>
       <c r="O336" s="4" t="inlineStr">
         <is>
@@ -26588,89 +26388,10 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
-    </row>
-    <row r="337">
-      <c r="A337" s="4" t="inlineStr">
-        <is>
-          <t>Venezuela</t>
-        </is>
-      </c>
-      <c r="B337" s="4" t="inlineStr">
-        <is>
-          <t>Venezuela, RB</t>
-        </is>
-      </c>
-      <c r="C337" s="4" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D337" s="4" t="inlineStr">
-        <is>
-          <t>VEN</t>
-        </is>
-      </c>
-      <c r="E337" s="4" t="inlineStr">
-        <is>
-          <t>Latin America &amp; Caribbean</t>
-        </is>
-      </c>
-      <c r="F337" s="4" t="inlineStr">
-        <is>
-          <t>Not classified</t>
-        </is>
-      </c>
-      <c r="G337" s="5" t="n">
-        <v>2025</v>
-      </c>
-      <c r="H337" s="4" t="inlineStr">
-        <is>
-          <t>Género</t>
-        </is>
-      </c>
-      <c r="I337" s="4" t="inlineStr">
-        <is>
-          <t>genero</t>
-        </is>
-      </c>
-      <c r="J337" s="4" t="inlineStr">
-        <is>
-          <t>Mercado laboral</t>
-        </is>
-      </c>
-      <c r="K337" s="4" t="inlineStr">
-        <is>
-          <t>mercado_laboral</t>
-        </is>
-      </c>
-      <c r="L337" s="4" t="inlineStr">
-        <is>
-          <t>SL.UEM.TOTL.FE.ZS</t>
-        </is>
-      </c>
-      <c r="M337" s="4" t="inlineStr">
-        <is>
-          <t>Desempleo femenino</t>
-        </is>
-      </c>
-      <c r="N337" s="6" t="n">
-        <v>5.835</v>
-      </c>
-      <c r="O337" s="4" t="inlineStr">
-        <is>
-          <t>Banco Mundial - World Development Indicators</t>
-        </is>
-      </c>
-      <c r="P337" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="Q337" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -26752,7 +26473,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -26773,7 +26494,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
   </sheetData>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_genero.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_genero.xlsx
@@ -715,7 +715,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2745,7 +2745,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3217,7 +3217,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3685,7 +3685,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3764,7 +3764,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3843,7 +3843,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4159,7 +4159,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4238,7 +4238,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4317,7 +4317,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4554,7 +4554,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4633,7 +4633,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4712,7 +4712,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4791,7 +4791,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4870,7 +4870,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5107,7 +5107,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5186,7 +5186,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5263,7 +5263,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5417,7 +5417,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5571,7 +5571,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5725,7 +5725,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5879,7 +5879,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6033,7 +6033,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6110,7 +6110,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6264,7 +6264,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6495,7 +6495,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6572,7 +6572,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6649,7 +6649,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6728,7 +6728,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6807,7 +6807,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6886,7 +6886,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6965,7 +6965,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7044,7 +7044,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7121,7 +7121,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7275,7 +7275,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7352,7 +7352,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7429,7 +7429,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7506,7 +7506,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7583,7 +7583,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7739,7 +7739,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7818,7 +7818,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7897,7 +7897,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -7976,7 +7976,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8055,7 +8055,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8134,7 +8134,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8211,7 +8211,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8290,7 +8290,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8369,7 +8369,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8448,7 +8448,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8525,7 +8525,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8602,7 +8602,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8679,7 +8679,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8756,7 +8756,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8912,7 +8912,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -8991,7 +8991,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9070,7 +9070,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9149,7 +9149,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9228,7 +9228,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9307,7 +9307,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9386,7 +9386,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9465,7 +9465,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9544,7 +9544,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9623,7 +9623,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9702,7 +9702,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9781,7 +9781,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9860,7 +9860,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9939,7 +9939,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -10018,7 +10018,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10097,7 +10097,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10176,7 +10176,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10255,7 +10255,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10334,7 +10334,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10411,7 +10411,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10488,7 +10488,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10565,7 +10565,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10642,7 +10642,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10719,7 +10719,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10796,7 +10796,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10873,7 +10873,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -10950,7 +10950,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11027,7 +11027,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11104,7 +11104,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11181,7 +11181,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11258,7 +11258,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11335,7 +11335,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11412,7 +11412,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11489,7 +11489,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11566,7 +11566,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11643,7 +11643,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11720,7 +11720,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11797,7 +11797,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11874,7 +11874,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -11951,7 +11951,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12028,7 +12028,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12105,7 +12105,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12182,7 +12182,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12259,7 +12259,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12336,7 +12336,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12413,7 +12413,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12490,7 +12490,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12567,7 +12567,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12644,7 +12644,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12721,7 +12721,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12798,7 +12798,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12875,7 +12875,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -12952,7 +12952,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13029,7 +13029,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13106,7 +13106,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13183,7 +13183,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13260,7 +13260,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13337,7 +13337,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13414,7 +13414,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13491,7 +13491,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13568,7 +13568,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13645,7 +13645,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13722,7 +13722,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13799,7 +13799,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13878,7 +13878,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -13957,7 +13957,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14036,7 +14036,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14113,7 +14113,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14192,7 +14192,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14271,7 +14271,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14350,7 +14350,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14429,7 +14429,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14508,7 +14508,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14587,7 +14587,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14666,7 +14666,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14745,7 +14745,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14824,7 +14824,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -14982,7 +14982,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15061,7 +15061,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15140,7 +15140,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15219,7 +15219,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15298,7 +15298,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15377,7 +15377,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15456,7 +15456,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15535,7 +15535,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15614,7 +15614,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15693,7 +15693,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15772,7 +15772,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15849,7 +15849,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15926,7 +15926,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16003,7 +16003,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16082,7 +16082,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16159,7 +16159,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16236,7 +16236,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16313,7 +16313,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16390,7 +16390,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16467,7 +16467,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16544,7 +16544,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16621,7 +16621,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16698,7 +16698,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16775,7 +16775,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16852,7 +16852,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16929,7 +16929,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17006,7 +17006,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17083,7 +17083,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17160,7 +17160,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17237,7 +17237,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17314,7 +17314,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17391,7 +17391,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17468,7 +17468,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17545,7 +17545,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17622,7 +17622,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17699,7 +17699,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17776,7 +17776,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17853,7 +17853,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17930,7 +17930,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18007,7 +18007,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18084,7 +18084,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18161,7 +18161,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18238,7 +18238,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18315,7 +18315,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18392,7 +18392,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18471,7 +18471,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18550,7 +18550,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18629,7 +18629,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18708,7 +18708,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18787,7 +18787,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18866,7 +18866,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18945,7 +18945,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19024,7 +19024,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19103,7 +19103,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19182,7 +19182,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19261,7 +19261,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19340,7 +19340,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19419,7 +19419,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19498,7 +19498,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19577,7 +19577,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19656,7 +19656,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19735,7 +19735,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19893,7 +19893,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -19972,7 +19972,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20051,7 +20051,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20130,7 +20130,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20209,7 +20209,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20288,7 +20288,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20367,7 +20367,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20446,7 +20446,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20525,7 +20525,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20604,7 +20604,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20683,7 +20683,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20762,7 +20762,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20841,7 +20841,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20920,7 +20920,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -20999,7 +20999,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21078,7 +21078,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21157,7 +21157,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21236,7 +21236,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21313,7 +21313,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21390,7 +21390,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21467,7 +21467,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21544,7 +21544,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21621,7 +21621,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21698,7 +21698,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21775,7 +21775,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -21852,7 +21852,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -21929,7 +21929,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -22006,7 +22006,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22083,7 +22083,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22160,7 +22160,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22237,7 +22237,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22314,7 +22314,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22391,7 +22391,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22468,7 +22468,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22545,7 +22545,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22622,7 +22622,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22699,7 +22699,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22776,7 +22776,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -22853,7 +22853,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -22930,7 +22930,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -23007,7 +23007,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23084,7 +23084,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23161,7 +23161,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23238,7 +23238,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23315,7 +23315,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23392,7 +23392,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23469,7 +23469,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23546,7 +23546,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23623,7 +23623,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23702,7 +23702,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23781,7 +23781,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -23860,7 +23860,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -23939,7 +23939,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24018,7 +24018,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24097,7 +24097,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24176,7 +24176,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24255,7 +24255,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24334,7 +24334,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24413,7 +24413,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24492,7 +24492,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24571,7 +24571,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24650,7 +24650,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24729,7 +24729,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24808,7 +24808,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -24887,7 +24887,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -24966,7 +24966,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25045,7 +25045,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25124,7 +25124,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25203,7 +25203,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25282,7 +25282,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25361,7 +25361,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25440,7 +25440,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25519,7 +25519,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25598,7 +25598,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25677,7 +25677,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25756,7 +25756,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25835,7 +25835,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -25914,7 +25914,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -25993,7 +25993,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26072,7 +26072,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26151,7 +26151,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26230,7 +26230,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26309,7 +26309,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26388,7 +26388,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26473,7 +26473,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_genero.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_genero.xlsx
@@ -715,7 +715,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2745,7 +2745,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3217,7 +3217,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3685,7 +3685,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3764,7 +3764,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3843,7 +3843,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4159,7 +4159,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4238,7 +4238,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4317,7 +4317,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4554,7 +4554,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4633,7 +4633,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4712,7 +4712,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4791,7 +4791,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4870,7 +4870,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5107,7 +5107,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5186,7 +5186,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5263,7 +5263,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5417,7 +5417,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5571,7 +5571,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5725,7 +5725,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5879,7 +5879,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6033,7 +6033,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6110,7 +6110,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6264,7 +6264,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6495,7 +6495,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6572,7 +6572,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6649,7 +6649,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6728,7 +6728,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6807,7 +6807,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6886,7 +6886,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6965,7 +6965,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7044,7 +7044,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7121,7 +7121,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7275,7 +7275,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7352,7 +7352,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7429,7 +7429,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7506,7 +7506,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7583,7 +7583,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7739,7 +7739,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7818,7 +7818,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7897,7 +7897,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -7976,7 +7976,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8055,7 +8055,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8134,7 +8134,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8211,7 +8211,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8290,7 +8290,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8369,7 +8369,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8448,7 +8448,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8525,7 +8525,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8602,7 +8602,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8679,7 +8679,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8756,7 +8756,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8912,7 +8912,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -8991,7 +8991,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9070,7 +9070,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9149,7 +9149,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9228,7 +9228,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9307,7 +9307,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9386,7 +9386,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9465,7 +9465,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9544,7 +9544,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9623,7 +9623,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9702,7 +9702,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9781,7 +9781,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9860,7 +9860,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9939,7 +9939,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -10018,7 +10018,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10097,7 +10097,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10176,7 +10176,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10255,7 +10255,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10334,7 +10334,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10411,7 +10411,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10488,7 +10488,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10565,7 +10565,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10642,7 +10642,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10719,7 +10719,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10796,7 +10796,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10873,7 +10873,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -10950,7 +10950,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11027,7 +11027,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11104,7 +11104,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11181,7 +11181,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11258,7 +11258,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11335,7 +11335,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11412,7 +11412,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11489,7 +11489,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11566,7 +11566,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11643,7 +11643,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11720,7 +11720,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11797,7 +11797,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11874,7 +11874,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -11951,7 +11951,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12028,7 +12028,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12105,7 +12105,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12182,7 +12182,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12259,7 +12259,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12336,7 +12336,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12413,7 +12413,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12490,7 +12490,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12567,7 +12567,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12644,7 +12644,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12721,7 +12721,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12798,7 +12798,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12875,7 +12875,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -12952,7 +12952,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13029,7 +13029,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13106,7 +13106,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13183,7 +13183,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13260,7 +13260,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13337,7 +13337,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13414,7 +13414,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13491,7 +13491,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13568,7 +13568,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13645,7 +13645,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13722,7 +13722,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13799,7 +13799,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13878,7 +13878,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -13957,7 +13957,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14036,7 +14036,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14113,7 +14113,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14192,7 +14192,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14271,7 +14271,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14350,7 +14350,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14429,7 +14429,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14508,7 +14508,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14587,7 +14587,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14666,7 +14666,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14745,7 +14745,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14824,7 +14824,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -14982,7 +14982,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15061,7 +15061,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15140,7 +15140,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15219,7 +15219,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15298,7 +15298,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15377,7 +15377,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15456,7 +15456,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15535,7 +15535,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15614,7 +15614,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15693,7 +15693,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15772,7 +15772,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15849,7 +15849,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15926,7 +15926,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16003,7 +16003,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16082,7 +16082,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16159,7 +16159,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16236,7 +16236,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16313,7 +16313,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16390,7 +16390,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16467,7 +16467,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16544,7 +16544,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16621,7 +16621,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16698,7 +16698,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16775,7 +16775,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16852,7 +16852,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16929,7 +16929,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17006,7 +17006,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17083,7 +17083,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17160,7 +17160,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17237,7 +17237,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17314,7 +17314,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17391,7 +17391,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17468,7 +17468,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17545,7 +17545,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17622,7 +17622,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17699,7 +17699,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17776,7 +17776,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17853,7 +17853,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17930,7 +17930,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18007,7 +18007,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18084,7 +18084,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18161,7 +18161,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18238,7 +18238,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18315,7 +18315,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18392,7 +18392,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18471,7 +18471,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18550,7 +18550,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18629,7 +18629,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18708,7 +18708,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18787,7 +18787,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18866,7 +18866,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18945,7 +18945,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19024,7 +19024,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19103,7 +19103,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19182,7 +19182,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19261,7 +19261,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19340,7 +19340,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19419,7 +19419,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19498,7 +19498,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19577,7 +19577,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19656,7 +19656,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19735,7 +19735,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19893,7 +19893,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -19972,7 +19972,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20051,7 +20051,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20130,7 +20130,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20209,7 +20209,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20288,7 +20288,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20367,7 +20367,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20446,7 +20446,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20525,7 +20525,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20604,7 +20604,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20683,7 +20683,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20762,7 +20762,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20841,7 +20841,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20920,7 +20920,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -20999,7 +20999,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21078,7 +21078,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21157,7 +21157,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21236,7 +21236,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21313,7 +21313,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21390,7 +21390,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21467,7 +21467,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21544,7 +21544,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21621,7 +21621,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21698,7 +21698,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21775,7 +21775,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -21852,7 +21852,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -21929,7 +21929,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -22006,7 +22006,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22083,7 +22083,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22160,7 +22160,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22237,7 +22237,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22314,7 +22314,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22391,7 +22391,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22468,7 +22468,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22545,7 +22545,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22622,7 +22622,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22699,7 +22699,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22776,7 +22776,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -22853,7 +22853,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -22930,7 +22930,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -23007,7 +23007,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23084,7 +23084,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23161,7 +23161,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23238,7 +23238,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23315,7 +23315,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23392,7 +23392,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23469,7 +23469,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23546,7 +23546,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23623,7 +23623,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23702,7 +23702,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23781,7 +23781,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -23860,7 +23860,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -23939,7 +23939,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24018,7 +24018,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24097,7 +24097,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24176,7 +24176,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24255,7 +24255,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24334,7 +24334,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24413,7 +24413,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24492,7 +24492,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24571,7 +24571,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24650,7 +24650,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24729,7 +24729,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24808,7 +24808,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -24887,7 +24887,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -24966,7 +24966,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25045,7 +25045,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25124,7 +25124,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25203,7 +25203,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25282,7 +25282,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25361,7 +25361,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25440,7 +25440,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25519,7 +25519,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25598,7 +25598,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25677,7 +25677,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25756,7 +25756,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25835,7 +25835,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -25914,7 +25914,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -25993,7 +25993,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26072,7 +26072,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26151,7 +26151,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26230,7 +26230,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26309,7 +26309,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26388,7 +26388,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26473,7 +26473,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
